--- a/app/templates/informes/Proctor/Template_Proctor.xlsx
+++ b/app/templates/informes/Proctor/Template_Proctor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\Sistemas-suelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA68BA5-5FAC-4B62-AD1C-35CF9515FA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A975107-C2E1-4785-AA9A-3F700DCEF80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="613" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3400,7 +3400,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3513,12 +3513,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -5679,7 +5673,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1597">
+  <cellXfs count="1592">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
@@ -9635,35 +9629,8 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="81" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="81" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="4" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="82" fillId="4" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="82" fillId="4" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="104" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9673,6 +9640,154 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="22" fillId="3" borderId="166" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="209" fontId="25" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="3" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -9680,19 +9795,6 @@
     <xf numFmtId="0" fontId="58" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9700,15 +9802,11 @@
     <xf numFmtId="0" fontId="58" fillId="3" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -9720,220 +9818,82 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="22" fillId="3" borderId="166" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="209" fontId="25" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="3" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9977,72 +9937,73 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10051,6 +10012,69 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -10060,89 +10084,29 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="18" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="102" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10168,28 +10132,44 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="18" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="193" fontId="81" fillId="0" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10233,18 +10213,79 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -10252,16 +10293,10 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10290,10 +10325,6 @@
     <xf numFmtId="0" fontId="58" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -10312,9 +10343,6 @@
     <xf numFmtId="164" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10327,87 +10355,19 @@
     <xf numFmtId="0" fontId="58" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10448,39 +10408,97 @@
     <xf numFmtId="172" fontId="56" fillId="3" borderId="58" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="117" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="117" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="112" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="113" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="119" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="11" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -10533,57 +10551,6 @@
     <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="117" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="117" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="112" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="113" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="119" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="9" borderId="149" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10672,6 +10639,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="81" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="81" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="82" fillId="3" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="82" fillId="3" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -17517,90 +17502,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1324"/>
-      <c r="B1" s="1325"/>
-      <c r="C1" s="1325"/>
-      <c r="D1" s="1325"/>
-      <c r="E1" s="1325"/>
-      <c r="F1" s="1325"/>
-      <c r="G1" s="1325"/>
-      <c r="H1" s="1325"/>
-      <c r="I1" s="1326"/>
+      <c r="A1" s="1274"/>
+      <c r="B1" s="1275"/>
+      <c r="C1" s="1275"/>
+      <c r="D1" s="1275"/>
+      <c r="E1" s="1275"/>
+      <c r="F1" s="1275"/>
+      <c r="G1" s="1275"/>
+      <c r="H1" s="1275"/>
+      <c r="I1" s="1276"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1327"/>
-      <c r="B2" s="1328"/>
-      <c r="C2" s="1328"/>
-      <c r="D2" s="1328"/>
-      <c r="E2" s="1328"/>
-      <c r="F2" s="1328"/>
-      <c r="G2" s="1328"/>
-      <c r="H2" s="1328"/>
-      <c r="I2" s="1329"/>
+      <c r="A2" s="1277"/>
+      <c r="B2" s="1278"/>
+      <c r="C2" s="1278"/>
+      <c r="D2" s="1278"/>
+      <c r="E2" s="1278"/>
+      <c r="F2" s="1278"/>
+      <c r="G2" s="1278"/>
+      <c r="H2" s="1278"/>
+      <c r="I2" s="1279"/>
       <c r="K2" s="329" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="1252"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1327"/>
-      <c r="B3" s="1328"/>
-      <c r="C3" s="1328"/>
-      <c r="D3" s="1328"/>
-      <c r="E3" s="1328"/>
-      <c r="F3" s="1328"/>
-      <c r="G3" s="1328"/>
-      <c r="H3" s="1328"/>
-      <c r="I3" s="1329"/>
+      <c r="A3" s="1277"/>
+      <c r="B3" s="1278"/>
+      <c r="C3" s="1278"/>
+      <c r="D3" s="1278"/>
+      <c r="E3" s="1278"/>
+      <c r="F3" s="1278"/>
+      <c r="G3" s="1278"/>
+      <c r="H3" s="1278"/>
+      <c r="I3" s="1279"/>
       <c r="K3" s="329" t="s">
         <v>5</v>
       </c>
       <c r="L3" s="1253"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1330"/>
-      <c r="B4" s="1331"/>
-      <c r="C4" s="1331"/>
-      <c r="D4" s="1331"/>
-      <c r="E4" s="1331"/>
-      <c r="F4" s="1331"/>
-      <c r="G4" s="1331"/>
-      <c r="H4" s="1331"/>
-      <c r="I4" s="1332"/>
+      <c r="A4" s="1280"/>
+      <c r="B4" s="1281"/>
+      <c r="C4" s="1281"/>
+      <c r="D4" s="1281"/>
+      <c r="E4" s="1281"/>
+      <c r="F4" s="1281"/>
+      <c r="G4" s="1281"/>
+      <c r="H4" s="1281"/>
+      <c r="I4" s="1282"/>
       <c r="K4" s="329" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="1253"/>
     </row>
     <row r="5" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1333" t="s">
+      <c r="A5" s="1283" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1333"/>
-      <c r="C5" s="1333"/>
-      <c r="D5" s="1333"/>
-      <c r="E5" s="1333"/>
-      <c r="F5" s="1333"/>
-      <c r="G5" s="1333"/>
-      <c r="H5" s="1333"/>
-      <c r="I5" s="1333"/>
+      <c r="B5" s="1283"/>
+      <c r="C5" s="1283"/>
+      <c r="D5" s="1283"/>
+      <c r="E5" s="1283"/>
+      <c r="F5" s="1283"/>
+      <c r="G5" s="1283"/>
+      <c r="H5" s="1283"/>
+      <c r="I5" s="1283"/>
       <c r="K5" s="329" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="1253"/>
     </row>
     <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1334" t="s">
+      <c r="A6" s="1284" t="s">
         <v>593</v>
       </c>
-      <c r="B6" s="1334"/>
-      <c r="C6" s="1334"/>
-      <c r="D6" s="1334"/>
-      <c r="E6" s="1334"/>
-      <c r="F6" s="1334"/>
-      <c r="G6" s="1334"/>
-      <c r="H6" s="1334"/>
-      <c r="I6" s="1334"/>
+      <c r="B6" s="1284"/>
+      <c r="C6" s="1284"/>
+      <c r="D6" s="1284"/>
+      <c r="E6" s="1284"/>
+      <c r="F6" s="1284"/>
+      <c r="G6" s="1284"/>
+      <c r="H6" s="1284"/>
+      <c r="I6" s="1284"/>
       <c r="K6" s="1254"/>
       <c r="L6" s="1255"/>
     </row>
@@ -17624,15 +17609,15 @@
       <c r="B8" s="1163" t="s">
         <v>594</v>
       </c>
-      <c r="C8" s="1335" t="s">
+      <c r="C8" s="1285" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1336"/>
+      <c r="D8" s="1286"/>
       <c r="E8" s="1165"/>
-      <c r="F8" s="1337" t="s">
+      <c r="F8" s="1287" t="s">
         <v>595</v>
       </c>
-      <c r="G8" s="1336"/>
+      <c r="G8" s="1286"/>
       <c r="H8" s="1164" t="s">
         <v>596</v>
       </c>
@@ -17644,11 +17629,11 @@
     </row>
     <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1166"/>
-      <c r="C9" s="1321"/>
-      <c r="D9" s="1322"/>
+      <c r="C9" s="1271"/>
+      <c r="D9" s="1272"/>
       <c r="E9" s="1167"/>
-      <c r="F9" s="1323"/>
-      <c r="G9" s="1322"/>
+      <c r="F9" s="1273"/>
+      <c r="G9" s="1272"/>
       <c r="H9" s="1168"/>
       <c r="I9" s="243"/>
       <c r="K9" s="329" t="s">
@@ -17658,46 +17643,46 @@
     </row>
     <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1169"/>
-      <c r="B10" s="1312"/>
-      <c r="C10" s="1312"/>
-      <c r="D10" s="1312"/>
+      <c r="B10" s="1288"/>
+      <c r="C10" s="1288"/>
+      <c r="D10" s="1288"/>
       <c r="E10" s="1170"/>
-      <c r="F10" s="1312"/>
-      <c r="G10" s="1312"/>
+      <c r="F10" s="1288"/>
+      <c r="G10" s="1288"/>
       <c r="H10" s="1170"/>
       <c r="I10" s="1171"/>
       <c r="K10" s="1254"/>
       <c r="L10" s="1255"/>
     </row>
     <row r="11" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1313" t="s">
+      <c r="A11" s="1289" t="s">
         <v>597</v>
       </c>
-      <c r="B11" s="1314"/>
-      <c r="C11" s="1314"/>
-      <c r="D11" s="1314"/>
-      <c r="E11" s="1314"/>
-      <c r="F11" s="1314"/>
-      <c r="G11" s="1314"/>
-      <c r="H11" s="1314"/>
-      <c r="I11" s="1315"/>
+      <c r="B11" s="1290"/>
+      <c r="C11" s="1290"/>
+      <c r="D11" s="1290"/>
+      <c r="E11" s="1290"/>
+      <c r="F11" s="1290"/>
+      <c r="G11" s="1290"/>
+      <c r="H11" s="1290"/>
+      <c r="I11" s="1291"/>
       <c r="K11" s="329" t="s">
         <v>15</v>
       </c>
       <c r="L11" s="1255"/>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1316" t="s">
+      <c r="A12" s="1292" t="s">
         <v>535</v>
       </c>
-      <c r="B12" s="1317"/>
-      <c r="C12" s="1317"/>
-      <c r="D12" s="1317"/>
-      <c r="E12" s="1317"/>
-      <c r="F12" s="1317"/>
-      <c r="G12" s="1317"/>
-      <c r="H12" s="1317"/>
-      <c r="I12" s="1318"/>
+      <c r="B12" s="1293"/>
+      <c r="C12" s="1293"/>
+      <c r="D12" s="1293"/>
+      <c r="E12" s="1293"/>
+      <c r="F12" s="1293"/>
+      <c r="G12" s="1293"/>
+      <c r="H12" s="1293"/>
+      <c r="I12" s="1294"/>
       <c r="K12" s="329" t="s">
         <v>18</v>
       </c>
@@ -17736,17 +17721,17 @@
       <c r="L14" s="1255"/>
     </row>
     <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1303" t="s">
+      <c r="A15" s="1295" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1303"/>
+      <c r="B15" s="1295"/>
       <c r="C15" s="1181" t="s">
         <v>599</v>
       </c>
-      <c r="D15" s="1319">
+      <c r="D15" s="1296">
         <v>1</v>
       </c>
-      <c r="E15" s="1320"/>
+      <c r="E15" s="1297"/>
       <c r="F15" s="1183">
         <v>2</v>
       </c>
@@ -17765,17 +17750,17 @@
       <c r="L15" s="1257"/>
     </row>
     <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1295" t="s">
+      <c r="A16" s="1298" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1295"/>
+      <c r="B16" s="1298"/>
       <c r="C16" s="1184" t="s">
         <v>599</v>
       </c>
-      <c r="D16" s="1306">
+      <c r="D16" s="1299">
         <v>5</v>
       </c>
-      <c r="E16" s="1307"/>
+      <c r="E16" s="1300"/>
       <c r="F16" s="1186">
         <v>5</v>
       </c>
@@ -17794,15 +17779,15 @@
       <c r="L16" s="1257"/>
     </row>
     <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1295" t="s">
+      <c r="A17" s="1298" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1295"/>
+      <c r="B17" s="1298"/>
       <c r="C17" s="1184" t="s">
         <v>599</v>
       </c>
-      <c r="D17" s="1306"/>
-      <c r="E17" s="1307"/>
+      <c r="D17" s="1299"/>
+      <c r="E17" s="1300"/>
       <c r="F17" s="1186"/>
       <c r="G17" s="1185"/>
       <c r="H17" s="1185"/>
@@ -17813,75 +17798,75 @@
       <c r="L17" s="1258"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1295" t="s">
+      <c r="A18" s="1298" t="s">
         <v>600</v>
       </c>
-      <c r="B18" s="1295"/>
+      <c r="B18" s="1298"/>
       <c r="C18" s="1185" t="s">
         <v>186</v>
       </c>
-      <c r="D18" s="1306"/>
-      <c r="E18" s="1307"/>
+      <c r="D18" s="1299"/>
+      <c r="E18" s="1300"/>
       <c r="F18" s="1187"/>
       <c r="G18" s="1188"/>
       <c r="H18" s="1188"/>
       <c r="I18" s="1187"/>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1295" t="s">
+      <c r="A19" s="1298" t="s">
         <v>601</v>
       </c>
-      <c r="B19" s="1295"/>
+      <c r="B19" s="1298"/>
       <c r="C19" s="1185" t="s">
         <v>186</v>
       </c>
-      <c r="D19" s="1306"/>
-      <c r="E19" s="1307"/>
+      <c r="D19" s="1299"/>
+      <c r="E19" s="1300"/>
       <c r="F19" s="1186"/>
       <c r="G19" s="1185"/>
       <c r="H19" s="1189"/>
       <c r="I19" s="1190"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1308" t="s">
+      <c r="A20" s="1301" t="s">
         <v>602</v>
       </c>
-      <c r="B20" s="1309"/>
+      <c r="B20" s="1302"/>
       <c r="C20" s="1191" t="s">
         <v>186</v>
       </c>
-      <c r="D20" s="1306"/>
-      <c r="E20" s="1307"/>
+      <c r="D20" s="1299"/>
+      <c r="E20" s="1300"/>
       <c r="F20" s="1186"/>
       <c r="G20" s="1185"/>
       <c r="H20" s="1189"/>
       <c r="I20" s="1190"/>
     </row>
     <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1295" t="s">
+      <c r="A21" s="1298" t="s">
         <v>603</v>
       </c>
-      <c r="B21" s="1295"/>
+      <c r="B21" s="1298"/>
       <c r="C21" s="1185" t="s">
         <v>604</v>
       </c>
-      <c r="D21" s="1310"/>
-      <c r="E21" s="1311"/>
+      <c r="D21" s="1303"/>
+      <c r="E21" s="1304"/>
       <c r="F21" s="1186"/>
       <c r="G21" s="1185"/>
       <c r="H21" s="1185"/>
       <c r="I21" s="1186"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1298" t="s">
+      <c r="A22" s="1305" t="s">
         <v>605</v>
       </c>
-      <c r="B22" s="1298"/>
+      <c r="B22" s="1305"/>
       <c r="C22" s="1192" t="s">
         <v>606</v>
       </c>
-      <c r="D22" s="1301"/>
-      <c r="E22" s="1302"/>
+      <c r="D22" s="1306"/>
+      <c r="E22" s="1307"/>
       <c r="F22" s="1193"/>
       <c r="G22" s="1194"/>
       <c r="H22" s="1194"/>
@@ -17901,148 +17886,148 @@
       <c r="I23" s="1195"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1303" t="s">
+      <c r="A24" s="1295" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="1303"/>
+      <c r="B24" s="1295"/>
       <c r="C24" s="1196"/>
-      <c r="D24" s="1304"/>
-      <c r="E24" s="1305"/>
+      <c r="D24" s="1308"/>
+      <c r="E24" s="1309"/>
       <c r="F24" s="1198"/>
       <c r="G24" s="1197"/>
       <c r="H24" s="1197"/>
       <c r="I24" s="1198"/>
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1295" t="s">
+      <c r="A25" s="1298" t="s">
         <v>607</v>
       </c>
-      <c r="B25" s="1295"/>
+      <c r="B25" s="1298"/>
       <c r="C25" s="1191" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="1296"/>
-      <c r="E25" s="1297"/>
+      <c r="D25" s="1310"/>
+      <c r="E25" s="1311"/>
       <c r="F25" s="1200"/>
       <c r="G25" s="1199"/>
       <c r="H25" s="1199"/>
       <c r="I25" s="1200"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1295" t="s">
+      <c r="A26" s="1298" t="s">
         <v>608</v>
       </c>
-      <c r="B26" s="1295"/>
+      <c r="B26" s="1298"/>
       <c r="C26" s="1191" t="s">
         <v>186</v>
       </c>
-      <c r="D26" s="1296"/>
-      <c r="E26" s="1297"/>
+      <c r="D26" s="1310"/>
+      <c r="E26" s="1311"/>
       <c r="F26" s="1200"/>
       <c r="G26" s="1199"/>
       <c r="H26" s="1199"/>
       <c r="I26" s="1200"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1295" t="s">
+      <c r="A27" s="1298" t="s">
         <v>609</v>
       </c>
-      <c r="B27" s="1295"/>
+      <c r="B27" s="1298"/>
       <c r="C27" s="1191" t="s">
         <v>186</v>
       </c>
-      <c r="D27" s="1296"/>
-      <c r="E27" s="1297"/>
+      <c r="D27" s="1310"/>
+      <c r="E27" s="1311"/>
       <c r="F27" s="1200"/>
       <c r="G27" s="1199"/>
       <c r="H27" s="1199"/>
       <c r="I27" s="1200"/>
     </row>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1295" t="s">
+      <c r="A28" s="1298" t="s">
         <v>610</v>
       </c>
-      <c r="B28" s="1295"/>
+      <c r="B28" s="1298"/>
       <c r="C28" s="1191" t="s">
         <v>186</v>
       </c>
-      <c r="D28" s="1296"/>
-      <c r="E28" s="1297"/>
+      <c r="D28" s="1310"/>
+      <c r="E28" s="1311"/>
       <c r="F28" s="1200"/>
       <c r="G28" s="1199"/>
       <c r="H28" s="1199"/>
       <c r="I28" s="1200"/>
     </row>
     <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1295" t="s">
+      <c r="A29" s="1298" t="s">
         <v>611</v>
       </c>
-      <c r="B29" s="1295"/>
+      <c r="B29" s="1298"/>
       <c r="C29" s="1191" t="s">
         <v>186</v>
       </c>
-      <c r="D29" s="1296"/>
-      <c r="E29" s="1297"/>
+      <c r="D29" s="1310"/>
+      <c r="E29" s="1311"/>
       <c r="F29" s="1201"/>
       <c r="G29" s="1202"/>
       <c r="H29" s="1202"/>
       <c r="I29" s="1201"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1295" t="s">
+      <c r="A30" s="1298" t="s">
         <v>612</v>
       </c>
-      <c r="B30" s="1295"/>
+      <c r="B30" s="1298"/>
       <c r="C30" s="1191" t="s">
         <v>186</v>
       </c>
-      <c r="D30" s="1296"/>
-      <c r="E30" s="1297"/>
+      <c r="D30" s="1310"/>
+      <c r="E30" s="1311"/>
       <c r="F30" s="1201"/>
       <c r="G30" s="1202"/>
       <c r="H30" s="1202"/>
       <c r="I30" s="1201"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1295" t="s">
+      <c r="A31" s="1298" t="s">
         <v>613</v>
       </c>
-      <c r="B31" s="1295"/>
+      <c r="B31" s="1298"/>
       <c r="C31" s="1191" t="s">
         <v>186</v>
       </c>
-      <c r="D31" s="1296"/>
-      <c r="E31" s="1297"/>
+      <c r="D31" s="1310"/>
+      <c r="E31" s="1311"/>
       <c r="F31" s="1201"/>
       <c r="G31" s="1202"/>
       <c r="H31" s="1202"/>
       <c r="I31" s="1201"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1295" t="s">
+      <c r="A32" s="1298" t="s">
         <v>614</v>
       </c>
-      <c r="B32" s="1295"/>
+      <c r="B32" s="1298"/>
       <c r="C32" s="1185" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="1296"/>
-      <c r="E32" s="1297"/>
+      <c r="D32" s="1310"/>
+      <c r="E32" s="1311"/>
       <c r="F32" s="1203"/>
       <c r="G32" s="1204"/>
       <c r="H32" s="1204"/>
       <c r="I32" s="1203"/>
     </row>
     <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1298" t="s">
+      <c r="A33" s="1305" t="s">
         <v>615</v>
       </c>
-      <c r="B33" s="1298"/>
+      <c r="B33" s="1305"/>
       <c r="C33" s="1192" t="s">
         <v>606</v>
       </c>
-      <c r="D33" s="1299"/>
-      <c r="E33" s="1300"/>
+      <c r="D33" s="1312"/>
+      <c r="E33" s="1313"/>
       <c r="F33" s="1193"/>
       <c r="G33" s="1194"/>
       <c r="H33" s="1194"/>
@@ -18068,19 +18053,19 @@
         <v>617</v>
       </c>
       <c r="B35" s="1210"/>
-      <c r="C35" s="1290"/>
-      <c r="D35" s="1291"/>
+      <c r="C35" s="1314"/>
+      <c r="D35" s="1315"/>
       <c r="E35" s="1211"/>
-      <c r="F35" s="1288" t="s">
+      <c r="F35" s="1318" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="1288" t="s">
+      <c r="G35" s="1318" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="1288" t="s">
+      <c r="H35" s="1318" t="s">
         <v>618</v>
       </c>
-      <c r="I35" s="1288" t="s">
+      <c r="I35" s="1318" t="s">
         <v>235</v>
       </c>
     </row>
@@ -18089,21 +18074,21 @@
         <v>619</v>
       </c>
       <c r="B36" s="1213"/>
-      <c r="C36" s="1290"/>
-      <c r="D36" s="1291"/>
+      <c r="C36" s="1314"/>
+      <c r="D36" s="1315"/>
       <c r="E36" s="1211"/>
-      <c r="F36" s="1289"/>
-      <c r="G36" s="1289"/>
-      <c r="H36" s="1289"/>
-      <c r="I36" s="1289"/>
+      <c r="F36" s="1319"/>
+      <c r="G36" s="1319"/>
+      <c r="H36" s="1319"/>
+      <c r="I36" s="1319"/>
     </row>
     <row r="37" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1212" t="s">
         <v>620</v>
       </c>
       <c r="B37" s="1213"/>
-      <c r="C37" s="1292"/>
-      <c r="D37" s="1291"/>
+      <c r="C37" s="1320"/>
+      <c r="D37" s="1315"/>
       <c r="E37" s="1214"/>
       <c r="F37" s="1215" t="s">
         <v>621</v>
@@ -18117,8 +18102,8 @@
         <v>622</v>
       </c>
       <c r="B38" s="1220"/>
-      <c r="C38" s="1290"/>
-      <c r="D38" s="1291"/>
+      <c r="C38" s="1314"/>
+      <c r="D38" s="1315"/>
       <c r="E38" s="1211"/>
       <c r="F38" s="1215" t="s">
         <v>623</v>
@@ -18132,8 +18117,8 @@
         <v>624</v>
       </c>
       <c r="B39" s="1213"/>
-      <c r="C39" s="1290"/>
-      <c r="D39" s="1291"/>
+      <c r="C39" s="1314"/>
+      <c r="D39" s="1315"/>
       <c r="E39" s="1211"/>
       <c r="F39" s="1215" t="s">
         <v>114</v>
@@ -18162,8 +18147,8 @@
         <v>625</v>
       </c>
       <c r="B41" s="1223"/>
-      <c r="C41" s="1284"/>
-      <c r="D41" s="1284"/>
+      <c r="C41" s="1321"/>
+      <c r="D41" s="1321"/>
       <c r="E41" s="1221"/>
       <c r="F41" s="1215" t="s">
         <v>626</v>
@@ -18177,8 +18162,8 @@
         <v>627</v>
       </c>
       <c r="B42" s="1225"/>
-      <c r="C42" s="1284"/>
-      <c r="D42" s="1284"/>
+      <c r="C42" s="1321"/>
+      <c r="D42" s="1321"/>
       <c r="E42" s="1226"/>
       <c r="J42" s="1227"/>
     </row>
@@ -18187,17 +18172,17 @@
         <v>628</v>
       </c>
       <c r="B43" s="1229"/>
-      <c r="C43" s="1284"/>
-      <c r="D43" s="1284"/>
+      <c r="C43" s="1321"/>
+      <c r="D43" s="1321"/>
       <c r="E43" s="1226"/>
-      <c r="F43" s="1293" t="s">
+      <c r="F43" s="1322" t="s">
         <v>629</v>
       </c>
-      <c r="G43" s="1294"/>
-      <c r="H43" s="1282" t="s">
+      <c r="G43" s="1323"/>
+      <c r="H43" s="1316" t="s">
         <v>630</v>
       </c>
-      <c r="I43" s="1283"/>
+      <c r="I43" s="1317"/>
       <c r="J43" s="1227"/>
     </row>
     <row r="44" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18205,31 +18190,31 @@
         <v>631</v>
       </c>
       <c r="B44" s="1225"/>
-      <c r="C44" s="1284"/>
-      <c r="D44" s="1284"/>
+      <c r="C44" s="1321"/>
+      <c r="D44" s="1321"/>
       <c r="E44" s="1226"/>
       <c r="F44" s="1230" t="s">
         <v>632</v>
       </c>
       <c r="G44" s="1231"/>
-      <c r="H44" s="1282"/>
-      <c r="I44" s="1283"/>
+      <c r="H44" s="1316"/>
+      <c r="I44" s="1317"/>
       <c r="J44" s="1227"/>
     </row>
     <row r="45" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1286" t="s">
+      <c r="A45" s="1325" t="s">
         <v>633</v>
       </c>
-      <c r="B45" s="1287"/>
-      <c r="C45" s="1284"/>
-      <c r="D45" s="1284"/>
+      <c r="B45" s="1326"/>
+      <c r="C45" s="1321"/>
+      <c r="D45" s="1321"/>
       <c r="E45" s="1226"/>
       <c r="F45" s="1230" t="s">
         <v>634</v>
       </c>
       <c r="G45" s="1231"/>
-      <c r="H45" s="1282"/>
-      <c r="I45" s="1283"/>
+      <c r="H45" s="1316"/>
+      <c r="I45" s="1317"/>
       <c r="J45" s="1227"/>
     </row>
     <row r="46" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18243,8 +18228,8 @@
         <v>635</v>
       </c>
       <c r="G46" s="1231"/>
-      <c r="H46" s="1282"/>
-      <c r="I46" s="1283"/>
+      <c r="H46" s="1316"/>
+      <c r="I46" s="1317"/>
     </row>
     <row r="47" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1235"/>
@@ -18255,8 +18240,8 @@
         <v>636</v>
       </c>
       <c r="G47" s="1231"/>
-      <c r="H47" s="1282"/>
-      <c r="I47" s="1283"/>
+      <c r="H47" s="1316"/>
+      <c r="I47" s="1317"/>
     </row>
     <row r="48" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1235"/>
@@ -18267,8 +18252,8 @@
         <v>588</v>
       </c>
       <c r="G48" s="1238"/>
-      <c r="H48" s="1282"/>
-      <c r="I48" s="1283"/>
+      <c r="H48" s="1316"/>
+      <c r="I48" s="1317"/>
     </row>
     <row r="49" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1239"/>
@@ -18279,8 +18264,8 @@
         <v>637</v>
       </c>
       <c r="G49" s="1231"/>
-      <c r="H49" s="1284"/>
-      <c r="I49" s="1284"/>
+      <c r="H49" s="1321"/>
+      <c r="I49" s="1321"/>
     </row>
     <row r="50" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E50" s="352"/>
@@ -18321,17 +18306,17 @@
     </row>
     <row r="55" spans="1:9" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1285" t="s">
+      <c r="A56" s="1324" t="s">
         <v>640</v>
       </c>
-      <c r="B56" s="1285"/>
-      <c r="C56" s="1285"/>
-      <c r="D56" s="1285"/>
-      <c r="E56" s="1285"/>
-      <c r="F56" s="1285"/>
-      <c r="G56" s="1285"/>
-      <c r="H56" s="1285"/>
-      <c r="I56" s="1285"/>
+      <c r="B56" s="1324"/>
+      <c r="C56" s="1324"/>
+      <c r="D56" s="1324"/>
+      <c r="E56" s="1324"/>
+      <c r="F56" s="1324"/>
+      <c r="G56" s="1324"/>
+      <c r="H56" s="1324"/>
+      <c r="I56" s="1324"/>
     </row>
     <row r="57" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -18341,54 +18326,16 @@
     <protectedRange sqref="B9:C10" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="71">
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="H35:H36"/>
@@ -18402,16 +18349,54 @@
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:G8"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.3" top="0.75" bottom="0.15" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="80" fitToWidth="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -18518,33 +18503,33 @@
       <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1525" t="s">
+      <c r="A8" s="1496" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1525"/>
-      <c r="C8" s="1525"/>
-      <c r="D8" s="1525"/>
-      <c r="E8" s="1525"/>
-      <c r="F8" s="1525"/>
-      <c r="G8" s="1525"/>
-      <c r="H8" s="1525"/>
-      <c r="I8" s="1525"/>
-      <c r="J8" s="1525"/>
+      <c r="B8" s="1496"/>
+      <c r="C8" s="1496"/>
+      <c r="D8" s="1496"/>
+      <c r="E8" s="1496"/>
+      <c r="F8" s="1496"/>
+      <c r="G8" s="1496"/>
+      <c r="H8" s="1496"/>
+      <c r="I8" s="1496"/>
+      <c r="J8" s="1496"/>
     </row>
     <row r="9" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1528">
+      <c r="A9" s="1521">
         <f>J13</f>
         <v>1</v>
       </c>
-      <c r="B9" s="1528"/>
-      <c r="C9" s="1528"/>
-      <c r="D9" s="1528"/>
-      <c r="E9" s="1528"/>
-      <c r="F9" s="1528"/>
-      <c r="G9" s="1528"/>
-      <c r="H9" s="1528"/>
-      <c r="I9" s="1528"/>
-      <c r="J9" s="1528"/>
+      <c r="B9" s="1521"/>
+      <c r="C9" s="1521"/>
+      <c r="D9" s="1521"/>
+      <c r="E9" s="1521"/>
+      <c r="F9" s="1521"/>
+      <c r="G9" s="1521"/>
+      <c r="H9" s="1521"/>
+      <c r="I9" s="1521"/>
+      <c r="J9" s="1521"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18566,13 +18551,13 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1527" t="s">
+      <c r="C11" s="1498" t="s">
         <v>281</v>
       </c>
-      <c r="D11" s="1527"/>
-      <c r="E11" s="1527"/>
-      <c r="F11" s="1527"/>
-      <c r="G11" s="1527"/>
+      <c r="D11" s="1498"/>
+      <c r="E11" s="1498"/>
+      <c r="F11" s="1498"/>
+      <c r="G11" s="1498"/>
       <c r="H11" s="121" t="s">
         <v>3</v>
       </c>
@@ -18594,13 +18579,13 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1527" t="s">
+      <c r="C12" s="1498" t="s">
         <v>286</v>
       </c>
-      <c r="D12" s="1527"/>
-      <c r="E12" s="1527"/>
-      <c r="F12" s="1527"/>
-      <c r="G12" s="1527"/>
+      <c r="D12" s="1498"/>
+      <c r="E12" s="1498"/>
+      <c r="F12" s="1498"/>
+      <c r="G12" s="1498"/>
       <c r="H12" s="26" t="s">
         <v>6</v>
       </c>
@@ -18624,13 +18609,13 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1527" t="s">
+      <c r="C13" s="1498" t="s">
         <v>291</v>
       </c>
-      <c r="D13" s="1527"/>
-      <c r="E13" s="1527"/>
-      <c r="F13" s="1527"/>
-      <c r="G13" s="1527"/>
+      <c r="D13" s="1498"/>
+      <c r="E13" s="1498"/>
+      <c r="F13" s="1498"/>
+      <c r="G13" s="1498"/>
       <c r="H13" s="26" t="s">
         <v>292</v>
       </c>
@@ -18643,8 +18628,8 @@
       <c r="K13" s="124"/>
       <c r="L13" s="124"/>
       <c r="M13" s="124"/>
-      <c r="P13" s="1524"/>
-      <c r="Q13" s="1524"/>
+      <c r="P13" s="1495"/>
+      <c r="Q13" s="1495"/>
     </row>
     <row r="14" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -18664,34 +18649,34 @@
       <c r="Q14" s="734"/>
     </row>
     <row r="15" spans="1:17" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1513" t="s">
+      <c r="A15" s="1499" t="s">
         <v>371</v>
       </c>
-      <c r="B15" s="1514"/>
-      <c r="C15" s="1514"/>
-      <c r="D15" s="1514"/>
-      <c r="E15" s="1514"/>
-      <c r="F15" s="1514"/>
-      <c r="G15" s="1514"/>
-      <c r="H15" s="1514"/>
-      <c r="I15" s="1514"/>
-      <c r="J15" s="1515"/>
+      <c r="B15" s="1500"/>
+      <c r="C15" s="1500"/>
+      <c r="D15" s="1500"/>
+      <c r="E15" s="1500"/>
+      <c r="F15" s="1500"/>
+      <c r="G15" s="1500"/>
+      <c r="H15" s="1500"/>
+      <c r="I15" s="1500"/>
+      <c r="J15" s="1501"/>
       <c r="K15" s="124"/>
       <c r="L15" s="124"/>
     </row>
     <row r="16" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1516" t="s">
+      <c r="A16" s="1502" t="s">
         <v>372</v>
       </c>
-      <c r="B16" s="1517"/>
-      <c r="C16" s="1517"/>
-      <c r="D16" s="1517"/>
-      <c r="E16" s="1517"/>
-      <c r="F16" s="1517"/>
-      <c r="G16" s="1517"/>
-      <c r="H16" s="1517"/>
-      <c r="I16" s="1517"/>
-      <c r="J16" s="1518"/>
+      <c r="B16" s="1503"/>
+      <c r="C16" s="1503"/>
+      <c r="D16" s="1503"/>
+      <c r="E16" s="1503"/>
+      <c r="F16" s="1503"/>
+      <c r="G16" s="1503"/>
+      <c r="H16" s="1503"/>
+      <c r="I16" s="1503"/>
+      <c r="J16" s="1504"/>
       <c r="K16" s="124"/>
       <c r="L16" s="124"/>
     </row>
@@ -18710,18 +18695,18 @@
       <c r="L17" s="124"/>
     </row>
     <row r="18" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1488" t="s">
+      <c r="A18" s="1469" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1489"/>
-      <c r="C18" s="1489"/>
-      <c r="D18" s="1489"/>
-      <c r="E18" s="1489"/>
-      <c r="F18" s="1489"/>
-      <c r="G18" s="1489"/>
-      <c r="H18" s="1489"/>
-      <c r="I18" s="1489"/>
-      <c r="J18" s="1490"/>
+      <c r="B18" s="1470"/>
+      <c r="C18" s="1470"/>
+      <c r="D18" s="1470"/>
+      <c r="E18" s="1470"/>
+      <c r="F18" s="1470"/>
+      <c r="G18" s="1470"/>
+      <c r="H18" s="1470"/>
+      <c r="I18" s="1470"/>
+      <c r="J18" s="1471"/>
       <c r="L18" s="124"/>
     </row>
     <row r="19" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18836,12 +18821,12 @@
     <row r="24" spans="1:18" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="251"/>
       <c r="B24" s="249"/>
-      <c r="C24" s="1529" t="s">
+      <c r="C24" s="1517" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="1530"/>
-      <c r="E24" s="1530"/>
-      <c r="F24" s="1531"/>
+      <c r="D24" s="1518"/>
+      <c r="E24" s="1518"/>
+      <c r="F24" s="1519"/>
       <c r="G24" s="249"/>
       <c r="H24" s="249"/>
       <c r="I24" s="249"/>
@@ -18958,10 +18943,10 @@
     <row r="28" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="251"/>
       <c r="B28" s="173"/>
-      <c r="C28" s="1532"/>
-      <c r="D28" s="1532"/>
-      <c r="E28" s="1532"/>
-      <c r="F28" s="1532"/>
+      <c r="C28" s="1520"/>
+      <c r="D28" s="1520"/>
+      <c r="E28" s="1520"/>
+      <c r="F28" s="1520"/>
       <c r="G28" s="247"/>
       <c r="H28" s="260"/>
       <c r="I28" s="260"/>
@@ -18985,12 +18970,12 @@
     <row r="29" spans="1:18" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="251"/>
       <c r="B29" s="173"/>
-      <c r="C29" s="1529" t="s">
+      <c r="C29" s="1517" t="s">
         <v>383</v>
       </c>
-      <c r="D29" s="1530"/>
-      <c r="E29" s="1530"/>
-      <c r="F29" s="1531"/>
+      <c r="D29" s="1518"/>
+      <c r="E29" s="1518"/>
+      <c r="F29" s="1519"/>
       <c r="G29" s="275" t="s">
         <v>384</v>
       </c>
@@ -19419,18 +19404,18 @@
     </row>
     <row r="53" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1466" t="s">
+      <c r="A54" s="1477" t="s">
         <v>349</v>
       </c>
-      <c r="B54" s="1466"/>
-      <c r="C54" s="1466"/>
-      <c r="D54" s="1466"/>
-      <c r="E54" s="1466"/>
-      <c r="F54" s="1466"/>
-      <c r="G54" s="1466"/>
-      <c r="H54" s="1466"/>
-      <c r="I54" s="1466"/>
-      <c r="J54" s="1466"/>
+      <c r="B54" s="1477"/>
+      <c r="C54" s="1477"/>
+      <c r="D54" s="1477"/>
+      <c r="E54" s="1477"/>
+      <c r="F54" s="1477"/>
+      <c r="G54" s="1477"/>
+      <c r="H54" s="1477"/>
+      <c r="I54" s="1477"/>
+      <c r="J54" s="1477"/>
     </row>
     <row r="55" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19440,6 +19425,12 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="13">
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A16:J16"/>
@@ -19447,12 +19438,6 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -19484,15 +19469,15 @@
       <c r="A1" s="82" t="s">
         <v>393</v>
       </c>
-      <c r="B1" s="1550" t="s">
+      <c r="B1" s="1522" t="s">
         <v>394</v>
       </c>
-      <c r="C1" s="1550"/>
-      <c r="D1" s="1550"/>
-      <c r="E1" s="1550"/>
-      <c r="F1" s="1550"/>
-      <c r="G1" s="1550"/>
-      <c r="H1" s="1550"/>
+      <c r="C1" s="1522"/>
+      <c r="D1" s="1522"/>
+      <c r="E1" s="1522"/>
+      <c r="F1" s="1522"/>
+      <c r="G1" s="1522"/>
+      <c r="H1" s="1522"/>
       <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -19630,29 +19615,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="82"/>
-      <c r="B8" s="1551" t="s">
+      <c r="B8" s="1523" t="s">
         <v>406</v>
       </c>
-      <c r="C8" s="1551"/>
-      <c r="D8" s="1551"/>
+      <c r="C8" s="1523"/>
+      <c r="D8" s="1523"/>
       <c r="E8" s="827" t="s">
         <v>407</v>
       </c>
       <c r="F8" s="828" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="1552" t="s">
+      <c r="G8" s="1524" t="s">
         <v>409</v>
       </c>
-      <c r="H8" s="1552"/>
+      <c r="H8" s="1524"/>
       <c r="I8" s="82"/>
       <c r="L8" s="90" t="s">
         <v>410</v>
       </c>
-      <c r="M8" s="1553" t="s">
+      <c r="M8" s="1525" t="s">
         <v>411</v>
       </c>
-      <c r="N8" s="1553"/>
+      <c r="N8" s="1525"/>
       <c r="O8" s="91" t="s">
         <v>412</v>
       </c>
@@ -19665,13 +19650,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="82"/>
-      <c r="B9" s="1554" t="s">
+      <c r="B9" s="1526" t="s">
         <v>415</v>
       </c>
-      <c r="C9" s="1556" t="s">
+      <c r="C9" s="1528" t="s">
         <v>416</v>
       </c>
-      <c r="D9" s="1558" t="s">
+      <c r="D9" s="1530" t="s">
         <v>417</v>
       </c>
       <c r="E9" s="829" t="s">
@@ -19680,10 +19665,10 @@
       <c r="F9" s="830" t="s">
         <v>419</v>
       </c>
-      <c r="G9" s="1559" t="s">
+      <c r="G9" s="1531" t="s">
         <v>420</v>
       </c>
-      <c r="H9" s="1560"/>
+      <c r="H9" s="1532"/>
       <c r="I9" s="82"/>
       <c r="L9" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -19712,19 +19697,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="82"/>
-      <c r="B10" s="1554"/>
-      <c r="C10" s="1556"/>
-      <c r="D10" s="1558"/>
+      <c r="B10" s="1526"/>
+      <c r="C10" s="1528"/>
+      <c r="D10" s="1530"/>
       <c r="E10" s="831" t="s">
         <v>421</v>
       </c>
       <c r="F10" s="832" t="s">
         <v>422</v>
       </c>
-      <c r="G10" s="1561" t="s">
+      <c r="G10" s="1533" t="s">
         <v>423</v>
       </c>
-      <c r="H10" s="1562"/>
+      <c r="H10" s="1534"/>
       <c r="I10" s="82"/>
       <c r="L10" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -19749,9 +19734,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="82"/>
-      <c r="B11" s="1554"/>
-      <c r="C11" s="1556"/>
-      <c r="D11" s="1558" t="s">
+      <c r="B11" s="1526"/>
+      <c r="C11" s="1528"/>
+      <c r="D11" s="1530" t="s">
         <v>424</v>
       </c>
       <c r="E11" s="831" t="s">
@@ -19763,7 +19748,7 @@
       <c r="G11" s="834" t="s">
         <v>427</v>
       </c>
-      <c r="H11" s="1563" t="s">
+      <c r="H11" s="1535" t="s">
         <v>428</v>
       </c>
       <c r="I11" s="82"/>
@@ -19782,9 +19767,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="82"/>
-      <c r="B12" s="1554"/>
-      <c r="C12" s="1557"/>
-      <c r="D12" s="1558"/>
+      <c r="B12" s="1526"/>
+      <c r="C12" s="1529"/>
+      <c r="D12" s="1530"/>
       <c r="E12" s="93" t="s">
         <v>429</v>
       </c>
@@ -19794,7 +19779,7 @@
       <c r="G12" s="834" t="s">
         <v>431</v>
       </c>
-      <c r="H12" s="1564"/>
+      <c r="H12" s="1536"/>
       <c r="I12" s="82"/>
       <c r="L12" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -19807,11 +19792,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="82"/>
-      <c r="B13" s="1554"/>
-      <c r="C13" s="1556" t="s">
+      <c r="B13" s="1526"/>
+      <c r="C13" s="1528" t="s">
         <v>432</v>
       </c>
-      <c r="D13" s="1558" t="s">
+      <c r="D13" s="1530" t="s">
         <v>433</v>
       </c>
       <c r="E13" s="835" t="s">
@@ -19820,10 +19805,10 @@
       <c r="F13" s="836" t="s">
         <v>435</v>
       </c>
-      <c r="G13" s="1565" t="s">
+      <c r="G13" s="1537" t="s">
         <v>436</v>
       </c>
-      <c r="H13" s="1566"/>
+      <c r="H13" s="1538"/>
       <c r="I13" s="82"/>
       <c r="L13" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -19848,19 +19833,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="82"/>
-      <c r="B14" s="1554"/>
-      <c r="C14" s="1556"/>
-      <c r="D14" s="1558"/>
+      <c r="B14" s="1526"/>
+      <c r="C14" s="1528"/>
+      <c r="D14" s="1530"/>
       <c r="E14" s="835" t="s">
         <v>437</v>
       </c>
       <c r="F14" s="836" t="s">
         <v>438</v>
       </c>
-      <c r="G14" s="1565" t="s">
+      <c r="G14" s="1537" t="s">
         <v>439</v>
       </c>
-      <c r="H14" s="1566"/>
+      <c r="H14" s="1538"/>
       <c r="I14" s="82"/>
       <c r="L14" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -19885,9 +19870,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="82"/>
-      <c r="B15" s="1554"/>
-      <c r="C15" s="1556"/>
-      <c r="D15" s="1558" t="s">
+      <c r="B15" s="1526"/>
+      <c r="C15" s="1528"/>
+      <c r="D15" s="1530" t="s">
         <v>440</v>
       </c>
       <c r="E15" s="835" t="s">
@@ -19899,7 +19884,7 @@
       <c r="G15" s="838" t="s">
         <v>443</v>
       </c>
-      <c r="H15" s="1533" t="s">
+      <c r="H15" s="1539" t="s">
         <v>444</v>
       </c>
       <c r="I15" s="82"/>
@@ -19918,9 +19903,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="82"/>
-      <c r="B16" s="1555"/>
-      <c r="C16" s="1556"/>
-      <c r="D16" s="1558"/>
+      <c r="B16" s="1527"/>
+      <c r="C16" s="1528"/>
+      <c r="D16" s="1530"/>
       <c r="E16" s="94" t="s">
         <v>445</v>
       </c>
@@ -19930,7 +19915,7 @@
       <c r="G16" s="836" t="s">
         <v>447</v>
       </c>
-      <c r="H16" s="1534"/>
+      <c r="H16" s="1540"/>
       <c r="I16" s="82"/>
       <c r="L16" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -19943,23 +19928,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="82"/>
-      <c r="B17" s="1535" t="s">
+      <c r="B17" s="1541" t="s">
         <v>448</v>
       </c>
-      <c r="C17" s="1538" t="s">
+      <c r="C17" s="1544" t="s">
         <v>449</v>
       </c>
-      <c r="D17" s="1539"/>
+      <c r="D17" s="1545"/>
       <c r="E17" s="839" t="s">
         <v>450</v>
       </c>
       <c r="F17" s="840" t="s">
         <v>451</v>
       </c>
-      <c r="G17" s="1544" t="s">
+      <c r="G17" s="1550" t="s">
         <v>452</v>
       </c>
-      <c r="H17" s="1545"/>
+      <c r="H17" s="1551"/>
       <c r="I17" s="82"/>
       <c r="L17" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -19972,17 +19957,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="82"/>
-      <c r="B18" s="1536"/>
-      <c r="C18" s="1540"/>
-      <c r="D18" s="1541"/>
+      <c r="B18" s="1542"/>
+      <c r="C18" s="1546"/>
+      <c r="D18" s="1547"/>
       <c r="E18" s="839" t="s">
         <v>453</v>
       </c>
       <c r="F18" s="840" t="s">
         <v>454</v>
       </c>
-      <c r="G18" s="1546"/>
-      <c r="H18" s="1547"/>
+      <c r="G18" s="1552"/>
+      <c r="H18" s="1553"/>
       <c r="I18" s="82"/>
       <c r="L18" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -19995,9 +19980,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="82"/>
-      <c r="B19" s="1536"/>
-      <c r="C19" s="1542"/>
-      <c r="D19" s="1543"/>
+      <c r="B19" s="1542"/>
+      <c r="C19" s="1548"/>
+      <c r="D19" s="1549"/>
       <c r="E19" s="839" t="s">
         <v>455</v>
       </c>
@@ -20018,11 +20003,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="82"/>
-      <c r="B20" s="1536"/>
-      <c r="C20" s="1540" t="s">
+      <c r="B20" s="1542"/>
+      <c r="C20" s="1546" t="s">
         <v>457</v>
       </c>
-      <c r="D20" s="1548"/>
+      <c r="D20" s="1554"/>
       <c r="E20" s="841" t="s">
         <v>458</v>
       </c>
@@ -20043,9 +20028,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="82"/>
-      <c r="B21" s="1536"/>
-      <c r="C21" s="1540"/>
-      <c r="D21" s="1548"/>
+      <c r="B21" s="1542"/>
+      <c r="C21" s="1546"/>
+      <c r="D21" s="1554"/>
       <c r="E21" s="841" t="s">
         <v>145</v>
       </c>
@@ -20066,9 +20051,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="82"/>
-      <c r="B22" s="1536"/>
-      <c r="C22" s="1542"/>
-      <c r="D22" s="1549"/>
+      <c r="B22" s="1542"/>
+      <c r="C22" s="1548"/>
+      <c r="D22" s="1555"/>
       <c r="E22" s="98" t="s">
         <v>461</v>
       </c>
@@ -20089,11 +20074,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="82"/>
-      <c r="B23" s="1536"/>
-      <c r="C23" s="1538" t="s">
+      <c r="B23" s="1542"/>
+      <c r="C23" s="1544" t="s">
         <v>463</v>
       </c>
-      <c r="D23" s="1539"/>
+      <c r="D23" s="1545"/>
       <c r="E23" s="842" t="s">
         <v>464</v>
       </c>
@@ -20114,7 +20099,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="82"/>
-      <c r="B24" s="1537"/>
+      <c r="B24" s="1543"/>
       <c r="C24" s="844"/>
       <c r="D24" s="845"/>
       <c r="E24" s="846"/>
@@ -20221,6 +20206,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -20237,12 +20228,6 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20318,71 +20303,71 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="53"/>
-      <c r="B4" s="1573" t="s">
+      <c r="B4" s="1562" t="s">
         <v>466</v>
       </c>
-      <c r="C4" s="1574"/>
-      <c r="D4" s="1575" t="s">
+      <c r="C4" s="1563"/>
+      <c r="D4" s="1564" t="s">
         <v>467</v>
       </c>
-      <c r="E4" s="1575"/>
-      <c r="F4" s="1575"/>
-      <c r="G4" s="1575"/>
-      <c r="H4" s="1575"/>
-      <c r="I4" s="1575"/>
-      <c r="J4" s="1575"/>
-      <c r="K4" s="1576" t="s">
+      <c r="E4" s="1564"/>
+      <c r="F4" s="1564"/>
+      <c r="G4" s="1564"/>
+      <c r="H4" s="1564"/>
+      <c r="I4" s="1564"/>
+      <c r="J4" s="1564"/>
+      <c r="K4" s="1565" t="s">
         <v>468</v>
       </c>
-      <c r="L4" s="1577"/>
-      <c r="M4" s="1577"/>
-      <c r="N4" s="1577"/>
-      <c r="O4" s="1578"/>
+      <c r="L4" s="1566"/>
+      <c r="M4" s="1566"/>
+      <c r="N4" s="1566"/>
+      <c r="O4" s="1567"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="53"/>
-      <c r="B5" s="1579" t="s">
+      <c r="B5" s="1568" t="s">
         <v>469</v>
       </c>
-      <c r="C5" s="1580"/>
-      <c r="D5" s="1583" t="s">
+      <c r="C5" s="1569"/>
+      <c r="D5" s="1572" t="s">
         <v>470</v>
       </c>
-      <c r="E5" s="1584"/>
-      <c r="F5" s="1585" t="s">
+      <c r="E5" s="1573"/>
+      <c r="F5" s="1574" t="s">
         <v>471</v>
       </c>
-      <c r="G5" s="1583" t="s">
+      <c r="G5" s="1572" t="s">
         <v>472</v>
       </c>
-      <c r="H5" s="1587"/>
-      <c r="I5" s="1587"/>
-      <c r="J5" s="1584"/>
-      <c r="K5" s="1588" t="s">
+      <c r="H5" s="1576"/>
+      <c r="I5" s="1576"/>
+      <c r="J5" s="1573"/>
+      <c r="K5" s="1577" t="s">
         <v>473</v>
       </c>
-      <c r="L5" s="1590" t="s">
+      <c r="L5" s="1579" t="s">
         <v>474</v>
       </c>
-      <c r="M5" s="1592" t="s">
+      <c r="M5" s="1581" t="s">
         <v>475</v>
       </c>
-      <c r="N5" s="1594" t="s">
+      <c r="N5" s="1583" t="s">
         <v>476</v>
       </c>
-      <c r="O5" s="1595"/>
+      <c r="O5" s="1584"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="53"/>
-      <c r="B6" s="1581"/>
-      <c r="C6" s="1582"/>
+      <c r="B6" s="1570"/>
+      <c r="C6" s="1571"/>
       <c r="D6" s="848" t="s">
         <v>477</v>
       </c>
       <c r="E6" s="849" t="s">
         <v>478</v>
       </c>
-      <c r="F6" s="1586"/>
+      <c r="F6" s="1575"/>
       <c r="G6" s="848" t="s">
         <v>479</v>
       </c>
@@ -20395,9 +20380,9 @@
       <c r="J6" s="849" t="s">
         <v>482</v>
       </c>
-      <c r="K6" s="1589"/>
-      <c r="L6" s="1591"/>
-      <c r="M6" s="1593"/>
+      <c r="K6" s="1578"/>
+      <c r="L6" s="1580"/>
+      <c r="M6" s="1582"/>
       <c r="N6" s="852" t="s">
         <v>483</v>
       </c>
@@ -20797,21 +20782,21 @@
         <f>+D38</f>
         <v>0</v>
       </c>
-      <c r="D23" s="1567">
+      <c r="D23" s="1556">
         <v>0</v>
       </c>
-      <c r="E23" s="1568"/>
+      <c r="E23" s="1557"/>
       <c r="F23" s="886">
         <v>0</v>
       </c>
-      <c r="G23" s="1567">
+      <c r="G23" s="1556">
         <v>0</v>
       </c>
-      <c r="H23" s="1569"/>
-      <c r="I23" s="1570" t="s">
+      <c r="H23" s="1558"/>
+      <c r="I23" s="1559" t="s">
         <v>510</v>
       </c>
-      <c r="J23" s="1568"/>
+      <c r="J23" s="1557"/>
       <c r="K23" s="887" t="s">
         <v>511</v>
       </c>
@@ -20874,11 +20859,11 @@
       <c r="G26" s="76"/>
       <c r="H26" s="55"/>
       <c r="I26" s="55"/>
-      <c r="J26" s="1571" t="str">
+      <c r="J26" s="1560" t="str">
         <f>+D31&amp;" "&amp;F38</f>
         <v>A-1-a (0)</v>
       </c>
-      <c r="K26" s="1572"/>
+      <c r="K26" s="1561"/>
       <c r="L26" s="53"/>
       <c r="M26" s="53"/>
       <c r="N26" s="53"/>
@@ -21138,10 +21123,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1596" t="s">
+      <c r="A2" s="1585" t="s">
         <v>516</v>
       </c>
-      <c r="B2" s="1596"/>
+      <c r="B2" s="1585"/>
       <c r="C2" s="891" t="s">
         <v>517</v>
       </c>
@@ -21533,37 +21518,37 @@
       <c r="N5" s="1097"/>
     </row>
     <row r="6" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1363" t="s">
+      <c r="A6" s="1350" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1363"/>
-      <c r="C6" s="1363"/>
-      <c r="D6" s="1363"/>
-      <c r="E6" s="1363"/>
-      <c r="F6" s="1363"/>
-      <c r="G6" s="1363"/>
-      <c r="H6" s="1363"/>
-      <c r="I6" s="1363"/>
-      <c r="J6" s="1363"/>
-      <c r="K6" s="1363"/>
-      <c r="L6" s="1363"/>
+      <c r="B6" s="1350"/>
+      <c r="C6" s="1350"/>
+      <c r="D6" s="1350"/>
+      <c r="E6" s="1350"/>
+      <c r="F6" s="1350"/>
+      <c r="G6" s="1350"/>
+      <c r="H6" s="1350"/>
+      <c r="I6" s="1350"/>
+      <c r="J6" s="1350"/>
+      <c r="K6" s="1350"/>
+      <c r="L6" s="1350"/>
       <c r="N6" s="958"/>
     </row>
     <row r="7" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1364">
+      <c r="A7" s="1351">
         <v>0</v>
       </c>
-      <c r="B7" s="1364"/>
-      <c r="C7" s="1364"/>
-      <c r="D7" s="1364"/>
-      <c r="E7" s="1364"/>
-      <c r="F7" s="1364"/>
-      <c r="G7" s="1364"/>
-      <c r="H7" s="1364"/>
-      <c r="I7" s="1364"/>
-      <c r="J7" s="1364"/>
-      <c r="K7" s="1364"/>
-      <c r="L7" s="1364"/>
+      <c r="B7" s="1351"/>
+      <c r="C7" s="1351"/>
+      <c r="D7" s="1351"/>
+      <c r="E7" s="1351"/>
+      <c r="F7" s="1351"/>
+      <c r="G7" s="1351"/>
+      <c r="H7" s="1351"/>
+      <c r="I7" s="1351"/>
+      <c r="J7" s="1351"/>
+      <c r="K7" s="1351"/>
+      <c r="L7" s="1351"/>
       <c r="N7" s="959"/>
     </row>
     <row r="8" spans="1:40" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -21591,15 +21576,15 @@
       <c r="B9" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="1374">
+      <c r="C9" s="1361">
         <f>+formato!L2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="1374"/>
-      <c r="E9" s="1374"/>
-      <c r="F9" s="1374"/>
-      <c r="G9" s="1374"/>
-      <c r="H9" s="1374"/>
+      <c r="D9" s="1361"/>
+      <c r="E9" s="1361"/>
+      <c r="F9" s="1361"/>
+      <c r="G9" s="1361"/>
+      <c r="H9" s="1361"/>
       <c r="I9" s="960"/>
       <c r="J9" s="329" t="s">
         <v>3</v>
@@ -21634,15 +21619,15 @@
       <c r="B10" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1374">
+      <c r="C10" s="1361">
         <f>+formato!L3</f>
         <v>0</v>
       </c>
-      <c r="D10" s="1374"/>
-      <c r="E10" s="1374"/>
-      <c r="F10" s="1374"/>
-      <c r="G10" s="1374"/>
-      <c r="H10" s="1374"/>
+      <c r="D10" s="1361"/>
+      <c r="E10" s="1361"/>
+      <c r="F10" s="1361"/>
+      <c r="G10" s="1361"/>
+      <c r="H10" s="1361"/>
       <c r="I10" s="961"/>
       <c r="J10" s="329" t="s">
         <v>538</v>
@@ -21678,15 +21663,15 @@
       <c r="B11" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1374">
+      <c r="C11" s="1361">
         <f>+formato!L4</f>
         <v>0</v>
       </c>
-      <c r="D11" s="1374"/>
-      <c r="E11" s="1374"/>
-      <c r="F11" s="1374"/>
-      <c r="G11" s="1374"/>
-      <c r="H11" s="1374"/>
+      <c r="D11" s="1361"/>
+      <c r="E11" s="1361"/>
+      <c r="F11" s="1361"/>
+      <c r="G11" s="1361"/>
+      <c r="H11" s="1361"/>
       <c r="I11" s="961"/>
       <c r="J11" s="329" t="s">
         <v>8</v>
@@ -21722,16 +21707,16 @@
       <c r="B12" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1374">
+      <c r="C12" s="1361">
         <f>+formato!L5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="1374"/>
-      <c r="E12" s="1374"/>
-      <c r="F12" s="1374"/>
-      <c r="G12" s="1374"/>
-      <c r="H12" s="1374"/>
-      <c r="I12" s="1374"/>
+      <c r="D12" s="1361"/>
+      <c r="E12" s="1361"/>
+      <c r="F12" s="1361"/>
+      <c r="G12" s="1361"/>
+      <c r="H12" s="1361"/>
+      <c r="I12" s="1361"/>
       <c r="J12" s="478"/>
       <c r="K12" s="478"/>
       <c r="M12" s="1098"/>
@@ -21784,20 +21769,20 @@
       <c r="AN13" s="719"/>
     </row>
     <row r="14" spans="1:40" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1365" t="s">
+      <c r="A14" s="1352" t="s">
         <v>576</v>
       </c>
-      <c r="B14" s="1366"/>
-      <c r="C14" s="1366"/>
-      <c r="D14" s="1366"/>
-      <c r="E14" s="1366"/>
-      <c r="F14" s="1366"/>
-      <c r="G14" s="1366"/>
-      <c r="H14" s="1366"/>
-      <c r="I14" s="1366"/>
-      <c r="J14" s="1366"/>
-      <c r="K14" s="1366"/>
-      <c r="L14" s="1367"/>
+      <c r="B14" s="1353"/>
+      <c r="C14" s="1353"/>
+      <c r="D14" s="1353"/>
+      <c r="E14" s="1353"/>
+      <c r="F14" s="1353"/>
+      <c r="G14" s="1353"/>
+      <c r="H14" s="1353"/>
+      <c r="I14" s="1353"/>
+      <c r="J14" s="1353"/>
+      <c r="K14" s="1353"/>
+      <c r="L14" s="1354"/>
       <c r="M14" s="1098"/>
       <c r="Z14" s="717"/>
       <c r="AA14" s="716"/>
@@ -21816,20 +21801,20 @@
       <c r="AN14" s="719"/>
     </row>
     <row r="15" spans="1:40" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1368" t="s">
+      <c r="A15" s="1355" t="s">
         <v>535</v>
       </c>
-      <c r="B15" s="1369"/>
-      <c r="C15" s="1369"/>
-      <c r="D15" s="1369"/>
-      <c r="E15" s="1369"/>
-      <c r="F15" s="1369"/>
-      <c r="G15" s="1369"/>
-      <c r="H15" s="1369"/>
-      <c r="I15" s="1369"/>
-      <c r="J15" s="1369"/>
-      <c r="K15" s="1369"/>
-      <c r="L15" s="1370"/>
+      <c r="B15" s="1356"/>
+      <c r="C15" s="1356"/>
+      <c r="D15" s="1356"/>
+      <c r="E15" s="1356"/>
+      <c r="F15" s="1356"/>
+      <c r="G15" s="1356"/>
+      <c r="H15" s="1356"/>
+      <c r="I15" s="1356"/>
+      <c r="J15" s="1356"/>
+      <c r="K15" s="1356"/>
+      <c r="L15" s="1357"/>
       <c r="M15" s="1098"/>
       <c r="N15" s="1098"/>
       <c r="Z15" s="717"/>
@@ -21880,20 +21865,20 @@
       <c r="AN16" s="719"/>
     </row>
     <row r="17" spans="1:40" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1371" t="s">
+      <c r="A17" s="1358" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1372"/>
-      <c r="C17" s="1372"/>
-      <c r="D17" s="1372"/>
-      <c r="E17" s="1372"/>
-      <c r="F17" s="1372"/>
-      <c r="G17" s="1372"/>
-      <c r="H17" s="1372"/>
-      <c r="I17" s="1372"/>
-      <c r="J17" s="1372"/>
-      <c r="K17" s="1372"/>
-      <c r="L17" s="1373"/>
+      <c r="B17" s="1359"/>
+      <c r="C17" s="1359"/>
+      <c r="D17" s="1359"/>
+      <c r="E17" s="1359"/>
+      <c r="F17" s="1359"/>
+      <c r="G17" s="1359"/>
+      <c r="H17" s="1359"/>
+      <c r="I17" s="1359"/>
+      <c r="J17" s="1359"/>
+      <c r="K17" s="1359"/>
+      <c r="L17" s="1360"/>
       <c r="N17" s="1098"/>
       <c r="Z17" s="475"/>
       <c r="AI17" s="475"/>
@@ -22241,10 +22226,10 @@
       <c r="J26" s="330"/>
       <c r="K26" s="478"/>
       <c r="L26" s="969"/>
-      <c r="N26" s="1339" t="s">
+      <c r="N26" s="1363" t="s">
         <v>49</v>
       </c>
-      <c r="O26" s="1340"/>
+      <c r="O26" s="1364"/>
       <c r="Y26" s="1100"/>
       <c r="Z26" s="475"/>
       <c r="AA26" s="1100"/>
@@ -22509,11 +22494,11 @@
       <c r="D32" s="1118"/>
       <c r="E32" s="1118"/>
       <c r="F32" s="1119"/>
-      <c r="G32" s="1361">
+      <c r="G32" s="1382">
         <f>DATOS!F41</f>
         <v>0</v>
       </c>
-      <c r="H32" s="1361"/>
+      <c r="H32" s="1382"/>
       <c r="I32" s="988"/>
       <c r="J32" s="330"/>
       <c r="K32" s="478"/>
@@ -22605,13 +22590,13 @@
       <c r="AN34" s="719"/>
     </row>
     <row r="35" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="1357" t="s">
+      <c r="A35" s="1336" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="1357"/>
-      <c r="C35" s="1357"/>
-      <c r="D35" s="1357"/>
-      <c r="E35" s="1357"/>
+      <c r="B35" s="1336"/>
+      <c r="C35" s="1336"/>
+      <c r="D35" s="1336"/>
+      <c r="E35" s="1336"/>
       <c r="F35" s="1079">
         <v>1</v>
       </c>
@@ -22624,9 +22609,9 @@
       <c r="I35" s="1079">
         <v>4</v>
       </c>
-      <c r="J35" s="1362"/>
-      <c r="K35" s="1362"/>
-      <c r="L35" s="1362"/>
+      <c r="J35" s="1349"/>
+      <c r="K35" s="1349"/>
+      <c r="L35" s="1349"/>
       <c r="M35" s="1098"/>
       <c r="N35" s="991"/>
       <c r="Y35" s="475"/>
@@ -22647,13 +22632,13 @@
       <c r="AN35" s="719"/>
     </row>
     <row r="36" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1357" t="s">
+      <c r="A36" s="1336" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="1357"/>
-      <c r="C36" s="1357"/>
-      <c r="D36" s="1357"/>
-      <c r="E36" s="1357"/>
+      <c r="B36" s="1336"/>
+      <c r="C36" s="1336"/>
+      <c r="D36" s="1336"/>
+      <c r="E36" s="1336"/>
       <c r="F36" s="1080">
         <f>+DATOS!F15</f>
         <v>5</v>
@@ -22670,9 +22655,9 @@
         <f>+DATOS!L15</f>
         <v>5</v>
       </c>
-      <c r="J36" s="1362"/>
-      <c r="K36" s="1362"/>
-      <c r="L36" s="1362"/>
+      <c r="J36" s="1349"/>
+      <c r="K36" s="1349"/>
+      <c r="L36" s="1349"/>
       <c r="M36" s="1098"/>
       <c r="N36" s="992"/>
       <c r="Y36" s="475"/>
@@ -22693,13 +22678,13 @@
       <c r="AN36" s="719"/>
     </row>
     <row r="37" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1357" t="s">
+      <c r="A37" s="1336" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="1357"/>
-      <c r="C37" s="1357"/>
-      <c r="D37" s="1357"/>
-      <c r="E37" s="1357"/>
+      <c r="B37" s="1336"/>
+      <c r="C37" s="1336"/>
+      <c r="D37" s="1336"/>
+      <c r="E37" s="1336"/>
       <c r="F37" s="1080">
         <f>+DATOS!F16</f>
         <v>0</v>
@@ -22716,9 +22701,9 @@
         <f>+DATOS!L16</f>
         <v>0</v>
       </c>
-      <c r="J37" s="1362"/>
-      <c r="K37" s="1362"/>
-      <c r="L37" s="1362"/>
+      <c r="J37" s="1349"/>
+      <c r="K37" s="1349"/>
+      <c r="L37" s="1349"/>
       <c r="M37" s="1103"/>
       <c r="N37" s="992"/>
       <c r="Y37" s="475"/>
@@ -22739,13 +22724,13 @@
       <c r="AN37" s="719"/>
     </row>
     <row r="38" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1357" t="s">
+      <c r="A38" s="1336" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="1357"/>
-      <c r="C38" s="1357"/>
-      <c r="D38" s="1357"/>
-      <c r="E38" s="1357"/>
+      <c r="B38" s="1336"/>
+      <c r="C38" s="1336"/>
+      <c r="D38" s="1336"/>
+      <c r="E38" s="1336"/>
       <c r="F38" s="1082" t="e">
         <f>+DATOS!F21</f>
         <v>#DIV/0!</v>
@@ -22762,9 +22747,9 @@
         <f>+DATOS!L21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J38" s="1362"/>
-      <c r="K38" s="1362"/>
-      <c r="L38" s="1362"/>
+      <c r="J38" s="1349"/>
+      <c r="K38" s="1349"/>
+      <c r="L38" s="1349"/>
       <c r="M38" s="1098"/>
       <c r="N38" s="1098"/>
       <c r="V38" s="715"/>
@@ -22824,13 +22809,13 @@
       <c r="AN39" s="719"/>
     </row>
     <row r="40" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1357" t="s">
+      <c r="A40" s="1336" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="1357"/>
-      <c r="C40" s="1357"/>
-      <c r="D40" s="1357"/>
-      <c r="E40" s="1357"/>
+      <c r="B40" s="1336"/>
+      <c r="C40" s="1336"/>
+      <c r="D40" s="1336"/>
+      <c r="E40" s="1336"/>
       <c r="F40" s="1085" t="e">
         <f>+DATOS!F31</f>
         <v>#DIV/0!</v>
@@ -22847,9 +22832,9 @@
         <f>+DATOS!L31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="1358"/>
-      <c r="K40" s="1359"/>
-      <c r="L40" s="1360"/>
+      <c r="J40" s="1379"/>
+      <c r="K40" s="1380"/>
+      <c r="L40" s="1381"/>
       <c r="M40" s="1104"/>
       <c r="N40" s="1098"/>
       <c r="Q40" s="1105"/>
@@ -22874,13 +22859,13 @@
       <c r="AN40" s="719"/>
     </row>
     <row r="41" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1357" t="s">
+      <c r="A41" s="1336" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="1357"/>
-      <c r="C41" s="1357"/>
-      <c r="D41" s="1357"/>
-      <c r="E41" s="1357"/>
+      <c r="B41" s="1336"/>
+      <c r="C41" s="1336"/>
+      <c r="D41" s="1336"/>
+      <c r="E41" s="1336"/>
       <c r="F41" s="1082" t="e">
         <f>+DATOS!F32</f>
         <v>#DIV/0!</v>
@@ -22897,9 +22882,9 @@
         <f>+DATOS!L32</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="1358"/>
-      <c r="K41" s="1359"/>
-      <c r="L41" s="1360"/>
+      <c r="J41" s="1379"/>
+      <c r="K41" s="1380"/>
+      <c r="L41" s="1381"/>
       <c r="M41" s="1106"/>
       <c r="N41" s="1098"/>
       <c r="V41" s="715"/>
@@ -22946,9 +22931,9 @@
         <f>+DATOS!L33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J42" s="1358"/>
-      <c r="K42" s="1359"/>
-      <c r="L42" s="1360"/>
+      <c r="J42" s="1379"/>
+      <c r="K42" s="1380"/>
+      <c r="L42" s="1381"/>
       <c r="M42" s="1106"/>
       <c r="N42" s="1098"/>
       <c r="V42" s="715"/>
@@ -23016,16 +23001,16 @@
       <c r="G44" s="480"/>
       <c r="H44" s="407"/>
       <c r="I44" s="994"/>
-      <c r="J44" s="1375" t="s">
+      <c r="J44" s="1337" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="1376"/>
-      <c r="L44" s="1377"/>
+      <c r="K44" s="1338"/>
+      <c r="L44" s="1339"/>
       <c r="M44" s="1098"/>
-      <c r="N44" s="1341" t="s">
+      <c r="N44" s="1365" t="s">
         <v>38</v>
       </c>
-      <c r="O44" s="1341"/>
+      <c r="O44" s="1365"/>
       <c r="V44" s="715"/>
       <c r="W44" s="475"/>
       <c r="X44" s="475"/>
@@ -23056,12 +23041,12 @@
       <c r="G45" s="480"/>
       <c r="H45" s="407"/>
       <c r="I45" s="994"/>
-      <c r="J45" s="1378" t="e">
+      <c r="J45" s="1340" t="e">
         <f>+DATOS!C50</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K45" s="1379"/>
-      <c r="L45" s="1380"/>
+      <c r="K45" s="1341"/>
+      <c r="L45" s="1342"/>
       <c r="M45" s="1098"/>
       <c r="N45" s="680">
         <v>0</v>
@@ -23100,11 +23085,11 @@
       <c r="G46" s="480"/>
       <c r="H46" s="407"/>
       <c r="I46" s="994"/>
-      <c r="J46" s="1342" t="s">
+      <c r="J46" s="1366" t="s">
         <v>36</v>
       </c>
-      <c r="K46" s="1343"/>
-      <c r="L46" s="1344"/>
+      <c r="K46" s="1367"/>
+      <c r="L46" s="1368"/>
       <c r="M46" s="1098"/>
       <c r="N46" s="680" t="e">
         <f>+DATOS!J75</f>
@@ -23144,12 +23129,12 @@
       <c r="G47" s="480"/>
       <c r="H47" s="480"/>
       <c r="I47" s="994"/>
-      <c r="J47" s="1345" t="e">
+      <c r="J47" s="1369" t="e">
         <f>MROUND(N52,0.02)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K47" s="1346"/>
-      <c r="L47" s="1347"/>
+      <c r="K47" s="1370"/>
+      <c r="L47" s="1371"/>
       <c r="M47" s="1098" t="s">
         <v>574</v>
       </c>
@@ -23190,11 +23175,11 @@
       <c r="G48" s="480"/>
       <c r="H48" s="480"/>
       <c r="I48" s="994"/>
-      <c r="J48" s="1381" t="s">
+      <c r="J48" s="1343" t="s">
         <v>37</v>
       </c>
-      <c r="K48" s="1382"/>
-      <c r="L48" s="1383"/>
+      <c r="K48" s="1344"/>
+      <c r="L48" s="1345"/>
       <c r="M48" s="1098"/>
       <c r="N48" s="725"/>
       <c r="O48" s="725"/>
@@ -23229,14 +23214,14 @@
       <c r="G49" s="480"/>
       <c r="H49" s="480"/>
       <c r="I49" s="994"/>
-      <c r="J49" s="1384"/>
-      <c r="K49" s="1385"/>
-      <c r="L49" s="1386"/>
+      <c r="J49" s="1346"/>
+      <c r="K49" s="1347"/>
+      <c r="L49" s="1348"/>
       <c r="M49" s="1098"/>
-      <c r="N49" s="1341" t="s">
+      <c r="N49" s="1365" t="s">
         <v>571</v>
       </c>
-      <c r="O49" s="1341"/>
+      <c r="O49" s="1365"/>
       <c r="S49" s="348"/>
       <c r="V49" s="715"/>
       <c r="W49" s="475"/>
@@ -23268,12 +23253,12 @@
       <c r="G50" s="480"/>
       <c r="H50" s="480"/>
       <c r="I50" s="994"/>
-      <c r="J50" s="1349" t="e">
+      <c r="J50" s="1372" t="e">
         <f>+DATOS!J74</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K50" s="1350"/>
-      <c r="L50" s="1351"/>
+      <c r="K50" s="1373"/>
+      <c r="L50" s="1374"/>
       <c r="M50" s="1104"/>
       <c r="N50" s="984">
         <v>0</v>
@@ -23312,9 +23297,9 @@
       <c r="G51" s="480"/>
       <c r="H51" s="480"/>
       <c r="I51" s="994"/>
-      <c r="J51" s="1352"/>
-      <c r="K51" s="1353"/>
-      <c r="L51" s="1354"/>
+      <c r="J51" s="1375"/>
+      <c r="K51" s="1376"/>
+      <c r="L51" s="1377"/>
       <c r="M51" s="1098"/>
       <c r="N51" s="680" t="e">
         <f>+N46*9.8066</f>
@@ -23611,9 +23596,9 @@
       <c r="G60" s="480"/>
       <c r="H60" s="480"/>
       <c r="I60" s="994"/>
-      <c r="J60" s="1348"/>
-      <c r="K60" s="1348"/>
-      <c r="L60" s="1348"/>
+      <c r="J60" s="1329"/>
+      <c r="K60" s="1329"/>
+      <c r="L60" s="1329"/>
       <c r="M60" s="1098"/>
       <c r="Q60" s="997"/>
       <c r="R60" s="997"/>
@@ -23649,9 +23634,9 @@
       <c r="G61" s="480"/>
       <c r="H61" s="480"/>
       <c r="I61" s="994"/>
-      <c r="J61" s="1387"/>
-      <c r="K61" s="1387"/>
-      <c r="L61" s="1387"/>
+      <c r="J61" s="1328"/>
+      <c r="K61" s="1328"/>
+      <c r="L61" s="1328"/>
       <c r="M61" s="1098"/>
       <c r="Q61" s="998"/>
       <c r="R61" s="998"/>
@@ -23687,9 +23672,9 @@
       <c r="G62" s="480"/>
       <c r="H62" s="480"/>
       <c r="I62" s="994"/>
-      <c r="J62" s="1348"/>
-      <c r="K62" s="1348"/>
-      <c r="L62" s="1348"/>
+      <c r="J62" s="1329"/>
+      <c r="K62" s="1329"/>
+      <c r="L62" s="1329"/>
       <c r="M62" s="1098"/>
       <c r="P62" s="997"/>
       <c r="Q62" s="997"/>
@@ -23831,11 +23816,11 @@
       <c r="C66" s="1111"/>
       <c r="D66" s="478"/>
       <c r="E66" s="478"/>
-      <c r="F66" s="1388">
+      <c r="F66" s="1330">
         <f>+formato!C36</f>
         <v>0</v>
       </c>
-      <c r="G66" s="1388"/>
+      <c r="G66" s="1330"/>
       <c r="H66" s="478"/>
       <c r="I66" s="378"/>
       <c r="J66" s="478"/>
@@ -23869,11 +23854,11 @@
       <c r="C67" s="1111"/>
       <c r="D67" s="478"/>
       <c r="E67" s="478"/>
-      <c r="F67" s="1389">
+      <c r="F67" s="1331">
         <f>+formato!C37</f>
         <v>0</v>
       </c>
-      <c r="G67" s="1389"/>
+      <c r="G67" s="1331"/>
       <c r="H67" s="478"/>
       <c r="I67" s="378"/>
       <c r="J67" s="1112"/>
@@ -23907,11 +23892,11 @@
       <c r="C68" s="1111"/>
       <c r="D68" s="478"/>
       <c r="E68" s="478"/>
-      <c r="F68" s="1388">
+      <c r="F68" s="1330">
         <f>+formato!C38</f>
         <v>0</v>
       </c>
-      <c r="G68" s="1388"/>
+      <c r="G68" s="1330"/>
       <c r="H68" s="478"/>
       <c r="I68" s="1113"/>
       <c r="J68" s="1112"/>
@@ -24128,11 +24113,11 @@
       <c r="G74" s="1011" t="s">
         <v>67</v>
       </c>
-      <c r="H74" s="1390">
+      <c r="H74" s="1332">
         <f>DATOS!F37</f>
         <v>0</v>
       </c>
-      <c r="I74" s="1391"/>
+      <c r="I74" s="1333"/>
       <c r="J74" s="1112"/>
       <c r="K74" s="478"/>
       <c r="L74" s="478"/>
@@ -24173,11 +24158,11 @@
       <c r="G75" s="1011" t="s">
         <v>67</v>
       </c>
-      <c r="H75" s="1392">
+      <c r="H75" s="1334">
         <f>DATOS!F38</f>
         <v>0</v>
       </c>
-      <c r="I75" s="1393"/>
+      <c r="I75" s="1335"/>
       <c r="J75" s="1112"/>
       <c r="K75" s="478"/>
       <c r="L75" s="478"/>
@@ -24242,18 +24227,18 @@
       <c r="AN76" s="719"/>
     </row>
     <row r="77" spans="1:40" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="1356"/>
-      <c r="B77" s="1356"/>
-      <c r="C77" s="1356"/>
-      <c r="D77" s="1356"/>
-      <c r="E77" s="1356"/>
-      <c r="F77" s="1356"/>
-      <c r="G77" s="1356"/>
-      <c r="H77" s="1356"/>
-      <c r="I77" s="1356"/>
-      <c r="J77" s="1356"/>
-      <c r="K77" s="1356"/>
-      <c r="L77" s="1356"/>
+      <c r="A77" s="1378"/>
+      <c r="B77" s="1378"/>
+      <c r="C77" s="1378"/>
+      <c r="D77" s="1378"/>
+      <c r="E77" s="1378"/>
+      <c r="F77" s="1378"/>
+      <c r="G77" s="1378"/>
+      <c r="H77" s="1378"/>
+      <c r="I77" s="1378"/>
+      <c r="J77" s="1378"/>
+      <c r="K77" s="1378"/>
+      <c r="L77" s="1378"/>
       <c r="V77" s="715"/>
       <c r="W77" s="475"/>
       <c r="X77" s="475"/>
@@ -24386,20 +24371,20 @@
       <c r="AN80" s="719"/>
     </row>
     <row r="81" spans="1:40" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="1355" t="s">
+      <c r="A81" s="1327" t="s">
         <v>73</v>
       </c>
-      <c r="B81" s="1355"/>
-      <c r="C81" s="1355"/>
-      <c r="D81" s="1355"/>
-      <c r="E81" s="1355"/>
-      <c r="F81" s="1355"/>
-      <c r="G81" s="1355"/>
-      <c r="H81" s="1355"/>
-      <c r="I81" s="1355"/>
-      <c r="J81" s="1355"/>
-      <c r="K81" s="1355"/>
-      <c r="L81" s="1355"/>
+      <c r="B81" s="1327"/>
+      <c r="C81" s="1327"/>
+      <c r="D81" s="1327"/>
+      <c r="E81" s="1327"/>
+      <c r="F81" s="1327"/>
+      <c r="G81" s="1327"/>
+      <c r="H81" s="1327"/>
+      <c r="I81" s="1327"/>
+      <c r="J81" s="1327"/>
+      <c r="K81" s="1327"/>
+      <c r="L81" s="1327"/>
       <c r="M81" s="1014"/>
       <c r="N81" s="1014"/>
       <c r="V81" s="715"/>
@@ -24460,20 +24445,20 @@
       <c r="AN82" s="719"/>
     </row>
     <row r="83" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="1355" t="s">
+      <c r="A83" s="1327" t="s">
         <v>537</v>
       </c>
-      <c r="B83" s="1355"/>
-      <c r="C83" s="1355"/>
-      <c r="D83" s="1355"/>
-      <c r="E83" s="1355"/>
-      <c r="F83" s="1355"/>
-      <c r="G83" s="1355"/>
-      <c r="H83" s="1355"/>
-      <c r="I83" s="1355"/>
-      <c r="J83" s="1355"/>
-      <c r="K83" s="1355"/>
-      <c r="L83" s="1355"/>
+      <c r="B83" s="1327"/>
+      <c r="C83" s="1327"/>
+      <c r="D83" s="1327"/>
+      <c r="E83" s="1327"/>
+      <c r="F83" s="1327"/>
+      <c r="G83" s="1327"/>
+      <c r="H83" s="1327"/>
+      <c r="I83" s="1327"/>
+      <c r="J83" s="1327"/>
+      <c r="K83" s="1327"/>
+      <c r="L83" s="1327"/>
       <c r="M83" s="1116"/>
       <c r="N83" s="1116"/>
       <c r="V83" s="715"/>
@@ -24569,18 +24554,18 @@
       <c r="AN85" s="719"/>
     </row>
     <row r="86" spans="1:40" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="1338"/>
-      <c r="B86" s="1338"/>
-      <c r="C86" s="1338"/>
-      <c r="D86" s="1338"/>
-      <c r="E86" s="1338"/>
-      <c r="F86" s="1338"/>
-      <c r="G86" s="1338"/>
-      <c r="H86" s="1338"/>
-      <c r="I86" s="1338"/>
-      <c r="J86" s="1338"/>
-      <c r="K86" s="1338"/>
-      <c r="L86" s="1338"/>
+      <c r="A86" s="1362"/>
+      <c r="B86" s="1362"/>
+      <c r="C86" s="1362"/>
+      <c r="D86" s="1362"/>
+      <c r="E86" s="1362"/>
+      <c r="F86" s="1362"/>
+      <c r="G86" s="1362"/>
+      <c r="H86" s="1362"/>
+      <c r="I86" s="1362"/>
+      <c r="J86" s="1362"/>
+      <c r="K86" s="1362"/>
+      <c r="L86" s="1362"/>
       <c r="M86" s="1116"/>
       <c r="N86" s="1116"/>
       <c r="V86" s="715"/>
@@ -25874,34 +25859,6 @@
     <protectedRange sqref="E9:E10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="44">
-    <mergeCell ref="A81:L81"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J48:L49"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:I12"/>
     <mergeCell ref="A86:L86"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="N44:O44"/>
@@ -25918,6 +25875,34 @@
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="J40:L40"/>
     <mergeCell ref="J38:L38"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J48:L49"/>
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.70866141732283472" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -25960,40 +25945,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="1412" t="s">
+      <c r="B2" s="1389" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1413"/>
-      <c r="D2" s="1413"/>
-      <c r="E2" s="1413"/>
-      <c r="F2" s="1413"/>
-      <c r="G2" s="1413"/>
-      <c r="H2" s="1413"/>
-      <c r="I2" s="1413"/>
-      <c r="J2" s="1413"/>
-      <c r="K2" s="1413"/>
-      <c r="L2" s="1413"/>
-      <c r="M2" s="1413"/>
-      <c r="N2" s="1413"/>
-      <c r="O2" s="1414"/>
+      <c r="C2" s="1390"/>
+      <c r="D2" s="1390"/>
+      <c r="E2" s="1390"/>
+      <c r="F2" s="1390"/>
+      <c r="G2" s="1390"/>
+      <c r="H2" s="1390"/>
+      <c r="I2" s="1390"/>
+      <c r="J2" s="1390"/>
+      <c r="K2" s="1390"/>
+      <c r="L2" s="1390"/>
+      <c r="M2" s="1390"/>
+      <c r="N2" s="1390"/>
+      <c r="O2" s="1391"/>
     </row>
     <row r="3" spans="2:19" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="1415" t="s">
+      <c r="B3" s="1392" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1416"/>
-      <c r="D3" s="1416"/>
-      <c r="E3" s="1416"/>
-      <c r="F3" s="1416"/>
-      <c r="G3" s="1416"/>
-      <c r="H3" s="1416"/>
-      <c r="I3" s="1416"/>
-      <c r="J3" s="1416"/>
-      <c r="K3" s="1416"/>
-      <c r="L3" s="1416"/>
-      <c r="M3" s="1416"/>
-      <c r="N3" s="1416"/>
-      <c r="O3" s="1417"/>
+      <c r="C3" s="1393"/>
+      <c r="D3" s="1393"/>
+      <c r="E3" s="1393"/>
+      <c r="F3" s="1393"/>
+      <c r="G3" s="1393"/>
+      <c r="H3" s="1393"/>
+      <c r="I3" s="1393"/>
+      <c r="J3" s="1393"/>
+      <c r="K3" s="1393"/>
+      <c r="L3" s="1393"/>
+      <c r="M3" s="1393"/>
+      <c r="N3" s="1393"/>
+      <c r="O3" s="1394"/>
     </row>
     <row r="5" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="682" t="s">
@@ -26183,31 +26168,31 @@
       <c r="N11" s="494"/>
     </row>
     <row r="12" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="1408" t="s">
+      <c r="B12" s="1383" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="1408"/>
-      <c r="D12" s="1408"/>
-      <c r="E12" s="1408">
+      <c r="C12" s="1383"/>
+      <c r="D12" s="1383"/>
+      <c r="E12" s="1383">
         <v>1</v>
       </c>
-      <c r="F12" s="1408"/>
-      <c r="G12" s="1408">
+      <c r="F12" s="1383"/>
+      <c r="G12" s="1383">
         <v>2</v>
       </c>
-      <c r="H12" s="1408"/>
-      <c r="I12" s="1408">
+      <c r="H12" s="1383"/>
+      <c r="I12" s="1383">
         <v>3</v>
       </c>
-      <c r="J12" s="1408"/>
-      <c r="K12" s="1408">
+      <c r="J12" s="1383"/>
+      <c r="K12" s="1383">
         <v>4</v>
       </c>
-      <c r="L12" s="1408"/>
-      <c r="M12" s="1408">
+      <c r="L12" s="1383"/>
+      <c r="M12" s="1383">
         <v>5</v>
       </c>
-      <c r="N12" s="1408"/>
+      <c r="N12" s="1383"/>
       <c r="Q12" s="1131" t="s">
         <v>585</v>
       </c>
@@ -26219,9 +26204,9 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="1408"/>
-      <c r="C13" s="1408"/>
-      <c r="D13" s="1408"/>
+      <c r="B13" s="1383"/>
+      <c r="C13" s="1383"/>
+      <c r="D13" s="1383"/>
       <c r="E13" s="727" t="s">
         <v>88</v>
       </c>
@@ -26263,11 +26248,11 @@
       </c>
     </row>
     <row r="14" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="1402" t="s">
+      <c r="B14" s="1395" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1402"/>
-      <c r="D14" s="1403"/>
+      <c r="C14" s="1395"/>
+      <c r="D14" s="1396"/>
       <c r="E14" s="1248">
         <v>1</v>
       </c>
@@ -26293,11 +26278,11 @@
       </c>
     </row>
     <row r="15" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="1397" t="s">
+      <c r="B15" s="1384" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="1397"/>
-      <c r="D15" s="1398"/>
+      <c r="C15" s="1384"/>
+      <c r="D15" s="1385"/>
       <c r="E15" s="1132">
         <v>5</v>
       </c>
@@ -26342,11 +26327,11 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="1397" t="s">
+      <c r="B16" s="1384" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="1397"/>
-      <c r="D16" s="1398"/>
+      <c r="C16" s="1384"/>
+      <c r="D16" s="1385"/>
       <c r="E16" s="1132">
         <f>+formato!D17</f>
         <v>0</v>
@@ -26392,11 +26377,11 @@
       </c>
     </row>
     <row r="17" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="1397" t="s">
+      <c r="B17" s="1384" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="1397"/>
-      <c r="D17" s="1398"/>
+      <c r="C17" s="1384"/>
+      <c r="D17" s="1385"/>
       <c r="E17" s="1132">
         <f>+formato!D18</f>
         <v>0</v>
@@ -26442,11 +26427,11 @@
       </c>
     </row>
     <row r="18" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="1397" t="s">
+      <c r="B18" s="1384" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="1397"/>
-      <c r="D18" s="1398"/>
+      <c r="C18" s="1384"/>
+      <c r="D18" s="1385"/>
       <c r="E18" s="1132">
         <f>+formato!D19</f>
         <v>0</v>
@@ -26483,11 +26468,11 @@
       <c r="N18" s="1138"/>
     </row>
     <row r="19" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="1398" t="s">
+      <c r="B19" s="1385" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1399"/>
-      <c r="D19" s="1399"/>
+      <c r="C19" s="1406"/>
+      <c r="D19" s="1406"/>
       <c r="E19" s="1135">
         <f t="shared" ref="E19:K19" si="0">+E17-E18</f>
         <v>0</v>
@@ -26524,11 +26509,11 @@
       <c r="N19" s="1138"/>
     </row>
     <row r="20" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="1397" t="s">
+      <c r="B20" s="1384" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="1397"/>
-      <c r="D20" s="1398"/>
+      <c r="C20" s="1384"/>
+      <c r="D20" s="1385"/>
       <c r="E20" s="1132">
         <f>+formato!D21</f>
         <v>0</v>
@@ -26578,11 +26563,11 @@
       <c r="U20" s="945"/>
     </row>
     <row r="21" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="1400" t="s">
+      <c r="B21" s="1407" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="1400"/>
-      <c r="D21" s="1401"/>
+      <c r="C21" s="1407"/>
+      <c r="D21" s="1408"/>
       <c r="E21" s="1135" t="e">
         <f t="shared" ref="E21:K21" si="1">+E19/E20</f>
         <v>#DIV/0!</v>
@@ -26663,11 +26648,11 @@
       <c r="U22" s="947"/>
     </row>
     <row r="23" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="1402" t="s">
+      <c r="B23" s="1395" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="1402"/>
-      <c r="D23" s="1403"/>
+      <c r="C23" s="1395"/>
+      <c r="D23" s="1396"/>
       <c r="E23" s="1132">
         <f>+formato!D24</f>
         <v>0</v>
@@ -26706,11 +26691,11 @@
       <c r="U23" s="950"/>
     </row>
     <row r="24" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="1397" t="s">
+      <c r="B24" s="1384" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="1397"/>
-      <c r="D24" s="1398"/>
+      <c r="C24" s="1384"/>
+      <c r="D24" s="1385"/>
       <c r="E24" s="1132">
         <f>+formato!D25</f>
         <v>0</v>
@@ -26766,11 +26751,11 @@
       </c>
     </row>
     <row r="25" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="1397" t="s">
+      <c r="B25" s="1384" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="1397"/>
-      <c r="D25" s="1398"/>
+      <c r="C25" s="1384"/>
+      <c r="D25" s="1385"/>
       <c r="E25" s="1132">
         <f>+formato!D26</f>
         <v>0</v>
@@ -26822,11 +26807,11 @@
       </c>
     </row>
     <row r="26" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="1397" t="s">
+      <c r="B26" s="1384" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="1397"/>
-      <c r="D26" s="1398"/>
+      <c r="C26" s="1384"/>
+      <c r="D26" s="1385"/>
       <c r="E26" s="1132">
         <f>+formato!D27</f>
         <v>0</v>
@@ -26882,11 +26867,11 @@
       </c>
     </row>
     <row r="27" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="1397" t="s">
+      <c r="B27" s="1384" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="1397"/>
-      <c r="D27" s="1398"/>
+      <c r="C27" s="1384"/>
+      <c r="D27" s="1385"/>
       <c r="E27" s="1132">
         <f>+formato!D28</f>
         <v>0</v>
@@ -26930,11 +26915,11 @@
       </c>
     </row>
     <row r="28" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="1397" t="s">
+      <c r="B28" s="1384" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="1397"/>
-      <c r="D28" s="1398"/>
+      <c r="C28" s="1384"/>
+      <c r="D28" s="1385"/>
       <c r="E28" s="1148">
         <f t="shared" ref="E28:L28" si="6">+E24-E27</f>
         <v>0</v>
@@ -26971,11 +26956,11 @@
       <c r="N28" s="1138"/>
     </row>
     <row r="29" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="1397" t="s">
+      <c r="B29" s="1384" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="1397"/>
-      <c r="D29" s="1398"/>
+      <c r="C29" s="1384"/>
+      <c r="D29" s="1385"/>
       <c r="E29" s="1132">
         <f>+formato!D30</f>
         <v>0</v>
@@ -27012,11 +26997,11 @@
       <c r="N29" s="1138"/>
     </row>
     <row r="30" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="1398" t="s">
+      <c r="B30" s="1385" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="1399"/>
-      <c r="D30" s="1399"/>
+      <c r="C30" s="1406"/>
+      <c r="D30" s="1406"/>
       <c r="E30" s="1135"/>
       <c r="F30" s="1135" t="e">
         <f t="shared" ref="F30:L30" si="7">+F27-F29</f>
@@ -27041,11 +27026,11 @@
       <c r="N30" s="1138"/>
     </row>
     <row r="31" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="1398" t="s">
+      <c r="B31" s="1385" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="1399"/>
-      <c r="D31" s="1399"/>
+      <c r="C31" s="1406"/>
+      <c r="D31" s="1406"/>
       <c r="E31" s="1135"/>
       <c r="F31" s="1135" t="e">
         <f t="shared" ref="F31:L31" si="8">+F28/F30*100</f>
@@ -27073,11 +27058,11 @@
       </c>
     </row>
     <row r="32" spans="2:21" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="1401" t="s">
+      <c r="B32" s="1408" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="1404"/>
-      <c r="D32" s="1404"/>
+      <c r="C32" s="1409"/>
+      <c r="D32" s="1409"/>
       <c r="E32" s="1135"/>
       <c r="F32" s="1135" t="e">
         <f t="shared" ref="F32:L32" si="9">+F21/(1+F31/100)</f>
@@ -27203,11 +27188,11 @@
       </c>
       <c r="D37" s="703"/>
       <c r="E37" s="704"/>
-      <c r="F37" s="1405">
+      <c r="F37" s="1400">
         <v>0</v>
       </c>
-      <c r="G37" s="1405"/>
-      <c r="H37" s="1405"/>
+      <c r="G37" s="1400"/>
+      <c r="H37" s="1400"/>
     </row>
     <row r="38" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C38" s="678" t="s">
@@ -27215,11 +27200,11 @@
       </c>
       <c r="D38" s="703"/>
       <c r="E38" s="704"/>
-      <c r="F38" s="1406">
+      <c r="F38" s="1401">
         <v>0</v>
       </c>
-      <c r="G38" s="1406"/>
-      <c r="H38" s="1406"/>
+      <c r="G38" s="1401"/>
+      <c r="H38" s="1401"/>
     </row>
     <row r="39" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="40" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -27244,17 +27229,17 @@
       </c>
       <c r="D41" s="1026"/>
       <c r="E41" s="1027"/>
-      <c r="F41" s="1407">
+      <c r="F41" s="1402">
         <v>0</v>
       </c>
-      <c r="G41" s="1407"/>
-      <c r="H41" s="1407"/>
-      <c r="K41" s="1420" t="s">
+      <c r="G41" s="1402"/>
+      <c r="H41" s="1402"/>
+      <c r="K41" s="1399" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="1420"/>
+      <c r="L41" s="1399"/>
       <c r="M41" s="478"/>
-      <c r="N41" s="1418" t="s">
+      <c r="N41" s="1397" t="s">
         <v>106</v>
       </c>
     </row>
@@ -27267,7 +27252,7 @@
         <v>52</v>
       </c>
       <c r="M42" s="478"/>
-      <c r="N42" s="1419"/>
+      <c r="N42" s="1398"/>
     </row>
     <row r="43" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="1024"/>
@@ -27440,21 +27425,21 @@
     </row>
     <row r="49" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="708"/>
-      <c r="C49" s="1409" t="s">
+      <c r="C49" s="1386" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="1410"/>
-      <c r="E49" s="1411"/>
+      <c r="D49" s="1387"/>
+      <c r="E49" s="1388"/>
       <c r="N49" s="709"/>
     </row>
     <row r="50" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="708"/>
-      <c r="C50" s="1394" t="e">
+      <c r="C50" s="1403" t="e">
         <f>IF(G54="","",IF(AND(G54&lt;=25),"A",IF(AND(G54&gt;25,G53&lt;=25),"B",IF(AND(G53&gt;25,G52&lt;30),"C"))))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D50" s="1395"/>
-      <c r="E50" s="1396"/>
+      <c r="D50" s="1404"/>
+      <c r="E50" s="1405"/>
       <c r="F50" s="475"/>
       <c r="N50" s="709"/>
       <c r="O50" s="710"/>
@@ -29119,6 +29104,23 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="e49E/OysaywdZI0JcuM+C0cQuCvqe9PMqZ/ilP9GIY/P45QRK0Ai6JyKU7eB4WtZltnkC9BaQI8vpXNlfCIiIw==" saltValue="LOl5Rt57JcvlkUy4kBpOXg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="33">
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="I12:J12"/>
@@ -29135,23 +29137,6 @@
     <mergeCell ref="N41:N42"/>
     <mergeCell ref="K41:L41"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
   </mergeCells>
   <conditionalFormatting sqref="F34:F35">
     <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="No Cumple">
@@ -29225,16 +29210,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1429"/>
-      <c r="B1" s="1429"/>
-      <c r="C1" s="1429"/>
-      <c r="D1" s="1430" t="s">
+      <c r="A1" s="1417"/>
+      <c r="B1" s="1417"/>
+      <c r="C1" s="1417"/>
+      <c r="D1" s="1418" t="s">
         <v>132</v>
       </c>
-      <c r="E1" s="1430"/>
-      <c r="F1" s="1430"/>
-      <c r="G1" s="1430"/>
-      <c r="H1" s="1430"/>
+      <c r="E1" s="1418"/>
+      <c r="F1" s="1418"/>
+      <c r="G1" s="1418"/>
+      <c r="H1" s="1418"/>
       <c r="I1" s="484" t="s">
         <v>133</v>
       </c>
@@ -29243,14 +29228,14 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1429"/>
-      <c r="B2" s="1429"/>
-      <c r="C2" s="1429"/>
-      <c r="D2" s="1430"/>
-      <c r="E2" s="1430"/>
-      <c r="F2" s="1430"/>
-      <c r="G2" s="1430"/>
-      <c r="H2" s="1430"/>
+      <c r="A2" s="1417"/>
+      <c r="B2" s="1417"/>
+      <c r="C2" s="1417"/>
+      <c r="D2" s="1418"/>
+      <c r="E2" s="1418"/>
+      <c r="F2" s="1418"/>
+      <c r="G2" s="1418"/>
+      <c r="H2" s="1418"/>
       <c r="I2" s="484" t="s">
         <v>135</v>
       </c>
@@ -29259,14 +29244,14 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1429"/>
-      <c r="B3" s="1429"/>
-      <c r="C3" s="1429"/>
-      <c r="D3" s="1430"/>
-      <c r="E3" s="1430"/>
-      <c r="F3" s="1430"/>
-      <c r="G3" s="1430"/>
-      <c r="H3" s="1430"/>
+      <c r="A3" s="1417"/>
+      <c r="B3" s="1417"/>
+      <c r="C3" s="1417"/>
+      <c r="D3" s="1418"/>
+      <c r="E3" s="1418"/>
+      <c r="F3" s="1418"/>
+      <c r="G3" s="1418"/>
+      <c r="H3" s="1418"/>
       <c r="I3" s="484" t="s">
         <v>136</v>
       </c>
@@ -29275,14 +29260,14 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1429"/>
-      <c r="B4" s="1429"/>
-      <c r="C4" s="1429"/>
-      <c r="D4" s="1430"/>
-      <c r="E4" s="1430"/>
-      <c r="F4" s="1430"/>
-      <c r="G4" s="1430"/>
-      <c r="H4" s="1430"/>
+      <c r="A4" s="1417"/>
+      <c r="B4" s="1417"/>
+      <c r="C4" s="1417"/>
+      <c r="D4" s="1418"/>
+      <c r="E4" s="1418"/>
+      <c r="F4" s="1418"/>
+      <c r="G4" s="1418"/>
+      <c r="H4" s="1418"/>
       <c r="I4" s="484" t="s">
         <v>137</v>
       </c>
@@ -29294,17 +29279,17 @@
       <c r="A6" s="741" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="1440" t="s">
+      <c r="B6" s="1413" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="1441"/>
-      <c r="D6" s="1441"/>
-      <c r="E6" s="1441"/>
-      <c r="F6" s="1441"/>
-      <c r="G6" s="1441"/>
-      <c r="H6" s="1441"/>
-      <c r="I6" s="1441"/>
-      <c r="J6" s="1442"/>
+      <c r="C6" s="1414"/>
+      <c r="D6" s="1414"/>
+      <c r="E6" s="1414"/>
+      <c r="F6" s="1414"/>
+      <c r="G6" s="1414"/>
+      <c r="H6" s="1414"/>
+      <c r="I6" s="1414"/>
+      <c r="J6" s="1415"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="741" t="s">
@@ -29579,9 +29564,9 @@
       <c r="F30" s="470"/>
       <c r="G30" s="471"/>
       <c r="H30" s="470"/>
-      <c r="L30" s="1431"/>
-      <c r="R30" s="1443"/>
-      <c r="S30" s="1443"/>
+      <c r="L30" s="1419"/>
+      <c r="R30" s="1416"/>
+      <c r="S30" s="1416"/>
       <c r="T30" s="674"/>
       <c r="U30" s="675"/>
     </row>
@@ -29594,9 +29579,9 @@
       <c r="F31" s="470"/>
       <c r="G31" s="471"/>
       <c r="H31" s="471"/>
-      <c r="L31" s="1431"/>
-      <c r="R31" s="1443"/>
-      <c r="S31" s="1443"/>
+      <c r="L31" s="1419"/>
+      <c r="R31" s="1416"/>
+      <c r="S31" s="1416"/>
       <c r="T31" s="674"/>
       <c r="U31" s="675"/>
     </row>
@@ -29609,9 +29594,9 @@
       <c r="F32" s="471"/>
       <c r="G32" s="471"/>
       <c r="H32" s="471"/>
-      <c r="L32" s="1431"/>
-      <c r="R32" s="1443"/>
-      <c r="S32" s="1443"/>
+      <c r="L32" s="1419"/>
+      <c r="R32" s="1416"/>
+      <c r="S32" s="1416"/>
       <c r="T32" s="674"/>
       <c r="U32" s="675"/>
     </row>
@@ -29624,10 +29609,10 @@
       <c r="F33" s="471"/>
       <c r="G33" s="471"/>
       <c r="H33" s="471"/>
-      <c r="L33" s="1431"/>
+      <c r="L33" s="1419"/>
       <c r="O33" s="673"/>
-      <c r="R33" s="1443"/>
-      <c r="S33" s="1443"/>
+      <c r="R33" s="1416"/>
+      <c r="S33" s="1416"/>
       <c r="T33" s="488"/>
       <c r="U33" s="675"/>
     </row>
@@ -29642,42 +29627,42 @@
       <c r="H34" s="471"/>
       <c r="I34" s="467"/>
       <c r="J34" s="467"/>
-      <c r="L34" s="1432"/>
-      <c r="M34" s="1432"/>
-      <c r="N34" s="1432"/>
-      <c r="O34" s="1432"/>
-      <c r="P34" s="1432"/>
-      <c r="Q34" s="1432"/>
-      <c r="R34" s="1432"/>
-      <c r="S34" s="1432"/>
-      <c r="T34" s="1432"/>
-      <c r="U34" s="1432"/>
+      <c r="L34" s="1420"/>
+      <c r="M34" s="1420"/>
+      <c r="N34" s="1420"/>
+      <c r="O34" s="1420"/>
+      <c r="P34" s="1420"/>
+      <c r="Q34" s="1420"/>
+      <c r="R34" s="1420"/>
+      <c r="S34" s="1420"/>
+      <c r="T34" s="1420"/>
+      <c r="U34" s="1420"/>
     </row>
     <row r="35" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35"/>
       <c r="F35" s="470"/>
       <c r="I35" s="467"/>
       <c r="J35" s="467"/>
-      <c r="L35" s="1433"/>
-      <c r="M35" s="1433"/>
+      <c r="L35" s="1421"/>
+      <c r="M35" s="1421"/>
       <c r="N35" s="676"/>
-      <c r="P35" s="1434"/>
+      <c r="P35" s="1422"/>
       <c r="Q35" s="676"/>
-      <c r="S35" s="1435"/>
-      <c r="T35" s="1436"/>
-      <c r="U35" s="1436"/>
+      <c r="S35" s="1423"/>
+      <c r="T35" s="1424"/>
+      <c r="U35" s="1424"/>
     </row>
     <row r="36" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I36" s="467"/>
       <c r="J36" s="467"/>
-      <c r="L36" s="1433"/>
-      <c r="M36" s="1433"/>
+      <c r="L36" s="1421"/>
+      <c r="M36" s="1421"/>
       <c r="N36" s="677"/>
-      <c r="P36" s="1435"/>
+      <c r="P36" s="1423"/>
       <c r="Q36" s="677"/>
-      <c r="S36" s="1435"/>
-      <c r="T36" s="1436"/>
-      <c r="U36" s="1436"/>
+      <c r="S36" s="1423"/>
+      <c r="T36" s="1424"/>
+      <c r="U36" s="1424"/>
     </row>
     <row r="37" spans="1:26" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="534" t="s">
@@ -32195,12 +32180,12 @@
       <c r="M74" s="471"/>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A75" s="1439" t="s">
+      <c r="A75" s="1412" t="s">
         <v>192</v>
       </c>
-      <c r="B75" s="1439"/>
-      <c r="C75" s="1439"/>
-      <c r="D75" s="1439"/>
+      <c r="B75" s="1412"/>
+      <c r="C75" s="1412"/>
+      <c r="D75" s="1412"/>
       <c r="E75" s="467"/>
       <c r="F75" s="467"/>
       <c r="G75" s="467"/>
@@ -32210,10 +32195,10 @@
       <c r="M75" s="471"/>
     </row>
     <row r="76" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="1438" t="s">
+      <c r="A76" s="1411" t="s">
         <v>193</v>
       </c>
-      <c r="B76" s="1438"/>
+      <c r="B76" s="1411"/>
       <c r="C76" s="641" t="s">
         <v>194</v>
       </c>
@@ -32400,16 +32385,16 @@
       <c r="R87" s="486" t="s">
         <v>202</v>
       </c>
-      <c r="T87" s="1437" t="s">
+      <c r="T87" s="1410" t="s">
         <v>531</v>
       </c>
-      <c r="U87" s="1437"/>
-      <c r="V87" s="1437"/>
-      <c r="W87" s="1437" t="s">
+      <c r="U87" s="1410"/>
+      <c r="V87" s="1410"/>
+      <c r="W87" s="1410" t="s">
         <v>532</v>
       </c>
-      <c r="X87" s="1437"/>
-      <c r="Y87" s="1437"/>
+      <c r="X87" s="1410"/>
+      <c r="Y87" s="1410"/>
     </row>
     <row r="88" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="596" t="s">
@@ -32933,19 +32918,19 @@
       <c r="A100" s="1262" t="s">
         <v>654</v>
       </c>
-      <c r="B100" s="1421" t="s">
+      <c r="B100" s="1425" t="s">
         <v>655</v>
       </c>
-      <c r="C100" s="1422"/>
+      <c r="C100" s="1426"/>
       <c r="D100" s="1263"/>
-      <c r="E100" s="1423" t="s">
+      <c r="E100" s="1427" t="s">
         <v>656</v>
       </c>
-      <c r="F100" s="1423"/>
-      <c r="G100" s="1424" t="s">
+      <c r="F100" s="1427"/>
+      <c r="G100" s="1428" t="s">
         <v>657</v>
       </c>
-      <c r="H100" s="1425"/>
+      <c r="H100" s="1429"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="937"/>
@@ -32961,19 +32946,19 @@
       <c r="A102" s="1264" t="s">
         <v>658</v>
       </c>
-      <c r="B102" s="1426">
+      <c r="B102" s="1430">
         <v>44944</v>
       </c>
-      <c r="C102" s="1427"/>
+      <c r="C102" s="1431"/>
       <c r="D102" s="937"/>
-      <c r="E102" s="1428" t="s">
+      <c r="E102" s="1432" t="s">
         <v>659</v>
       </c>
-      <c r="F102" s="1428"/>
-      <c r="G102" s="1426">
+      <c r="F102" s="1432"/>
+      <c r="G102" s="1430">
         <v>44944</v>
       </c>
-      <c r="H102" s="1427"/>
+      <c r="H102" s="1431"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="937"/>
@@ -32988,12 +32973,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wd0Sk3J/OeT0TxJIAnp4S2dGatByENh6gH5lE7pLCIYYn5xv110dK84OeIJzfd1un3raa/Q0kk7gUzEP+5w5+g==" saltValue="Nxfv9eN1cqS8LPjiSFaCXw==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="T87:V87"/>
-    <mergeCell ref="W87:Y87"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="R30:S33"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G102:H102"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:H4"/>
     <mergeCell ref="L30:L33"/>
@@ -33002,12 +32987,12 @@
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="S35:S36"/>
     <mergeCell ref="T35:U36"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="T87:V87"/>
+    <mergeCell ref="W87:Y87"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="R30:S33"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -33045,7 +33030,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A2:AC65"/>
+  <dimension ref="B2:AC65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="470"/>
@@ -33060,23 +33045,23 @@
     <col min="14" max="16384" width="11.42578125" style="470"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B2" s="1279" t="s">
+    <row r="2" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B2" s="1268" t="s">
         <v>210</v>
       </c>
-      <c r="C2" s="1279"/>
-      <c r="D2" s="1279"/>
-      <c r="E2" s="1279"/>
-      <c r="F2" s="1279"/>
-      <c r="G2" s="1279"/>
-      <c r="L2" s="1279" t="s">
+      <c r="C2" s="1268"/>
+      <c r="D2" s="1268"/>
+      <c r="E2" s="1268"/>
+      <c r="F2" s="1268"/>
+      <c r="G2" s="1268"/>
+      <c r="L2" s="1268" t="s">
         <v>210</v>
       </c>
-      <c r="M2" s="1279"/>
-      <c r="N2" s="1279"/>
-      <c r="O2" s="1279"/>
-      <c r="P2" s="1279"/>
-      <c r="Q2" s="1279"/>
+      <c r="M2" s="1268"/>
+      <c r="N2" s="1268"/>
+      <c r="O2" s="1268"/>
+      <c r="P2" s="1268"/>
+      <c r="Q2" s="1268"/>
       <c r="T2" s="471"/>
       <c r="U2" s="471"/>
       <c r="V2" s="1047" t="s">
@@ -33088,15 +33073,7 @@
       <c r="Z2" s="471"/>
       <c r="AA2" s="471"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="1273"/>
-      <c r="B3" s="1273"/>
-      <c r="C3" s="1273"/>
-      <c r="D3" s="1273"/>
-      <c r="E3" s="1273"/>
-      <c r="F3" s="1273"/>
-      <c r="G3" s="1273"/>
-      <c r="H3" s="1273"/>
+    <row r="3" spans="2:27" x14ac:dyDescent="0.2">
       <c r="T3" s="471"/>
       <c r="U3" s="471"/>
       <c r="V3" s="471"/>
@@ -33106,15 +33083,7 @@
       <c r="Z3" s="471"/>
       <c r="AA3" s="471"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="1273"/>
-      <c r="B4" s="1273"/>
-      <c r="C4" s="1273"/>
-      <c r="D4" s="1273"/>
-      <c r="E4" s="1273"/>
-      <c r="F4" s="1273"/>
-      <c r="G4" s="1273"/>
-      <c r="H4" s="1273"/>
+    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
       <c r="T4" s="471"/>
       <c r="U4" s="471"/>
       <c r="V4" s="471"/>
@@ -33124,15 +33093,7 @@
       <c r="Z4" s="471"/>
       <c r="AA4" s="471"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="1273"/>
-      <c r="B5" s="1273"/>
-      <c r="C5" s="1273"/>
-      <c r="D5" s="1273"/>
-      <c r="E5" s="1273"/>
-      <c r="F5" s="1273"/>
-      <c r="G5" s="1273"/>
-      <c r="H5" s="1273"/>
+    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
       <c r="T5" s="471"/>
       <c r="U5" s="471"/>
       <c r="V5" s="471"/>
@@ -33142,19 +33103,11 @@
       <c r="Z5" s="471"/>
       <c r="AA5" s="471"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="1273"/>
-      <c r="B6" s="1273"/>
-      <c r="C6" s="1273"/>
-      <c r="D6" s="1273"/>
-      <c r="E6" s="1273"/>
-      <c r="F6" s="1273"/>
-      <c r="G6" s="1273"/>
-      <c r="H6" s="1273"/>
-      <c r="I6" s="1280" t="s">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="I6" s="1269" t="s">
         <v>211</v>
       </c>
-      <c r="J6" s="1281"/>
+      <c r="J6" s="1270"/>
       <c r="T6" s="471"/>
       <c r="U6" s="471"/>
       <c r="V6" s="471"/>
@@ -33164,15 +33117,15 @@
       <c r="Z6" s="471"/>
       <c r="AA6" s="471"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B7" s="508" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="1266">
+      <c r="C7" s="1586">
         <v>-1.4899999999999999E-6</v>
       </c>
-      <c r="D7" s="1267"/>
-      <c r="E7" s="1267"/>
+      <c r="D7" s="471"/>
+      <c r="E7" s="471"/>
       <c r="F7" s="471"/>
       <c r="G7" s="471"/>
       <c r="H7" s="471"/>
@@ -33205,17 +33158,17 @@
       <c r="Z7" s="471"/>
       <c r="AA7" s="471"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B8" s="509" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="1268">
+      <c r="C8" s="1587">
         <v>1.1399999999999999</v>
       </c>
-      <c r="D8" s="1269">
+      <c r="D8" s="1588">
         <v>2.4800000000000002E-10</v>
       </c>
-      <c r="E8" s="1267"/>
+      <c r="E8" s="471"/>
       <c r="F8" s="471"/>
       <c r="G8" s="471"/>
       <c r="H8" s="471"/>
@@ -33246,15 +33199,15 @@
       <c r="Z8" s="471"/>
       <c r="AA8" s="471"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B9" s="509" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="1270" t="s">
+      <c r="C9" s="1589" t="s">
         <v>666</v>
       </c>
-      <c r="D9" s="1271"/>
-      <c r="E9" s="1267"/>
+      <c r="D9" s="472"/>
+      <c r="E9" s="471"/>
       <c r="F9" s="646" t="s">
         <v>186</v>
       </c>
@@ -33283,7 +33236,7 @@
       <c r="Z9" s="471"/>
       <c r="AA9" s="471"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B10" s="509" t="s">
         <v>214</v>
       </c>
@@ -33321,7 +33274,7 @@
       <c r="Z10" s="471"/>
       <c r="AA10" s="471"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B11" s="509" t="s">
         <v>215</v>
       </c>
@@ -33355,12 +33308,12 @@
       <c r="Z11" s="471"/>
       <c r="AA11" s="471"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B12" s="509" t="s">
         <v>575</v>
       </c>
       <c r="C12" s="508"/>
-      <c r="D12" s="1272">
+      <c r="D12" s="1251">
         <v>46160</v>
       </c>
       <c r="E12" s="471"/>
@@ -33387,7 +33340,7 @@
       <c r="Z12" s="471"/>
       <c r="AA12" s="471"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B13" s="693" t="s">
         <v>216</v>
       </c>
@@ -33455,7 +33408,7 @@
       <c r="Z13" s="471"/>
       <c r="AA13" s="471"/>
     </row>
-    <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="951"/>
       <c r="C14" s="952"/>
       <c r="D14" s="936"/>
@@ -33481,7 +33434,7 @@
       <c r="Z14" s="471"/>
       <c r="AA14" s="471"/>
     </row>
-    <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="951"/>
       <c r="C15" s="952"/>
       <c r="D15" s="936"/>
@@ -33507,7 +33460,7 @@
       <c r="Z15" s="471"/>
       <c r="AA15" s="471"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B16" s="471"/>
       <c r="C16" s="471"/>
       <c r="D16" s="471"/>
@@ -34183,17 +34136,16 @@
         <v>225</v>
       </c>
       <c r="C34" s="651"/>
-      <c r="D34" s="1276">
+      <c r="D34" s="1590">
         <v>4529.7</v>
       </c>
       <c r="E34" s="500">
         <f>IF(D34&lt;$D$20,$D$21,IF(AND(D34&gt;=$D$20,D34&lt;$E$20),$E$21,IF(AND(D34&gt;=$E$20,D34&lt;$F$20),$F$21,IF(AND(D34&gt;=$F$20,D34&lt;$G$20),$G$21,IF(AND(D34&gt;=$G$20,D34&lt;$H$20),$H$21,IF(AND(D34&gt;=$H$20,D34&lt;$I$20),$I$21,IF(AND(D34&gt;=$I$20,D34&lt;$J$20),$J$21)))))))</f>
         <v>0</v>
       </c>
-      <c r="G34" s="1278" t="s">
+      <c r="G34" s="413" t="s">
         <v>667</v>
       </c>
-      <c r="H34" s="1273"/>
       <c r="I34" s="535"/>
       <c r="J34" s="535"/>
     </row>
@@ -34202,7 +34154,7 @@
         <v>226</v>
       </c>
       <c r="C35" s="650"/>
-      <c r="D35" s="1274"/>
+      <c r="D35" s="1266"/>
       <c r="E35" s="650"/>
       <c r="F35" s="413"/>
     </row>
@@ -34211,7 +34163,7 @@
         <v>227</v>
       </c>
       <c r="C36" s="652"/>
-      <c r="D36" s="1277">
+      <c r="D36" s="1591">
         <v>2130</v>
       </c>
       <c r="E36" s="500">
@@ -34219,17 +34171,16 @@
         <v>0</v>
       </c>
       <c r="F36" s="413"/>
-      <c r="G36" s="1278" t="s">
+      <c r="G36" s="413" t="s">
         <v>667</v>
       </c>
-      <c r="H36" s="1273"/>
     </row>
     <row r="37" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="649" t="s">
         <v>228</v>
       </c>
       <c r="C37" s="650"/>
-      <c r="D37" s="1275"/>
+      <c r="D37" s="1267"/>
       <c r="E37" s="650"/>
       <c r="F37" s="413"/>
     </row>
@@ -34238,7 +34189,7 @@
         <v>227</v>
       </c>
       <c r="C38" s="652"/>
-      <c r="D38" s="1277">
+      <c r="D38" s="1591">
         <v>937.1</v>
       </c>
       <c r="E38" s="500">
@@ -34246,10 +34197,9 @@
         <v>0</v>
       </c>
       <c r="F38" s="413"/>
-      <c r="G38" s="1278" t="s">
+      <c r="G38" s="413" t="s">
         <v>668</v>
       </c>
-      <c r="H38" s="1273"/>
     </row>
     <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B39" s="413"/>
@@ -34257,8 +34207,6 @@
       <c r="D39" s="413"/>
       <c r="E39" s="413"/>
       <c r="F39" s="413"/>
-      <c r="G39" s="1273"/>
-      <c r="H39" s="1273"/>
     </row>
     <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B41" s="507"/>
@@ -34477,6 +34425,7 @@
       <c r="V65" s="539"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Dr0EYdFyveBIrnPlE0G6EO9gYgdS5j2eGRm5Xt42jm/4NjZixJhhSIMn9NAS5aordaN3RsKCWWvp8LFR1WOa3Q==" saltValue="Ia8IbgGb82CAd3qADU1Wyg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="L2:Q2"/>
@@ -34541,39 +34490,39 @@
       <c r="A7" s="1128" t="s">
         <v>580</v>
       </c>
-      <c r="B7" s="1444">
+      <c r="B7" s="1433">
         <v>2.0947951371589977E-2</v>
       </c>
-      <c r="C7" s="1444"/>
-      <c r="D7" s="1444"/>
+      <c r="C7" s="1433"/>
+      <c r="D7" s="1433"/>
       <c r="E7" s="482"/>
       <c r="G7" s="1128" t="s">
         <v>580</v>
       </c>
-      <c r="H7" s="1444">
+      <c r="H7" s="1433">
         <v>0.11030261405182915</v>
       </c>
-      <c r="I7" s="1444"/>
-      <c r="J7" s="1444"/>
+      <c r="I7" s="1433"/>
+      <c r="J7" s="1433"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1128" t="s">
         <v>581</v>
       </c>
-      <c r="B8" s="1444">
+      <c r="B8" s="1433">
         <v>2.1813476975842898E-2</v>
       </c>
-      <c r="C8" s="1444"/>
-      <c r="D8" s="1444"/>
+      <c r="C8" s="1433"/>
+      <c r="D8" s="1433"/>
       <c r="E8" s="482"/>
       <c r="G8" s="1128" t="s">
         <v>581</v>
       </c>
-      <c r="H8" s="1444">
+      <c r="H8" s="1433">
         <v>0.11377365443927613</v>
       </c>
-      <c r="I8" s="1444"/>
-      <c r="J8" s="1444"/>
+      <c r="I8" s="1433"/>
+      <c r="J8" s="1433"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="FYJq3GhyQBF7Pmjc4398tmgpF0gfeMaFowah8hdIzkRnEppsVQu7MC046WcPkrhdaONzABmyez2teHVIMA3rRQ==" saltValue="QmbXxEwr+jVZyr/mMxd6pw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -34671,18 +34620,18 @@
       <c r="V6" s="365"/>
     </row>
     <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1363" t="s">
+      <c r="A7" s="1350" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1363"/>
-      <c r="C7" s="1363"/>
-      <c r="D7" s="1363"/>
-      <c r="E7" s="1363"/>
-      <c r="F7" s="1363"/>
-      <c r="G7" s="1363"/>
-      <c r="H7" s="1363"/>
-      <c r="I7" s="1363"/>
-      <c r="J7" s="1363"/>
+      <c r="B7" s="1350"/>
+      <c r="C7" s="1350"/>
+      <c r="D7" s="1350"/>
+      <c r="E7" s="1350"/>
+      <c r="F7" s="1350"/>
+      <c r="G7" s="1350"/>
+      <c r="H7" s="1350"/>
+      <c r="I7" s="1350"/>
+      <c r="J7" s="1350"/>
       <c r="L7" s="326"/>
       <c r="M7" s="364"/>
       <c r="N7" s="365"/>
@@ -34696,18 +34645,18 @@
       <c r="V7" s="365"/>
     </row>
     <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1448">
+      <c r="A8" s="1441">
         <v>1</v>
       </c>
-      <c r="B8" s="1448"/>
-      <c r="C8" s="1448"/>
-      <c r="D8" s="1448"/>
-      <c r="E8" s="1448"/>
-      <c r="F8" s="1448"/>
-      <c r="G8" s="1448"/>
-      <c r="H8" s="1448"/>
-      <c r="I8" s="1448"/>
-      <c r="J8" s="1448"/>
+      <c r="B8" s="1441"/>
+      <c r="C8" s="1441"/>
+      <c r="D8" s="1441"/>
+      <c r="E8" s="1441"/>
+      <c r="F8" s="1441"/>
+      <c r="G8" s="1441"/>
+      <c r="H8" s="1441"/>
+      <c r="I8" s="1441"/>
+      <c r="J8" s="1441"/>
       <c r="L8" s="334"/>
       <c r="M8" s="366"/>
       <c r="N8" s="367"/>
@@ -34986,18 +34935,18 @@
       <c r="AL14" s="315"/>
     </row>
     <row r="15" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1449" t="s">
+      <c r="A15" s="1442" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="1450"/>
-      <c r="C15" s="1450"/>
-      <c r="D15" s="1450"/>
-      <c r="E15" s="1450"/>
-      <c r="F15" s="1450"/>
-      <c r="G15" s="1450"/>
-      <c r="H15" s="1450"/>
-      <c r="I15" s="1450"/>
-      <c r="J15" s="1451"/>
+      <c r="B15" s="1443"/>
+      <c r="C15" s="1443"/>
+      <c r="D15" s="1443"/>
+      <c r="E15" s="1443"/>
+      <c r="F15" s="1443"/>
+      <c r="G15" s="1443"/>
+      <c r="H15" s="1443"/>
+      <c r="I15" s="1443"/>
+      <c r="J15" s="1444"/>
       <c r="K15" s="341"/>
       <c r="M15" s="365"/>
       <c r="N15" s="365"/>
@@ -35026,18 +34975,18 @@
       <c r="AL15" s="315"/>
     </row>
     <row r="16" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1452" t="s">
+      <c r="A16" s="1445" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="1453"/>
-      <c r="C16" s="1453"/>
-      <c r="D16" s="1453"/>
-      <c r="E16" s="1453"/>
-      <c r="F16" s="1453"/>
-      <c r="G16" s="1453"/>
-      <c r="H16" s="1453"/>
-      <c r="I16" s="1453"/>
-      <c r="J16" s="1454"/>
+      <c r="B16" s="1446"/>
+      <c r="C16" s="1446"/>
+      <c r="D16" s="1446"/>
+      <c r="E16" s="1446"/>
+      <c r="F16" s="1446"/>
+      <c r="G16" s="1446"/>
+      <c r="H16" s="1446"/>
+      <c r="I16" s="1446"/>
+      <c r="J16" s="1447"/>
       <c r="K16" s="341"/>
       <c r="L16" s="341"/>
       <c r="M16" s="365"/>
@@ -35106,18 +35055,18 @@
       <c r="AL17" s="315"/>
     </row>
     <row r="18" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1371" t="s">
+      <c r="A18" s="1358" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1372"/>
-      <c r="C18" s="1372"/>
-      <c r="D18" s="1372"/>
-      <c r="E18" s="1372"/>
-      <c r="F18" s="1372"/>
-      <c r="G18" s="1372"/>
-      <c r="H18" s="1372"/>
-      <c r="I18" s="1372"/>
-      <c r="J18" s="1373"/>
+      <c r="B18" s="1359"/>
+      <c r="C18" s="1359"/>
+      <c r="D18" s="1359"/>
+      <c r="E18" s="1359"/>
+      <c r="F18" s="1359"/>
+      <c r="G18" s="1359"/>
+      <c r="H18" s="1359"/>
+      <c r="I18" s="1359"/>
+      <c r="J18" s="1360"/>
       <c r="L18" s="341"/>
       <c r="M18" s="365"/>
       <c r="N18" s="365"/>
@@ -35163,10 +35112,10 @@
       </c>
       <c r="L19" s="341"/>
       <c r="M19" s="361"/>
-      <c r="N19" s="1446" t="s">
+      <c r="N19" s="1439" t="s">
         <v>234</v>
       </c>
-      <c r="O19" s="1446" t="s">
+      <c r="O19" s="1439" t="s">
         <v>235</v>
       </c>
       <c r="P19" s="361"/>
@@ -35218,8 +35167,8 @@
       </c>
       <c r="L20" s="341"/>
       <c r="M20" s="361"/>
-      <c r="N20" s="1447"/>
-      <c r="O20" s="1447"/>
+      <c r="N20" s="1440"/>
+      <c r="O20" s="1440"/>
       <c r="P20" s="371"/>
       <c r="Q20" s="372"/>
       <c r="R20" s="361"/>
@@ -35348,18 +35297,18 @@
       <c r="AL22" s="315"/>
     </row>
     <row r="23" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1455" t="s">
+      <c r="A23" s="1448" t="s">
         <v>239</v>
       </c>
-      <c r="B23" s="1455"/>
-      <c r="C23" s="1455"/>
-      <c r="D23" s="1455"/>
-      <c r="E23" s="1455"/>
-      <c r="F23" s="1455"/>
-      <c r="G23" s="1455"/>
-      <c r="H23" s="1455"/>
-      <c r="I23" s="1455"/>
-      <c r="J23" s="1455"/>
+      <c r="B23" s="1448"/>
+      <c r="C23" s="1448"/>
+      <c r="D23" s="1448"/>
+      <c r="E23" s="1448"/>
+      <c r="F23" s="1448"/>
+      <c r="G23" s="1448"/>
+      <c r="H23" s="1448"/>
+      <c r="I23" s="1448"/>
+      <c r="J23" s="1448"/>
       <c r="K23" s="341"/>
       <c r="L23" s="344"/>
       <c r="M23" s="361"/>
@@ -35802,18 +35751,18 @@
       <c r="AL32" s="315"/>
     </row>
     <row r="33" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1455" t="s">
+      <c r="A33" s="1448" t="s">
         <v>257</v>
       </c>
-      <c r="B33" s="1455"/>
-      <c r="C33" s="1455"/>
-      <c r="D33" s="1455"/>
-      <c r="E33" s="1455"/>
-      <c r="F33" s="1455"/>
-      <c r="G33" s="1455"/>
-      <c r="H33" s="1455"/>
-      <c r="I33" s="1455"/>
-      <c r="J33" s="1455"/>
+      <c r="B33" s="1448"/>
+      <c r="C33" s="1448"/>
+      <c r="D33" s="1448"/>
+      <c r="E33" s="1448"/>
+      <c r="F33" s="1448"/>
+      <c r="G33" s="1448"/>
+      <c r="H33" s="1448"/>
+      <c r="I33" s="1448"/>
+      <c r="J33" s="1448"/>
       <c r="K33" s="437"/>
       <c r="L33" s="437"/>
       <c r="T33" s="314"/>
@@ -35838,15 +35787,15 @@
     </row>
     <row r="34" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="746"/>
-      <c r="B34" s="1445" t="s">
+      <c r="B34" s="1438" t="s">
         <v>258</v>
       </c>
-      <c r="C34" s="1445"/>
-      <c r="D34" s="1445"/>
-      <c r="E34" s="1445"/>
-      <c r="F34" s="1445"/>
-      <c r="G34" s="1445"/>
-      <c r="H34" s="1445"/>
+      <c r="C34" s="1438"/>
+      <c r="D34" s="1438"/>
+      <c r="E34" s="1438"/>
+      <c r="F34" s="1438"/>
+      <c r="G34" s="1438"/>
+      <c r="H34" s="1438"/>
       <c r="I34" s="754"/>
       <c r="J34" s="755"/>
       <c r="K34" s="341"/>
@@ -35916,18 +35865,18 @@
       <c r="AL35" s="315"/>
     </row>
     <row r="36" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1455" t="s">
+      <c r="A36" s="1448" t="s">
         <v>261</v>
       </c>
-      <c r="B36" s="1455"/>
-      <c r="C36" s="1455"/>
-      <c r="D36" s="1455"/>
-      <c r="E36" s="1455"/>
-      <c r="F36" s="1455"/>
-      <c r="G36" s="1455"/>
-      <c r="H36" s="1455"/>
-      <c r="I36" s="1455"/>
-      <c r="J36" s="1455"/>
+      <c r="B36" s="1448"/>
+      <c r="C36" s="1448"/>
+      <c r="D36" s="1448"/>
+      <c r="E36" s="1448"/>
+      <c r="F36" s="1448"/>
+      <c r="G36" s="1448"/>
+      <c r="H36" s="1448"/>
+      <c r="I36" s="1448"/>
+      <c r="J36" s="1448"/>
       <c r="K36" s="341"/>
       <c r="L36" s="341"/>
       <c r="T36" s="314"/>
@@ -35952,15 +35901,15 @@
     </row>
     <row r="37" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="746"/>
-      <c r="B37" s="1445" t="s">
+      <c r="B37" s="1438" t="s">
         <v>262</v>
       </c>
-      <c r="C37" s="1445"/>
-      <c r="D37" s="1445"/>
-      <c r="E37" s="1445"/>
-      <c r="F37" s="1445"/>
-      <c r="G37" s="1445"/>
-      <c r="H37" s="1445"/>
+      <c r="C37" s="1438"/>
+      <c r="D37" s="1438"/>
+      <c r="E37" s="1438"/>
+      <c r="F37" s="1438"/>
+      <c r="G37" s="1438"/>
+      <c r="H37" s="1438"/>
       <c r="I37" s="754"/>
       <c r="J37" s="755"/>
       <c r="K37" s="341"/>
@@ -36063,18 +36012,18 @@
       <c r="AL39" s="315"/>
     </row>
     <row r="40" spans="1:38" ht="29.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1459" t="s">
+      <c r="A40" s="1434" t="s">
         <v>265</v>
       </c>
-      <c r="B40" s="1459"/>
-      <c r="C40" s="1459"/>
-      <c r="D40" s="1459"/>
-      <c r="E40" s="1459"/>
-      <c r="F40" s="1459"/>
-      <c r="G40" s="1459"/>
-      <c r="H40" s="1459"/>
-      <c r="I40" s="1459"/>
-      <c r="J40" s="1459"/>
+      <c r="B40" s="1434"/>
+      <c r="C40" s="1434"/>
+      <c r="D40" s="1434"/>
+      <c r="E40" s="1434"/>
+      <c r="F40" s="1434"/>
+      <c r="G40" s="1434"/>
+      <c r="H40" s="1434"/>
+      <c r="I40" s="1434"/>
+      <c r="J40" s="1434"/>
       <c r="K40" s="341"/>
       <c r="L40" s="341"/>
       <c r="T40" s="314"/>
@@ -36098,16 +36047,16 @@
       <c r="AL40" s="315"/>
     </row>
     <row r="41" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1459"/>
-      <c r="B41" s="1459"/>
-      <c r="C41" s="1459"/>
-      <c r="D41" s="1459"/>
-      <c r="E41" s="1459"/>
-      <c r="F41" s="1459"/>
-      <c r="G41" s="1459"/>
-      <c r="H41" s="1459"/>
-      <c r="I41" s="1459"/>
-      <c r="J41" s="1459"/>
+      <c r="A41" s="1434"/>
+      <c r="B41" s="1434"/>
+      <c r="C41" s="1434"/>
+      <c r="D41" s="1434"/>
+      <c r="E41" s="1434"/>
+      <c r="F41" s="1434"/>
+      <c r="G41" s="1434"/>
+      <c r="H41" s="1434"/>
+      <c r="I41" s="1434"/>
+      <c r="J41" s="1434"/>
       <c r="K41" s="341"/>
       <c r="L41" s="341"/>
       <c r="T41" s="314"/>
@@ -36131,16 +36080,16 @@
       <c r="AL41" s="315"/>
     </row>
     <row r="42" spans="1:38" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1459"/>
-      <c r="B42" s="1459"/>
-      <c r="C42" s="1459"/>
-      <c r="D42" s="1459"/>
-      <c r="E42" s="1459"/>
-      <c r="F42" s="1459"/>
-      <c r="G42" s="1459"/>
-      <c r="H42" s="1459"/>
-      <c r="I42" s="1459"/>
-      <c r="J42" s="1459"/>
+      <c r="A42" s="1434"/>
+      <c r="B42" s="1434"/>
+      <c r="C42" s="1434"/>
+      <c r="D42" s="1434"/>
+      <c r="E42" s="1434"/>
+      <c r="F42" s="1434"/>
+      <c r="G42" s="1434"/>
+      <c r="H42" s="1434"/>
+      <c r="I42" s="1434"/>
+      <c r="J42" s="1434"/>
       <c r="K42" s="418"/>
       <c r="L42" s="381"/>
       <c r="N42" s="378"/>
@@ -36220,9 +36169,9 @@
       <c r="K44" s="341"/>
       <c r="L44" s="383"/>
       <c r="M44" s="383"/>
-      <c r="N44" s="1348"/>
-      <c r="O44" s="1348"/>
-      <c r="P44" s="1348"/>
+      <c r="N44" s="1329"/>
+      <c r="O44" s="1329"/>
+      <c r="P44" s="1329"/>
       <c r="T44" s="314"/>
       <c r="U44" s="325"/>
       <c r="V44" s="325"/>
@@ -36251,15 +36200,15 @@
       <c r="E45" s="197"/>
       <c r="F45" s="197"/>
       <c r="G45" s="200"/>
-      <c r="H45" s="1387"/>
-      <c r="I45" s="1387"/>
-      <c r="J45" s="1387"/>
+      <c r="H45" s="1328"/>
+      <c r="I45" s="1328"/>
+      <c r="J45" s="1328"/>
       <c r="K45" s="341"/>
       <c r="L45" s="384"/>
       <c r="M45" s="385"/>
-      <c r="N45" s="1456"/>
-      <c r="O45" s="1456"/>
-      <c r="P45" s="1456"/>
+      <c r="N45" s="1436"/>
+      <c r="O45" s="1436"/>
+      <c r="P45" s="1436"/>
       <c r="T45" s="314"/>
       <c r="U45" s="325"/>
       <c r="V45" s="325"/>
@@ -36288,15 +36237,15 @@
       <c r="E46" s="197"/>
       <c r="F46" s="197"/>
       <c r="G46" s="200"/>
-      <c r="H46" s="1348"/>
-      <c r="I46" s="1348"/>
-      <c r="J46" s="1348"/>
+      <c r="H46" s="1329"/>
+      <c r="I46" s="1329"/>
+      <c r="J46" s="1329"/>
       <c r="K46" s="341"/>
       <c r="L46" s="386"/>
       <c r="M46" s="387"/>
-      <c r="N46" s="1348"/>
-      <c r="O46" s="1348"/>
-      <c r="P46" s="1348"/>
+      <c r="N46" s="1329"/>
+      <c r="O46" s="1329"/>
+      <c r="P46" s="1329"/>
       <c r="T46" s="314"/>
       <c r="U46" s="325"/>
       <c r="V46" s="325"/>
@@ -36325,15 +36274,15 @@
       <c r="E47" s="197"/>
       <c r="F47" s="197"/>
       <c r="G47" s="200"/>
-      <c r="H47" s="1456"/>
-      <c r="I47" s="1456"/>
-      <c r="J47" s="1456"/>
+      <c r="H47" s="1436"/>
+      <c r="I47" s="1436"/>
+      <c r="J47" s="1436"/>
       <c r="K47" s="341"/>
       <c r="L47" s="386"/>
       <c r="M47" s="387"/>
-      <c r="N47" s="1387"/>
-      <c r="O47" s="1387"/>
-      <c r="P47" s="1387"/>
+      <c r="N47" s="1328"/>
+      <c r="O47" s="1328"/>
+      <c r="P47" s="1328"/>
       <c r="T47" s="314"/>
       <c r="U47" s="325"/>
       <c r="V47" s="325"/>
@@ -36362,15 +36311,15 @@
       <c r="E48" s="197"/>
       <c r="F48" s="197"/>
       <c r="G48" s="200"/>
-      <c r="H48" s="1348"/>
-      <c r="I48" s="1348"/>
-      <c r="J48" s="1348"/>
+      <c r="H48" s="1329"/>
+      <c r="I48" s="1329"/>
+      <c r="J48" s="1329"/>
       <c r="K48" s="341"/>
       <c r="L48" s="386"/>
       <c r="M48" s="387"/>
-      <c r="N48" s="1458"/>
-      <c r="O48" s="1458"/>
-      <c r="P48" s="1458"/>
+      <c r="N48" s="1437"/>
+      <c r="O48" s="1437"/>
+      <c r="P48" s="1437"/>
       <c r="T48" s="314"/>
       <c r="U48" s="325"/>
       <c r="V48" s="325"/>
@@ -36399,15 +36348,15 @@
       <c r="E49" s="200"/>
       <c r="F49" s="200"/>
       <c r="G49" s="200"/>
-      <c r="H49" s="1387"/>
-      <c r="I49" s="1387"/>
-      <c r="J49" s="1387"/>
+      <c r="H49" s="1328"/>
+      <c r="I49" s="1328"/>
+      <c r="J49" s="1328"/>
       <c r="K49" s="341"/>
       <c r="L49" s="386"/>
       <c r="M49" s="387"/>
-      <c r="N49" s="1456"/>
-      <c r="O49" s="1456"/>
-      <c r="P49" s="1456"/>
+      <c r="N49" s="1436"/>
+      <c r="O49" s="1436"/>
+      <c r="P49" s="1436"/>
       <c r="T49" s="314"/>
       <c r="U49" s="325"/>
       <c r="V49" s="325"/>
@@ -37177,16 +37126,16 @@
       <c r="AL74" s="315"/>
     </row>
     <row r="75" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="1459"/>
-      <c r="B75" s="1459"/>
-      <c r="C75" s="1459"/>
-      <c r="D75" s="1459"/>
-      <c r="E75" s="1459"/>
-      <c r="F75" s="1459"/>
-      <c r="G75" s="1459"/>
-      <c r="H75" s="1459"/>
-      <c r="I75" s="1459"/>
-      <c r="J75" s="1459"/>
+      <c r="A75" s="1434"/>
+      <c r="B75" s="1434"/>
+      <c r="C75" s="1434"/>
+      <c r="D75" s="1434"/>
+      <c r="E75" s="1434"/>
+      <c r="F75" s="1434"/>
+      <c r="G75" s="1434"/>
+      <c r="H75" s="1434"/>
+      <c r="I75" s="1434"/>
+      <c r="J75" s="1434"/>
       <c r="T75" s="314"/>
       <c r="U75" s="325"/>
       <c r="V75" s="325"/>
@@ -37208,16 +37157,16 @@
       <c r="AL75" s="315"/>
     </row>
     <row r="76" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="1459"/>
-      <c r="B76" s="1459"/>
-      <c r="C76" s="1459"/>
-      <c r="D76" s="1459"/>
-      <c r="E76" s="1459"/>
-      <c r="F76" s="1459"/>
-      <c r="G76" s="1459"/>
-      <c r="H76" s="1459"/>
-      <c r="I76" s="1459"/>
-      <c r="J76" s="1459"/>
+      <c r="A76" s="1434"/>
+      <c r="B76" s="1434"/>
+      <c r="C76" s="1434"/>
+      <c r="D76" s="1434"/>
+      <c r="E76" s="1434"/>
+      <c r="F76" s="1434"/>
+      <c r="G76" s="1434"/>
+      <c r="H76" s="1434"/>
+      <c r="I76" s="1434"/>
+      <c r="J76" s="1434"/>
       <c r="T76" s="314"/>
       <c r="U76" s="325"/>
       <c r="V76" s="325"/>
@@ -37239,16 +37188,16 @@
       <c r="AL76" s="315"/>
     </row>
     <row r="77" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="1459"/>
-      <c r="B77" s="1459"/>
-      <c r="C77" s="1459"/>
-      <c r="D77" s="1459"/>
-      <c r="E77" s="1459"/>
-      <c r="F77" s="1459"/>
-      <c r="G77" s="1459"/>
-      <c r="H77" s="1459"/>
-      <c r="I77" s="1459"/>
-      <c r="J77" s="1459"/>
+      <c r="A77" s="1434"/>
+      <c r="B77" s="1434"/>
+      <c r="C77" s="1434"/>
+      <c r="D77" s="1434"/>
+      <c r="E77" s="1434"/>
+      <c r="F77" s="1434"/>
+      <c r="G77" s="1434"/>
+      <c r="H77" s="1434"/>
+      <c r="I77" s="1434"/>
+      <c r="J77" s="1434"/>
       <c r="T77" s="314"/>
       <c r="U77" s="325"/>
       <c r="V77" s="325"/>
@@ -37363,10 +37312,10 @@
       <c r="AL80" s="315"/>
     </row>
     <row r="81" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G81" s="1457"/>
-      <c r="H81" s="1457"/>
-      <c r="I81" s="1457"/>
-      <c r="J81" s="1457"/>
+      <c r="G81" s="1435"/>
+      <c r="H81" s="1435"/>
+      <c r="I81" s="1435"/>
+      <c r="J81" s="1435"/>
       <c r="T81" s="314"/>
       <c r="U81" s="325"/>
       <c r="V81" s="325"/>
@@ -37411,10 +37360,10 @@
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A83" s="313"/>
-      <c r="G83" s="1457"/>
-      <c r="H83" s="1457"/>
-      <c r="I83" s="1457"/>
-      <c r="J83" s="1457"/>
+      <c r="G83" s="1435"/>
+      <c r="H83" s="1435"/>
+      <c r="I83" s="1435"/>
+      <c r="J83" s="1435"/>
       <c r="T83" s="314"/>
       <c r="U83" s="325"/>
       <c r="V83" s="325"/>
@@ -39896,23 +39845,6 @@
     <protectedRange sqref="C10:C13" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="29">
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J42"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A76:J77"/>
-    <mergeCell ref="G81:J81"/>
-    <mergeCell ref="H47:J47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="G83:J83"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="N46:P46"/>
     <mergeCell ref="B37:H37"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
@@ -39925,6 +39857,23 @@
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="B34:H34"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A41:J42"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A76:J77"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="H47:J47"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.78740157480314965" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -40137,19 +40086,19 @@
       <c r="Z6" s="37"/>
     </row>
     <row r="7" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1467" t="s">
+      <c r="A7" s="1478" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1467"/>
-      <c r="C7" s="1467"/>
-      <c r="D7" s="1467"/>
-      <c r="E7" s="1467"/>
-      <c r="F7" s="1467"/>
-      <c r="G7" s="1467"/>
-      <c r="H7" s="1467"/>
-      <c r="I7" s="1467"/>
-      <c r="J7" s="1467"/>
-      <c r="K7" s="1467"/>
+      <c r="B7" s="1478"/>
+      <c r="C7" s="1478"/>
+      <c r="D7" s="1478"/>
+      <c r="E7" s="1478"/>
+      <c r="F7" s="1478"/>
+      <c r="G7" s="1478"/>
+      <c r="H7" s="1478"/>
+      <c r="I7" s="1478"/>
+      <c r="J7" s="1478"/>
+      <c r="K7" s="1478"/>
       <c r="N7" s="309" t="s">
         <v>276</v>
       </c>
@@ -40174,20 +40123,20 @@
       <c r="Z7" s="37"/>
     </row>
     <row r="8" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1468">
+      <c r="A8" s="1479">
         <f>+K12</f>
         <v>1</v>
       </c>
-      <c r="B8" s="1468"/>
-      <c r="C8" s="1468"/>
-      <c r="D8" s="1468"/>
-      <c r="E8" s="1468"/>
-      <c r="F8" s="1468"/>
-      <c r="G8" s="1468"/>
-      <c r="H8" s="1468"/>
-      <c r="I8" s="1468"/>
-      <c r="J8" s="1468"/>
-      <c r="K8" s="1468"/>
+      <c r="B8" s="1479"/>
+      <c r="C8" s="1479"/>
+      <c r="D8" s="1479"/>
+      <c r="E8" s="1479"/>
+      <c r="F8" s="1479"/>
+      <c r="G8" s="1479"/>
+      <c r="H8" s="1479"/>
+      <c r="I8" s="1479"/>
+      <c r="J8" s="1479"/>
+      <c r="K8" s="1479"/>
       <c r="N8" s="766" t="s">
         <v>278</v>
       </c>
@@ -40242,14 +40191,14 @@
       <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1491" t="s">
+      <c r="C10" s="1472" t="s">
         <v>281</v>
       </c>
-      <c r="D10" s="1491"/>
-      <c r="E10" s="1491"/>
-      <c r="F10" s="1491"/>
-      <c r="G10" s="1491"/>
-      <c r="H10" s="1491"/>
+      <c r="D10" s="1472"/>
+      <c r="E10" s="1472"/>
+      <c r="F10" s="1472"/>
+      <c r="G10" s="1472"/>
+      <c r="H10" s="1472"/>
       <c r="I10" s="23" t="s">
         <v>3</v>
       </c>
@@ -40292,14 +40241,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1491" t="s">
+      <c r="C11" s="1472" t="s">
         <v>286</v>
       </c>
-      <c r="D11" s="1491"/>
-      <c r="E11" s="1491"/>
-      <c r="F11" s="1491"/>
-      <c r="G11" s="1491"/>
-      <c r="H11" s="1491"/>
+      <c r="D11" s="1472"/>
+      <c r="E11" s="1472"/>
+      <c r="F11" s="1472"/>
+      <c r="G11" s="1472"/>
+      <c r="H11" s="1472"/>
       <c r="I11" s="26" t="s">
         <v>6</v>
       </c>
@@ -40341,14 +40290,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1491" t="s">
+      <c r="C12" s="1472" t="s">
         <v>291</v>
       </c>
-      <c r="D12" s="1491"/>
-      <c r="E12" s="1491"/>
-      <c r="F12" s="1491"/>
-      <c r="G12" s="1491"/>
-      <c r="H12" s="1491"/>
+      <c r="D12" s="1472"/>
+      <c r="E12" s="1472"/>
+      <c r="F12" s="1472"/>
+      <c r="G12" s="1472"/>
+      <c r="H12" s="1472"/>
       <c r="I12" s="26" t="s">
         <v>292</v>
       </c>
@@ -40428,19 +40377,19 @@
       <c r="Z13" s="37"/>
     </row>
     <row r="14" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1449" t="s">
+      <c r="A14" s="1442" t="s">
         <v>297</v>
       </c>
-      <c r="B14" s="1450"/>
-      <c r="C14" s="1450"/>
-      <c r="D14" s="1450"/>
-      <c r="E14" s="1450"/>
-      <c r="F14" s="1450"/>
-      <c r="G14" s="1450"/>
-      <c r="H14" s="1450"/>
-      <c r="I14" s="1450"/>
-      <c r="J14" s="1450"/>
-      <c r="K14" s="1451"/>
+      <c r="B14" s="1443"/>
+      <c r="C14" s="1443"/>
+      <c r="D14" s="1443"/>
+      <c r="E14" s="1443"/>
+      <c r="F14" s="1443"/>
+      <c r="G14" s="1443"/>
+      <c r="H14" s="1443"/>
+      <c r="I14" s="1443"/>
+      <c r="J14" s="1443"/>
+      <c r="K14" s="1444"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="766" t="s">
@@ -40463,19 +40412,19 @@
       <c r="Z14" s="37"/>
     </row>
     <row r="15" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1452" t="s">
+      <c r="A15" s="1445" t="s">
         <v>299</v>
       </c>
-      <c r="B15" s="1453"/>
-      <c r="C15" s="1453"/>
-      <c r="D15" s="1453"/>
-      <c r="E15" s="1453"/>
-      <c r="F15" s="1453"/>
-      <c r="G15" s="1453"/>
-      <c r="H15" s="1453"/>
-      <c r="I15" s="1453"/>
-      <c r="J15" s="1453"/>
-      <c r="K15" s="1454"/>
+      <c r="B15" s="1446"/>
+      <c r="C15" s="1446"/>
+      <c r="D15" s="1446"/>
+      <c r="E15" s="1446"/>
+      <c r="F15" s="1446"/>
+      <c r="G15" s="1446"/>
+      <c r="H15" s="1446"/>
+      <c r="I15" s="1446"/>
+      <c r="J15" s="1446"/>
+      <c r="K15" s="1447"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="25"/>
@@ -40522,30 +40471,30 @@
       <c r="S16" s="232" t="s">
         <v>303</v>
       </c>
-      <c r="T16" s="1495" t="s">
+      <c r="T16" s="1452" t="s">
         <v>304</v>
       </c>
-      <c r="U16" s="1496"/>
-      <c r="V16" s="1497"/>
+      <c r="U16" s="1453"/>
+      <c r="V16" s="1454"/>
       <c r="W16" s="37"/>
       <c r="X16" s="37"/>
       <c r="Y16" s="37"/>
       <c r="Z16" s="37"/>
     </row>
     <row r="17" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1488" t="s">
+      <c r="A17" s="1469" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1489"/>
-      <c r="C17" s="1489"/>
-      <c r="D17" s="1489"/>
-      <c r="E17" s="1489"/>
-      <c r="F17" s="1489"/>
-      <c r="G17" s="1489"/>
-      <c r="H17" s="1489"/>
-      <c r="I17" s="1489"/>
-      <c r="J17" s="1489"/>
-      <c r="K17" s="1490"/>
+      <c r="B17" s="1470"/>
+      <c r="C17" s="1470"/>
+      <c r="D17" s="1470"/>
+      <c r="E17" s="1470"/>
+      <c r="F17" s="1470"/>
+      <c r="G17" s="1470"/>
+      <c r="H17" s="1470"/>
+      <c r="I17" s="1470"/>
+      <c r="J17" s="1470"/>
+      <c r="K17" s="1471"/>
       <c r="M17" s="3"/>
       <c r="N17" s="772" t="s">
         <v>234</v>
@@ -40565,11 +40514,11 @@
       <c r="S17" s="773" t="s">
         <v>309</v>
       </c>
-      <c r="T17" s="1492" t="s">
+      <c r="T17" s="1449" t="s">
         <v>310</v>
       </c>
-      <c r="U17" s="1493"/>
-      <c r="V17" s="1494"/>
+      <c r="U17" s="1450"/>
+      <c r="V17" s="1451"/>
       <c r="W17" s="37"/>
       <c r="X17" s="37"/>
       <c r="Y17" s="37"/>
@@ -40829,21 +40778,21 @@
       <c r="Z22" s="37"/>
     </row>
     <row r="23" spans="1:26" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1471" t="s">
+      <c r="A23" s="1482" t="s">
         <v>234</v>
       </c>
-      <c r="B23" s="1472"/>
-      <c r="C23" s="1473"/>
-      <c r="D23" s="1499" t="s">
+      <c r="B23" s="1483"/>
+      <c r="C23" s="1484"/>
+      <c r="D23" s="1457" t="s">
         <v>324</v>
       </c>
       <c r="E23" s="197"/>
-      <c r="F23" s="1475" t="s">
+      <c r="F23" s="1485" t="s">
         <v>325</v>
       </c>
-      <c r="G23" s="1476"/>
-      <c r="H23" s="1477"/>
-      <c r="I23" s="1481" t="s">
+      <c r="G23" s="1486"/>
+      <c r="H23" s="1487"/>
+      <c r="I23" s="1462" t="s">
         <v>321</v>
       </c>
       <c r="J23" s="191"/>
@@ -40887,16 +40836,16 @@
       <c r="A24" s="782" t="s">
         <v>327</v>
       </c>
-      <c r="B24" s="1470" t="s">
+      <c r="B24" s="1481" t="s">
         <v>305</v>
       </c>
-      <c r="C24" s="1470"/>
-      <c r="D24" s="1500"/>
+      <c r="C24" s="1481"/>
+      <c r="D24" s="1458"/>
       <c r="E24" s="197"/>
-      <c r="F24" s="1478"/>
-      <c r="G24" s="1479"/>
-      <c r="H24" s="1480"/>
-      <c r="I24" s="1482"/>
+      <c r="F24" s="1488"/>
+      <c r="G24" s="1489"/>
+      <c r="H24" s="1490"/>
+      <c r="I24" s="1491"/>
       <c r="J24" s="191"/>
       <c r="K24" s="192"/>
       <c r="L24" s="3"/>
@@ -40934,10 +40883,10 @@
       <c r="A25" s="783" t="s">
         <v>314</v>
       </c>
-      <c r="B25" s="1469">
+      <c r="B25" s="1480">
         <v>76.2</v>
       </c>
-      <c r="C25" s="1469"/>
+      <c r="C25" s="1480"/>
       <c r="D25" s="784">
         <f>+S18</f>
         <v>100</v>
@@ -40988,21 +40937,21 @@
       <c r="A26" s="198" t="s">
         <v>321</v>
       </c>
-      <c r="B26" s="1474">
+      <c r="B26" s="1456">
         <v>50.6</v>
       </c>
-      <c r="C26" s="1474"/>
+      <c r="C26" s="1456"/>
       <c r="D26" s="199">
         <f>+S20</f>
         <v>96.737365729020368</v>
       </c>
       <c r="E26" s="197"/>
-      <c r="F26" s="1471" t="s">
+      <c r="F26" s="1482" t="s">
         <v>330</v>
       </c>
-      <c r="G26" s="1472"/>
-      <c r="H26" s="1472"/>
-      <c r="I26" s="1473"/>
+      <c r="G26" s="1483"/>
+      <c r="H26" s="1483"/>
+      <c r="I26" s="1484"/>
       <c r="J26" s="200"/>
       <c r="K26" s="201"/>
       <c r="L26" s="3"/>
@@ -41040,19 +40989,19 @@
       <c r="A27" s="202" t="s">
         <v>322</v>
       </c>
-      <c r="B27" s="1474">
+      <c r="B27" s="1456">
         <v>38.1</v>
       </c>
-      <c r="C27" s="1474"/>
+      <c r="C27" s="1456"/>
       <c r="D27" s="199">
         <f>+S21</f>
         <v>90.324022891039832</v>
       </c>
       <c r="E27" s="197"/>
-      <c r="F27" s="1483"/>
-      <c r="G27" s="1484"/>
-      <c r="H27" s="1484"/>
-      <c r="I27" s="1485"/>
+      <c r="F27" s="1492"/>
+      <c r="G27" s="1493"/>
+      <c r="H27" s="1493"/>
+      <c r="I27" s="1494"/>
       <c r="J27" s="200"/>
       <c r="K27" s="201"/>
       <c r="L27" s="3"/>
@@ -41094,19 +41043,19 @@
       <c r="A28" s="198" t="s">
         <v>323</v>
       </c>
-      <c r="B28" s="1474">
+      <c r="B28" s="1456">
         <v>25.4</v>
       </c>
-      <c r="C28" s="1474"/>
+      <c r="C28" s="1456"/>
       <c r="D28" s="199">
         <f>+S22</f>
         <v>84.873241107276272</v>
       </c>
       <c r="E28" s="197"/>
-      <c r="F28" s="1486" t="s">
+      <c r="F28" s="1465" t="s">
         <v>333</v>
       </c>
-      <c r="G28" s="1487">
+      <c r="G28" s="1467">
         <f>R27</f>
         <v>45.788805497693524</v>
       </c>
@@ -41154,17 +41103,17 @@
       <c r="A29" s="198" t="s">
         <v>326</v>
       </c>
-      <c r="B29" s="1474">
+      <c r="B29" s="1456">
         <v>19.05</v>
       </c>
-      <c r="C29" s="1474"/>
+      <c r="C29" s="1456"/>
       <c r="D29" s="199">
         <f>+S23</f>
         <v>73.456819301447041</v>
       </c>
       <c r="E29" s="197"/>
-      <c r="F29" s="1462"/>
-      <c r="G29" s="1465"/>
+      <c r="F29" s="1466"/>
+      <c r="G29" s="1468"/>
       <c r="H29" s="203" t="s">
         <v>335</v>
       </c>
@@ -41213,19 +41162,19 @@
       <c r="A30" s="198" t="s">
         <v>329</v>
       </c>
-      <c r="B30" s="1474">
+      <c r="B30" s="1456">
         <v>9.5250000000000004</v>
       </c>
-      <c r="C30" s="1474"/>
+      <c r="C30" s="1456"/>
       <c r="D30" s="199">
         <f>+S25</f>
         <v>62.661585152699679</v>
       </c>
       <c r="E30" s="197"/>
-      <c r="F30" s="1460" t="s">
+      <c r="F30" s="1473" t="s">
         <v>336</v>
       </c>
-      <c r="G30" s="1463">
+      <c r="G30" s="1475">
         <f>100-(G28+G33)</f>
         <v>40.754382185876274</v>
       </c>
@@ -41273,17 +41222,17 @@
       <c r="A31" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="B31" s="1474">
+      <c r="B31" s="1456">
         <v>4.76</v>
       </c>
-      <c r="C31" s="1474"/>
+      <c r="C31" s="1456"/>
       <c r="D31" s="199">
         <f>+S27</f>
         <v>54.211194502306476</v>
       </c>
       <c r="E31" s="197"/>
-      <c r="F31" s="1461"/>
-      <c r="G31" s="1464"/>
+      <c r="F31" s="1474"/>
+      <c r="G31" s="1476"/>
       <c r="H31" s="203" t="s">
         <v>337</v>
       </c>
@@ -41331,17 +41280,17 @@
       <c r="A32" s="198">
         <v>8</v>
       </c>
-      <c r="B32" s="1474">
+      <c r="B32" s="1456">
         <v>2.36</v>
       </c>
-      <c r="C32" s="1474"/>
+      <c r="C32" s="1456"/>
       <c r="D32" s="199">
         <f>+S28</f>
         <v>49.032616067382399</v>
       </c>
       <c r="E32" s="197"/>
-      <c r="F32" s="1462"/>
-      <c r="G32" s="1465"/>
+      <c r="F32" s="1466"/>
+      <c r="G32" s="1468"/>
       <c r="H32" s="203" t="s">
         <v>335</v>
       </c>
@@ -41393,10 +41342,10 @@
       <c r="A33" s="198">
         <v>16</v>
       </c>
-      <c r="B33" s="1474">
+      <c r="B33" s="1456">
         <v>1.19</v>
       </c>
-      <c r="C33" s="1474"/>
+      <c r="C33" s="1456"/>
       <c r="D33" s="199">
         <f t="shared" ref="D33:D38" si="4">+S30</f>
         <v>40.351707913359583</v>
@@ -41451,10 +41400,10 @@
       <c r="A34" s="198">
         <v>30</v>
       </c>
-      <c r="B34" s="1474">
+      <c r="B34" s="1456">
         <v>0.6</v>
       </c>
-      <c r="C34" s="1474"/>
+      <c r="C34" s="1456"/>
       <c r="D34" s="199">
         <f t="shared" si="4"/>
         <v>31.408593256302638</v>
@@ -41501,25 +41450,25 @@
       <c r="A35" s="198">
         <v>40</v>
       </c>
-      <c r="B35" s="1474">
+      <c r="B35" s="1456">
         <v>0.42</v>
       </c>
-      <c r="C35" s="1474"/>
+      <c r="C35" s="1456"/>
       <c r="D35" s="199">
         <f t="shared" si="4"/>
         <v>27.175831135894526</v>
       </c>
       <c r="E35" s="197"/>
-      <c r="F35" s="1501" t="str">
+      <c r="F35" s="1459" t="str">
         <f>IF(O3="No","","Clasificacion SUCS")</f>
         <v/>
       </c>
-      <c r="G35" s="1501"/>
-      <c r="H35" s="1481" t="str">
+      <c r="G35" s="1459"/>
+      <c r="H35" s="1462" t="str">
         <f>IF(O3="No","",'Sucs '!G4)</f>
         <v/>
       </c>
-      <c r="I35" s="1481"/>
+      <c r="I35" s="1462"/>
       <c r="J35" s="200"/>
       <c r="K35" s="201"/>
       <c r="L35" s="3"/>
@@ -41561,19 +41510,19 @@
       <c r="A36" s="198">
         <v>50</v>
       </c>
-      <c r="B36" s="1474">
+      <c r="B36" s="1456">
         <v>0.3</v>
       </c>
-      <c r="C36" s="1474"/>
+      <c r="C36" s="1456"/>
       <c r="D36" s="199">
         <f t="shared" si="4"/>
         <v>23.785875632381845</v>
       </c>
       <c r="E36" s="197"/>
-      <c r="F36" s="1502"/>
-      <c r="G36" s="1502"/>
-      <c r="H36" s="1504"/>
-      <c r="I36" s="1504"/>
+      <c r="F36" s="1460"/>
+      <c r="G36" s="1460"/>
+      <c r="H36" s="1463"/>
+      <c r="I36" s="1463"/>
       <c r="J36" s="200"/>
       <c r="K36" s="201"/>
       <c r="L36" s="3"/>
@@ -41612,25 +41561,25 @@
       <c r="A37" s="198">
         <v>100</v>
       </c>
-      <c r="B37" s="1474">
+      <c r="B37" s="1456">
         <v>0.14899999999999999</v>
       </c>
-      <c r="C37" s="1474"/>
+      <c r="C37" s="1456"/>
       <c r="D37" s="199">
         <f t="shared" si="4"/>
         <v>17.820677688355374</v>
       </c>
       <c r="E37" s="197"/>
-      <c r="F37" s="1502" t="str">
+      <c r="F37" s="1460" t="str">
         <f>IF(O3="No","","Clasificacion AASHTO")</f>
         <v/>
       </c>
-      <c r="G37" s="1502"/>
-      <c r="H37" s="1504" t="str">
+      <c r="G37" s="1460"/>
+      <c r="H37" s="1463" t="str">
         <f>IF(O3="No","",Aashto!J26)</f>
         <v/>
       </c>
-      <c r="I37" s="1504"/>
+      <c r="I37" s="1463"/>
       <c r="J37" s="200"/>
       <c r="K37" s="201"/>
       <c r="L37" s="3"/>
@@ -41656,19 +41605,19 @@
       <c r="A38" s="208">
         <v>200</v>
       </c>
-      <c r="B38" s="1498">
+      <c r="B38" s="1455">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="C38" s="1498"/>
+      <c r="C38" s="1455"/>
       <c r="D38" s="209">
         <f t="shared" si="4"/>
         <v>13.456812316430202</v>
       </c>
       <c r="E38" s="197"/>
-      <c r="F38" s="1503"/>
-      <c r="G38" s="1503"/>
-      <c r="H38" s="1505"/>
-      <c r="I38" s="1505"/>
+      <c r="F38" s="1461"/>
+      <c r="G38" s="1461"/>
+      <c r="H38" s="1464"/>
+      <c r="I38" s="1464"/>
       <c r="J38" s="200"/>
       <c r="K38" s="201"/>
       <c r="L38" s="3"/>
@@ -42560,19 +42509,19 @@
       <c r="Z63" s="37"/>
     </row>
     <row r="64" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1466" t="s">
+      <c r="A64" s="1477" t="s">
         <v>349</v>
       </c>
-      <c r="B64" s="1466"/>
-      <c r="C64" s="1466"/>
-      <c r="D64" s="1466"/>
-      <c r="E64" s="1466"/>
-      <c r="F64" s="1466"/>
-      <c r="G64" s="1466"/>
-      <c r="H64" s="1466"/>
-      <c r="I64" s="1466"/>
-      <c r="J64" s="1466"/>
-      <c r="K64" s="1466"/>
+      <c r="B64" s="1477"/>
+      <c r="C64" s="1477"/>
+      <c r="D64" s="1477"/>
+      <c r="E64" s="1477"/>
+      <c r="F64" s="1477"/>
+      <c r="G64" s="1477"/>
+      <c r="H64" s="1477"/>
+      <c r="I64" s="1477"/>
+      <c r="J64" s="1477"/>
+      <c r="K64" s="1477"/>
       <c r="W64" s="37"/>
       <c r="X64" s="37"/>
       <c r="Y64" s="37"/>
@@ -42608,6 +42557,29 @@
     <protectedRange sqref="C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="F26:I27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="T17:V17"/>
     <mergeCell ref="T16:V16"/>
     <mergeCell ref="B38:C38"/>
@@ -42624,29 +42596,6 @@
     <mergeCell ref="F37:G38"/>
     <mergeCell ref="H35:I36"/>
     <mergeCell ref="H37:I38"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="A64:K64"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -42774,35 +42723,35 @@
       <c r="K7" s="118"/>
     </row>
     <row r="8" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1525" t="s">
+      <c r="A8" s="1496" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1525"/>
-      <c r="C8" s="1525"/>
-      <c r="D8" s="1525"/>
-      <c r="E8" s="1525"/>
-      <c r="F8" s="1525"/>
-      <c r="G8" s="1525"/>
-      <c r="H8" s="1525"/>
-      <c r="I8" s="1525"/>
-      <c r="J8" s="1525"/>
-      <c r="K8" s="1525"/>
+      <c r="B8" s="1496"/>
+      <c r="C8" s="1496"/>
+      <c r="D8" s="1496"/>
+      <c r="E8" s="1496"/>
+      <c r="F8" s="1496"/>
+      <c r="G8" s="1496"/>
+      <c r="H8" s="1496"/>
+      <c r="I8" s="1496"/>
+      <c r="J8" s="1496"/>
+      <c r="K8" s="1496"/>
     </row>
     <row r="9" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1526">
+      <c r="A9" s="1497">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="1526"/>
-      <c r="C9" s="1526"/>
-      <c r="D9" s="1526"/>
-      <c r="E9" s="1526"/>
-      <c r="F9" s="1526"/>
-      <c r="G9" s="1526"/>
-      <c r="H9" s="1526"/>
-      <c r="I9" s="1526"/>
-      <c r="J9" s="1526"/>
-      <c r="K9" s="1526"/>
+      <c r="B9" s="1497"/>
+      <c r="C9" s="1497"/>
+      <c r="D9" s="1497"/>
+      <c r="E9" s="1497"/>
+      <c r="F9" s="1497"/>
+      <c r="G9" s="1497"/>
+      <c r="H9" s="1497"/>
+      <c r="I9" s="1497"/>
+      <c r="J9" s="1497"/>
+      <c r="K9" s="1497"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -42825,14 +42774,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1527" t="s">
+      <c r="C11" s="1498" t="s">
         <v>281</v>
       </c>
-      <c r="D11" s="1527"/>
-      <c r="E11" s="1527"/>
-      <c r="F11" s="1527"/>
-      <c r="G11" s="1527"/>
-      <c r="H11" s="1527"/>
+      <c r="D11" s="1498"/>
+      <c r="E11" s="1498"/>
+      <c r="F11" s="1498"/>
+      <c r="G11" s="1498"/>
+      <c r="H11" s="1498"/>
       <c r="I11" s="121" t="s">
         <v>3</v>
       </c>
@@ -42853,14 +42802,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1527" t="s">
+      <c r="C12" s="1498" t="s">
         <v>286</v>
       </c>
-      <c r="D12" s="1527"/>
-      <c r="E12" s="1527"/>
-      <c r="F12" s="1527"/>
-      <c r="G12" s="1527"/>
-      <c r="H12" s="1527"/>
+      <c r="D12" s="1498"/>
+      <c r="E12" s="1498"/>
+      <c r="F12" s="1498"/>
+      <c r="G12" s="1498"/>
+      <c r="H12" s="1498"/>
       <c r="I12" s="26" t="s">
         <v>6</v>
       </c>
@@ -42884,14 +42833,14 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1527" t="s">
+      <c r="C13" s="1498" t="s">
         <v>291</v>
       </c>
-      <c r="D13" s="1527"/>
-      <c r="E13" s="1527"/>
-      <c r="F13" s="1527"/>
-      <c r="G13" s="1527"/>
-      <c r="H13" s="1527"/>
+      <c r="D13" s="1498"/>
+      <c r="E13" s="1498"/>
+      <c r="F13" s="1498"/>
+      <c r="G13" s="1498"/>
+      <c r="H13" s="1498"/>
       <c r="I13" s="26" t="s">
         <v>292</v>
       </c>
@@ -42905,8 +42854,8 @@
       <c r="M13" s="124"/>
       <c r="P13" s="127"/>
       <c r="Q13" s="127"/>
-      <c r="R13" s="1524"/>
-      <c r="S13" s="1524"/>
+      <c r="R13" s="1495"/>
+      <c r="S13" s="1495"/>
     </row>
     <row r="14" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -42928,19 +42877,19 @@
       <c r="S14" s="734"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1513" t="s">
+      <c r="A15" s="1499" t="s">
         <v>351</v>
       </c>
-      <c r="B15" s="1514"/>
-      <c r="C15" s="1514"/>
-      <c r="D15" s="1514"/>
-      <c r="E15" s="1514"/>
-      <c r="F15" s="1514"/>
-      <c r="G15" s="1514"/>
-      <c r="H15" s="1514"/>
-      <c r="I15" s="1514"/>
-      <c r="J15" s="1514"/>
-      <c r="K15" s="1515"/>
+      <c r="B15" s="1500"/>
+      <c r="C15" s="1500"/>
+      <c r="D15" s="1500"/>
+      <c r="E15" s="1500"/>
+      <c r="F15" s="1500"/>
+      <c r="G15" s="1500"/>
+      <c r="H15" s="1500"/>
+      <c r="I15" s="1500"/>
+      <c r="J15" s="1500"/>
+      <c r="K15" s="1501"/>
       <c r="L15" s="124"/>
       <c r="M15" s="124"/>
       <c r="P15" s="127"/>
@@ -42949,19 +42898,19 @@
       <c r="S15" s="734"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1516" t="s">
+      <c r="A16" s="1502" t="s">
         <v>352</v>
       </c>
-      <c r="B16" s="1517"/>
-      <c r="C16" s="1517"/>
-      <c r="D16" s="1517"/>
-      <c r="E16" s="1517"/>
-      <c r="F16" s="1517"/>
-      <c r="G16" s="1517"/>
-      <c r="H16" s="1517"/>
-      <c r="I16" s="1517"/>
-      <c r="J16" s="1517"/>
-      <c r="K16" s="1518"/>
+      <c r="B16" s="1503"/>
+      <c r="C16" s="1503"/>
+      <c r="D16" s="1503"/>
+      <c r="E16" s="1503"/>
+      <c r="F16" s="1503"/>
+      <c r="G16" s="1503"/>
+      <c r="H16" s="1503"/>
+      <c r="I16" s="1503"/>
+      <c r="J16" s="1503"/>
+      <c r="K16" s="1504"/>
       <c r="L16" s="124"/>
       <c r="M16" s="124"/>
       <c r="P16" s="127"/>
@@ -42989,19 +42938,19 @@
       <c r="S17" s="734"/>
     </row>
     <row r="18" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1488" t="s">
+      <c r="A18" s="1469" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1489"/>
-      <c r="C18" s="1489"/>
-      <c r="D18" s="1489"/>
-      <c r="E18" s="1489"/>
-      <c r="F18" s="1489"/>
-      <c r="G18" s="1489"/>
-      <c r="H18" s="1489"/>
-      <c r="I18" s="1489"/>
-      <c r="J18" s="1489"/>
-      <c r="K18" s="1490"/>
+      <c r="B18" s="1470"/>
+      <c r="C18" s="1470"/>
+      <c r="D18" s="1470"/>
+      <c r="E18" s="1470"/>
+      <c r="F18" s="1470"/>
+      <c r="G18" s="1470"/>
+      <c r="H18" s="1470"/>
+      <c r="I18" s="1470"/>
+      <c r="J18" s="1470"/>
+      <c r="K18" s="1471"/>
       <c r="M18" s="124"/>
       <c r="P18" s="127"/>
       <c r="Q18" s="127"/>
@@ -43118,8 +43067,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="802"/>
-      <c r="I23" s="1519"/>
-      <c r="J23" s="1519"/>
+      <c r="I23" s="1505"/>
+      <c r="J23" s="1505"/>
       <c r="K23" s="803"/>
       <c r="L23" s="124"/>
       <c r="M23" s="139"/>
@@ -43127,41 +43076,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="141"/>
-      <c r="D24" s="1520" t="s">
+      <c r="D24" s="1506" t="s">
         <v>355</v>
       </c>
-      <c r="E24" s="1521"/>
-      <c r="F24" s="1521"/>
-      <c r="G24" s="1522" t="s">
+      <c r="E24" s="1507"/>
+      <c r="F24" s="1507"/>
+      <c r="G24" s="1508" t="s">
         <v>356</v>
       </c>
-      <c r="H24" s="1523"/>
-      <c r="I24" s="1511"/>
-      <c r="J24" s="1511"/>
+      <c r="H24" s="1509"/>
+      <c r="I24" s="1510"/>
+      <c r="J24" s="1510"/>
       <c r="K24" s="142"/>
       <c r="L24" s="124"/>
       <c r="M24" s="143"/>
-      <c r="O24" s="1506" t="s">
+      <c r="O24" s="1511" t="s">
         <v>355</v>
       </c>
-      <c r="P24" s="1507"/>
+      <c r="P24" s="1512"/>
       <c r="Q24" s="804" t="s">
         <v>354</v>
       </c>
-      <c r="R24" s="1506" t="s">
+      <c r="R24" s="1511" t="s">
         <v>356</v>
       </c>
-      <c r="S24" s="1508"/>
+      <c r="S24" s="1513"/>
       <c r="T24" s="804" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="141"/>
-      <c r="B25" s="1509" t="s">
+      <c r="B25" s="1514" t="s">
         <v>357</v>
       </c>
-      <c r="C25" s="1510"/>
+      <c r="C25" s="1515"/>
       <c r="D25" s="805" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -43182,8 +43131,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="1511"/>
-      <c r="J25" s="1511"/>
+      <c r="I25" s="1510"/>
+      <c r="J25" s="1510"/>
       <c r="K25" s="142"/>
       <c r="L25" s="124"/>
       <c r="M25" s="143"/>
@@ -43232,8 +43181,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="1512"/>
-      <c r="J26" s="1512"/>
+      <c r="I26" s="1516"/>
+      <c r="J26" s="1516"/>
       <c r="K26" s="151"/>
       <c r="L26" s="152"/>
       <c r="M26" s="143"/>
@@ -43948,19 +43897,19 @@
     </row>
     <row r="49" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1466" t="s">
+      <c r="A50" s="1477" t="s">
         <v>349</v>
       </c>
-      <c r="B50" s="1466"/>
-      <c r="C50" s="1466"/>
-      <c r="D50" s="1466"/>
-      <c r="E50" s="1466"/>
-      <c r="F50" s="1466"/>
-      <c r="G50" s="1466"/>
-      <c r="H50" s="1466"/>
-      <c r="I50" s="1466"/>
-      <c r="J50" s="1466"/>
-      <c r="K50" s="1466"/>
+      <c r="B50" s="1477"/>
+      <c r="C50" s="1477"/>
+      <c r="D50" s="1477"/>
+      <c r="E50" s="1477"/>
+      <c r="F50" s="1477"/>
+      <c r="G50" s="1477"/>
+      <c r="H50" s="1477"/>
+      <c r="I50" s="1477"/>
+      <c r="J50" s="1477"/>
+      <c r="K50" s="1477"/>
     </row>
     <row r="51" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -43970,12 +43919,11 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -43984,11 +43932,12 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0700-000000000000}">

--- a/app/templates/informes/Proctor/Template_Proctor.xlsx
+++ b/app/templates/informes/Proctor/Template_Proctor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Proctor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC1CE8F-A459-4899-B417-273FDC6EE7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1452E359-22A3-4FDB-BA7A-97C1E538353F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="613" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="669">
   <si>
     <t>LABORATORIO DE ENSAYO DE MATERIALES</t>
   </si>
@@ -2558,6 +2558,9 @@
   </si>
   <si>
     <t>Versión: 08 (15-06-2026)</t>
+  </si>
+  <si>
+    <t>Versión: 08 (11-06-2026)</t>
   </si>
 </sst>
 </file>
@@ -2613,7 +2616,7 @@
     <numFmt numFmtId="209" formatCode="&quot;CERTIFICADO N°&quot;000&quot;-20 SU08&quot;"/>
     <numFmt numFmtId="210" formatCode="000&quot;-20 SU08&quot;"/>
   </numFmts>
-  <fonts count="124" x14ac:knownFonts="1">
+  <fonts count="125" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3393,6 +3396,12 @@
       <u/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -5670,7 +5679,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1594">
+  <cellXfs count="1595">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
@@ -9652,6 +9661,141 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9704,211 +9848,80 @@
     <xf numFmtId="0" fontId="122" fillId="3" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9952,73 +9965,75 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10027,32 +10042,14 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -10060,48 +10057,108 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10123,54 +10180,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="18" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="104" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10181,146 +10190,78 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="193" fontId="81" fillId="0" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="189" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="189" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10349,6 +10290,10 @@
     <xf numFmtId="0" fontId="58" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -10367,6 +10312,9 @@
     <xf numFmtId="164" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10378,6 +10326,127 @@
     </xf>
     <xf numFmtId="0" fontId="58" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="51" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="58" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -10393,65 +10462,9 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="51" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="58" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10469,9 +10482,56 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="122" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="131" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="124" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="128" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="125" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="126" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="127" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10524,57 +10584,6 @@
     <xf numFmtId="0" fontId="49" fillId="11" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="122" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="131" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="124" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="128" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="125" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="126" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="127" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="9" borderId="149" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10664,6 +10673,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -11210,7 +11222,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="141997568"/>
@@ -11339,7 +11351,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="141818880"/>
@@ -11386,7 +11398,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11539,7 +11551,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="145561856"/>
@@ -11575,7 +11587,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="145560320"/>
@@ -11613,7 +11625,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12151,7 +12163,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="182790784"/>
@@ -12251,7 +12263,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="182788096"/>
@@ -12294,7 +12306,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12626,7 +12638,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="239970560"/>
@@ -12729,7 +12741,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="239913984"/>
@@ -12778,7 +12790,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -16369,7 +16381,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16428,7 +16440,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -16547,7 +16559,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16598,7 +16610,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16650,7 +16662,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -16682,7 +16694,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16724,7 +16736,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -17442,90 +17454,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1278"/>
-      <c r="B1" s="1279"/>
-      <c r="C1" s="1279"/>
-      <c r="D1" s="1279"/>
-      <c r="E1" s="1279"/>
-      <c r="F1" s="1279"/>
-      <c r="G1" s="1279"/>
-      <c r="H1" s="1279"/>
-      <c r="I1" s="1280"/>
+      <c r="A1" s="1317"/>
+      <c r="B1" s="1318"/>
+      <c r="C1" s="1318"/>
+      <c r="D1" s="1318"/>
+      <c r="E1" s="1318"/>
+      <c r="F1" s="1318"/>
+      <c r="G1" s="1318"/>
+      <c r="H1" s="1318"/>
+      <c r="I1" s="1319"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1281"/>
-      <c r="B2" s="1282"/>
-      <c r="C2" s="1282"/>
-      <c r="D2" s="1282"/>
-      <c r="E2" s="1282"/>
-      <c r="F2" s="1282"/>
-      <c r="G2" s="1282"/>
-      <c r="H2" s="1282"/>
-      <c r="I2" s="1283"/>
+      <c r="A2" s="1320"/>
+      <c r="B2" s="1321"/>
+      <c r="C2" s="1321"/>
+      <c r="D2" s="1321"/>
+      <c r="E2" s="1321"/>
+      <c r="F2" s="1321"/>
+      <c r="G2" s="1321"/>
+      <c r="H2" s="1321"/>
+      <c r="I2" s="1322"/>
       <c r="K2" s="1266" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="1267"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1281"/>
-      <c r="B3" s="1282"/>
-      <c r="C3" s="1282"/>
-      <c r="D3" s="1282"/>
-      <c r="E3" s="1282"/>
-      <c r="F3" s="1282"/>
-      <c r="G3" s="1282"/>
-      <c r="H3" s="1282"/>
-      <c r="I3" s="1283"/>
+      <c r="A3" s="1320"/>
+      <c r="B3" s="1321"/>
+      <c r="C3" s="1321"/>
+      <c r="D3" s="1321"/>
+      <c r="E3" s="1321"/>
+      <c r="F3" s="1321"/>
+      <c r="G3" s="1321"/>
+      <c r="H3" s="1321"/>
+      <c r="I3" s="1322"/>
       <c r="K3" s="1266" t="s">
         <v>5</v>
       </c>
       <c r="L3" s="1268"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1284"/>
-      <c r="B4" s="1285"/>
-      <c r="C4" s="1285"/>
-      <c r="D4" s="1285"/>
-      <c r="E4" s="1285"/>
-      <c r="F4" s="1285"/>
-      <c r="G4" s="1285"/>
-      <c r="H4" s="1285"/>
-      <c r="I4" s="1286"/>
+      <c r="A4" s="1323"/>
+      <c r="B4" s="1324"/>
+      <c r="C4" s="1324"/>
+      <c r="D4" s="1324"/>
+      <c r="E4" s="1324"/>
+      <c r="F4" s="1324"/>
+      <c r="G4" s="1324"/>
+      <c r="H4" s="1324"/>
+      <c r="I4" s="1325"/>
       <c r="K4" s="1266" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="1268"/>
     </row>
     <row r="5" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1287" t="s">
+      <c r="A5" s="1326" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1287"/>
-      <c r="C5" s="1287"/>
-      <c r="D5" s="1287"/>
-      <c r="E5" s="1287"/>
-      <c r="F5" s="1287"/>
-      <c r="G5" s="1287"/>
-      <c r="H5" s="1287"/>
-      <c r="I5" s="1287"/>
+      <c r="B5" s="1326"/>
+      <c r="C5" s="1326"/>
+      <c r="D5" s="1326"/>
+      <c r="E5" s="1326"/>
+      <c r="F5" s="1326"/>
+      <c r="G5" s="1326"/>
+      <c r="H5" s="1326"/>
+      <c r="I5" s="1326"/>
       <c r="K5" s="1266" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="1268"/>
     </row>
     <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1288" t="s">
+      <c r="A6" s="1327" t="s">
         <v>587</v>
       </c>
-      <c r="B6" s="1288"/>
-      <c r="C6" s="1288"/>
-      <c r="D6" s="1288"/>
-      <c r="E6" s="1288"/>
-      <c r="F6" s="1288"/>
-      <c r="G6" s="1288"/>
-      <c r="H6" s="1288"/>
-      <c r="I6" s="1288"/>
+      <c r="B6" s="1327"/>
+      <c r="C6" s="1327"/>
+      <c r="D6" s="1327"/>
+      <c r="E6" s="1327"/>
+      <c r="F6" s="1327"/>
+      <c r="G6" s="1327"/>
+      <c r="H6" s="1327"/>
+      <c r="I6" s="1327"/>
       <c r="K6" s="1269"/>
       <c r="L6" s="1270"/>
     </row>
@@ -17549,15 +17561,15 @@
       <c r="B8" s="1170" t="s">
         <v>588</v>
       </c>
-      <c r="C8" s="1289" t="s">
+      <c r="C8" s="1328" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1290"/>
+      <c r="D8" s="1329"/>
       <c r="E8" s="1172"/>
-      <c r="F8" s="1291" t="s">
+      <c r="F8" s="1330" t="s">
         <v>589</v>
       </c>
-      <c r="G8" s="1290"/>
+      <c r="G8" s="1329"/>
       <c r="H8" s="1171" t="s">
         <v>590</v>
       </c>
@@ -17569,11 +17581,11 @@
     </row>
     <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1173"/>
-      <c r="C9" s="1275"/>
-      <c r="D9" s="1276"/>
+      <c r="C9" s="1314"/>
+      <c r="D9" s="1315"/>
       <c r="E9" s="1174"/>
-      <c r="F9" s="1277"/>
-      <c r="G9" s="1276"/>
+      <c r="F9" s="1316"/>
+      <c r="G9" s="1315"/>
       <c r="H9" s="1175"/>
       <c r="I9" s="243"/>
       <c r="K9" s="1266" t="s">
@@ -17583,46 +17595,46 @@
     </row>
     <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1176"/>
-      <c r="B10" s="1292"/>
-      <c r="C10" s="1292"/>
-      <c r="D10" s="1292"/>
+      <c r="B10" s="1305"/>
+      <c r="C10" s="1305"/>
+      <c r="D10" s="1305"/>
       <c r="E10" s="1177"/>
-      <c r="F10" s="1292"/>
-      <c r="G10" s="1292"/>
+      <c r="F10" s="1305"/>
+      <c r="G10" s="1305"/>
       <c r="H10" s="1177"/>
       <c r="I10" s="1178"/>
       <c r="K10" s="1269"/>
       <c r="L10" s="1270"/>
     </row>
     <row r="11" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1293" t="s">
+      <c r="A11" s="1306" t="s">
         <v>591</v>
       </c>
-      <c r="B11" s="1294"/>
-      <c r="C11" s="1294"/>
-      <c r="D11" s="1294"/>
-      <c r="E11" s="1294"/>
-      <c r="F11" s="1294"/>
-      <c r="G11" s="1294"/>
-      <c r="H11" s="1294"/>
-      <c r="I11" s="1295"/>
+      <c r="B11" s="1307"/>
+      <c r="C11" s="1307"/>
+      <c r="D11" s="1307"/>
+      <c r="E11" s="1307"/>
+      <c r="F11" s="1307"/>
+      <c r="G11" s="1307"/>
+      <c r="H11" s="1307"/>
+      <c r="I11" s="1308"/>
       <c r="K11" s="1266" t="s">
         <v>15</v>
       </c>
       <c r="L11" s="1270"/>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1296" t="s">
+      <c r="A12" s="1309" t="s">
         <v>531</v>
       </c>
-      <c r="B12" s="1297"/>
-      <c r="C12" s="1297"/>
-      <c r="D12" s="1297"/>
-      <c r="E12" s="1297"/>
-      <c r="F12" s="1297"/>
-      <c r="G12" s="1297"/>
-      <c r="H12" s="1297"/>
-      <c r="I12" s="1298"/>
+      <c r="B12" s="1310"/>
+      <c r="C12" s="1310"/>
+      <c r="D12" s="1310"/>
+      <c r="E12" s="1310"/>
+      <c r="F12" s="1310"/>
+      <c r="G12" s="1310"/>
+      <c r="H12" s="1310"/>
+      <c r="I12" s="1311"/>
       <c r="K12" s="1266" t="s">
         <v>18</v>
       </c>
@@ -17661,17 +17673,17 @@
       <c r="L14" s="1270"/>
     </row>
     <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1299" t="s">
+      <c r="A15" s="1296" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1299"/>
+      <c r="B15" s="1296"/>
       <c r="C15" s="1188" t="s">
         <v>593</v>
       </c>
-      <c r="D15" s="1300">
+      <c r="D15" s="1312">
         <v>1</v>
       </c>
-      <c r="E15" s="1301"/>
+      <c r="E15" s="1313"/>
       <c r="F15" s="1190">
         <v>2</v>
       </c>
@@ -17690,17 +17702,17 @@
       <c r="L15" s="1272"/>
     </row>
     <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1302" t="s">
+      <c r="A16" s="1288" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1302"/>
+      <c r="B16" s="1288"/>
       <c r="C16" s="1191" t="s">
         <v>593</v>
       </c>
-      <c r="D16" s="1303">
+      <c r="D16" s="1299">
         <v>5</v>
       </c>
-      <c r="E16" s="1304"/>
+      <c r="E16" s="1300"/>
       <c r="F16" s="1193">
         <v>5</v>
       </c>
@@ -17719,15 +17731,15 @@
       <c r="L16" s="1272"/>
     </row>
     <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1302" t="s">
+      <c r="A17" s="1288" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1302"/>
+      <c r="B17" s="1288"/>
       <c r="C17" s="1191" t="s">
         <v>593</v>
       </c>
-      <c r="D17" s="1303"/>
-      <c r="E17" s="1304"/>
+      <c r="D17" s="1299"/>
+      <c r="E17" s="1300"/>
       <c r="F17" s="1193"/>
       <c r="G17" s="1192"/>
       <c r="H17" s="1192"/>
@@ -17738,75 +17750,75 @@
       <c r="L17" s="1273"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1302" t="s">
+      <c r="A18" s="1288" t="s">
         <v>594</v>
       </c>
-      <c r="B18" s="1302"/>
+      <c r="B18" s="1288"/>
       <c r="C18" s="1192" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="1303"/>
-      <c r="E18" s="1304"/>
+      <c r="D18" s="1299"/>
+      <c r="E18" s="1300"/>
       <c r="F18" s="1194"/>
       <c r="G18" s="1195"/>
       <c r="H18" s="1195"/>
       <c r="I18" s="1194"/>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1302" t="s">
+      <c r="A19" s="1288" t="s">
         <v>595</v>
       </c>
-      <c r="B19" s="1302"/>
+      <c r="B19" s="1288"/>
       <c r="C19" s="1192" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="1303"/>
-      <c r="E19" s="1304"/>
+      <c r="D19" s="1299"/>
+      <c r="E19" s="1300"/>
       <c r="F19" s="1193"/>
       <c r="G19" s="1192"/>
       <c r="H19" s="1196"/>
       <c r="I19" s="1197"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1305" t="s">
+      <c r="A20" s="1301" t="s">
         <v>596</v>
       </c>
-      <c r="B20" s="1306"/>
+      <c r="B20" s="1302"/>
       <c r="C20" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D20" s="1303"/>
-      <c r="E20" s="1304"/>
+      <c r="D20" s="1299"/>
+      <c r="E20" s="1300"/>
       <c r="F20" s="1193"/>
       <c r="G20" s="1192"/>
       <c r="H20" s="1196"/>
       <c r="I20" s="1197"/>
     </row>
     <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1302" t="s">
+      <c r="A21" s="1288" t="s">
         <v>597</v>
       </c>
-      <c r="B21" s="1302"/>
+      <c r="B21" s="1288"/>
       <c r="C21" s="1192" t="s">
         <v>598</v>
       </c>
-      <c r="D21" s="1307"/>
-      <c r="E21" s="1308"/>
+      <c r="D21" s="1303"/>
+      <c r="E21" s="1304"/>
       <c r="F21" s="1193"/>
       <c r="G21" s="1192"/>
       <c r="H21" s="1192"/>
       <c r="I21" s="1193"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1309" t="s">
+      <c r="A22" s="1291" t="s">
         <v>599</v>
       </c>
-      <c r="B22" s="1309"/>
+      <c r="B22" s="1291"/>
       <c r="C22" s="1199" t="s">
         <v>600</v>
       </c>
-      <c r="D22" s="1310"/>
-      <c r="E22" s="1311"/>
+      <c r="D22" s="1294"/>
+      <c r="E22" s="1295"/>
       <c r="F22" s="1200"/>
       <c r="G22" s="1201"/>
       <c r="H22" s="1201"/>
@@ -17826,148 +17838,148 @@
       <c r="I23" s="1202"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1299" t="s">
+      <c r="A24" s="1296" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="1299"/>
+      <c r="B24" s="1296"/>
       <c r="C24" s="1203"/>
-      <c r="D24" s="1312"/>
-      <c r="E24" s="1313"/>
+      <c r="D24" s="1297"/>
+      <c r="E24" s="1298"/>
       <c r="F24" s="1205"/>
       <c r="G24" s="1204"/>
       <c r="H24" s="1204"/>
       <c r="I24" s="1205"/>
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1302" t="s">
+      <c r="A25" s="1288" t="s">
         <v>601</v>
       </c>
-      <c r="B25" s="1302"/>
+      <c r="B25" s="1288"/>
       <c r="C25" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D25" s="1314"/>
-      <c r="E25" s="1315"/>
+      <c r="D25" s="1289"/>
+      <c r="E25" s="1290"/>
       <c r="F25" s="1207"/>
       <c r="G25" s="1206"/>
       <c r="H25" s="1206"/>
       <c r="I25" s="1207"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1302" t="s">
+      <c r="A26" s="1288" t="s">
         <v>602</v>
       </c>
-      <c r="B26" s="1302"/>
+      <c r="B26" s="1288"/>
       <c r="C26" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="1314"/>
-      <c r="E26" s="1315"/>
+      <c r="D26" s="1289"/>
+      <c r="E26" s="1290"/>
       <c r="F26" s="1207"/>
       <c r="G26" s="1206"/>
       <c r="H26" s="1206"/>
       <c r="I26" s="1207"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1302" t="s">
+      <c r="A27" s="1288" t="s">
         <v>603</v>
       </c>
-      <c r="B27" s="1302"/>
+      <c r="B27" s="1288"/>
       <c r="C27" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="1314"/>
-      <c r="E27" s="1315"/>
+      <c r="D27" s="1289"/>
+      <c r="E27" s="1290"/>
       <c r="F27" s="1207"/>
       <c r="G27" s="1206"/>
       <c r="H27" s="1206"/>
       <c r="I27" s="1207"/>
     </row>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1302" t="s">
+      <c r="A28" s="1288" t="s">
         <v>604</v>
       </c>
-      <c r="B28" s="1302"/>
+      <c r="B28" s="1288"/>
       <c r="C28" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D28" s="1314"/>
-      <c r="E28" s="1315"/>
+      <c r="D28" s="1289"/>
+      <c r="E28" s="1290"/>
       <c r="F28" s="1207"/>
       <c r="G28" s="1206"/>
       <c r="H28" s="1206"/>
       <c r="I28" s="1207"/>
     </row>
     <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1302" t="s">
+      <c r="A29" s="1288" t="s">
         <v>605</v>
       </c>
-      <c r="B29" s="1302"/>
+      <c r="B29" s="1288"/>
       <c r="C29" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="1314"/>
-      <c r="E29" s="1315"/>
+      <c r="D29" s="1289"/>
+      <c r="E29" s="1290"/>
       <c r="F29" s="1208"/>
       <c r="G29" s="1209"/>
       <c r="H29" s="1209"/>
       <c r="I29" s="1208"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1302" t="s">
+      <c r="A30" s="1288" t="s">
         <v>606</v>
       </c>
-      <c r="B30" s="1302"/>
+      <c r="B30" s="1288"/>
       <c r="C30" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D30" s="1314"/>
-      <c r="E30" s="1315"/>
+      <c r="D30" s="1289"/>
+      <c r="E30" s="1290"/>
       <c r="F30" s="1208"/>
       <c r="G30" s="1209"/>
       <c r="H30" s="1209"/>
       <c r="I30" s="1208"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1302" t="s">
+      <c r="A31" s="1288" t="s">
         <v>607</v>
       </c>
-      <c r="B31" s="1302"/>
+      <c r="B31" s="1288"/>
       <c r="C31" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D31" s="1314"/>
-      <c r="E31" s="1315"/>
+      <c r="D31" s="1289"/>
+      <c r="E31" s="1290"/>
       <c r="F31" s="1208"/>
       <c r="G31" s="1209"/>
       <c r="H31" s="1209"/>
       <c r="I31" s="1208"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1302" t="s">
+      <c r="A32" s="1288" t="s">
         <v>608</v>
       </c>
-      <c r="B32" s="1302"/>
+      <c r="B32" s="1288"/>
       <c r="C32" s="1192" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="1314"/>
-      <c r="E32" s="1315"/>
+      <c r="D32" s="1289"/>
+      <c r="E32" s="1290"/>
       <c r="F32" s="1210"/>
       <c r="G32" s="1211"/>
       <c r="H32" s="1211"/>
       <c r="I32" s="1210"/>
     </row>
     <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1309" t="s">
+      <c r="A33" s="1291" t="s">
         <v>609</v>
       </c>
-      <c r="B33" s="1309"/>
+      <c r="B33" s="1291"/>
       <c r="C33" s="1199" t="s">
         <v>600</v>
       </c>
-      <c r="D33" s="1316"/>
-      <c r="E33" s="1317"/>
+      <c r="D33" s="1292"/>
+      <c r="E33" s="1293"/>
       <c r="F33" s="1200"/>
       <c r="G33" s="1201"/>
       <c r="H33" s="1201"/>
@@ -17993,19 +18005,19 @@
         <v>611</v>
       </c>
       <c r="B35" s="1217"/>
-      <c r="C35" s="1318"/>
-      <c r="D35" s="1319"/>
+      <c r="C35" s="1283"/>
+      <c r="D35" s="1284"/>
       <c r="E35" s="1218"/>
-      <c r="F35" s="1322" t="s">
+      <c r="F35" s="1281" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="1322" t="s">
+      <c r="G35" s="1281" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="1322" t="s">
+      <c r="H35" s="1281" t="s">
         <v>612</v>
       </c>
-      <c r="I35" s="1322" t="s">
+      <c r="I35" s="1281" t="s">
         <v>231</v>
       </c>
     </row>
@@ -18014,21 +18026,21 @@
         <v>613</v>
       </c>
       <c r="B36" s="1220"/>
-      <c r="C36" s="1318"/>
-      <c r="D36" s="1319"/>
+      <c r="C36" s="1283"/>
+      <c r="D36" s="1284"/>
       <c r="E36" s="1218"/>
-      <c r="F36" s="1323"/>
-      <c r="G36" s="1323"/>
-      <c r="H36" s="1323"/>
-      <c r="I36" s="1323"/>
+      <c r="F36" s="1282"/>
+      <c r="G36" s="1282"/>
+      <c r="H36" s="1282"/>
+      <c r="I36" s="1282"/>
     </row>
     <row r="37" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1219" t="s">
         <v>614</v>
       </c>
       <c r="B37" s="1220"/>
-      <c r="C37" s="1324"/>
-      <c r="D37" s="1319"/>
+      <c r="C37" s="1285"/>
+      <c r="D37" s="1284"/>
       <c r="E37" s="1221"/>
       <c r="F37" s="1222" t="s">
         <v>615</v>
@@ -18042,8 +18054,8 @@
         <v>616</v>
       </c>
       <c r="B38" s="1227"/>
-      <c r="C38" s="1318"/>
-      <c r="D38" s="1319"/>
+      <c r="C38" s="1283"/>
+      <c r="D38" s="1284"/>
       <c r="E38" s="1218"/>
       <c r="F38" s="1222" t="s">
         <v>617</v>
@@ -18057,8 +18069,8 @@
         <v>618</v>
       </c>
       <c r="B39" s="1220"/>
-      <c r="C39" s="1318"/>
-      <c r="D39" s="1319"/>
+      <c r="C39" s="1283"/>
+      <c r="D39" s="1284"/>
       <c r="E39" s="1218"/>
       <c r="F39" s="1222" t="s">
         <v>110</v>
@@ -18087,8 +18099,8 @@
         <v>619</v>
       </c>
       <c r="B41" s="1230"/>
-      <c r="C41" s="1325"/>
-      <c r="D41" s="1325"/>
+      <c r="C41" s="1277"/>
+      <c r="D41" s="1277"/>
       <c r="E41" s="1228"/>
       <c r="F41" s="1222" t="s">
         <v>620</v>
@@ -18102,8 +18114,8 @@
         <v>621</v>
       </c>
       <c r="B42" s="1232"/>
-      <c r="C42" s="1325"/>
-      <c r="D42" s="1325"/>
+      <c r="C42" s="1277"/>
+      <c r="D42" s="1277"/>
       <c r="E42" s="1233"/>
       <c r="J42" s="1234"/>
     </row>
@@ -18112,17 +18124,17 @@
         <v>622</v>
       </c>
       <c r="B43" s="1236"/>
-      <c r="C43" s="1325"/>
-      <c r="D43" s="1325"/>
+      <c r="C43" s="1277"/>
+      <c r="D43" s="1277"/>
       <c r="E43" s="1233"/>
-      <c r="F43" s="1326" t="s">
+      <c r="F43" s="1286" t="s">
         <v>623</v>
       </c>
-      <c r="G43" s="1327"/>
-      <c r="H43" s="1320" t="s">
+      <c r="G43" s="1287"/>
+      <c r="H43" s="1275" t="s">
         <v>624</v>
       </c>
-      <c r="I43" s="1321"/>
+      <c r="I43" s="1276"/>
       <c r="J43" s="1234"/>
     </row>
     <row r="44" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18130,31 +18142,31 @@
         <v>625</v>
       </c>
       <c r="B44" s="1232"/>
-      <c r="C44" s="1325"/>
-      <c r="D44" s="1325"/>
+      <c r="C44" s="1277"/>
+      <c r="D44" s="1277"/>
       <c r="E44" s="1233"/>
       <c r="F44" s="1237" t="s">
         <v>626</v>
       </c>
       <c r="G44" s="1238"/>
-      <c r="H44" s="1320"/>
-      <c r="I44" s="1321"/>
+      <c r="H44" s="1275"/>
+      <c r="I44" s="1276"/>
       <c r="J44" s="1234"/>
     </row>
     <row r="45" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1329" t="s">
+      <c r="A45" s="1279" t="s">
         <v>627</v>
       </c>
-      <c r="B45" s="1330"/>
-      <c r="C45" s="1325"/>
-      <c r="D45" s="1325"/>
+      <c r="B45" s="1280"/>
+      <c r="C45" s="1277"/>
+      <c r="D45" s="1277"/>
       <c r="E45" s="1233"/>
       <c r="F45" s="1237" t="s">
         <v>628</v>
       </c>
       <c r="G45" s="1238"/>
-      <c r="H45" s="1320"/>
-      <c r="I45" s="1321"/>
+      <c r="H45" s="1275"/>
+      <c r="I45" s="1276"/>
       <c r="J45" s="1234"/>
     </row>
     <row r="46" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18168,8 +18180,8 @@
         <v>629</v>
       </c>
       <c r="G46" s="1238"/>
-      <c r="H46" s="1320"/>
-      <c r="I46" s="1321"/>
+      <c r="H46" s="1275"/>
+      <c r="I46" s="1276"/>
     </row>
     <row r="47" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1242"/>
@@ -18180,8 +18192,8 @@
         <v>630</v>
       </c>
       <c r="G47" s="1238"/>
-      <c r="H47" s="1320"/>
-      <c r="I47" s="1321"/>
+      <c r="H47" s="1275"/>
+      <c r="I47" s="1276"/>
     </row>
     <row r="48" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1242"/>
@@ -18192,8 +18204,8 @@
         <v>582</v>
       </c>
       <c r="G48" s="1245"/>
-      <c r="H48" s="1320"/>
-      <c r="I48" s="1321"/>
+      <c r="H48" s="1275"/>
+      <c r="I48" s="1276"/>
     </row>
     <row r="49" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1246"/>
@@ -18204,8 +18216,8 @@
         <v>631</v>
       </c>
       <c r="G49" s="1238"/>
-      <c r="H49" s="1325"/>
-      <c r="I49" s="1325"/>
+      <c r="H49" s="1277"/>
+      <c r="I49" s="1277"/>
     </row>
     <row r="50" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E50" s="352"/>
@@ -18246,17 +18258,17 @@
     </row>
     <row r="55" spans="1:9" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1328" t="s">
+      <c r="A56" s="1278" t="s">
         <v>634</v>
       </c>
-      <c r="B56" s="1328"/>
-      <c r="C56" s="1328"/>
-      <c r="D56" s="1328"/>
-      <c r="E56" s="1328"/>
-      <c r="F56" s="1328"/>
-      <c r="G56" s="1328"/>
-      <c r="H56" s="1328"/>
-      <c r="I56" s="1328"/>
+      <c r="B56" s="1278"/>
+      <c r="C56" s="1278"/>
+      <c r="D56" s="1278"/>
+      <c r="E56" s="1278"/>
+      <c r="F56" s="1278"/>
+      <c r="G56" s="1278"/>
+      <c r="H56" s="1278"/>
+      <c r="I56" s="1278"/>
     </row>
     <row r="57" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -18266,16 +18278,54 @@
     <protectedRange sqref="B9:C10" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="71">
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="H35:H36"/>
@@ -18289,54 +18339,16 @@
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -18442,33 +18454,33 @@
       <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1504" t="s">
+      <c r="A8" s="1522" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1504"/>
-      <c r="C8" s="1504"/>
-      <c r="D8" s="1504"/>
-      <c r="E8" s="1504"/>
-      <c r="F8" s="1504"/>
-      <c r="G8" s="1504"/>
-      <c r="H8" s="1504"/>
-      <c r="I8" s="1504"/>
-      <c r="J8" s="1504"/>
+      <c r="B8" s="1522"/>
+      <c r="C8" s="1522"/>
+      <c r="D8" s="1522"/>
+      <c r="E8" s="1522"/>
+      <c r="F8" s="1522"/>
+      <c r="G8" s="1522"/>
+      <c r="H8" s="1522"/>
+      <c r="I8" s="1522"/>
+      <c r="J8" s="1522"/>
     </row>
     <row r="9" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1529">
+      <c r="A9" s="1525">
         <f>J13</f>
         <v>1</v>
       </c>
-      <c r="B9" s="1529"/>
-      <c r="C9" s="1529"/>
-      <c r="D9" s="1529"/>
-      <c r="E9" s="1529"/>
-      <c r="F9" s="1529"/>
-      <c r="G9" s="1529"/>
-      <c r="H9" s="1529"/>
-      <c r="I9" s="1529"/>
-      <c r="J9" s="1529"/>
+      <c r="B9" s="1525"/>
+      <c r="C9" s="1525"/>
+      <c r="D9" s="1525"/>
+      <c r="E9" s="1525"/>
+      <c r="F9" s="1525"/>
+      <c r="G9" s="1525"/>
+      <c r="H9" s="1525"/>
+      <c r="I9" s="1525"/>
+      <c r="J9" s="1525"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -18490,13 +18502,13 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1506" t="s">
+      <c r="C11" s="1524" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="1506"/>
-      <c r="E11" s="1506"/>
-      <c r="F11" s="1506"/>
-      <c r="G11" s="1506"/>
+      <c r="D11" s="1524"/>
+      <c r="E11" s="1524"/>
+      <c r="F11" s="1524"/>
+      <c r="G11" s="1524"/>
       <c r="H11" s="121" t="s">
         <v>3</v>
       </c>
@@ -18518,13 +18530,13 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1506" t="s">
+      <c r="C12" s="1524" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="1506"/>
-      <c r="E12" s="1506"/>
-      <c r="F12" s="1506"/>
-      <c r="G12" s="1506"/>
+      <c r="D12" s="1524"/>
+      <c r="E12" s="1524"/>
+      <c r="F12" s="1524"/>
+      <c r="G12" s="1524"/>
       <c r="H12" s="26" t="s">
         <v>6</v>
       </c>
@@ -18548,13 +18560,13 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1506" t="s">
+      <c r="C13" s="1524" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="1506"/>
-      <c r="E13" s="1506"/>
-      <c r="F13" s="1506"/>
-      <c r="G13" s="1506"/>
+      <c r="D13" s="1524"/>
+      <c r="E13" s="1524"/>
+      <c r="F13" s="1524"/>
+      <c r="G13" s="1524"/>
       <c r="H13" s="26" t="s">
         <v>288</v>
       </c>
@@ -18567,8 +18579,8 @@
       <c r="K13" s="124"/>
       <c r="L13" s="124"/>
       <c r="M13" s="124"/>
-      <c r="P13" s="1503"/>
-      <c r="Q13" s="1503"/>
+      <c r="P13" s="1521"/>
+      <c r="Q13" s="1521"/>
     </row>
     <row r="14" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -18588,34 +18600,34 @@
       <c r="Q14" s="737"/>
     </row>
     <row r="15" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1507" t="s">
+      <c r="A15" s="1510" t="s">
         <v>367</v>
       </c>
-      <c r="B15" s="1508"/>
-      <c r="C15" s="1508"/>
-      <c r="D15" s="1508"/>
-      <c r="E15" s="1508"/>
-      <c r="F15" s="1508"/>
-      <c r="G15" s="1508"/>
-      <c r="H15" s="1508"/>
-      <c r="I15" s="1508"/>
-      <c r="J15" s="1509"/>
+      <c r="B15" s="1511"/>
+      <c r="C15" s="1511"/>
+      <c r="D15" s="1511"/>
+      <c r="E15" s="1511"/>
+      <c r="F15" s="1511"/>
+      <c r="G15" s="1511"/>
+      <c r="H15" s="1511"/>
+      <c r="I15" s="1511"/>
+      <c r="J15" s="1512"/>
       <c r="K15" s="124"/>
       <c r="L15" s="124"/>
     </row>
     <row r="16" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1510" t="s">
+      <c r="A16" s="1513" t="s">
         <v>368</v>
       </c>
-      <c r="B16" s="1511"/>
-      <c r="C16" s="1511"/>
-      <c r="D16" s="1511"/>
-      <c r="E16" s="1511"/>
-      <c r="F16" s="1511"/>
-      <c r="G16" s="1511"/>
-      <c r="H16" s="1511"/>
-      <c r="I16" s="1511"/>
-      <c r="J16" s="1512"/>
+      <c r="B16" s="1514"/>
+      <c r="C16" s="1514"/>
+      <c r="D16" s="1514"/>
+      <c r="E16" s="1514"/>
+      <c r="F16" s="1514"/>
+      <c r="G16" s="1514"/>
+      <c r="H16" s="1514"/>
+      <c r="I16" s="1514"/>
+      <c r="J16" s="1515"/>
       <c r="K16" s="124"/>
       <c r="L16" s="124"/>
     </row>
@@ -18634,18 +18646,18 @@
       <c r="L17" s="124"/>
     </row>
     <row r="18" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1477" t="s">
+      <c r="A18" s="1485" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1478"/>
-      <c r="C18" s="1478"/>
-      <c r="D18" s="1478"/>
-      <c r="E18" s="1478"/>
-      <c r="F18" s="1478"/>
-      <c r="G18" s="1478"/>
-      <c r="H18" s="1478"/>
-      <c r="I18" s="1478"/>
-      <c r="J18" s="1479"/>
+      <c r="B18" s="1486"/>
+      <c r="C18" s="1486"/>
+      <c r="D18" s="1486"/>
+      <c r="E18" s="1486"/>
+      <c r="F18" s="1486"/>
+      <c r="G18" s="1486"/>
+      <c r="H18" s="1486"/>
+      <c r="I18" s="1486"/>
+      <c r="J18" s="1487"/>
       <c r="L18" s="124"/>
     </row>
     <row r="19" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -18760,12 +18772,12 @@
     <row r="24" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="251"/>
       <c r="B24" s="249"/>
-      <c r="C24" s="1525" t="s">
+      <c r="C24" s="1526" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="1526"/>
-      <c r="E24" s="1526"/>
-      <c r="F24" s="1527"/>
+      <c r="D24" s="1527"/>
+      <c r="E24" s="1527"/>
+      <c r="F24" s="1528"/>
       <c r="G24" s="249"/>
       <c r="H24" s="249"/>
       <c r="I24" s="249"/>
@@ -18882,10 +18894,10 @@
     <row r="28" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="251"/>
       <c r="B28" s="173"/>
-      <c r="C28" s="1528"/>
-      <c r="D28" s="1528"/>
-      <c r="E28" s="1528"/>
-      <c r="F28" s="1528"/>
+      <c r="C28" s="1529"/>
+      <c r="D28" s="1529"/>
+      <c r="E28" s="1529"/>
+      <c r="F28" s="1529"/>
       <c r="G28" s="247"/>
       <c r="H28" s="260"/>
       <c r="I28" s="260"/>
@@ -18909,12 +18921,12 @@
     <row r="29" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="251"/>
       <c r="B29" s="173"/>
-      <c r="C29" s="1525" t="s">
+      <c r="C29" s="1526" t="s">
         <v>379</v>
       </c>
-      <c r="D29" s="1526"/>
-      <c r="E29" s="1526"/>
-      <c r="F29" s="1527"/>
+      <c r="D29" s="1527"/>
+      <c r="E29" s="1527"/>
+      <c r="F29" s="1528"/>
       <c r="G29" s="275" t="s">
         <v>380</v>
       </c>
@@ -19343,18 +19355,18 @@
     </row>
     <row r="53" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1485" t="s">
+      <c r="A54" s="1463" t="s">
         <v>345</v>
       </c>
-      <c r="B54" s="1485"/>
-      <c r="C54" s="1485"/>
-      <c r="D54" s="1485"/>
-      <c r="E54" s="1485"/>
-      <c r="F54" s="1485"/>
-      <c r="G54" s="1485"/>
-      <c r="H54" s="1485"/>
-      <c r="I54" s="1485"/>
-      <c r="J54" s="1485"/>
+      <c r="B54" s="1463"/>
+      <c r="C54" s="1463"/>
+      <c r="D54" s="1463"/>
+      <c r="E54" s="1463"/>
+      <c r="F54" s="1463"/>
+      <c r="G54" s="1463"/>
+      <c r="H54" s="1463"/>
+      <c r="I54" s="1463"/>
+      <c r="J54" s="1463"/>
     </row>
     <row r="55" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19364,12 +19376,6 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="13">
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A16:J16"/>
@@ -19377,6 +19383,12 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -19408,15 +19420,15 @@
       <c r="A1" s="82" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="1530" t="s">
+      <c r="B1" s="1547" t="s">
         <v>390</v>
       </c>
-      <c r="C1" s="1530"/>
-      <c r="D1" s="1530"/>
-      <c r="E1" s="1530"/>
-      <c r="F1" s="1530"/>
-      <c r="G1" s="1530"/>
-      <c r="H1" s="1530"/>
+      <c r="C1" s="1547"/>
+      <c r="D1" s="1547"/>
+      <c r="E1" s="1547"/>
+      <c r="F1" s="1547"/>
+      <c r="G1" s="1547"/>
+      <c r="H1" s="1547"/>
       <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -19554,29 +19566,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="82"/>
-      <c r="B8" s="1531" t="s">
+      <c r="B8" s="1548" t="s">
         <v>402</v>
       </c>
-      <c r="C8" s="1531"/>
-      <c r="D8" s="1531"/>
+      <c r="C8" s="1548"/>
+      <c r="D8" s="1548"/>
       <c r="E8" s="830" t="s">
         <v>403</v>
       </c>
       <c r="F8" s="831" t="s">
         <v>404</v>
       </c>
-      <c r="G8" s="1532" t="s">
+      <c r="G8" s="1549" t="s">
         <v>405</v>
       </c>
-      <c r="H8" s="1532"/>
+      <c r="H8" s="1549"/>
       <c r="I8" s="82"/>
       <c r="L8" s="90" t="s">
         <v>406</v>
       </c>
-      <c r="M8" s="1533" t="s">
+      <c r="M8" s="1550" t="s">
         <v>407</v>
       </c>
-      <c r="N8" s="1533"/>
+      <c r="N8" s="1550"/>
       <c r="O8" s="91" t="s">
         <v>408</v>
       </c>
@@ -19589,13 +19601,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82"/>
-      <c r="B9" s="1534" t="s">
+      <c r="B9" s="1551" t="s">
         <v>411</v>
       </c>
-      <c r="C9" s="1536" t="s">
+      <c r="C9" s="1553" t="s">
         <v>412</v>
       </c>
-      <c r="D9" s="1538" t="s">
+      <c r="D9" s="1555" t="s">
         <v>413</v>
       </c>
       <c r="E9" s="832" t="s">
@@ -19604,10 +19616,10 @@
       <c r="F9" s="833" t="s">
         <v>415</v>
       </c>
-      <c r="G9" s="1539" t="s">
+      <c r="G9" s="1556" t="s">
         <v>416</v>
       </c>
-      <c r="H9" s="1540"/>
+      <c r="H9" s="1557"/>
       <c r="I9" s="82"/>
       <c r="L9" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -19636,19 +19648,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="82"/>
-      <c r="B10" s="1534"/>
-      <c r="C10" s="1536"/>
-      <c r="D10" s="1538"/>
+      <c r="B10" s="1551"/>
+      <c r="C10" s="1553"/>
+      <c r="D10" s="1555"/>
       <c r="E10" s="834" t="s">
         <v>417</v>
       </c>
       <c r="F10" s="835" t="s">
         <v>418</v>
       </c>
-      <c r="G10" s="1541" t="s">
+      <c r="G10" s="1558" t="s">
         <v>419</v>
       </c>
-      <c r="H10" s="1542"/>
+      <c r="H10" s="1559"/>
       <c r="I10" s="82"/>
       <c r="L10" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -19673,9 +19685,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="82"/>
-      <c r="B11" s="1534"/>
-      <c r="C11" s="1536"/>
-      <c r="D11" s="1538" t="s">
+      <c r="B11" s="1551"/>
+      <c r="C11" s="1553"/>
+      <c r="D11" s="1555" t="s">
         <v>420</v>
       </c>
       <c r="E11" s="834" t="s">
@@ -19687,7 +19699,7 @@
       <c r="G11" s="837" t="s">
         <v>423</v>
       </c>
-      <c r="H11" s="1543" t="s">
+      <c r="H11" s="1560" t="s">
         <v>424</v>
       </c>
       <c r="I11" s="82"/>
@@ -19706,9 +19718,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="82"/>
-      <c r="B12" s="1534"/>
-      <c r="C12" s="1537"/>
-      <c r="D12" s="1538"/>
+      <c r="B12" s="1551"/>
+      <c r="C12" s="1554"/>
+      <c r="D12" s="1555"/>
       <c r="E12" s="93" t="s">
         <v>425</v>
       </c>
@@ -19718,7 +19730,7 @@
       <c r="G12" s="837" t="s">
         <v>427</v>
       </c>
-      <c r="H12" s="1544"/>
+      <c r="H12" s="1561"/>
       <c r="I12" s="82"/>
       <c r="L12" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -19731,11 +19743,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="82"/>
-      <c r="B13" s="1534"/>
-      <c r="C13" s="1536" t="s">
+      <c r="B13" s="1551"/>
+      <c r="C13" s="1553" t="s">
         <v>428</v>
       </c>
-      <c r="D13" s="1538" t="s">
+      <c r="D13" s="1555" t="s">
         <v>429</v>
       </c>
       <c r="E13" s="838" t="s">
@@ -19744,10 +19756,10 @@
       <c r="F13" s="839" t="s">
         <v>431</v>
       </c>
-      <c r="G13" s="1545" t="s">
+      <c r="G13" s="1562" t="s">
         <v>432</v>
       </c>
-      <c r="H13" s="1546"/>
+      <c r="H13" s="1563"/>
       <c r="I13" s="82"/>
       <c r="L13" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -19772,19 +19784,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="82"/>
-      <c r="B14" s="1534"/>
-      <c r="C14" s="1536"/>
-      <c r="D14" s="1538"/>
+      <c r="B14" s="1551"/>
+      <c r="C14" s="1553"/>
+      <c r="D14" s="1555"/>
       <c r="E14" s="838" t="s">
         <v>433</v>
       </c>
       <c r="F14" s="839" t="s">
         <v>434</v>
       </c>
-      <c r="G14" s="1545" t="s">
+      <c r="G14" s="1562" t="s">
         <v>435</v>
       </c>
-      <c r="H14" s="1546"/>
+      <c r="H14" s="1563"/>
       <c r="I14" s="82"/>
       <c r="L14" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -19809,9 +19821,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="82"/>
-      <c r="B15" s="1534"/>
-      <c r="C15" s="1536"/>
-      <c r="D15" s="1538" t="s">
+      <c r="B15" s="1551"/>
+      <c r="C15" s="1553"/>
+      <c r="D15" s="1555" t="s">
         <v>436</v>
       </c>
       <c r="E15" s="838" t="s">
@@ -19823,7 +19835,7 @@
       <c r="G15" s="841" t="s">
         <v>439</v>
       </c>
-      <c r="H15" s="1547" t="s">
+      <c r="H15" s="1530" t="s">
         <v>440</v>
       </c>
       <c r="I15" s="82"/>
@@ -19842,9 +19854,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="82"/>
-      <c r="B16" s="1535"/>
-      <c r="C16" s="1536"/>
-      <c r="D16" s="1538"/>
+      <c r="B16" s="1552"/>
+      <c r="C16" s="1553"/>
+      <c r="D16" s="1555"/>
       <c r="E16" s="94" t="s">
         <v>441</v>
       </c>
@@ -19854,7 +19866,7 @@
       <c r="G16" s="839" t="s">
         <v>443</v>
       </c>
-      <c r="H16" s="1548"/>
+      <c r="H16" s="1531"/>
       <c r="I16" s="82"/>
       <c r="L16" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -19867,23 +19879,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="82"/>
-      <c r="B17" s="1549" t="s">
+      <c r="B17" s="1532" t="s">
         <v>444</v>
       </c>
-      <c r="C17" s="1552" t="s">
+      <c r="C17" s="1535" t="s">
         <v>445</v>
       </c>
-      <c r="D17" s="1553"/>
+      <c r="D17" s="1536"/>
       <c r="E17" s="842" t="s">
         <v>446</v>
       </c>
       <c r="F17" s="843" t="s">
         <v>447</v>
       </c>
-      <c r="G17" s="1558" t="s">
+      <c r="G17" s="1541" t="s">
         <v>448</v>
       </c>
-      <c r="H17" s="1559"/>
+      <c r="H17" s="1542"/>
       <c r="I17" s="82"/>
       <c r="L17" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -19896,17 +19908,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="82"/>
-      <c r="B18" s="1550"/>
-      <c r="C18" s="1554"/>
-      <c r="D18" s="1555"/>
+      <c r="B18" s="1533"/>
+      <c r="C18" s="1537"/>
+      <c r="D18" s="1538"/>
       <c r="E18" s="842" t="s">
         <v>449</v>
       </c>
       <c r="F18" s="843" t="s">
         <v>450</v>
       </c>
-      <c r="G18" s="1560"/>
-      <c r="H18" s="1561"/>
+      <c r="G18" s="1543"/>
+      <c r="H18" s="1544"/>
       <c r="I18" s="82"/>
       <c r="L18" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -19919,9 +19931,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="82"/>
-      <c r="B19" s="1550"/>
-      <c r="C19" s="1556"/>
-      <c r="D19" s="1557"/>
+      <c r="B19" s="1533"/>
+      <c r="C19" s="1539"/>
+      <c r="D19" s="1540"/>
       <c r="E19" s="842" t="s">
         <v>451</v>
       </c>
@@ -19942,11 +19954,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="82"/>
-      <c r="B20" s="1550"/>
-      <c r="C20" s="1554" t="s">
+      <c r="B20" s="1533"/>
+      <c r="C20" s="1537" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="1562"/>
+      <c r="D20" s="1545"/>
       <c r="E20" s="844" t="s">
         <v>454</v>
       </c>
@@ -19967,9 +19979,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="82"/>
-      <c r="B21" s="1550"/>
-      <c r="C21" s="1554"/>
-      <c r="D21" s="1562"/>
+      <c r="B21" s="1533"/>
+      <c r="C21" s="1537"/>
+      <c r="D21" s="1545"/>
       <c r="E21" s="844" t="s">
         <v>141</v>
       </c>
@@ -19990,9 +20002,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="82"/>
-      <c r="B22" s="1550"/>
-      <c r="C22" s="1556"/>
-      <c r="D22" s="1563"/>
+      <c r="B22" s="1533"/>
+      <c r="C22" s="1539"/>
+      <c r="D22" s="1546"/>
       <c r="E22" s="98" t="s">
         <v>457</v>
       </c>
@@ -20013,11 +20025,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="82"/>
-      <c r="B23" s="1550"/>
-      <c r="C23" s="1552" t="s">
+      <c r="B23" s="1533"/>
+      <c r="C23" s="1535" t="s">
         <v>459</v>
       </c>
-      <c r="D23" s="1553"/>
+      <c r="D23" s="1536"/>
       <c r="E23" s="845" t="s">
         <v>460</v>
       </c>
@@ -20038,7 +20050,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="82"/>
-      <c r="B24" s="1551"/>
+      <c r="B24" s="1534"/>
       <c r="C24" s="847"/>
       <c r="D24" s="848"/>
       <c r="E24" s="849"/>
@@ -20145,12 +20157,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -20167,6 +20173,12 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21457,37 +21469,37 @@
       <c r="N5" s="1100"/>
     </row>
     <row r="6" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1355" t="s">
+      <c r="A6" s="1356" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1355"/>
-      <c r="C6" s="1355"/>
-      <c r="D6" s="1355"/>
-      <c r="E6" s="1355"/>
-      <c r="F6" s="1355"/>
-      <c r="G6" s="1355"/>
-      <c r="H6" s="1355"/>
-      <c r="I6" s="1355"/>
-      <c r="J6" s="1355"/>
-      <c r="K6" s="1355"/>
-      <c r="L6" s="1355"/>
+      <c r="B6" s="1356"/>
+      <c r="C6" s="1356"/>
+      <c r="D6" s="1356"/>
+      <c r="E6" s="1356"/>
+      <c r="F6" s="1356"/>
+      <c r="G6" s="1356"/>
+      <c r="H6" s="1356"/>
+      <c r="I6" s="1356"/>
+      <c r="J6" s="1356"/>
+      <c r="K6" s="1356"/>
+      <c r="L6" s="1356"/>
       <c r="N6" s="961"/>
     </row>
     <row r="7" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1356">
+      <c r="A7" s="1357">
         <v>0</v>
       </c>
-      <c r="B7" s="1356"/>
-      <c r="C7" s="1356"/>
-      <c r="D7" s="1356"/>
-      <c r="E7" s="1356"/>
-      <c r="F7" s="1356"/>
-      <c r="G7" s="1356"/>
-      <c r="H7" s="1356"/>
-      <c r="I7" s="1356"/>
-      <c r="J7" s="1356"/>
-      <c r="K7" s="1356"/>
-      <c r="L7" s="1356"/>
+      <c r="B7" s="1357"/>
+      <c r="C7" s="1357"/>
+      <c r="D7" s="1357"/>
+      <c r="E7" s="1357"/>
+      <c r="F7" s="1357"/>
+      <c r="G7" s="1357"/>
+      <c r="H7" s="1357"/>
+      <c r="I7" s="1357"/>
+      <c r="J7" s="1357"/>
+      <c r="K7" s="1357"/>
+      <c r="L7" s="1357"/>
       <c r="N7" s="962"/>
     </row>
     <row r="8" spans="1:40" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -21515,15 +21527,15 @@
       <c r="B9" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="1366">
+      <c r="C9" s="1367">
         <f>+formato!L2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="1366"/>
-      <c r="E9" s="1366"/>
-      <c r="F9" s="1366"/>
-      <c r="G9" s="1366"/>
-      <c r="H9" s="1366"/>
+      <c r="D9" s="1367"/>
+      <c r="E9" s="1367"/>
+      <c r="F9" s="1367"/>
+      <c r="G9" s="1367"/>
+      <c r="H9" s="1367"/>
       <c r="I9" s="963"/>
       <c r="J9" s="329" t="s">
         <v>3</v>
@@ -21558,15 +21570,15 @@
       <c r="B10" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1366">
+      <c r="C10" s="1367">
         <f>+formato!L3</f>
         <v>0</v>
       </c>
-      <c r="D10" s="1366"/>
-      <c r="E10" s="1366"/>
-      <c r="F10" s="1366"/>
-      <c r="G10" s="1366"/>
-      <c r="H10" s="1366"/>
+      <c r="D10" s="1367"/>
+      <c r="E10" s="1367"/>
+      <c r="F10" s="1367"/>
+      <c r="G10" s="1367"/>
+      <c r="H10" s="1367"/>
       <c r="I10" s="964"/>
       <c r="J10" s="329" t="s">
         <v>533</v>
@@ -21602,15 +21614,15 @@
       <c r="B11" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1366">
+      <c r="C11" s="1367">
         <f>+formato!L4</f>
         <v>0</v>
       </c>
-      <c r="D11" s="1366"/>
-      <c r="E11" s="1366"/>
-      <c r="F11" s="1366"/>
-      <c r="G11" s="1366"/>
-      <c r="H11" s="1366"/>
+      <c r="D11" s="1367"/>
+      <c r="E11" s="1367"/>
+      <c r="F11" s="1367"/>
+      <c r="G11" s="1367"/>
+      <c r="H11" s="1367"/>
       <c r="I11" s="964"/>
       <c r="J11" s="329" t="s">
         <v>641</v>
@@ -21646,15 +21658,15 @@
       <c r="B12" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1366">
+      <c r="C12" s="1367">
         <f>+formato!L5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="1366"/>
-      <c r="E12" s="1366"/>
-      <c r="F12" s="1366"/>
-      <c r="G12" s="1366"/>
-      <c r="H12" s="1366"/>
+      <c r="D12" s="1367"/>
+      <c r="E12" s="1367"/>
+      <c r="F12" s="1367"/>
+      <c r="G12" s="1367"/>
+      <c r="H12" s="1367"/>
       <c r="I12" s="1274"/>
       <c r="J12" s="329" t="s">
         <v>8</v>
@@ -21716,20 +21728,20 @@
       <c r="AN13" s="722"/>
     </row>
     <row r="14" spans="1:40" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1357" t="s">
+      <c r="A14" s="1358" t="s">
         <v>571</v>
       </c>
-      <c r="B14" s="1358"/>
-      <c r="C14" s="1358"/>
-      <c r="D14" s="1358"/>
-      <c r="E14" s="1358"/>
-      <c r="F14" s="1358"/>
-      <c r="G14" s="1358"/>
-      <c r="H14" s="1358"/>
-      <c r="I14" s="1358"/>
-      <c r="J14" s="1358"/>
-      <c r="K14" s="1358"/>
-      <c r="L14" s="1359"/>
+      <c r="B14" s="1359"/>
+      <c r="C14" s="1359"/>
+      <c r="D14" s="1359"/>
+      <c r="E14" s="1359"/>
+      <c r="F14" s="1359"/>
+      <c r="G14" s="1359"/>
+      <c r="H14" s="1359"/>
+      <c r="I14" s="1359"/>
+      <c r="J14" s="1359"/>
+      <c r="K14" s="1359"/>
+      <c r="L14" s="1360"/>
       <c r="M14" s="1101"/>
       <c r="Z14" s="720"/>
       <c r="AA14" s="719"/>
@@ -21748,20 +21760,20 @@
       <c r="AN14" s="722"/>
     </row>
     <row r="15" spans="1:40" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1360" t="s">
+      <c r="A15" s="1361" t="s">
         <v>531</v>
       </c>
-      <c r="B15" s="1361"/>
-      <c r="C15" s="1361"/>
-      <c r="D15" s="1361"/>
-      <c r="E15" s="1361"/>
-      <c r="F15" s="1361"/>
-      <c r="G15" s="1361"/>
-      <c r="H15" s="1361"/>
-      <c r="I15" s="1361"/>
-      <c r="J15" s="1361"/>
-      <c r="K15" s="1361"/>
-      <c r="L15" s="1362"/>
+      <c r="B15" s="1362"/>
+      <c r="C15" s="1362"/>
+      <c r="D15" s="1362"/>
+      <c r="E15" s="1362"/>
+      <c r="F15" s="1362"/>
+      <c r="G15" s="1362"/>
+      <c r="H15" s="1362"/>
+      <c r="I15" s="1362"/>
+      <c r="J15" s="1362"/>
+      <c r="K15" s="1362"/>
+      <c r="L15" s="1363"/>
       <c r="M15" s="1101"/>
       <c r="N15" s="1101"/>
       <c r="Z15" s="720"/>
@@ -21812,20 +21824,20 @@
       <c r="AN16" s="722"/>
     </row>
     <row r="17" spans="1:40" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1363" t="s">
+      <c r="A17" s="1364" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1364"/>
-      <c r="C17" s="1364"/>
-      <c r="D17" s="1364"/>
-      <c r="E17" s="1364"/>
-      <c r="F17" s="1364"/>
-      <c r="G17" s="1364"/>
-      <c r="H17" s="1364"/>
-      <c r="I17" s="1364"/>
-      <c r="J17" s="1364"/>
-      <c r="K17" s="1364"/>
-      <c r="L17" s="1365"/>
+      <c r="B17" s="1365"/>
+      <c r="C17" s="1365"/>
+      <c r="D17" s="1365"/>
+      <c r="E17" s="1365"/>
+      <c r="F17" s="1365"/>
+      <c r="G17" s="1365"/>
+      <c r="H17" s="1365"/>
+      <c r="I17" s="1365"/>
+      <c r="J17" s="1365"/>
+      <c r="K17" s="1365"/>
+      <c r="L17" s="1366"/>
       <c r="N17" s="1101"/>
       <c r="Z17" s="475"/>
       <c r="AI17" s="475"/>
@@ -22173,10 +22185,10 @@
       <c r="J26" s="330"/>
       <c r="K26" s="478"/>
       <c r="L26" s="972"/>
-      <c r="N26" s="1368" t="s">
+      <c r="N26" s="1332" t="s">
         <v>49</v>
       </c>
-      <c r="O26" s="1369"/>
+      <c r="O26" s="1333"/>
       <c r="Y26" s="1103"/>
       <c r="Z26" s="475"/>
       <c r="AA26" s="1103"/>
@@ -22441,11 +22453,11 @@
       <c r="D32" s="1125"/>
       <c r="E32" s="1125"/>
       <c r="F32" s="1126"/>
-      <c r="G32" s="1387">
+      <c r="G32" s="1354">
         <f>DATOS!F41</f>
         <v>0</v>
       </c>
-      <c r="H32" s="1387"/>
+      <c r="H32" s="1354"/>
       <c r="I32" s="991"/>
       <c r="J32" s="330"/>
       <c r="K32" s="478"/>
@@ -22537,13 +22549,13 @@
       <c r="AN34" s="722"/>
     </row>
     <row r="35" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1341" t="s">
+      <c r="A35" s="1350" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="1341"/>
-      <c r="C35" s="1341"/>
-      <c r="D35" s="1341"/>
-      <c r="E35" s="1341"/>
+      <c r="B35" s="1350"/>
+      <c r="C35" s="1350"/>
+      <c r="D35" s="1350"/>
+      <c r="E35" s="1350"/>
       <c r="F35" s="1082">
         <v>1</v>
       </c>
@@ -22556,9 +22568,9 @@
       <c r="I35" s="1082">
         <v>4</v>
       </c>
-      <c r="J35" s="1354"/>
-      <c r="K35" s="1354"/>
-      <c r="L35" s="1354"/>
+      <c r="J35" s="1355"/>
+      <c r="K35" s="1355"/>
+      <c r="L35" s="1355"/>
       <c r="M35" s="1101"/>
       <c r="N35" s="994"/>
       <c r="Y35" s="475"/>
@@ -22579,13 +22591,13 @@
       <c r="AN35" s="722"/>
     </row>
     <row r="36" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1341" t="s">
+      <c r="A36" s="1350" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="1341"/>
-      <c r="C36" s="1341"/>
-      <c r="D36" s="1341"/>
-      <c r="E36" s="1341"/>
+      <c r="B36" s="1350"/>
+      <c r="C36" s="1350"/>
+      <c r="D36" s="1350"/>
+      <c r="E36" s="1350"/>
       <c r="F36" s="1083">
         <f>+DATOS!F15</f>
         <v>5</v>
@@ -22602,9 +22614,9 @@
         <f>+DATOS!L15</f>
         <v>5</v>
       </c>
-      <c r="J36" s="1354"/>
-      <c r="K36" s="1354"/>
-      <c r="L36" s="1354"/>
+      <c r="J36" s="1355"/>
+      <c r="K36" s="1355"/>
+      <c r="L36" s="1355"/>
       <c r="M36" s="1101"/>
       <c r="N36" s="995"/>
       <c r="Y36" s="475"/>
@@ -22625,13 +22637,13 @@
       <c r="AN36" s="722"/>
     </row>
     <row r="37" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1341" t="s">
+      <c r="A37" s="1350" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="1341"/>
-      <c r="C37" s="1341"/>
-      <c r="D37" s="1341"/>
-      <c r="E37" s="1341"/>
+      <c r="B37" s="1350"/>
+      <c r="C37" s="1350"/>
+      <c r="D37" s="1350"/>
+      <c r="E37" s="1350"/>
       <c r="F37" s="1083">
         <f>+DATOS!F16</f>
         <v>0</v>
@@ -22648,9 +22660,9 @@
         <f>+DATOS!L16</f>
         <v>0</v>
       </c>
-      <c r="J37" s="1354"/>
-      <c r="K37" s="1354"/>
-      <c r="L37" s="1354"/>
+      <c r="J37" s="1355"/>
+      <c r="K37" s="1355"/>
+      <c r="L37" s="1355"/>
       <c r="M37" s="1106"/>
       <c r="N37" s="995"/>
       <c r="Y37" s="475"/>
@@ -22671,13 +22683,13 @@
       <c r="AN37" s="722"/>
     </row>
     <row r="38" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1341" t="s">
+      <c r="A38" s="1350" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="1341"/>
-      <c r="C38" s="1341"/>
-      <c r="D38" s="1341"/>
-      <c r="E38" s="1341"/>
+      <c r="B38" s="1350"/>
+      <c r="C38" s="1350"/>
+      <c r="D38" s="1350"/>
+      <c r="E38" s="1350"/>
       <c r="F38" s="1085" t="e">
         <f>+DATOS!F21</f>
         <v>#DIV/0!</v>
@@ -22694,9 +22706,9 @@
         <f>+DATOS!L21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J38" s="1354"/>
-      <c r="K38" s="1354"/>
-      <c r="L38" s="1354"/>
+      <c r="J38" s="1355"/>
+      <c r="K38" s="1355"/>
+      <c r="L38" s="1355"/>
       <c r="M38" s="1101"/>
       <c r="N38" s="1101"/>
       <c r="V38" s="718"/>
@@ -22756,13 +22768,13 @@
       <c r="AN39" s="722"/>
     </row>
     <row r="40" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1341" t="s">
+      <c r="A40" s="1350" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="1341"/>
-      <c r="C40" s="1341"/>
-      <c r="D40" s="1341"/>
-      <c r="E40" s="1341"/>
+      <c r="B40" s="1350"/>
+      <c r="C40" s="1350"/>
+      <c r="D40" s="1350"/>
+      <c r="E40" s="1350"/>
       <c r="F40" s="1088" t="e">
         <f>+DATOS!F31</f>
         <v>#DIV/0!</v>
@@ -22779,9 +22791,9 @@
         <f>+DATOS!L31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="1384"/>
-      <c r="K40" s="1385"/>
-      <c r="L40" s="1386"/>
+      <c r="J40" s="1351"/>
+      <c r="K40" s="1352"/>
+      <c r="L40" s="1353"/>
       <c r="M40" s="1107"/>
       <c r="N40" s="1101"/>
       <c r="Q40" s="1108"/>
@@ -22806,13 +22818,13 @@
       <c r="AN40" s="722"/>
     </row>
     <row r="41" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1341" t="s">
+      <c r="A41" s="1350" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="1341"/>
-      <c r="C41" s="1341"/>
-      <c r="D41" s="1341"/>
-      <c r="E41" s="1341"/>
+      <c r="B41" s="1350"/>
+      <c r="C41" s="1350"/>
+      <c r="D41" s="1350"/>
+      <c r="E41" s="1350"/>
       <c r="F41" s="1085" t="e">
         <f>+DATOS!F32</f>
         <v>#DIV/0!</v>
@@ -22829,9 +22841,9 @@
         <f>+DATOS!L32</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="1384"/>
-      <c r="K41" s="1385"/>
-      <c r="L41" s="1386"/>
+      <c r="J41" s="1351"/>
+      <c r="K41" s="1352"/>
+      <c r="L41" s="1353"/>
       <c r="M41" s="1109"/>
       <c r="N41" s="1101"/>
       <c r="V41" s="718"/>
@@ -22878,9 +22890,9 @@
         <f>+DATOS!L33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J42" s="1384"/>
-      <c r="K42" s="1385"/>
-      <c r="L42" s="1386"/>
+      <c r="J42" s="1351"/>
+      <c r="K42" s="1352"/>
+      <c r="L42" s="1353"/>
       <c r="M42" s="1109"/>
       <c r="N42" s="1101"/>
       <c r="V42" s="718"/>
@@ -22948,16 +22960,16 @@
       <c r="G44" s="480"/>
       <c r="H44" s="407"/>
       <c r="I44" s="997"/>
-      <c r="J44" s="1342" t="s">
+      <c r="J44" s="1368" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="1343"/>
-      <c r="L44" s="1344"/>
+      <c r="K44" s="1369"/>
+      <c r="L44" s="1370"/>
       <c r="M44" s="1101"/>
-      <c r="N44" s="1370" t="s">
+      <c r="N44" s="1334" t="s">
         <v>38</v>
       </c>
-      <c r="O44" s="1370"/>
+      <c r="O44" s="1334"/>
       <c r="V44" s="718"/>
       <c r="W44" s="475"/>
       <c r="X44" s="475"/>
@@ -22988,12 +23000,12 @@
       <c r="G45" s="480"/>
       <c r="H45" s="407"/>
       <c r="I45" s="997"/>
-      <c r="J45" s="1345" t="e">
+      <c r="J45" s="1371" t="e">
         <f>+DATOS!C50</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K45" s="1346"/>
-      <c r="L45" s="1347"/>
+      <c r="K45" s="1372"/>
+      <c r="L45" s="1373"/>
       <c r="M45" s="1101"/>
       <c r="N45" s="680">
         <v>0</v>
@@ -23032,11 +23044,11 @@
       <c r="G46" s="480"/>
       <c r="H46" s="407"/>
       <c r="I46" s="997"/>
-      <c r="J46" s="1371" t="s">
+      <c r="J46" s="1335" t="s">
         <v>36</v>
       </c>
-      <c r="K46" s="1372"/>
-      <c r="L46" s="1373"/>
+      <c r="K46" s="1336"/>
+      <c r="L46" s="1337"/>
       <c r="M46" s="1101"/>
       <c r="N46" s="680" t="e">
         <f>+DATOS!J75</f>
@@ -23076,12 +23088,12 @@
       <c r="G47" s="480"/>
       <c r="H47" s="480"/>
       <c r="I47" s="997"/>
-      <c r="J47" s="1374" t="e">
+      <c r="J47" s="1338" t="e">
         <f>MROUND(N52,0.02)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K47" s="1375"/>
-      <c r="L47" s="1376"/>
+      <c r="K47" s="1339"/>
+      <c r="L47" s="1340"/>
       <c r="M47" s="1101" t="s">
         <v>569</v>
       </c>
@@ -23122,11 +23134,11 @@
       <c r="G48" s="480"/>
       <c r="H48" s="480"/>
       <c r="I48" s="997"/>
-      <c r="J48" s="1348" t="s">
+      <c r="J48" s="1374" t="s">
         <v>37</v>
       </c>
-      <c r="K48" s="1349"/>
-      <c r="L48" s="1350"/>
+      <c r="K48" s="1375"/>
+      <c r="L48" s="1376"/>
       <c r="M48" s="1101"/>
       <c r="N48" s="728"/>
       <c r="O48" s="728"/>
@@ -23161,14 +23173,14 @@
       <c r="G49" s="480"/>
       <c r="H49" s="480"/>
       <c r="I49" s="997"/>
-      <c r="J49" s="1351"/>
-      <c r="K49" s="1352"/>
-      <c r="L49" s="1353"/>
+      <c r="J49" s="1377"/>
+      <c r="K49" s="1378"/>
+      <c r="L49" s="1379"/>
       <c r="M49" s="1101"/>
-      <c r="N49" s="1370" t="s">
+      <c r="N49" s="1334" t="s">
         <v>566</v>
       </c>
-      <c r="O49" s="1370"/>
+      <c r="O49" s="1334"/>
       <c r="S49" s="348"/>
       <c r="V49" s="718"/>
       <c r="W49" s="475"/>
@@ -23200,12 +23212,12 @@
       <c r="G50" s="480"/>
       <c r="H50" s="480"/>
       <c r="I50" s="997"/>
-      <c r="J50" s="1377" t="e">
+      <c r="J50" s="1342" t="e">
         <f>+DATOS!J74</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K50" s="1378"/>
-      <c r="L50" s="1379"/>
+      <c r="K50" s="1343"/>
+      <c r="L50" s="1344"/>
       <c r="M50" s="1107"/>
       <c r="N50" s="987">
         <v>0</v>
@@ -23244,9 +23256,9 @@
       <c r="G51" s="480"/>
       <c r="H51" s="480"/>
       <c r="I51" s="997"/>
-      <c r="J51" s="1380"/>
-      <c r="K51" s="1381"/>
-      <c r="L51" s="1382"/>
+      <c r="J51" s="1345"/>
+      <c r="K51" s="1346"/>
+      <c r="L51" s="1347"/>
       <c r="M51" s="1101"/>
       <c r="N51" s="680" t="e">
         <f>+N46*9.8066</f>
@@ -23543,9 +23555,9 @@
       <c r="G60" s="480"/>
       <c r="H60" s="480"/>
       <c r="I60" s="997"/>
-      <c r="J60" s="1334"/>
-      <c r="K60" s="1334"/>
-      <c r="L60" s="1334"/>
+      <c r="J60" s="1341"/>
+      <c r="K60" s="1341"/>
+      <c r="L60" s="1341"/>
       <c r="M60" s="1101"/>
       <c r="Q60" s="1000"/>
       <c r="R60" s="1000"/>
@@ -23581,9 +23593,9 @@
       <c r="G61" s="480"/>
       <c r="H61" s="480"/>
       <c r="I61" s="997"/>
-      <c r="J61" s="1333"/>
-      <c r="K61" s="1333"/>
-      <c r="L61" s="1333"/>
+      <c r="J61" s="1381"/>
+      <c r="K61" s="1381"/>
+      <c r="L61" s="1381"/>
       <c r="M61" s="1101"/>
       <c r="Q61" s="1001"/>
       <c r="R61" s="1001"/>
@@ -23609,7 +23621,7 @@
     </row>
     <row r="62" spans="1:40" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="316" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B62" s="1112"/>
       <c r="C62" s="1112"/>
@@ -23619,9 +23631,9 @@
       <c r="G62" s="480"/>
       <c r="H62" s="480"/>
       <c r="I62" s="997"/>
-      <c r="J62" s="1334"/>
-      <c r="K62" s="1334"/>
-      <c r="L62" s="1334"/>
+      <c r="J62" s="1341"/>
+      <c r="K62" s="1341"/>
+      <c r="L62" s="1341"/>
       <c r="M62" s="1101"/>
       <c r="P62" s="1000"/>
       <c r="Q62" s="1000"/>
@@ -23648,7 +23660,7 @@
     </row>
     <row r="63" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="316"/>
-      <c r="C63" s="316"/>
+      <c r="C63" s="1594"/>
       <c r="D63" s="997"/>
       <c r="E63" s="997"/>
       <c r="F63" s="997"/>
@@ -23763,11 +23775,11 @@
       <c r="C66" s="1114"/>
       <c r="D66" s="478"/>
       <c r="E66" s="478"/>
-      <c r="F66" s="1335">
+      <c r="F66" s="1382">
         <f>+formato!C36</f>
         <v>0</v>
       </c>
-      <c r="G66" s="1335"/>
+      <c r="G66" s="1382"/>
       <c r="H66" s="478"/>
       <c r="I66" s="378"/>
       <c r="J66" s="478"/>
@@ -23801,11 +23813,11 @@
       <c r="C67" s="1114"/>
       <c r="D67" s="478"/>
       <c r="E67" s="478"/>
-      <c r="F67" s="1336">
+      <c r="F67" s="1383">
         <f>+formato!C37</f>
         <v>0</v>
       </c>
-      <c r="G67" s="1336"/>
+      <c r="G67" s="1383"/>
       <c r="H67" s="478"/>
       <c r="I67" s="378"/>
       <c r="J67" s="1115"/>
@@ -23839,11 +23851,11 @@
       <c r="C68" s="1114"/>
       <c r="D68" s="478"/>
       <c r="E68" s="478"/>
-      <c r="F68" s="1335">
+      <c r="F68" s="1382">
         <f>+formato!C38</f>
         <v>0</v>
       </c>
-      <c r="G68" s="1335"/>
+      <c r="G68" s="1382"/>
       <c r="H68" s="478"/>
       <c r="I68" s="1116"/>
       <c r="J68" s="1115"/>
@@ -24060,11 +24072,11 @@
       <c r="G74" s="1014" t="s">
         <v>67</v>
       </c>
-      <c r="H74" s="1337">
+      <c r="H74" s="1384">
         <f>DATOS!F37</f>
         <v>0</v>
       </c>
-      <c r="I74" s="1338"/>
+      <c r="I74" s="1385"/>
       <c r="J74" s="1115"/>
       <c r="K74" s="478"/>
       <c r="L74" s="478"/>
@@ -24105,11 +24117,11 @@
       <c r="G75" s="1014" t="s">
         <v>67</v>
       </c>
-      <c r="H75" s="1339">
+      <c r="H75" s="1386">
         <f>DATOS!F38</f>
         <v>0</v>
       </c>
-      <c r="I75" s="1340"/>
+      <c r="I75" s="1387"/>
       <c r="J75" s="1115"/>
       <c r="K75" s="478"/>
       <c r="L75" s="478"/>
@@ -24174,18 +24186,18 @@
       <c r="AN76" s="722"/>
     </row>
     <row r="77" spans="1:40" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1332"/>
-      <c r="B77" s="1332"/>
-      <c r="C77" s="1332"/>
-      <c r="D77" s="1332"/>
-      <c r="E77" s="1332"/>
-      <c r="F77" s="1332"/>
-      <c r="G77" s="1332"/>
-      <c r="H77" s="1332"/>
-      <c r="I77" s="1332"/>
-      <c r="J77" s="1332"/>
-      <c r="K77" s="1332"/>
-      <c r="L77" s="1332"/>
+      <c r="A77" s="1349"/>
+      <c r="B77" s="1349"/>
+      <c r="C77" s="1349"/>
+      <c r="D77" s="1349"/>
+      <c r="E77" s="1349"/>
+      <c r="F77" s="1349"/>
+      <c r="G77" s="1349"/>
+      <c r="H77" s="1349"/>
+      <c r="I77" s="1349"/>
+      <c r="J77" s="1349"/>
+      <c r="K77" s="1349"/>
+      <c r="L77" s="1349"/>
       <c r="V77" s="718"/>
       <c r="W77" s="475"/>
       <c r="X77" s="475"/>
@@ -24244,20 +24256,20 @@
       <c r="AN78" s="722"/>
     </row>
     <row r="79" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1331" t="s">
+      <c r="A79" s="1380" t="s">
         <v>662</v>
       </c>
-      <c r="B79" s="1331"/>
-      <c r="C79" s="1331"/>
-      <c r="D79" s="1331"/>
-      <c r="E79" s="1331"/>
-      <c r="F79" s="1331"/>
-      <c r="G79" s="1331"/>
-      <c r="H79" s="1331"/>
-      <c r="I79" s="1331"/>
-      <c r="J79" s="1331"/>
-      <c r="K79" s="1331"/>
-      <c r="L79" s="1331"/>
+      <c r="B79" s="1380"/>
+      <c r="C79" s="1380"/>
+      <c r="D79" s="1380"/>
+      <c r="E79" s="1380"/>
+      <c r="F79" s="1380"/>
+      <c r="G79" s="1380"/>
+      <c r="H79" s="1380"/>
+      <c r="I79" s="1380"/>
+      <c r="J79" s="1380"/>
+      <c r="K79" s="1380"/>
+      <c r="L79" s="1380"/>
       <c r="M79" s="1016"/>
       <c r="N79" s="1016"/>
       <c r="V79" s="718"/>
@@ -24281,20 +24293,20 @@
       <c r="AN79" s="722"/>
     </row>
     <row r="80" spans="1:40" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1332" t="s">
+      <c r="A80" s="1349" t="s">
         <v>663</v>
       </c>
-      <c r="B80" s="1332"/>
-      <c r="C80" s="1332"/>
-      <c r="D80" s="1332"/>
-      <c r="E80" s="1332"/>
-      <c r="F80" s="1332"/>
-      <c r="G80" s="1332"/>
-      <c r="H80" s="1332"/>
-      <c r="I80" s="1332"/>
-      <c r="J80" s="1332"/>
-      <c r="K80" s="1332"/>
-      <c r="L80" s="1332"/>
+      <c r="B80" s="1349"/>
+      <c r="C80" s="1349"/>
+      <c r="D80" s="1349"/>
+      <c r="E80" s="1349"/>
+      <c r="F80" s="1349"/>
+      <c r="G80" s="1349"/>
+      <c r="H80" s="1349"/>
+      <c r="I80" s="1349"/>
+      <c r="J80" s="1349"/>
+      <c r="K80" s="1349"/>
+      <c r="L80" s="1349"/>
       <c r="M80" s="1119"/>
       <c r="N80" s="1119"/>
       <c r="V80" s="718"/>
@@ -24318,20 +24330,20 @@
       <c r="AN80" s="722"/>
     </row>
     <row r="81" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1332" t="s">
+      <c r="A81" s="1349" t="s">
         <v>664</v>
       </c>
-      <c r="B81" s="1332"/>
-      <c r="C81" s="1332"/>
-      <c r="D81" s="1332"/>
-      <c r="E81" s="1332"/>
-      <c r="F81" s="1332"/>
-      <c r="G81" s="1332"/>
-      <c r="H81" s="1332"/>
-      <c r="I81" s="1332"/>
-      <c r="J81" s="1332"/>
-      <c r="K81" s="1332"/>
-      <c r="L81" s="1332"/>
+      <c r="B81" s="1349"/>
+      <c r="C81" s="1349"/>
+      <c r="D81" s="1349"/>
+      <c r="E81" s="1349"/>
+      <c r="F81" s="1349"/>
+      <c r="G81" s="1349"/>
+      <c r="H81" s="1349"/>
+      <c r="I81" s="1349"/>
+      <c r="J81" s="1349"/>
+      <c r="K81" s="1349"/>
+      <c r="L81" s="1349"/>
       <c r="M81" s="1017"/>
       <c r="N81" s="1017"/>
       <c r="V81" s="718"/>
@@ -24355,20 +24367,20 @@
       <c r="AN81" s="722"/>
     </row>
     <row r="82" spans="1:40" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1332" t="s">
+      <c r="A82" s="1349" t="s">
         <v>665</v>
       </c>
-      <c r="B82" s="1332"/>
-      <c r="C82" s="1332"/>
-      <c r="D82" s="1332"/>
-      <c r="E82" s="1332"/>
-      <c r="F82" s="1332"/>
-      <c r="G82" s="1332"/>
-      <c r="H82" s="1332"/>
-      <c r="I82" s="1332"/>
-      <c r="J82" s="1332"/>
-      <c r="K82" s="1332"/>
-      <c r="L82" s="1332"/>
+      <c r="B82" s="1349"/>
+      <c r="C82" s="1349"/>
+      <c r="D82" s="1349"/>
+      <c r="E82" s="1349"/>
+      <c r="F82" s="1349"/>
+      <c r="G82" s="1349"/>
+      <c r="H82" s="1349"/>
+      <c r="I82" s="1349"/>
+      <c r="J82" s="1349"/>
+      <c r="K82" s="1349"/>
+      <c r="L82" s="1349"/>
       <c r="M82" s="1119"/>
       <c r="N82" s="1119"/>
       <c r="V82" s="718"/>
@@ -24392,20 +24404,20 @@
       <c r="AN82" s="722"/>
     </row>
     <row r="83" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1383" t="s">
+      <c r="A83" s="1348" t="s">
         <v>666</v>
       </c>
-      <c r="B83" s="1383"/>
-      <c r="C83" s="1383"/>
-      <c r="D83" s="1383"/>
-      <c r="E83" s="1383"/>
-      <c r="F83" s="1383"/>
-      <c r="G83" s="1383"/>
-      <c r="H83" s="1383"/>
-      <c r="I83" s="1383"/>
-      <c r="J83" s="1383"/>
-      <c r="K83" s="1383"/>
-      <c r="L83" s="1383"/>
+      <c r="B83" s="1348"/>
+      <c r="C83" s="1348"/>
+      <c r="D83" s="1348"/>
+      <c r="E83" s="1348"/>
+      <c r="F83" s="1348"/>
+      <c r="G83" s="1348"/>
+      <c r="H83" s="1348"/>
+      <c r="I83" s="1348"/>
+      <c r="J83" s="1348"/>
+      <c r="K83" s="1348"/>
+      <c r="L83" s="1348"/>
       <c r="M83" s="1119"/>
       <c r="N83" s="1119"/>
       <c r="V83" s="718"/>
@@ -24501,18 +24513,18 @@
       <c r="AN85" s="722"/>
     </row>
     <row r="86" spans="1:40" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1367"/>
-      <c r="B86" s="1367"/>
-      <c r="C86" s="1367"/>
-      <c r="D86" s="1367"/>
-      <c r="E86" s="1367"/>
-      <c r="F86" s="1367"/>
-      <c r="G86" s="1367"/>
-      <c r="H86" s="1367"/>
-      <c r="I86" s="1367"/>
-      <c r="J86" s="1367"/>
-      <c r="K86" s="1367"/>
-      <c r="L86" s="1367"/>
+      <c r="A86" s="1331"/>
+      <c r="B86" s="1331"/>
+      <c r="C86" s="1331"/>
+      <c r="D86" s="1331"/>
+      <c r="E86" s="1331"/>
+      <c r="F86" s="1331"/>
+      <c r="G86" s="1331"/>
+      <c r="H86" s="1331"/>
+      <c r="I86" s="1331"/>
+      <c r="J86" s="1331"/>
+      <c r="K86" s="1331"/>
+      <c r="L86" s="1331"/>
       <c r="M86" s="1119"/>
       <c r="N86" s="1119"/>
       <c r="V86" s="718"/>
@@ -25799,13 +25811,44 @@
       <c r="AN136" s="722"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="X/g6Cm4x4y6xz9jCv0hhpkI4fERbEEet7b1kpbvazAjSBlgZslha+yMR47qdxWpzMsec/YBXGhRuEzTmQ57kDQ==" saltValue="kulnhHLT4XMBznIjhXCNew==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="E16" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E11:E13" name="Rango3_3_1_1_1_1_1_1_1_1_2"/>
     <protectedRange sqref="E9:E10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="47">
+    <mergeCell ref="A79:L79"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A82:L82"/>
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J48:L49"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="A86:L86"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="N44:O44"/>
@@ -25822,37 +25865,6 @@
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="J40:L40"/>
     <mergeCell ref="J38:L38"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J48:L49"/>
-    <mergeCell ref="A79:L79"/>
-    <mergeCell ref="A80:L80"/>
-    <mergeCell ref="A82:L82"/>
-    <mergeCell ref="A81:L81"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.70866141732283472" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -25895,40 +25907,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1394" t="s">
+      <c r="B2" s="1406" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1395"/>
-      <c r="D2" s="1395"/>
-      <c r="E2" s="1395"/>
-      <c r="F2" s="1395"/>
-      <c r="G2" s="1395"/>
-      <c r="H2" s="1395"/>
-      <c r="I2" s="1395"/>
-      <c r="J2" s="1395"/>
-      <c r="K2" s="1395"/>
-      <c r="L2" s="1395"/>
-      <c r="M2" s="1395"/>
-      <c r="N2" s="1395"/>
-      <c r="O2" s="1396"/>
+      <c r="C2" s="1407"/>
+      <c r="D2" s="1407"/>
+      <c r="E2" s="1407"/>
+      <c r="F2" s="1407"/>
+      <c r="G2" s="1407"/>
+      <c r="H2" s="1407"/>
+      <c r="I2" s="1407"/>
+      <c r="J2" s="1407"/>
+      <c r="K2" s="1407"/>
+      <c r="L2" s="1407"/>
+      <c r="M2" s="1407"/>
+      <c r="N2" s="1407"/>
+      <c r="O2" s="1408"/>
     </row>
     <row r="3" spans="2:19" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1397" t="s">
+      <c r="B3" s="1409" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1398"/>
-      <c r="D3" s="1398"/>
-      <c r="E3" s="1398"/>
-      <c r="F3" s="1398"/>
-      <c r="G3" s="1398"/>
-      <c r="H3" s="1398"/>
-      <c r="I3" s="1398"/>
-      <c r="J3" s="1398"/>
-      <c r="K3" s="1398"/>
-      <c r="L3" s="1398"/>
-      <c r="M3" s="1398"/>
-      <c r="N3" s="1398"/>
-      <c r="O3" s="1399"/>
+      <c r="C3" s="1410"/>
+      <c r="D3" s="1410"/>
+      <c r="E3" s="1410"/>
+      <c r="F3" s="1410"/>
+      <c r="G3" s="1410"/>
+      <c r="H3" s="1410"/>
+      <c r="I3" s="1410"/>
+      <c r="J3" s="1410"/>
+      <c r="K3" s="1410"/>
+      <c r="L3" s="1410"/>
+      <c r="M3" s="1410"/>
+      <c r="N3" s="1410"/>
+      <c r="O3" s="1411"/>
     </row>
     <row r="5" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="682" t="s">
@@ -26118,31 +26130,31 @@
       <c r="N11" s="494"/>
     </row>
     <row r="12" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1388" t="s">
+      <c r="B12" s="1402" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="1388"/>
-      <c r="D12" s="1388"/>
-      <c r="E12" s="1388">
+      <c r="C12" s="1402"/>
+      <c r="D12" s="1402"/>
+      <c r="E12" s="1402">
         <v>1</v>
       </c>
-      <c r="F12" s="1388"/>
-      <c r="G12" s="1388">
+      <c r="F12" s="1402"/>
+      <c r="G12" s="1402">
         <v>2</v>
       </c>
-      <c r="H12" s="1388"/>
-      <c r="I12" s="1388">
+      <c r="H12" s="1402"/>
+      <c r="I12" s="1402">
         <v>3</v>
       </c>
-      <c r="J12" s="1388"/>
-      <c r="K12" s="1388">
+      <c r="J12" s="1402"/>
+      <c r="K12" s="1402">
         <v>4</v>
       </c>
-      <c r="L12" s="1388"/>
-      <c r="M12" s="1388">
+      <c r="L12" s="1402"/>
+      <c r="M12" s="1402">
         <v>5</v>
       </c>
-      <c r="N12" s="1388"/>
+      <c r="N12" s="1402"/>
       <c r="Q12" s="1138" t="s">
         <v>579</v>
       </c>
@@ -26154,9 +26166,9 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1388"/>
-      <c r="C13" s="1388"/>
-      <c r="D13" s="1388"/>
+      <c r="B13" s="1402"/>
+      <c r="C13" s="1402"/>
+      <c r="D13" s="1402"/>
       <c r="E13" s="730" t="s">
         <v>84</v>
       </c>
@@ -26198,11 +26210,11 @@
       </c>
     </row>
     <row r="14" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1400" t="s">
+      <c r="B14" s="1396" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1400"/>
-      <c r="D14" s="1401"/>
+      <c r="C14" s="1396"/>
+      <c r="D14" s="1397"/>
       <c r="E14" s="1255">
         <v>1</v>
       </c>
@@ -26228,11 +26240,11 @@
       </c>
     </row>
     <row r="15" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1389" t="s">
+      <c r="B15" s="1391" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="1389"/>
-      <c r="D15" s="1390"/>
+      <c r="C15" s="1391"/>
+      <c r="D15" s="1392"/>
       <c r="E15" s="1139">
         <v>5</v>
       </c>
@@ -26277,11 +26289,11 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1389" t="s">
+      <c r="B16" s="1391" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="1389"/>
-      <c r="D16" s="1390"/>
+      <c r="C16" s="1391"/>
+      <c r="D16" s="1392"/>
       <c r="E16" s="1139">
         <f>+formato!D17</f>
         <v>0</v>
@@ -26327,11 +26339,11 @@
       </c>
     </row>
     <row r="17" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="1389" t="s">
+      <c r="B17" s="1391" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="1389"/>
-      <c r="D17" s="1390"/>
+      <c r="C17" s="1391"/>
+      <c r="D17" s="1392"/>
       <c r="E17" s="1139">
         <f>+formato!D18</f>
         <v>0</v>
@@ -26377,11 +26389,11 @@
       </c>
     </row>
     <row r="18" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1389" t="s">
+      <c r="B18" s="1391" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="1389"/>
-      <c r="D18" s="1390"/>
+      <c r="C18" s="1391"/>
+      <c r="D18" s="1392"/>
       <c r="E18" s="1139">
         <f>+formato!D19</f>
         <v>0</v>
@@ -26418,11 +26430,11 @@
       <c r="N18" s="1145"/>
     </row>
     <row r="19" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="1390" t="s">
+      <c r="B19" s="1392" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1411"/>
-      <c r="D19" s="1411"/>
+      <c r="C19" s="1393"/>
+      <c r="D19" s="1393"/>
       <c r="E19" s="1142">
         <f t="shared" ref="E19:K19" si="0">+E17-E18</f>
         <v>0</v>
@@ -26459,11 +26471,11 @@
       <c r="N19" s="1145"/>
     </row>
     <row r="20" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="1389" t="s">
+      <c r="B20" s="1391" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="1389"/>
-      <c r="D20" s="1390"/>
+      <c r="C20" s="1391"/>
+      <c r="D20" s="1392"/>
       <c r="E20" s="1139">
         <f>+formato!D21</f>
         <v>0</v>
@@ -26513,11 +26525,11 @@
       <c r="U20" s="948"/>
     </row>
     <row r="21" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="1412" t="s">
+      <c r="B21" s="1394" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="1412"/>
-      <c r="D21" s="1413"/>
+      <c r="C21" s="1394"/>
+      <c r="D21" s="1395"/>
       <c r="E21" s="1142" t="e">
         <f t="shared" ref="E21:K21" si="1">+E19/E20</f>
         <v>#DIV/0!</v>
@@ -26598,11 +26610,11 @@
       <c r="U22" s="950"/>
     </row>
     <row r="23" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="1400" t="s">
+      <c r="B23" s="1396" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="1400"/>
-      <c r="D23" s="1401"/>
+      <c r="C23" s="1396"/>
+      <c r="D23" s="1397"/>
       <c r="E23" s="1139">
         <f>+formato!D24</f>
         <v>0</v>
@@ -26641,11 +26653,11 @@
       <c r="U23" s="953"/>
     </row>
     <row r="24" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="1389" t="s">
+      <c r="B24" s="1391" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="1389"/>
-      <c r="D24" s="1390"/>
+      <c r="C24" s="1391"/>
+      <c r="D24" s="1392"/>
       <c r="E24" s="1139">
         <f>+formato!D25</f>
         <v>0</v>
@@ -26701,11 +26713,11 @@
       </c>
     </row>
     <row r="25" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="1389" t="s">
+      <c r="B25" s="1391" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="1389"/>
-      <c r="D25" s="1390"/>
+      <c r="C25" s="1391"/>
+      <c r="D25" s="1392"/>
       <c r="E25" s="1139">
         <f>+formato!D26</f>
         <v>0</v>
@@ -26757,11 +26769,11 @@
       </c>
     </row>
     <row r="26" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="1389" t="s">
+      <c r="B26" s="1391" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="1389"/>
-      <c r="D26" s="1390"/>
+      <c r="C26" s="1391"/>
+      <c r="D26" s="1392"/>
       <c r="E26" s="1139">
         <f>+formato!D27</f>
         <v>0</v>
@@ -26817,11 +26829,11 @@
       </c>
     </row>
     <row r="27" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="1389" t="s">
+      <c r="B27" s="1391" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="1389"/>
-      <c r="D27" s="1390"/>
+      <c r="C27" s="1391"/>
+      <c r="D27" s="1392"/>
       <c r="E27" s="1139">
         <f>+formato!D28</f>
         <v>0</v>
@@ -26865,11 +26877,11 @@
       </c>
     </row>
     <row r="28" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="1389" t="s">
+      <c r="B28" s="1391" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="1389"/>
-      <c r="D28" s="1390"/>
+      <c r="C28" s="1391"/>
+      <c r="D28" s="1392"/>
       <c r="E28" s="1155">
         <f t="shared" ref="E28:L28" si="6">+E24-E27</f>
         <v>0</v>
@@ -26906,11 +26918,11 @@
       <c r="N28" s="1145"/>
     </row>
     <row r="29" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="1389" t="s">
+      <c r="B29" s="1391" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="1389"/>
-      <c r="D29" s="1390"/>
+      <c r="C29" s="1391"/>
+      <c r="D29" s="1392"/>
       <c r="E29" s="1139">
         <f>+formato!D30</f>
         <v>0</v>
@@ -26947,11 +26959,11 @@
       <c r="N29" s="1145"/>
     </row>
     <row r="30" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="1390" t="s">
+      <c r="B30" s="1392" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="1411"/>
-      <c r="D30" s="1411"/>
+      <c r="C30" s="1393"/>
+      <c r="D30" s="1393"/>
       <c r="E30" s="1142"/>
       <c r="F30" s="1142" t="e">
         <f t="shared" ref="F30:L30" si="7">+F27-F29</f>
@@ -26976,11 +26988,11 @@
       <c r="N30" s="1145"/>
     </row>
     <row r="31" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="1390" t="s">
+      <c r="B31" s="1392" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="1411"/>
-      <c r="D31" s="1411"/>
+      <c r="C31" s="1393"/>
+      <c r="D31" s="1393"/>
       <c r="E31" s="1142"/>
       <c r="F31" s="1142" t="e">
         <f t="shared" ref="F31:L31" si="8">+F28/F30*100</f>
@@ -27008,11 +27020,11 @@
       </c>
     </row>
     <row r="32" spans="2:21" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="1413" t="s">
+      <c r="B32" s="1395" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="1414"/>
-      <c r="D32" s="1414"/>
+      <c r="C32" s="1398"/>
+      <c r="D32" s="1398"/>
       <c r="E32" s="1142"/>
       <c r="F32" s="1142" t="e">
         <f t="shared" ref="F32:L32" si="9">+F21/(1+F31/100)</f>
@@ -27138,11 +27150,11 @@
       </c>
       <c r="D37" s="706"/>
       <c r="E37" s="707"/>
-      <c r="F37" s="1405">
+      <c r="F37" s="1399">
         <v>0</v>
       </c>
-      <c r="G37" s="1405"/>
-      <c r="H37" s="1405"/>
+      <c r="G37" s="1399"/>
+      <c r="H37" s="1399"/>
     </row>
     <row r="38" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="678" t="s">
@@ -27150,11 +27162,11 @@
       </c>
       <c r="D38" s="706"/>
       <c r="E38" s="707"/>
-      <c r="F38" s="1406">
+      <c r="F38" s="1400">
         <v>0</v>
       </c>
-      <c r="G38" s="1406"/>
-      <c r="H38" s="1406"/>
+      <c r="G38" s="1400"/>
+      <c r="H38" s="1400"/>
     </row>
     <row r="39" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27179,17 +27191,17 @@
       </c>
       <c r="D41" s="1029"/>
       <c r="E41" s="1030"/>
-      <c r="F41" s="1407">
+      <c r="F41" s="1401">
         <v>0</v>
       </c>
-      <c r="G41" s="1407"/>
-      <c r="H41" s="1407"/>
-      <c r="K41" s="1404" t="s">
+      <c r="G41" s="1401"/>
+      <c r="H41" s="1401"/>
+      <c r="K41" s="1414" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="1404"/>
+      <c r="L41" s="1414"/>
       <c r="M41" s="478"/>
-      <c r="N41" s="1402" t="s">
+      <c r="N41" s="1412" t="s">
         <v>102</v>
       </c>
     </row>
@@ -27202,7 +27214,7 @@
         <v>52</v>
       </c>
       <c r="M42" s="478"/>
-      <c r="N42" s="1403"/>
+      <c r="N42" s="1413"/>
     </row>
     <row r="43" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1027"/>
@@ -27375,21 +27387,21 @@
     </row>
     <row r="49" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="711"/>
-      <c r="C49" s="1391" t="s">
+      <c r="C49" s="1403" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="1392"/>
-      <c r="E49" s="1393"/>
+      <c r="D49" s="1404"/>
+      <c r="E49" s="1405"/>
       <c r="N49" s="712"/>
     </row>
     <row r="50" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="711"/>
-      <c r="C50" s="1408" t="e">
+      <c r="C50" s="1388" t="e">
         <f>IF(G54="","",IF(AND(G54&lt;=25),"A",IF(AND(G54&gt;25,G53&lt;=25),"B",IF(AND(G53&gt;25,G52&lt;30),"C"))))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D50" s="1409"/>
-      <c r="E50" s="1410"/>
+      <c r="D50" s="1389"/>
+      <c r="E50" s="1390"/>
       <c r="F50" s="475"/>
       <c r="N50" s="712"/>
       <c r="O50" s="713"/>
@@ -29054,23 +29066,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="e49E/OysaywdZI0JcuM+C0cQuCvqe9PMqZ/ilP9GIY/P45QRK0Ai6JyKU7eB4WtZltnkC9BaQI8vpXNlfCIiIw==" saltValue="LOl5Rt57JcvlkUy4kBpOXg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="33">
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B29:D29"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="I12:J12"/>
@@ -29087,6 +29082,23 @@
     <mergeCell ref="N41:N42"/>
     <mergeCell ref="K41:L41"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
   </mergeCells>
   <conditionalFormatting sqref="F34:F35">
     <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="No Cumple">
@@ -29160,16 +29172,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1422"/>
-      <c r="B1" s="1422"/>
-      <c r="C1" s="1422"/>
-      <c r="D1" s="1423" t="s">
+      <c r="A1" s="1423"/>
+      <c r="B1" s="1423"/>
+      <c r="C1" s="1423"/>
+      <c r="D1" s="1424" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="1423"/>
-      <c r="F1" s="1423"/>
-      <c r="G1" s="1423"/>
-      <c r="H1" s="1423"/>
+      <c r="E1" s="1424"/>
+      <c r="F1" s="1424"/>
+      <c r="G1" s="1424"/>
+      <c r="H1" s="1424"/>
       <c r="I1" s="484" t="s">
         <v>129</v>
       </c>
@@ -29178,14 +29190,14 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1422"/>
-      <c r="B2" s="1422"/>
-      <c r="C2" s="1422"/>
-      <c r="D2" s="1423"/>
-      <c r="E2" s="1423"/>
-      <c r="F2" s="1423"/>
-      <c r="G2" s="1423"/>
-      <c r="H2" s="1423"/>
+      <c r="A2" s="1423"/>
+      <c r="B2" s="1423"/>
+      <c r="C2" s="1423"/>
+      <c r="D2" s="1424"/>
+      <c r="E2" s="1424"/>
+      <c r="F2" s="1424"/>
+      <c r="G2" s="1424"/>
+      <c r="H2" s="1424"/>
       <c r="I2" s="484" t="s">
         <v>131</v>
       </c>
@@ -29194,14 +29206,14 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1422"/>
-      <c r="B3" s="1422"/>
-      <c r="C3" s="1422"/>
-      <c r="D3" s="1423"/>
-      <c r="E3" s="1423"/>
-      <c r="F3" s="1423"/>
-      <c r="G3" s="1423"/>
-      <c r="H3" s="1423"/>
+      <c r="A3" s="1423"/>
+      <c r="B3" s="1423"/>
+      <c r="C3" s="1423"/>
+      <c r="D3" s="1424"/>
+      <c r="E3" s="1424"/>
+      <c r="F3" s="1424"/>
+      <c r="G3" s="1424"/>
+      <c r="H3" s="1424"/>
       <c r="I3" s="484" t="s">
         <v>132</v>
       </c>
@@ -29210,14 +29222,14 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1422"/>
-      <c r="B4" s="1422"/>
-      <c r="C4" s="1422"/>
-      <c r="D4" s="1423"/>
-      <c r="E4" s="1423"/>
-      <c r="F4" s="1423"/>
-      <c r="G4" s="1423"/>
-      <c r="H4" s="1423"/>
+      <c r="A4" s="1423"/>
+      <c r="B4" s="1423"/>
+      <c r="C4" s="1423"/>
+      <c r="D4" s="1424"/>
+      <c r="E4" s="1424"/>
+      <c r="F4" s="1424"/>
+      <c r="G4" s="1424"/>
+      <c r="H4" s="1424"/>
       <c r="I4" s="484" t="s">
         <v>133</v>
       </c>
@@ -29229,17 +29241,17 @@
       <c r="A6" s="744" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="1418" t="s">
+      <c r="B6" s="1434" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="1419"/>
-      <c r="D6" s="1419"/>
-      <c r="E6" s="1419"/>
-      <c r="F6" s="1419"/>
-      <c r="G6" s="1419"/>
-      <c r="H6" s="1419"/>
-      <c r="I6" s="1419"/>
-      <c r="J6" s="1420"/>
+      <c r="C6" s="1435"/>
+      <c r="D6" s="1435"/>
+      <c r="E6" s="1435"/>
+      <c r="F6" s="1435"/>
+      <c r="G6" s="1435"/>
+      <c r="H6" s="1435"/>
+      <c r="I6" s="1435"/>
+      <c r="J6" s="1436"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="744" t="s">
@@ -29514,9 +29526,9 @@
       <c r="F30" s="470"/>
       <c r="G30" s="471"/>
       <c r="H30" s="470"/>
-      <c r="L30" s="1424"/>
-      <c r="R30" s="1421"/>
-      <c r="S30" s="1421"/>
+      <c r="L30" s="1425"/>
+      <c r="R30" s="1437"/>
+      <c r="S30" s="1437"/>
       <c r="T30" s="674"/>
       <c r="U30" s="675"/>
     </row>
@@ -29529,9 +29541,9 @@
       <c r="F31" s="470"/>
       <c r="G31" s="471"/>
       <c r="H31" s="471"/>
-      <c r="L31" s="1424"/>
-      <c r="R31" s="1421"/>
-      <c r="S31" s="1421"/>
+      <c r="L31" s="1425"/>
+      <c r="R31" s="1437"/>
+      <c r="S31" s="1437"/>
       <c r="T31" s="674"/>
       <c r="U31" s="675"/>
     </row>
@@ -29544,9 +29556,9 @@
       <c r="F32" s="471"/>
       <c r="G32" s="471"/>
       <c r="H32" s="471"/>
-      <c r="L32" s="1424"/>
-      <c r="R32" s="1421"/>
-      <c r="S32" s="1421"/>
+      <c r="L32" s="1425"/>
+      <c r="R32" s="1437"/>
+      <c r="S32" s="1437"/>
       <c r="T32" s="674"/>
       <c r="U32" s="675"/>
     </row>
@@ -29559,10 +29571,10 @@
       <c r="F33" s="471"/>
       <c r="G33" s="471"/>
       <c r="H33" s="471"/>
-      <c r="L33" s="1424"/>
+      <c r="L33" s="1425"/>
       <c r="O33" s="673"/>
-      <c r="R33" s="1421"/>
-      <c r="S33" s="1421"/>
+      <c r="R33" s="1437"/>
+      <c r="S33" s="1437"/>
       <c r="T33" s="488"/>
       <c r="U33" s="675"/>
     </row>
@@ -29577,42 +29589,42 @@
       <c r="H34" s="471"/>
       <c r="I34" s="467"/>
       <c r="J34" s="467"/>
-      <c r="L34" s="1425"/>
-      <c r="M34" s="1425"/>
-      <c r="N34" s="1425"/>
-      <c r="O34" s="1425"/>
-      <c r="P34" s="1425"/>
-      <c r="Q34" s="1425"/>
-      <c r="R34" s="1425"/>
-      <c r="S34" s="1425"/>
-      <c r="T34" s="1425"/>
-      <c r="U34" s="1425"/>
+      <c r="L34" s="1426"/>
+      <c r="M34" s="1426"/>
+      <c r="N34" s="1426"/>
+      <c r="O34" s="1426"/>
+      <c r="P34" s="1426"/>
+      <c r="Q34" s="1426"/>
+      <c r="R34" s="1426"/>
+      <c r="S34" s="1426"/>
+      <c r="T34" s="1426"/>
+      <c r="U34" s="1426"/>
     </row>
     <row r="35" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35"/>
       <c r="F35" s="470"/>
       <c r="I35" s="467"/>
       <c r="J35" s="467"/>
-      <c r="L35" s="1426"/>
-      <c r="M35" s="1426"/>
+      <c r="L35" s="1427"/>
+      <c r="M35" s="1427"/>
       <c r="N35" s="676"/>
-      <c r="P35" s="1427"/>
+      <c r="P35" s="1428"/>
       <c r="Q35" s="676"/>
-      <c r="S35" s="1428"/>
-      <c r="T35" s="1429"/>
-      <c r="U35" s="1429"/>
+      <c r="S35" s="1429"/>
+      <c r="T35" s="1430"/>
+      <c r="U35" s="1430"/>
     </row>
     <row r="36" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I36" s="467"/>
       <c r="J36" s="467"/>
-      <c r="L36" s="1426"/>
-      <c r="M36" s="1426"/>
+      <c r="L36" s="1427"/>
+      <c r="M36" s="1427"/>
       <c r="N36" s="677"/>
-      <c r="P36" s="1428"/>
+      <c r="P36" s="1429"/>
       <c r="Q36" s="677"/>
-      <c r="S36" s="1428"/>
-      <c r="T36" s="1429"/>
-      <c r="U36" s="1429"/>
+      <c r="S36" s="1429"/>
+      <c r="T36" s="1430"/>
+      <c r="U36" s="1430"/>
     </row>
     <row r="37" spans="1:26" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="534" t="s">
@@ -32130,12 +32142,12 @@
       <c r="M74" s="471"/>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A75" s="1417" t="s">
+      <c r="A75" s="1433" t="s">
         <v>188</v>
       </c>
-      <c r="B75" s="1417"/>
-      <c r="C75" s="1417"/>
-      <c r="D75" s="1417"/>
+      <c r="B75" s="1433"/>
+      <c r="C75" s="1433"/>
+      <c r="D75" s="1433"/>
       <c r="E75" s="467"/>
       <c r="F75" s="467"/>
       <c r="G75" s="467"/>
@@ -32145,10 +32157,10 @@
       <c r="M75" s="471"/>
     </row>
     <row r="76" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1416" t="s">
+      <c r="A76" s="1432" t="s">
         <v>189</v>
       </c>
-      <c r="B76" s="1416"/>
+      <c r="B76" s="1432"/>
       <c r="C76" s="641" t="s">
         <v>190</v>
       </c>
@@ -32335,16 +32347,16 @@
       <c r="R87" s="486" t="s">
         <v>198</v>
       </c>
-      <c r="T87" s="1415" t="s">
+      <c r="T87" s="1431" t="s">
         <v>527</v>
       </c>
-      <c r="U87" s="1415"/>
-      <c r="V87" s="1415"/>
-      <c r="W87" s="1415" t="s">
+      <c r="U87" s="1431"/>
+      <c r="V87" s="1431"/>
+      <c r="W87" s="1431" t="s">
         <v>528</v>
       </c>
-      <c r="X87" s="1415"/>
-      <c r="Y87" s="1415"/>
+      <c r="X87" s="1431"/>
+      <c r="Y87" s="1431"/>
     </row>
     <row r="88" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="596" t="s">
@@ -32868,19 +32880,19 @@
       <c r="A100" s="1262" t="s">
         <v>648</v>
       </c>
-      <c r="B100" s="1430" t="s">
+      <c r="B100" s="1415" t="s">
         <v>649</v>
       </c>
-      <c r="C100" s="1431"/>
+      <c r="C100" s="1416"/>
       <c r="D100" s="1263"/>
-      <c r="E100" s="1432" t="s">
+      <c r="E100" s="1417" t="s">
         <v>650</v>
       </c>
-      <c r="F100" s="1432"/>
-      <c r="G100" s="1433" t="s">
+      <c r="F100" s="1417"/>
+      <c r="G100" s="1418" t="s">
         <v>651</v>
       </c>
-      <c r="H100" s="1434"/>
+      <c r="H100" s="1419"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="940"/>
@@ -32896,19 +32908,19 @@
       <c r="A102" s="1264" t="s">
         <v>652</v>
       </c>
-      <c r="B102" s="1435">
+      <c r="B102" s="1420">
         <v>44944</v>
       </c>
-      <c r="C102" s="1436"/>
+      <c r="C102" s="1421"/>
       <c r="D102" s="940"/>
-      <c r="E102" s="1437" t="s">
+      <c r="E102" s="1422" t="s">
         <v>653</v>
       </c>
-      <c r="F102" s="1437"/>
-      <c r="G102" s="1435">
+      <c r="F102" s="1422"/>
+      <c r="G102" s="1420">
         <v>44944</v>
       </c>
-      <c r="H102" s="1436"/>
+      <c r="H102" s="1421"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="940"/>
@@ -32923,12 +32935,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wd0Sk3J/OeT0TxJIAnp4S2dGatByENh6gH5lE7pLCIYYn5xv110dK84OeIJzfd1un3raa/Q0kk7gUzEP+5w5+g==" saltValue="Nxfv9eN1cqS8LPjiSFaCXw==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="T87:V87"/>
+    <mergeCell ref="W87:Y87"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="R30:S33"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:H4"/>
     <mergeCell ref="L30:L33"/>
@@ -32937,12 +32949,12 @@
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="S35:S36"/>
     <mergeCell ref="T35:U36"/>
-    <mergeCell ref="T87:V87"/>
-    <mergeCell ref="W87:Y87"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="R30:S33"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G102:H102"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -34570,18 +34582,18 @@
       <c r="V6" s="365"/>
     </row>
     <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1355" t="s">
+      <c r="A7" s="1356" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1355"/>
-      <c r="C7" s="1355"/>
-      <c r="D7" s="1355"/>
-      <c r="E7" s="1355"/>
-      <c r="F7" s="1355"/>
-      <c r="G7" s="1355"/>
-      <c r="H7" s="1355"/>
-      <c r="I7" s="1355"/>
-      <c r="J7" s="1355"/>
+      <c r="B7" s="1356"/>
+      <c r="C7" s="1356"/>
+      <c r="D7" s="1356"/>
+      <c r="E7" s="1356"/>
+      <c r="F7" s="1356"/>
+      <c r="G7" s="1356"/>
+      <c r="H7" s="1356"/>
+      <c r="I7" s="1356"/>
+      <c r="J7" s="1356"/>
       <c r="L7" s="326"/>
       <c r="M7" s="364"/>
       <c r="N7" s="365"/>
@@ -34595,18 +34607,18 @@
       <c r="V7" s="365"/>
     </row>
     <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1449">
+      <c r="A8" s="1445">
         <v>1</v>
       </c>
-      <c r="B8" s="1449"/>
-      <c r="C8" s="1449"/>
-      <c r="D8" s="1449"/>
-      <c r="E8" s="1449"/>
-      <c r="F8" s="1449"/>
-      <c r="G8" s="1449"/>
-      <c r="H8" s="1449"/>
-      <c r="I8" s="1449"/>
-      <c r="J8" s="1449"/>
+      <c r="B8" s="1445"/>
+      <c r="C8" s="1445"/>
+      <c r="D8" s="1445"/>
+      <c r="E8" s="1445"/>
+      <c r="F8" s="1445"/>
+      <c r="G8" s="1445"/>
+      <c r="H8" s="1445"/>
+      <c r="I8" s="1445"/>
+      <c r="J8" s="1445"/>
       <c r="L8" s="334"/>
       <c r="M8" s="366"/>
       <c r="N8" s="367"/>
@@ -34885,18 +34897,18 @@
       <c r="AL14" s="315"/>
     </row>
     <row r="15" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1450" t="s">
+      <c r="A15" s="1446" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="1451"/>
-      <c r="C15" s="1451"/>
-      <c r="D15" s="1451"/>
-      <c r="E15" s="1451"/>
-      <c r="F15" s="1451"/>
-      <c r="G15" s="1451"/>
-      <c r="H15" s="1451"/>
-      <c r="I15" s="1451"/>
-      <c r="J15" s="1452"/>
+      <c r="B15" s="1447"/>
+      <c r="C15" s="1447"/>
+      <c r="D15" s="1447"/>
+      <c r="E15" s="1447"/>
+      <c r="F15" s="1447"/>
+      <c r="G15" s="1447"/>
+      <c r="H15" s="1447"/>
+      <c r="I15" s="1447"/>
+      <c r="J15" s="1448"/>
       <c r="K15" s="341"/>
       <c r="M15" s="365"/>
       <c r="N15" s="365"/>
@@ -34925,18 +34937,18 @@
       <c r="AL15" s="315"/>
     </row>
     <row r="16" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1453" t="s">
+      <c r="A16" s="1449" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="1454"/>
-      <c r="C16" s="1454"/>
-      <c r="D16" s="1454"/>
-      <c r="E16" s="1454"/>
-      <c r="F16" s="1454"/>
-      <c r="G16" s="1454"/>
-      <c r="H16" s="1454"/>
-      <c r="I16" s="1454"/>
-      <c r="J16" s="1455"/>
+      <c r="B16" s="1450"/>
+      <c r="C16" s="1450"/>
+      <c r="D16" s="1450"/>
+      <c r="E16" s="1450"/>
+      <c r="F16" s="1450"/>
+      <c r="G16" s="1450"/>
+      <c r="H16" s="1450"/>
+      <c r="I16" s="1450"/>
+      <c r="J16" s="1451"/>
       <c r="K16" s="341"/>
       <c r="L16" s="341"/>
       <c r="M16" s="365"/>
@@ -35005,18 +35017,18 @@
       <c r="AL17" s="315"/>
     </row>
     <row r="18" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1363" t="s">
+      <c r="A18" s="1364" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1364"/>
-      <c r="C18" s="1364"/>
-      <c r="D18" s="1364"/>
-      <c r="E18" s="1364"/>
-      <c r="F18" s="1364"/>
-      <c r="G18" s="1364"/>
-      <c r="H18" s="1364"/>
-      <c r="I18" s="1364"/>
-      <c r="J18" s="1365"/>
+      <c r="B18" s="1365"/>
+      <c r="C18" s="1365"/>
+      <c r="D18" s="1365"/>
+      <c r="E18" s="1365"/>
+      <c r="F18" s="1365"/>
+      <c r="G18" s="1365"/>
+      <c r="H18" s="1365"/>
+      <c r="I18" s="1365"/>
+      <c r="J18" s="1366"/>
       <c r="L18" s="341"/>
       <c r="M18" s="365"/>
       <c r="N18" s="365"/>
@@ -35062,10 +35074,10 @@
       </c>
       <c r="L19" s="341"/>
       <c r="M19" s="361"/>
-      <c r="N19" s="1447" t="s">
+      <c r="N19" s="1443" t="s">
         <v>230</v>
       </c>
-      <c r="O19" s="1447" t="s">
+      <c r="O19" s="1443" t="s">
         <v>231</v>
       </c>
       <c r="P19" s="361"/>
@@ -35117,8 +35129,8 @@
       </c>
       <c r="L20" s="341"/>
       <c r="M20" s="361"/>
-      <c r="N20" s="1448"/>
-      <c r="O20" s="1448"/>
+      <c r="N20" s="1444"/>
+      <c r="O20" s="1444"/>
       <c r="P20" s="371"/>
       <c r="Q20" s="372"/>
       <c r="R20" s="361"/>
@@ -35247,18 +35259,18 @@
       <c r="AL22" s="315"/>
     </row>
     <row r="23" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1456" t="s">
+      <c r="A23" s="1452" t="s">
         <v>235</v>
       </c>
-      <c r="B23" s="1456"/>
-      <c r="C23" s="1456"/>
-      <c r="D23" s="1456"/>
-      <c r="E23" s="1456"/>
-      <c r="F23" s="1456"/>
-      <c r="G23" s="1456"/>
-      <c r="H23" s="1456"/>
-      <c r="I23" s="1456"/>
-      <c r="J23" s="1456"/>
+      <c r="B23" s="1452"/>
+      <c r="C23" s="1452"/>
+      <c r="D23" s="1452"/>
+      <c r="E23" s="1452"/>
+      <c r="F23" s="1452"/>
+      <c r="G23" s="1452"/>
+      <c r="H23" s="1452"/>
+      <c r="I23" s="1452"/>
+      <c r="J23" s="1452"/>
       <c r="K23" s="341"/>
       <c r="L23" s="344"/>
       <c r="M23" s="361"/>
@@ -35701,18 +35713,18 @@
       <c r="AL32" s="315"/>
     </row>
     <row r="33" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1456" t="s">
+      <c r="A33" s="1452" t="s">
         <v>253</v>
       </c>
-      <c r="B33" s="1456"/>
-      <c r="C33" s="1456"/>
-      <c r="D33" s="1456"/>
-      <c r="E33" s="1456"/>
-      <c r="F33" s="1456"/>
-      <c r="G33" s="1456"/>
-      <c r="H33" s="1456"/>
-      <c r="I33" s="1456"/>
-      <c r="J33" s="1456"/>
+      <c r="B33" s="1452"/>
+      <c r="C33" s="1452"/>
+      <c r="D33" s="1452"/>
+      <c r="E33" s="1452"/>
+      <c r="F33" s="1452"/>
+      <c r="G33" s="1452"/>
+      <c r="H33" s="1452"/>
+      <c r="I33" s="1452"/>
+      <c r="J33" s="1452"/>
       <c r="K33" s="437"/>
       <c r="L33" s="437"/>
       <c r="T33" s="314"/>
@@ -35737,15 +35749,15 @@
     </row>
     <row r="34" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="749"/>
-      <c r="B34" s="1446" t="s">
+      <c r="B34" s="1442" t="s">
         <v>254</v>
       </c>
-      <c r="C34" s="1446"/>
-      <c r="D34" s="1446"/>
-      <c r="E34" s="1446"/>
-      <c r="F34" s="1446"/>
-      <c r="G34" s="1446"/>
-      <c r="H34" s="1446"/>
+      <c r="C34" s="1442"/>
+      <c r="D34" s="1442"/>
+      <c r="E34" s="1442"/>
+      <c r="F34" s="1442"/>
+      <c r="G34" s="1442"/>
+      <c r="H34" s="1442"/>
       <c r="I34" s="757"/>
       <c r="J34" s="758"/>
       <c r="K34" s="341"/>
@@ -35815,18 +35827,18 @@
       <c r="AL35" s="315"/>
     </row>
     <row r="36" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1456" t="s">
+      <c r="A36" s="1452" t="s">
         <v>257</v>
       </c>
-      <c r="B36" s="1456"/>
-      <c r="C36" s="1456"/>
-      <c r="D36" s="1456"/>
-      <c r="E36" s="1456"/>
-      <c r="F36" s="1456"/>
-      <c r="G36" s="1456"/>
-      <c r="H36" s="1456"/>
-      <c r="I36" s="1456"/>
-      <c r="J36" s="1456"/>
+      <c r="B36" s="1452"/>
+      <c r="C36" s="1452"/>
+      <c r="D36" s="1452"/>
+      <c r="E36" s="1452"/>
+      <c r="F36" s="1452"/>
+      <c r="G36" s="1452"/>
+      <c r="H36" s="1452"/>
+      <c r="I36" s="1452"/>
+      <c r="J36" s="1452"/>
       <c r="K36" s="341"/>
       <c r="L36" s="341"/>
       <c r="T36" s="314"/>
@@ -35851,15 +35863,15 @@
     </row>
     <row r="37" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="749"/>
-      <c r="B37" s="1446" t="s">
+      <c r="B37" s="1442" t="s">
         <v>258</v>
       </c>
-      <c r="C37" s="1446"/>
-      <c r="D37" s="1446"/>
-      <c r="E37" s="1446"/>
-      <c r="F37" s="1446"/>
-      <c r="G37" s="1446"/>
-      <c r="H37" s="1446"/>
+      <c r="C37" s="1442"/>
+      <c r="D37" s="1442"/>
+      <c r="E37" s="1442"/>
+      <c r="F37" s="1442"/>
+      <c r="G37" s="1442"/>
+      <c r="H37" s="1442"/>
       <c r="I37" s="757"/>
       <c r="J37" s="758"/>
       <c r="K37" s="341"/>
@@ -35962,18 +35974,18 @@
       <c r="AL39" s="315"/>
     </row>
     <row r="40" spans="1:38" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1442" t="s">
+      <c r="A40" s="1456" t="s">
         <v>261</v>
       </c>
-      <c r="B40" s="1442"/>
-      <c r="C40" s="1442"/>
-      <c r="D40" s="1442"/>
-      <c r="E40" s="1442"/>
-      <c r="F40" s="1442"/>
-      <c r="G40" s="1442"/>
-      <c r="H40" s="1442"/>
-      <c r="I40" s="1442"/>
-      <c r="J40" s="1442"/>
+      <c r="B40" s="1456"/>
+      <c r="C40" s="1456"/>
+      <c r="D40" s="1456"/>
+      <c r="E40" s="1456"/>
+      <c r="F40" s="1456"/>
+      <c r="G40" s="1456"/>
+      <c r="H40" s="1456"/>
+      <c r="I40" s="1456"/>
+      <c r="J40" s="1456"/>
       <c r="K40" s="341"/>
       <c r="L40" s="341"/>
       <c r="T40" s="314"/>
@@ -35997,16 +36009,16 @@
       <c r="AL40" s="315"/>
     </row>
     <row r="41" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1442"/>
-      <c r="B41" s="1442"/>
-      <c r="C41" s="1442"/>
-      <c r="D41" s="1442"/>
-      <c r="E41" s="1442"/>
-      <c r="F41" s="1442"/>
-      <c r="G41" s="1442"/>
-      <c r="H41" s="1442"/>
-      <c r="I41" s="1442"/>
-      <c r="J41" s="1442"/>
+      <c r="A41" s="1456"/>
+      <c r="B41" s="1456"/>
+      <c r="C41" s="1456"/>
+      <c r="D41" s="1456"/>
+      <c r="E41" s="1456"/>
+      <c r="F41" s="1456"/>
+      <c r="G41" s="1456"/>
+      <c r="H41" s="1456"/>
+      <c r="I41" s="1456"/>
+      <c r="J41" s="1456"/>
       <c r="K41" s="341"/>
       <c r="L41" s="341"/>
       <c r="T41" s="314"/>
@@ -36030,16 +36042,16 @@
       <c r="AL41" s="315"/>
     </row>
     <row r="42" spans="1:38" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1442"/>
-      <c r="B42" s="1442"/>
-      <c r="C42" s="1442"/>
-      <c r="D42" s="1442"/>
-      <c r="E42" s="1442"/>
-      <c r="F42" s="1442"/>
-      <c r="G42" s="1442"/>
-      <c r="H42" s="1442"/>
-      <c r="I42" s="1442"/>
-      <c r="J42" s="1442"/>
+      <c r="A42" s="1456"/>
+      <c r="B42" s="1456"/>
+      <c r="C42" s="1456"/>
+      <c r="D42" s="1456"/>
+      <c r="E42" s="1456"/>
+      <c r="F42" s="1456"/>
+      <c r="G42" s="1456"/>
+      <c r="H42" s="1456"/>
+      <c r="I42" s="1456"/>
+      <c r="J42" s="1456"/>
       <c r="K42" s="418"/>
       <c r="L42" s="381"/>
       <c r="N42" s="378"/>
@@ -36119,9 +36131,9 @@
       <c r="K44" s="341"/>
       <c r="L44" s="383"/>
       <c r="M44" s="383"/>
-      <c r="N44" s="1334"/>
-      <c r="O44" s="1334"/>
-      <c r="P44" s="1334"/>
+      <c r="N44" s="1341"/>
+      <c r="O44" s="1341"/>
+      <c r="P44" s="1341"/>
       <c r="T44" s="314"/>
       <c r="U44" s="325"/>
       <c r="V44" s="325"/>
@@ -36150,15 +36162,15 @@
       <c r="E45" s="197"/>
       <c r="F45" s="197"/>
       <c r="G45" s="200"/>
-      <c r="H45" s="1333"/>
-      <c r="I45" s="1333"/>
-      <c r="J45" s="1333"/>
+      <c r="H45" s="1381"/>
+      <c r="I45" s="1381"/>
+      <c r="J45" s="1381"/>
       <c r="K45" s="341"/>
       <c r="L45" s="384"/>
       <c r="M45" s="385"/>
-      <c r="N45" s="1444"/>
-      <c r="O45" s="1444"/>
-      <c r="P45" s="1444"/>
+      <c r="N45" s="1453"/>
+      <c r="O45" s="1453"/>
+      <c r="P45" s="1453"/>
       <c r="T45" s="314"/>
       <c r="U45" s="325"/>
       <c r="V45" s="325"/>
@@ -36187,15 +36199,15 @@
       <c r="E46" s="197"/>
       <c r="F46" s="197"/>
       <c r="G46" s="200"/>
-      <c r="H46" s="1334"/>
-      <c r="I46" s="1334"/>
-      <c r="J46" s="1334"/>
+      <c r="H46" s="1341"/>
+      <c r="I46" s="1341"/>
+      <c r="J46" s="1341"/>
       <c r="K46" s="341"/>
       <c r="L46" s="386"/>
       <c r="M46" s="387"/>
-      <c r="N46" s="1334"/>
-      <c r="O46" s="1334"/>
-      <c r="P46" s="1334"/>
+      <c r="N46" s="1341"/>
+      <c r="O46" s="1341"/>
+      <c r="P46" s="1341"/>
       <c r="T46" s="314"/>
       <c r="U46" s="325"/>
       <c r="V46" s="325"/>
@@ -36224,15 +36236,15 @@
       <c r="E47" s="197"/>
       <c r="F47" s="197"/>
       <c r="G47" s="200"/>
-      <c r="H47" s="1444"/>
-      <c r="I47" s="1444"/>
-      <c r="J47" s="1444"/>
+      <c r="H47" s="1453"/>
+      <c r="I47" s="1453"/>
+      <c r="J47" s="1453"/>
       <c r="K47" s="341"/>
       <c r="L47" s="386"/>
       <c r="M47" s="387"/>
-      <c r="N47" s="1333"/>
-      <c r="O47" s="1333"/>
-      <c r="P47" s="1333"/>
+      <c r="N47" s="1381"/>
+      <c r="O47" s="1381"/>
+      <c r="P47" s="1381"/>
       <c r="T47" s="314"/>
       <c r="U47" s="325"/>
       <c r="V47" s="325"/>
@@ -36261,15 +36273,15 @@
       <c r="E48" s="197"/>
       <c r="F48" s="197"/>
       <c r="G48" s="200"/>
-      <c r="H48" s="1334"/>
-      <c r="I48" s="1334"/>
-      <c r="J48" s="1334"/>
+      <c r="H48" s="1341"/>
+      <c r="I48" s="1341"/>
+      <c r="J48" s="1341"/>
       <c r="K48" s="341"/>
       <c r="L48" s="386"/>
       <c r="M48" s="387"/>
-      <c r="N48" s="1445"/>
-      <c r="O48" s="1445"/>
-      <c r="P48" s="1445"/>
+      <c r="N48" s="1455"/>
+      <c r="O48" s="1455"/>
+      <c r="P48" s="1455"/>
       <c r="T48" s="314"/>
       <c r="U48" s="325"/>
       <c r="V48" s="325"/>
@@ -36298,15 +36310,15 @@
       <c r="E49" s="200"/>
       <c r="F49" s="200"/>
       <c r="G49" s="200"/>
-      <c r="H49" s="1333"/>
-      <c r="I49" s="1333"/>
-      <c r="J49" s="1333"/>
+      <c r="H49" s="1381"/>
+      <c r="I49" s="1381"/>
+      <c r="J49" s="1381"/>
       <c r="K49" s="341"/>
       <c r="L49" s="386"/>
       <c r="M49" s="387"/>
-      <c r="N49" s="1444"/>
-      <c r="O49" s="1444"/>
-      <c r="P49" s="1444"/>
+      <c r="N49" s="1453"/>
+      <c r="O49" s="1453"/>
+      <c r="P49" s="1453"/>
       <c r="T49" s="314"/>
       <c r="U49" s="325"/>
       <c r="V49" s="325"/>
@@ -37076,16 +37088,16 @@
       <c r="AL74" s="315"/>
     </row>
     <row r="75" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1442"/>
-      <c r="B75" s="1442"/>
-      <c r="C75" s="1442"/>
-      <c r="D75" s="1442"/>
-      <c r="E75" s="1442"/>
-      <c r="F75" s="1442"/>
-      <c r="G75" s="1442"/>
-      <c r="H75" s="1442"/>
-      <c r="I75" s="1442"/>
-      <c r="J75" s="1442"/>
+      <c r="A75" s="1456"/>
+      <c r="B75" s="1456"/>
+      <c r="C75" s="1456"/>
+      <c r="D75" s="1456"/>
+      <c r="E75" s="1456"/>
+      <c r="F75" s="1456"/>
+      <c r="G75" s="1456"/>
+      <c r="H75" s="1456"/>
+      <c r="I75" s="1456"/>
+      <c r="J75" s="1456"/>
       <c r="T75" s="314"/>
       <c r="U75" s="325"/>
       <c r="V75" s="325"/>
@@ -37107,16 +37119,16 @@
       <c r="AL75" s="315"/>
     </row>
     <row r="76" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1442"/>
-      <c r="B76" s="1442"/>
-      <c r="C76" s="1442"/>
-      <c r="D76" s="1442"/>
-      <c r="E76" s="1442"/>
-      <c r="F76" s="1442"/>
-      <c r="G76" s="1442"/>
-      <c r="H76" s="1442"/>
-      <c r="I76" s="1442"/>
-      <c r="J76" s="1442"/>
+      <c r="A76" s="1456"/>
+      <c r="B76" s="1456"/>
+      <c r="C76" s="1456"/>
+      <c r="D76" s="1456"/>
+      <c r="E76" s="1456"/>
+      <c r="F76" s="1456"/>
+      <c r="G76" s="1456"/>
+      <c r="H76" s="1456"/>
+      <c r="I76" s="1456"/>
+      <c r="J76" s="1456"/>
       <c r="T76" s="314"/>
       <c r="U76" s="325"/>
       <c r="V76" s="325"/>
@@ -37138,16 +37150,16 @@
       <c r="AL76" s="315"/>
     </row>
     <row r="77" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1442"/>
-      <c r="B77" s="1442"/>
-      <c r="C77" s="1442"/>
-      <c r="D77" s="1442"/>
-      <c r="E77" s="1442"/>
-      <c r="F77" s="1442"/>
-      <c r="G77" s="1442"/>
-      <c r="H77" s="1442"/>
-      <c r="I77" s="1442"/>
-      <c r="J77" s="1442"/>
+      <c r="A77" s="1456"/>
+      <c r="B77" s="1456"/>
+      <c r="C77" s="1456"/>
+      <c r="D77" s="1456"/>
+      <c r="E77" s="1456"/>
+      <c r="F77" s="1456"/>
+      <c r="G77" s="1456"/>
+      <c r="H77" s="1456"/>
+      <c r="I77" s="1456"/>
+      <c r="J77" s="1456"/>
       <c r="T77" s="314"/>
       <c r="U77" s="325"/>
       <c r="V77" s="325"/>
@@ -37262,10 +37274,10 @@
       <c r="AL80" s="315"/>
     </row>
     <row r="81" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G81" s="1443"/>
-      <c r="H81" s="1443"/>
-      <c r="I81" s="1443"/>
-      <c r="J81" s="1443"/>
+      <c r="G81" s="1454"/>
+      <c r="H81" s="1454"/>
+      <c r="I81" s="1454"/>
+      <c r="J81" s="1454"/>
       <c r="T81" s="314"/>
       <c r="U81" s="325"/>
       <c r="V81" s="325"/>
@@ -37310,10 +37322,10 @@
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" s="313"/>
-      <c r="G83" s="1443"/>
-      <c r="H83" s="1443"/>
-      <c r="I83" s="1443"/>
-      <c r="J83" s="1443"/>
+      <c r="G83" s="1454"/>
+      <c r="H83" s="1454"/>
+      <c r="I83" s="1454"/>
+      <c r="J83" s="1454"/>
       <c r="T83" s="314"/>
       <c r="U83" s="325"/>
       <c r="V83" s="325"/>
@@ -39795,6 +39807,23 @@
     <protectedRange sqref="C10:C13" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="29">
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A41:J42"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A76:J77"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="N46:P46"/>
     <mergeCell ref="B37:H37"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
@@ -39807,23 +39836,6 @@
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="B34:H34"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="G83:J83"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J42"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A76:J77"/>
-    <mergeCell ref="G81:J81"/>
-    <mergeCell ref="H47:J47"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.78740157480314965" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -40036,19 +40048,19 @@
       <c r="Z6" s="37"/>
     </row>
     <row r="7" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1486" t="s">
+      <c r="A7" s="1464" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1486"/>
-      <c r="C7" s="1486"/>
-      <c r="D7" s="1486"/>
-      <c r="E7" s="1486"/>
-      <c r="F7" s="1486"/>
-      <c r="G7" s="1486"/>
-      <c r="H7" s="1486"/>
-      <c r="I7" s="1486"/>
-      <c r="J7" s="1486"/>
-      <c r="K7" s="1486"/>
+      <c r="B7" s="1464"/>
+      <c r="C7" s="1464"/>
+      <c r="D7" s="1464"/>
+      <c r="E7" s="1464"/>
+      <c r="F7" s="1464"/>
+      <c r="G7" s="1464"/>
+      <c r="H7" s="1464"/>
+      <c r="I7" s="1464"/>
+      <c r="J7" s="1464"/>
+      <c r="K7" s="1464"/>
       <c r="N7" s="309" t="s">
         <v>272</v>
       </c>
@@ -40073,20 +40085,20 @@
       <c r="Z7" s="37"/>
     </row>
     <row r="8" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1487">
+      <c r="A8" s="1465">
         <f>+K12</f>
         <v>1</v>
       </c>
-      <c r="B8" s="1487"/>
-      <c r="C8" s="1487"/>
-      <c r="D8" s="1487"/>
-      <c r="E8" s="1487"/>
-      <c r="F8" s="1487"/>
-      <c r="G8" s="1487"/>
-      <c r="H8" s="1487"/>
-      <c r="I8" s="1487"/>
-      <c r="J8" s="1487"/>
-      <c r="K8" s="1487"/>
+      <c r="B8" s="1465"/>
+      <c r="C8" s="1465"/>
+      <c r="D8" s="1465"/>
+      <c r="E8" s="1465"/>
+      <c r="F8" s="1465"/>
+      <c r="G8" s="1465"/>
+      <c r="H8" s="1465"/>
+      <c r="I8" s="1465"/>
+      <c r="J8" s="1465"/>
+      <c r="K8" s="1465"/>
       <c r="N8" s="769" t="s">
         <v>274</v>
       </c>
@@ -40141,14 +40153,14 @@
       <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1480" t="s">
+      <c r="C10" s="1488" t="s">
         <v>277</v>
       </c>
-      <c r="D10" s="1480"/>
-      <c r="E10" s="1480"/>
-      <c r="F10" s="1480"/>
-      <c r="G10" s="1480"/>
-      <c r="H10" s="1480"/>
+      <c r="D10" s="1488"/>
+      <c r="E10" s="1488"/>
+      <c r="F10" s="1488"/>
+      <c r="G10" s="1488"/>
+      <c r="H10" s="1488"/>
       <c r="I10" s="23" t="s">
         <v>3</v>
       </c>
@@ -40191,14 +40203,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1480" t="s">
+      <c r="C11" s="1488" t="s">
         <v>282</v>
       </c>
-      <c r="D11" s="1480"/>
-      <c r="E11" s="1480"/>
-      <c r="F11" s="1480"/>
-      <c r="G11" s="1480"/>
-      <c r="H11" s="1480"/>
+      <c r="D11" s="1488"/>
+      <c r="E11" s="1488"/>
+      <c r="F11" s="1488"/>
+      <c r="G11" s="1488"/>
+      <c r="H11" s="1488"/>
       <c r="I11" s="26" t="s">
         <v>6</v>
       </c>
@@ -40240,14 +40252,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1480" t="s">
+      <c r="C12" s="1488" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="1480"/>
-      <c r="E12" s="1480"/>
-      <c r="F12" s="1480"/>
-      <c r="G12" s="1480"/>
-      <c r="H12" s="1480"/>
+      <c r="D12" s="1488"/>
+      <c r="E12" s="1488"/>
+      <c r="F12" s="1488"/>
+      <c r="G12" s="1488"/>
+      <c r="H12" s="1488"/>
       <c r="I12" s="26" t="s">
         <v>288</v>
       </c>
@@ -40327,19 +40339,19 @@
       <c r="Z13" s="37"/>
     </row>
     <row r="14" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1450" t="s">
+      <c r="A14" s="1446" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="1451"/>
-      <c r="C14" s="1451"/>
-      <c r="D14" s="1451"/>
-      <c r="E14" s="1451"/>
-      <c r="F14" s="1451"/>
-      <c r="G14" s="1451"/>
-      <c r="H14" s="1451"/>
-      <c r="I14" s="1451"/>
-      <c r="J14" s="1451"/>
-      <c r="K14" s="1452"/>
+      <c r="B14" s="1447"/>
+      <c r="C14" s="1447"/>
+      <c r="D14" s="1447"/>
+      <c r="E14" s="1447"/>
+      <c r="F14" s="1447"/>
+      <c r="G14" s="1447"/>
+      <c r="H14" s="1447"/>
+      <c r="I14" s="1447"/>
+      <c r="J14" s="1447"/>
+      <c r="K14" s="1448"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="769" t="s">
@@ -40362,19 +40374,19 @@
       <c r="Z14" s="37"/>
     </row>
     <row r="15" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1453" t="s">
+      <c r="A15" s="1449" t="s">
         <v>295</v>
       </c>
-      <c r="B15" s="1454"/>
-      <c r="C15" s="1454"/>
-      <c r="D15" s="1454"/>
-      <c r="E15" s="1454"/>
-      <c r="F15" s="1454"/>
-      <c r="G15" s="1454"/>
-      <c r="H15" s="1454"/>
-      <c r="I15" s="1454"/>
-      <c r="J15" s="1454"/>
-      <c r="K15" s="1455"/>
+      <c r="B15" s="1450"/>
+      <c r="C15" s="1450"/>
+      <c r="D15" s="1450"/>
+      <c r="E15" s="1450"/>
+      <c r="F15" s="1450"/>
+      <c r="G15" s="1450"/>
+      <c r="H15" s="1450"/>
+      <c r="I15" s="1450"/>
+      <c r="J15" s="1450"/>
+      <c r="K15" s="1451"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="25"/>
@@ -40421,30 +40433,30 @@
       <c r="S16" s="232" t="s">
         <v>299</v>
       </c>
-      <c r="T16" s="1460" t="s">
+      <c r="T16" s="1492" t="s">
         <v>300</v>
       </c>
-      <c r="U16" s="1461"/>
-      <c r="V16" s="1462"/>
+      <c r="U16" s="1493"/>
+      <c r="V16" s="1494"/>
       <c r="W16" s="37"/>
       <c r="X16" s="37"/>
       <c r="Y16" s="37"/>
       <c r="Z16" s="37"/>
     </row>
     <row r="17" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1477" t="s">
+      <c r="A17" s="1485" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1478"/>
-      <c r="C17" s="1478"/>
-      <c r="D17" s="1478"/>
-      <c r="E17" s="1478"/>
-      <c r="F17" s="1478"/>
-      <c r="G17" s="1478"/>
-      <c r="H17" s="1478"/>
-      <c r="I17" s="1478"/>
-      <c r="J17" s="1478"/>
-      <c r="K17" s="1479"/>
+      <c r="B17" s="1486"/>
+      <c r="C17" s="1486"/>
+      <c r="D17" s="1486"/>
+      <c r="E17" s="1486"/>
+      <c r="F17" s="1486"/>
+      <c r="G17" s="1486"/>
+      <c r="H17" s="1486"/>
+      <c r="I17" s="1486"/>
+      <c r="J17" s="1486"/>
+      <c r="K17" s="1487"/>
       <c r="M17" s="3"/>
       <c r="N17" s="775" t="s">
         <v>230</v>
@@ -40464,11 +40476,11 @@
       <c r="S17" s="776" t="s">
         <v>305</v>
       </c>
-      <c r="T17" s="1457" t="s">
+      <c r="T17" s="1489" t="s">
         <v>306</v>
       </c>
-      <c r="U17" s="1458"/>
-      <c r="V17" s="1459"/>
+      <c r="U17" s="1490"/>
+      <c r="V17" s="1491"/>
       <c r="W17" s="37"/>
       <c r="X17" s="37"/>
       <c r="Y17" s="37"/>
@@ -40728,21 +40740,21 @@
       <c r="Z22" s="37"/>
     </row>
     <row r="23" spans="1:26" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1490" t="s">
+      <c r="A23" s="1468" t="s">
         <v>230</v>
       </c>
-      <c r="B23" s="1491"/>
-      <c r="C23" s="1492"/>
-      <c r="D23" s="1465" t="s">
+      <c r="B23" s="1469"/>
+      <c r="C23" s="1470"/>
+      <c r="D23" s="1496" t="s">
         <v>320</v>
       </c>
       <c r="E23" s="197"/>
-      <c r="F23" s="1493" t="s">
+      <c r="F23" s="1472" t="s">
         <v>321</v>
       </c>
-      <c r="G23" s="1494"/>
-      <c r="H23" s="1495"/>
-      <c r="I23" s="1470" t="s">
+      <c r="G23" s="1473"/>
+      <c r="H23" s="1474"/>
+      <c r="I23" s="1478" t="s">
         <v>317</v>
       </c>
       <c r="J23" s="191"/>
@@ -40786,16 +40798,16 @@
       <c r="A24" s="785" t="s">
         <v>323</v>
       </c>
-      <c r="B24" s="1489" t="s">
+      <c r="B24" s="1467" t="s">
         <v>301</v>
       </c>
-      <c r="C24" s="1489"/>
-      <c r="D24" s="1466"/>
+      <c r="C24" s="1467"/>
+      <c r="D24" s="1497"/>
       <c r="E24" s="197"/>
-      <c r="F24" s="1496"/>
-      <c r="G24" s="1497"/>
-      <c r="H24" s="1498"/>
-      <c r="I24" s="1499"/>
+      <c r="F24" s="1475"/>
+      <c r="G24" s="1476"/>
+      <c r="H24" s="1477"/>
+      <c r="I24" s="1479"/>
       <c r="J24" s="191"/>
       <c r="K24" s="192"/>
       <c r="L24" s="3"/>
@@ -40833,10 +40845,10 @@
       <c r="A25" s="786" t="s">
         <v>310</v>
       </c>
-      <c r="B25" s="1488">
+      <c r="B25" s="1466">
         <v>76.2</v>
       </c>
-      <c r="C25" s="1488"/>
+      <c r="C25" s="1466"/>
       <c r="D25" s="787">
         <f>+S18</f>
         <v>100</v>
@@ -40887,21 +40899,21 @@
       <c r="A26" s="198" t="s">
         <v>317</v>
       </c>
-      <c r="B26" s="1464">
+      <c r="B26" s="1471">
         <v>50.6</v>
       </c>
-      <c r="C26" s="1464"/>
+      <c r="C26" s="1471"/>
       <c r="D26" s="199">
         <f>+S20</f>
         <v>96.737365729020368</v>
       </c>
       <c r="E26" s="197"/>
-      <c r="F26" s="1490" t="s">
+      <c r="F26" s="1468" t="s">
         <v>326</v>
       </c>
-      <c r="G26" s="1491"/>
-      <c r="H26" s="1491"/>
-      <c r="I26" s="1492"/>
+      <c r="G26" s="1469"/>
+      <c r="H26" s="1469"/>
+      <c r="I26" s="1470"/>
       <c r="J26" s="200"/>
       <c r="K26" s="201"/>
       <c r="L26" s="3"/>
@@ -40939,19 +40951,19 @@
       <c r="A27" s="202" t="s">
         <v>318</v>
       </c>
-      <c r="B27" s="1464">
+      <c r="B27" s="1471">
         <v>38.1</v>
       </c>
-      <c r="C27" s="1464"/>
+      <c r="C27" s="1471"/>
       <c r="D27" s="199">
         <f>+S21</f>
         <v>90.324022891039832</v>
       </c>
       <c r="E27" s="197"/>
-      <c r="F27" s="1500"/>
-      <c r="G27" s="1501"/>
-      <c r="H27" s="1501"/>
-      <c r="I27" s="1502"/>
+      <c r="F27" s="1480"/>
+      <c r="G27" s="1481"/>
+      <c r="H27" s="1481"/>
+      <c r="I27" s="1482"/>
       <c r="J27" s="200"/>
       <c r="K27" s="201"/>
       <c r="L27" s="3"/>
@@ -40993,19 +41005,19 @@
       <c r="A28" s="198" t="s">
         <v>319</v>
       </c>
-      <c r="B28" s="1464">
+      <c r="B28" s="1471">
         <v>25.4</v>
       </c>
-      <c r="C28" s="1464"/>
+      <c r="C28" s="1471"/>
       <c r="D28" s="199">
         <f>+S22</f>
         <v>84.873241107276272</v>
       </c>
       <c r="E28" s="197"/>
-      <c r="F28" s="1473" t="s">
+      <c r="F28" s="1483" t="s">
         <v>329</v>
       </c>
-      <c r="G28" s="1475">
+      <c r="G28" s="1484">
         <f>R27</f>
         <v>45.788805497693524</v>
       </c>
@@ -41053,17 +41065,17 @@
       <c r="A29" s="198" t="s">
         <v>322</v>
       </c>
-      <c r="B29" s="1464">
+      <c r="B29" s="1471">
         <v>19.05</v>
       </c>
-      <c r="C29" s="1464"/>
+      <c r="C29" s="1471"/>
       <c r="D29" s="199">
         <f>+S23</f>
         <v>73.456819301447041</v>
       </c>
       <c r="E29" s="197"/>
-      <c r="F29" s="1474"/>
-      <c r="G29" s="1476"/>
+      <c r="F29" s="1459"/>
+      <c r="G29" s="1462"/>
       <c r="H29" s="203" t="s">
         <v>331</v>
       </c>
@@ -41112,19 +41124,19 @@
       <c r="A30" s="198" t="s">
         <v>325</v>
       </c>
-      <c r="B30" s="1464">
+      <c r="B30" s="1471">
         <v>9.5250000000000004</v>
       </c>
-      <c r="C30" s="1464"/>
+      <c r="C30" s="1471"/>
       <c r="D30" s="199">
         <f>+S25</f>
         <v>62.661585152699679</v>
       </c>
       <c r="E30" s="197"/>
-      <c r="F30" s="1481" t="s">
+      <c r="F30" s="1457" t="s">
         <v>332</v>
       </c>
-      <c r="G30" s="1483">
+      <c r="G30" s="1460">
         <f>100-(G28+G33)</f>
         <v>40.754382185876274</v>
       </c>
@@ -41172,17 +41184,17 @@
       <c r="A31" s="198" t="s">
         <v>328</v>
       </c>
-      <c r="B31" s="1464">
+      <c r="B31" s="1471">
         <v>4.76</v>
       </c>
-      <c r="C31" s="1464"/>
+      <c r="C31" s="1471"/>
       <c r="D31" s="199">
         <f>+S27</f>
         <v>54.211194502306476</v>
       </c>
       <c r="E31" s="197"/>
-      <c r="F31" s="1482"/>
-      <c r="G31" s="1484"/>
+      <c r="F31" s="1458"/>
+      <c r="G31" s="1461"/>
       <c r="H31" s="203" t="s">
         <v>333</v>
       </c>
@@ -41230,17 +41242,17 @@
       <c r="A32" s="198">
         <v>8</v>
       </c>
-      <c r="B32" s="1464">
+      <c r="B32" s="1471">
         <v>2.36</v>
       </c>
-      <c r="C32" s="1464"/>
+      <c r="C32" s="1471"/>
       <c r="D32" s="199">
         <f>+S28</f>
         <v>49.032616067382399</v>
       </c>
       <c r="E32" s="197"/>
-      <c r="F32" s="1474"/>
-      <c r="G32" s="1476"/>
+      <c r="F32" s="1459"/>
+      <c r="G32" s="1462"/>
       <c r="H32" s="203" t="s">
         <v>331</v>
       </c>
@@ -41292,10 +41304,10 @@
       <c r="A33" s="198">
         <v>16</v>
       </c>
-      <c r="B33" s="1464">
+      <c r="B33" s="1471">
         <v>1.19</v>
       </c>
-      <c r="C33" s="1464"/>
+      <c r="C33" s="1471"/>
       <c r="D33" s="199">
         <f t="shared" ref="D33:D38" si="4">+S30</f>
         <v>40.351707913359583</v>
@@ -41350,10 +41362,10 @@
       <c r="A34" s="198">
         <v>30</v>
       </c>
-      <c r="B34" s="1464">
+      <c r="B34" s="1471">
         <v>0.6</v>
       </c>
-      <c r="C34" s="1464"/>
+      <c r="C34" s="1471"/>
       <c r="D34" s="199">
         <f t="shared" si="4"/>
         <v>31.408593256302638</v>
@@ -41400,25 +41412,25 @@
       <c r="A35" s="198">
         <v>40</v>
       </c>
-      <c r="B35" s="1464">
+      <c r="B35" s="1471">
         <v>0.42</v>
       </c>
-      <c r="C35" s="1464"/>
+      <c r="C35" s="1471"/>
       <c r="D35" s="199">
         <f t="shared" si="4"/>
         <v>27.175831135894526</v>
       </c>
       <c r="E35" s="197"/>
-      <c r="F35" s="1467" t="str">
+      <c r="F35" s="1498" t="str">
         <f>IF(O3="No","","Clasificacion SUCS")</f>
         <v/>
       </c>
-      <c r="G35" s="1467"/>
-      <c r="H35" s="1470" t="str">
+      <c r="G35" s="1498"/>
+      <c r="H35" s="1478" t="str">
         <f>IF(O3="No","",'Sucs '!G4)</f>
         <v/>
       </c>
-      <c r="I35" s="1470"/>
+      <c r="I35" s="1478"/>
       <c r="J35" s="200"/>
       <c r="K35" s="201"/>
       <c r="L35" s="3"/>
@@ -41460,19 +41472,19 @@
       <c r="A36" s="198">
         <v>50</v>
       </c>
-      <c r="B36" s="1464">
+      <c r="B36" s="1471">
         <v>0.3</v>
       </c>
-      <c r="C36" s="1464"/>
+      <c r="C36" s="1471"/>
       <c r="D36" s="199">
         <f t="shared" si="4"/>
         <v>23.785875632381845</v>
       </c>
       <c r="E36" s="197"/>
-      <c r="F36" s="1468"/>
-      <c r="G36" s="1468"/>
-      <c r="H36" s="1471"/>
-      <c r="I36" s="1471"/>
+      <c r="F36" s="1499"/>
+      <c r="G36" s="1499"/>
+      <c r="H36" s="1501"/>
+      <c r="I36" s="1501"/>
       <c r="J36" s="200"/>
       <c r="K36" s="201"/>
       <c r="L36" s="3"/>
@@ -41511,25 +41523,25 @@
       <c r="A37" s="198">
         <v>100</v>
       </c>
-      <c r="B37" s="1464">
+      <c r="B37" s="1471">
         <v>0.14899999999999999</v>
       </c>
-      <c r="C37" s="1464"/>
+      <c r="C37" s="1471"/>
       <c r="D37" s="199">
         <f t="shared" si="4"/>
         <v>17.820677688355374</v>
       </c>
       <c r="E37" s="197"/>
-      <c r="F37" s="1468" t="str">
+      <c r="F37" s="1499" t="str">
         <f>IF(O3="No","","Clasificacion AASHTO")</f>
         <v/>
       </c>
-      <c r="G37" s="1468"/>
-      <c r="H37" s="1471" t="str">
+      <c r="G37" s="1499"/>
+      <c r="H37" s="1501" t="str">
         <f>IF(O3="No","",Aashto!J26)</f>
         <v/>
       </c>
-      <c r="I37" s="1471"/>
+      <c r="I37" s="1501"/>
       <c r="J37" s="200"/>
       <c r="K37" s="201"/>
       <c r="L37" s="3"/>
@@ -41555,19 +41567,19 @@
       <c r="A38" s="208">
         <v>200</v>
       </c>
-      <c r="B38" s="1463">
+      <c r="B38" s="1495">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="C38" s="1463"/>
+      <c r="C38" s="1495"/>
       <c r="D38" s="209">
         <f t="shared" si="4"/>
         <v>13.456812316430202</v>
       </c>
       <c r="E38" s="197"/>
-      <c r="F38" s="1469"/>
-      <c r="G38" s="1469"/>
-      <c r="H38" s="1472"/>
-      <c r="I38" s="1472"/>
+      <c r="F38" s="1500"/>
+      <c r="G38" s="1500"/>
+      <c r="H38" s="1502"/>
+      <c r="I38" s="1502"/>
       <c r="J38" s="200"/>
       <c r="K38" s="201"/>
       <c r="L38" s="3"/>
@@ -42459,19 +42471,19 @@
       <c r="Z63" s="37"/>
     </row>
     <row r="64" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1485" t="s">
+      <c r="A64" s="1463" t="s">
         <v>345</v>
       </c>
-      <c r="B64" s="1485"/>
-      <c r="C64" s="1485"/>
-      <c r="D64" s="1485"/>
-      <c r="E64" s="1485"/>
-      <c r="F64" s="1485"/>
-      <c r="G64" s="1485"/>
-      <c r="H64" s="1485"/>
-      <c r="I64" s="1485"/>
-      <c r="J64" s="1485"/>
-      <c r="K64" s="1485"/>
+      <c r="B64" s="1463"/>
+      <c r="C64" s="1463"/>
+      <c r="D64" s="1463"/>
+      <c r="E64" s="1463"/>
+      <c r="F64" s="1463"/>
+      <c r="G64" s="1463"/>
+      <c r="H64" s="1463"/>
+      <c r="I64" s="1463"/>
+      <c r="J64" s="1463"/>
+      <c r="K64" s="1463"/>
       <c r="W64" s="37"/>
       <c r="X64" s="37"/>
       <c r="Y64" s="37"/>
@@ -42507,6 +42519,29 @@
     <protectedRange sqref="C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="F35:G36"/>
+    <mergeCell ref="F37:G38"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="F30:F32"/>
     <mergeCell ref="G30:G32"/>
     <mergeCell ref="A64:K64"/>
@@ -42523,29 +42558,6 @@
     <mergeCell ref="F23:H24"/>
     <mergeCell ref="I23:I24"/>
     <mergeCell ref="F26:I27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="F35:G36"/>
-    <mergeCell ref="F37:G38"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="H37:I38"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -42673,35 +42685,35 @@
       <c r="K7" s="118"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1504" t="s">
+      <c r="A8" s="1522" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1504"/>
-      <c r="C8" s="1504"/>
-      <c r="D8" s="1504"/>
-      <c r="E8" s="1504"/>
-      <c r="F8" s="1504"/>
-      <c r="G8" s="1504"/>
-      <c r="H8" s="1504"/>
-      <c r="I8" s="1504"/>
-      <c r="J8" s="1504"/>
-      <c r="K8" s="1504"/>
+      <c r="B8" s="1522"/>
+      <c r="C8" s="1522"/>
+      <c r="D8" s="1522"/>
+      <c r="E8" s="1522"/>
+      <c r="F8" s="1522"/>
+      <c r="G8" s="1522"/>
+      <c r="H8" s="1522"/>
+      <c r="I8" s="1522"/>
+      <c r="J8" s="1522"/>
+      <c r="K8" s="1522"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1505">
+      <c r="A9" s="1523">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="1505"/>
-      <c r="C9" s="1505"/>
-      <c r="D9" s="1505"/>
-      <c r="E9" s="1505"/>
-      <c r="F9" s="1505"/>
-      <c r="G9" s="1505"/>
-      <c r="H9" s="1505"/>
-      <c r="I9" s="1505"/>
-      <c r="J9" s="1505"/>
-      <c r="K9" s="1505"/>
+      <c r="B9" s="1523"/>
+      <c r="C9" s="1523"/>
+      <c r="D9" s="1523"/>
+      <c r="E9" s="1523"/>
+      <c r="F9" s="1523"/>
+      <c r="G9" s="1523"/>
+      <c r="H9" s="1523"/>
+      <c r="I9" s="1523"/>
+      <c r="J9" s="1523"/>
+      <c r="K9" s="1523"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -42724,14 +42736,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1506" t="s">
+      <c r="C11" s="1524" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="1506"/>
-      <c r="E11" s="1506"/>
-      <c r="F11" s="1506"/>
-      <c r="G11" s="1506"/>
-      <c r="H11" s="1506"/>
+      <c r="D11" s="1524"/>
+      <c r="E11" s="1524"/>
+      <c r="F11" s="1524"/>
+      <c r="G11" s="1524"/>
+      <c r="H11" s="1524"/>
       <c r="I11" s="121" t="s">
         <v>3</v>
       </c>
@@ -42752,14 +42764,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1506" t="s">
+      <c r="C12" s="1524" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="1506"/>
-      <c r="E12" s="1506"/>
-      <c r="F12" s="1506"/>
-      <c r="G12" s="1506"/>
-      <c r="H12" s="1506"/>
+      <c r="D12" s="1524"/>
+      <c r="E12" s="1524"/>
+      <c r="F12" s="1524"/>
+      <c r="G12" s="1524"/>
+      <c r="H12" s="1524"/>
       <c r="I12" s="26" t="s">
         <v>6</v>
       </c>
@@ -42783,14 +42795,14 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1506" t="s">
+      <c r="C13" s="1524" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="1506"/>
-      <c r="E13" s="1506"/>
-      <c r="F13" s="1506"/>
-      <c r="G13" s="1506"/>
-      <c r="H13" s="1506"/>
+      <c r="D13" s="1524"/>
+      <c r="E13" s="1524"/>
+      <c r="F13" s="1524"/>
+      <c r="G13" s="1524"/>
+      <c r="H13" s="1524"/>
       <c r="I13" s="26" t="s">
         <v>288</v>
       </c>
@@ -42804,8 +42816,8 @@
       <c r="M13" s="124"/>
       <c r="P13" s="127"/>
       <c r="Q13" s="127"/>
-      <c r="R13" s="1503"/>
-      <c r="S13" s="1503"/>
+      <c r="R13" s="1521"/>
+      <c r="S13" s="1521"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -42827,19 +42839,19 @@
       <c r="S14" s="737"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1507" t="s">
+      <c r="A15" s="1510" t="s">
         <v>347</v>
       </c>
-      <c r="B15" s="1508"/>
-      <c r="C15" s="1508"/>
-      <c r="D15" s="1508"/>
-      <c r="E15" s="1508"/>
-      <c r="F15" s="1508"/>
-      <c r="G15" s="1508"/>
-      <c r="H15" s="1508"/>
-      <c r="I15" s="1508"/>
-      <c r="J15" s="1508"/>
-      <c r="K15" s="1509"/>
+      <c r="B15" s="1511"/>
+      <c r="C15" s="1511"/>
+      <c r="D15" s="1511"/>
+      <c r="E15" s="1511"/>
+      <c r="F15" s="1511"/>
+      <c r="G15" s="1511"/>
+      <c r="H15" s="1511"/>
+      <c r="I15" s="1511"/>
+      <c r="J15" s="1511"/>
+      <c r="K15" s="1512"/>
       <c r="L15" s="124"/>
       <c r="M15" s="124"/>
       <c r="P15" s="127"/>
@@ -42848,19 +42860,19 @@
       <c r="S15" s="737"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1510" t="s">
+      <c r="A16" s="1513" t="s">
         <v>348</v>
       </c>
-      <c r="B16" s="1511"/>
-      <c r="C16" s="1511"/>
-      <c r="D16" s="1511"/>
-      <c r="E16" s="1511"/>
-      <c r="F16" s="1511"/>
-      <c r="G16" s="1511"/>
-      <c r="H16" s="1511"/>
-      <c r="I16" s="1511"/>
-      <c r="J16" s="1511"/>
-      <c r="K16" s="1512"/>
+      <c r="B16" s="1514"/>
+      <c r="C16" s="1514"/>
+      <c r="D16" s="1514"/>
+      <c r="E16" s="1514"/>
+      <c r="F16" s="1514"/>
+      <c r="G16" s="1514"/>
+      <c r="H16" s="1514"/>
+      <c r="I16" s="1514"/>
+      <c r="J16" s="1514"/>
+      <c r="K16" s="1515"/>
       <c r="L16" s="124"/>
       <c r="M16" s="124"/>
       <c r="P16" s="127"/>
@@ -42888,19 +42900,19 @@
       <c r="S17" s="737"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1477" t="s">
+      <c r="A18" s="1485" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1478"/>
-      <c r="C18" s="1478"/>
-      <c r="D18" s="1478"/>
-      <c r="E18" s="1478"/>
-      <c r="F18" s="1478"/>
-      <c r="G18" s="1478"/>
-      <c r="H18" s="1478"/>
-      <c r="I18" s="1478"/>
-      <c r="J18" s="1478"/>
-      <c r="K18" s="1479"/>
+      <c r="B18" s="1486"/>
+      <c r="C18" s="1486"/>
+      <c r="D18" s="1486"/>
+      <c r="E18" s="1486"/>
+      <c r="F18" s="1486"/>
+      <c r="G18" s="1486"/>
+      <c r="H18" s="1486"/>
+      <c r="I18" s="1486"/>
+      <c r="J18" s="1486"/>
+      <c r="K18" s="1487"/>
       <c r="M18" s="124"/>
       <c r="P18" s="127"/>
       <c r="Q18" s="127"/>
@@ -43017,8 +43029,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="805"/>
-      <c r="I23" s="1513"/>
-      <c r="J23" s="1513"/>
+      <c r="I23" s="1516"/>
+      <c r="J23" s="1516"/>
       <c r="K23" s="806"/>
       <c r="L23" s="124"/>
       <c r="M23" s="139"/>
@@ -43026,41 +43038,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="141"/>
-      <c r="D24" s="1514" t="s">
+      <c r="D24" s="1517" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="1515"/>
-      <c r="F24" s="1515"/>
-      <c r="G24" s="1516" t="s">
+      <c r="E24" s="1518"/>
+      <c r="F24" s="1518"/>
+      <c r="G24" s="1519" t="s">
         <v>352</v>
       </c>
-      <c r="H24" s="1517"/>
-      <c r="I24" s="1518"/>
-      <c r="J24" s="1518"/>
+      <c r="H24" s="1520"/>
+      <c r="I24" s="1508"/>
+      <c r="J24" s="1508"/>
       <c r="K24" s="142"/>
       <c r="L24" s="124"/>
       <c r="M24" s="143"/>
-      <c r="O24" s="1519" t="s">
+      <c r="O24" s="1503" t="s">
         <v>351</v>
       </c>
-      <c r="P24" s="1520"/>
+      <c r="P24" s="1504"/>
       <c r="Q24" s="807" t="s">
         <v>350</v>
       </c>
-      <c r="R24" s="1519" t="s">
+      <c r="R24" s="1503" t="s">
         <v>352</v>
       </c>
-      <c r="S24" s="1521"/>
+      <c r="S24" s="1505"/>
       <c r="T24" s="807" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="141"/>
-      <c r="B25" s="1522" t="s">
+      <c r="B25" s="1506" t="s">
         <v>353</v>
       </c>
-      <c r="C25" s="1523"/>
+      <c r="C25" s="1507"/>
       <c r="D25" s="808" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -43081,8 +43093,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="1518"/>
-      <c r="J25" s="1518"/>
+      <c r="I25" s="1508"/>
+      <c r="J25" s="1508"/>
       <c r="K25" s="142"/>
       <c r="L25" s="124"/>
       <c r="M25" s="143"/>
@@ -43131,8 +43143,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="1524"/>
-      <c r="J26" s="1524"/>
+      <c r="I26" s="1509"/>
+      <c r="J26" s="1509"/>
       <c r="K26" s="151"/>
       <c r="L26" s="152"/>
       <c r="M26" s="143"/>
@@ -43847,19 +43859,19 @@
     </row>
     <row r="49" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1485" t="s">
+      <c r="A50" s="1463" t="s">
         <v>345</v>
       </c>
-      <c r="B50" s="1485"/>
-      <c r="C50" s="1485"/>
-      <c r="D50" s="1485"/>
-      <c r="E50" s="1485"/>
-      <c r="F50" s="1485"/>
-      <c r="G50" s="1485"/>
-      <c r="H50" s="1485"/>
-      <c r="I50" s="1485"/>
-      <c r="J50" s="1485"/>
-      <c r="K50" s="1485"/>
+      <c r="B50" s="1463"/>
+      <c r="C50" s="1463"/>
+      <c r="D50" s="1463"/>
+      <c r="E50" s="1463"/>
+      <c r="F50" s="1463"/>
+      <c r="G50" s="1463"/>
+      <c r="H50" s="1463"/>
+      <c r="I50" s="1463"/>
+      <c r="J50" s="1463"/>
+      <c r="K50" s="1463"/>
     </row>
     <row r="51" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -43869,11 +43881,12 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -43882,12 +43895,11 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0700-000000000000}">

--- a/app/templates/informes/Proctor/Template_Proctor.xlsx
+++ b/app/templates/informes/Proctor/Template_Proctor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Proctor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1452E359-22A3-4FDB-BA7A-97C1E538353F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32786F6F-23D0-48A5-A7B1-610B1D93056E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="613" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="668">
   <si>
     <t>LABORATORIO DE ENSAYO DE MATERIALES</t>
   </si>
@@ -2555,9 +2555,6 @@
   </si>
   <si>
     <t>- De conformidad con lo dispuesto por el artículo 1321 del Código Civil, queda establecido que en ningún caso la responsabilidad de GEOFAL S.A.C. será mayor al valor del servicio prestado.</t>
-  </si>
-  <si>
-    <t>Versión: 08 (15-06-2026)</t>
   </si>
   <si>
     <t>Versión: 08 (11-06-2026)</t>
@@ -9661,6 +9658,157 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="22" fillId="3" borderId="166" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="209" fontId="25" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="3" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -9668,19 +9816,6 @@
     <xf numFmtId="0" fontId="58" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9688,15 +9823,11 @@
     <xf numFmtId="0" fontId="58" fillId="3" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -9708,220 +9839,85 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="22" fillId="3" borderId="166" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="209" fontId="25" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="3" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9965,75 +9961,73 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10042,6 +10036,69 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -10051,89 +10108,29 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="18" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="102" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10159,26 +10156,29 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="18" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10190,6 +10190,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="193" fontId="81" fillId="0" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10233,18 +10246,79 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -10252,16 +10326,10 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10290,10 +10358,6 @@
     <xf numFmtId="0" fontId="58" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -10312,9 +10376,6 @@
     <xf numFmtId="164" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10327,87 +10388,19 @@
     <xf numFmtId="0" fontId="58" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10448,39 +10441,97 @@
     <xf numFmtId="172" fontId="56" fillId="3" borderId="58" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="117" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="117" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="112" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="113" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="119" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="11" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -10533,57 +10584,6 @@
     <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="117" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="117" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="48" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="112" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="113" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="119" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="46" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="9" borderId="149" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10673,9 +10673,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -17454,90 +17451,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1317"/>
-      <c r="B1" s="1318"/>
-      <c r="C1" s="1318"/>
-      <c r="D1" s="1318"/>
-      <c r="E1" s="1318"/>
-      <c r="F1" s="1318"/>
-      <c r="G1" s="1318"/>
-      <c r="H1" s="1318"/>
-      <c r="I1" s="1319"/>
+      <c r="A1" s="1279"/>
+      <c r="B1" s="1280"/>
+      <c r="C1" s="1280"/>
+      <c r="D1" s="1280"/>
+      <c r="E1" s="1280"/>
+      <c r="F1" s="1280"/>
+      <c r="G1" s="1280"/>
+      <c r="H1" s="1280"/>
+      <c r="I1" s="1281"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1320"/>
-      <c r="B2" s="1321"/>
-      <c r="C2" s="1321"/>
-      <c r="D2" s="1321"/>
-      <c r="E2" s="1321"/>
-      <c r="F2" s="1321"/>
-      <c r="G2" s="1321"/>
-      <c r="H2" s="1321"/>
-      <c r="I2" s="1322"/>
+      <c r="A2" s="1282"/>
+      <c r="B2" s="1283"/>
+      <c r="C2" s="1283"/>
+      <c r="D2" s="1283"/>
+      <c r="E2" s="1283"/>
+      <c r="F2" s="1283"/>
+      <c r="G2" s="1283"/>
+      <c r="H2" s="1283"/>
+      <c r="I2" s="1284"/>
       <c r="K2" s="1266" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="1267"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1320"/>
-      <c r="B3" s="1321"/>
-      <c r="C3" s="1321"/>
-      <c r="D3" s="1321"/>
-      <c r="E3" s="1321"/>
-      <c r="F3" s="1321"/>
-      <c r="G3" s="1321"/>
-      <c r="H3" s="1321"/>
-      <c r="I3" s="1322"/>
+      <c r="A3" s="1282"/>
+      <c r="B3" s="1283"/>
+      <c r="C3" s="1283"/>
+      <c r="D3" s="1283"/>
+      <c r="E3" s="1283"/>
+      <c r="F3" s="1283"/>
+      <c r="G3" s="1283"/>
+      <c r="H3" s="1283"/>
+      <c r="I3" s="1284"/>
       <c r="K3" s="1266" t="s">
         <v>5</v>
       </c>
       <c r="L3" s="1268"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1323"/>
-      <c r="B4" s="1324"/>
-      <c r="C4" s="1324"/>
-      <c r="D4" s="1324"/>
-      <c r="E4" s="1324"/>
-      <c r="F4" s="1324"/>
-      <c r="G4" s="1324"/>
-      <c r="H4" s="1324"/>
-      <c r="I4" s="1325"/>
+      <c r="A4" s="1285"/>
+      <c r="B4" s="1286"/>
+      <c r="C4" s="1286"/>
+      <c r="D4" s="1286"/>
+      <c r="E4" s="1286"/>
+      <c r="F4" s="1286"/>
+      <c r="G4" s="1286"/>
+      <c r="H4" s="1286"/>
+      <c r="I4" s="1287"/>
       <c r="K4" s="1266" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="1268"/>
     </row>
     <row r="5" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1326" t="s">
+      <c r="A5" s="1288" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1326"/>
-      <c r="C5" s="1326"/>
-      <c r="D5" s="1326"/>
-      <c r="E5" s="1326"/>
-      <c r="F5" s="1326"/>
-      <c r="G5" s="1326"/>
-      <c r="H5" s="1326"/>
-      <c r="I5" s="1326"/>
+      <c r="B5" s="1288"/>
+      <c r="C5" s="1288"/>
+      <c r="D5" s="1288"/>
+      <c r="E5" s="1288"/>
+      <c r="F5" s="1288"/>
+      <c r="G5" s="1288"/>
+      <c r="H5" s="1288"/>
+      <c r="I5" s="1288"/>
       <c r="K5" s="1266" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="1268"/>
     </row>
     <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1327" t="s">
+      <c r="A6" s="1289" t="s">
         <v>587</v>
       </c>
-      <c r="B6" s="1327"/>
-      <c r="C6" s="1327"/>
-      <c r="D6" s="1327"/>
-      <c r="E6" s="1327"/>
-      <c r="F6" s="1327"/>
-      <c r="G6" s="1327"/>
-      <c r="H6" s="1327"/>
-      <c r="I6" s="1327"/>
+      <c r="B6" s="1289"/>
+      <c r="C6" s="1289"/>
+      <c r="D6" s="1289"/>
+      <c r="E6" s="1289"/>
+      <c r="F6" s="1289"/>
+      <c r="G6" s="1289"/>
+      <c r="H6" s="1289"/>
+      <c r="I6" s="1289"/>
       <c r="K6" s="1269"/>
       <c r="L6" s="1270"/>
     </row>
@@ -17561,15 +17558,15 @@
       <c r="B8" s="1170" t="s">
         <v>588</v>
       </c>
-      <c r="C8" s="1328" t="s">
+      <c r="C8" s="1290" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1329"/>
+      <c r="D8" s="1291"/>
       <c r="E8" s="1172"/>
-      <c r="F8" s="1330" t="s">
+      <c r="F8" s="1292" t="s">
         <v>589</v>
       </c>
-      <c r="G8" s="1329"/>
+      <c r="G8" s="1291"/>
       <c r="H8" s="1171" t="s">
         <v>590</v>
       </c>
@@ -17581,11 +17578,11 @@
     </row>
     <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1173"/>
-      <c r="C9" s="1314"/>
-      <c r="D9" s="1315"/>
+      <c r="C9" s="1276"/>
+      <c r="D9" s="1277"/>
       <c r="E9" s="1174"/>
-      <c r="F9" s="1316"/>
-      <c r="G9" s="1315"/>
+      <c r="F9" s="1278"/>
+      <c r="G9" s="1277"/>
       <c r="H9" s="1175"/>
       <c r="I9" s="243"/>
       <c r="K9" s="1266" t="s">
@@ -17595,46 +17592,46 @@
     </row>
     <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1176"/>
-      <c r="B10" s="1305"/>
-      <c r="C10" s="1305"/>
-      <c r="D10" s="1305"/>
+      <c r="B10" s="1293"/>
+      <c r="C10" s="1293"/>
+      <c r="D10" s="1293"/>
       <c r="E10" s="1177"/>
-      <c r="F10" s="1305"/>
-      <c r="G10" s="1305"/>
+      <c r="F10" s="1293"/>
+      <c r="G10" s="1293"/>
       <c r="H10" s="1177"/>
       <c r="I10" s="1178"/>
       <c r="K10" s="1269"/>
       <c r="L10" s="1270"/>
     </row>
     <row r="11" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1306" t="s">
+      <c r="A11" s="1294" t="s">
         <v>591</v>
       </c>
-      <c r="B11" s="1307"/>
-      <c r="C11" s="1307"/>
-      <c r="D11" s="1307"/>
-      <c r="E11" s="1307"/>
-      <c r="F11" s="1307"/>
-      <c r="G11" s="1307"/>
-      <c r="H11" s="1307"/>
-      <c r="I11" s="1308"/>
+      <c r="B11" s="1295"/>
+      <c r="C11" s="1295"/>
+      <c r="D11" s="1295"/>
+      <c r="E11" s="1295"/>
+      <c r="F11" s="1295"/>
+      <c r="G11" s="1295"/>
+      <c r="H11" s="1295"/>
+      <c r="I11" s="1296"/>
       <c r="K11" s="1266" t="s">
         <v>15</v>
       </c>
       <c r="L11" s="1270"/>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1309" t="s">
+      <c r="A12" s="1297" t="s">
         <v>531</v>
       </c>
-      <c r="B12" s="1310"/>
-      <c r="C12" s="1310"/>
-      <c r="D12" s="1310"/>
-      <c r="E12" s="1310"/>
-      <c r="F12" s="1310"/>
-      <c r="G12" s="1310"/>
-      <c r="H12" s="1310"/>
-      <c r="I12" s="1311"/>
+      <c r="B12" s="1298"/>
+      <c r="C12" s="1298"/>
+      <c r="D12" s="1298"/>
+      <c r="E12" s="1298"/>
+      <c r="F12" s="1298"/>
+      <c r="G12" s="1298"/>
+      <c r="H12" s="1298"/>
+      <c r="I12" s="1299"/>
       <c r="K12" s="1266" t="s">
         <v>18</v>
       </c>
@@ -17673,17 +17670,17 @@
       <c r="L14" s="1270"/>
     </row>
     <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1296" t="s">
+      <c r="A15" s="1300" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1296"/>
+      <c r="B15" s="1300"/>
       <c r="C15" s="1188" t="s">
         <v>593</v>
       </c>
-      <c r="D15" s="1312">
+      <c r="D15" s="1301">
         <v>1</v>
       </c>
-      <c r="E15" s="1313"/>
+      <c r="E15" s="1302"/>
       <c r="F15" s="1190">
         <v>2</v>
       </c>
@@ -17702,17 +17699,17 @@
       <c r="L15" s="1272"/>
     </row>
     <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1288" t="s">
+      <c r="A16" s="1303" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1288"/>
+      <c r="B16" s="1303"/>
       <c r="C16" s="1191" t="s">
         <v>593</v>
       </c>
-      <c r="D16" s="1299">
+      <c r="D16" s="1304">
         <v>5</v>
       </c>
-      <c r="E16" s="1300"/>
+      <c r="E16" s="1305"/>
       <c r="F16" s="1193">
         <v>5</v>
       </c>
@@ -17731,15 +17728,15 @@
       <c r="L16" s="1272"/>
     </row>
     <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1288" t="s">
+      <c r="A17" s="1303" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1288"/>
+      <c r="B17" s="1303"/>
       <c r="C17" s="1191" t="s">
         <v>593</v>
       </c>
-      <c r="D17" s="1299"/>
-      <c r="E17" s="1300"/>
+      <c r="D17" s="1304"/>
+      <c r="E17" s="1305"/>
       <c r="F17" s="1193"/>
       <c r="G17" s="1192"/>
       <c r="H17" s="1192"/>
@@ -17750,75 +17747,75 @@
       <c r="L17" s="1273"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1288" t="s">
+      <c r="A18" s="1303" t="s">
         <v>594</v>
       </c>
-      <c r="B18" s="1288"/>
+      <c r="B18" s="1303"/>
       <c r="C18" s="1192" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="1299"/>
-      <c r="E18" s="1300"/>
+      <c r="D18" s="1304"/>
+      <c r="E18" s="1305"/>
       <c r="F18" s="1194"/>
       <c r="G18" s="1195"/>
       <c r="H18" s="1195"/>
       <c r="I18" s="1194"/>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1288" t="s">
+      <c r="A19" s="1303" t="s">
         <v>595</v>
       </c>
-      <c r="B19" s="1288"/>
+      <c r="B19" s="1303"/>
       <c r="C19" s="1192" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="1299"/>
-      <c r="E19" s="1300"/>
+      <c r="D19" s="1304"/>
+      <c r="E19" s="1305"/>
       <c r="F19" s="1193"/>
       <c r="G19" s="1192"/>
       <c r="H19" s="1196"/>
       <c r="I19" s="1197"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1301" t="s">
+      <c r="A20" s="1306" t="s">
         <v>596</v>
       </c>
-      <c r="B20" s="1302"/>
+      <c r="B20" s="1307"/>
       <c r="C20" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D20" s="1299"/>
-      <c r="E20" s="1300"/>
+      <c r="D20" s="1304"/>
+      <c r="E20" s="1305"/>
       <c r="F20" s="1193"/>
       <c r="G20" s="1192"/>
       <c r="H20" s="1196"/>
       <c r="I20" s="1197"/>
     </row>
     <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1288" t="s">
+      <c r="A21" s="1303" t="s">
         <v>597</v>
       </c>
-      <c r="B21" s="1288"/>
+      <c r="B21" s="1303"/>
       <c r="C21" s="1192" t="s">
         <v>598</v>
       </c>
-      <c r="D21" s="1303"/>
-      <c r="E21" s="1304"/>
+      <c r="D21" s="1308"/>
+      <c r="E21" s="1309"/>
       <c r="F21" s="1193"/>
       <c r="G21" s="1192"/>
       <c r="H21" s="1192"/>
       <c r="I21" s="1193"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1291" t="s">
+      <c r="A22" s="1310" t="s">
         <v>599</v>
       </c>
-      <c r="B22" s="1291"/>
+      <c r="B22" s="1310"/>
       <c r="C22" s="1199" t="s">
         <v>600</v>
       </c>
-      <c r="D22" s="1294"/>
-      <c r="E22" s="1295"/>
+      <c r="D22" s="1311"/>
+      <c r="E22" s="1312"/>
       <c r="F22" s="1200"/>
       <c r="G22" s="1201"/>
       <c r="H22" s="1201"/>
@@ -17838,148 +17835,148 @@
       <c r="I23" s="1202"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1296" t="s">
+      <c r="A24" s="1300" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="1296"/>
+      <c r="B24" s="1300"/>
       <c r="C24" s="1203"/>
-      <c r="D24" s="1297"/>
-      <c r="E24" s="1298"/>
+      <c r="D24" s="1313"/>
+      <c r="E24" s="1314"/>
       <c r="F24" s="1205"/>
       <c r="G24" s="1204"/>
       <c r="H24" s="1204"/>
       <c r="I24" s="1205"/>
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1288" t="s">
+      <c r="A25" s="1303" t="s">
         <v>601</v>
       </c>
-      <c r="B25" s="1288"/>
+      <c r="B25" s="1303"/>
       <c r="C25" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D25" s="1289"/>
-      <c r="E25" s="1290"/>
+      <c r="D25" s="1315"/>
+      <c r="E25" s="1316"/>
       <c r="F25" s="1207"/>
       <c r="G25" s="1206"/>
       <c r="H25" s="1206"/>
       <c r="I25" s="1207"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1288" t="s">
+      <c r="A26" s="1303" t="s">
         <v>602</v>
       </c>
-      <c r="B26" s="1288"/>
+      <c r="B26" s="1303"/>
       <c r="C26" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="1289"/>
-      <c r="E26" s="1290"/>
+      <c r="D26" s="1315"/>
+      <c r="E26" s="1316"/>
       <c r="F26" s="1207"/>
       <c r="G26" s="1206"/>
       <c r="H26" s="1206"/>
       <c r="I26" s="1207"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1288" t="s">
+      <c r="A27" s="1303" t="s">
         <v>603</v>
       </c>
-      <c r="B27" s="1288"/>
+      <c r="B27" s="1303"/>
       <c r="C27" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="1289"/>
-      <c r="E27" s="1290"/>
+      <c r="D27" s="1315"/>
+      <c r="E27" s="1316"/>
       <c r="F27" s="1207"/>
       <c r="G27" s="1206"/>
       <c r="H27" s="1206"/>
       <c r="I27" s="1207"/>
     </row>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1288" t="s">
+      <c r="A28" s="1303" t="s">
         <v>604</v>
       </c>
-      <c r="B28" s="1288"/>
+      <c r="B28" s="1303"/>
       <c r="C28" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D28" s="1289"/>
-      <c r="E28" s="1290"/>
+      <c r="D28" s="1315"/>
+      <c r="E28" s="1316"/>
       <c r="F28" s="1207"/>
       <c r="G28" s="1206"/>
       <c r="H28" s="1206"/>
       <c r="I28" s="1207"/>
     </row>
     <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1288" t="s">
+      <c r="A29" s="1303" t="s">
         <v>605</v>
       </c>
-      <c r="B29" s="1288"/>
+      <c r="B29" s="1303"/>
       <c r="C29" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="1289"/>
-      <c r="E29" s="1290"/>
+      <c r="D29" s="1315"/>
+      <c r="E29" s="1316"/>
       <c r="F29" s="1208"/>
       <c r="G29" s="1209"/>
       <c r="H29" s="1209"/>
       <c r="I29" s="1208"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1288" t="s">
+      <c r="A30" s="1303" t="s">
         <v>606</v>
       </c>
-      <c r="B30" s="1288"/>
+      <c r="B30" s="1303"/>
       <c r="C30" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D30" s="1289"/>
-      <c r="E30" s="1290"/>
+      <c r="D30" s="1315"/>
+      <c r="E30" s="1316"/>
       <c r="F30" s="1208"/>
       <c r="G30" s="1209"/>
       <c r="H30" s="1209"/>
       <c r="I30" s="1208"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1288" t="s">
+      <c r="A31" s="1303" t="s">
         <v>607</v>
       </c>
-      <c r="B31" s="1288"/>
+      <c r="B31" s="1303"/>
       <c r="C31" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D31" s="1289"/>
-      <c r="E31" s="1290"/>
+      <c r="D31" s="1315"/>
+      <c r="E31" s="1316"/>
       <c r="F31" s="1208"/>
       <c r="G31" s="1209"/>
       <c r="H31" s="1209"/>
       <c r="I31" s="1208"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1288" t="s">
+      <c r="A32" s="1303" t="s">
         <v>608</v>
       </c>
-      <c r="B32" s="1288"/>
+      <c r="B32" s="1303"/>
       <c r="C32" s="1192" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="1289"/>
-      <c r="E32" s="1290"/>
+      <c r="D32" s="1315"/>
+      <c r="E32" s="1316"/>
       <c r="F32" s="1210"/>
       <c r="G32" s="1211"/>
       <c r="H32" s="1211"/>
       <c r="I32" s="1210"/>
     </row>
     <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1291" t="s">
+      <c r="A33" s="1310" t="s">
         <v>609</v>
       </c>
-      <c r="B33" s="1291"/>
+      <c r="B33" s="1310"/>
       <c r="C33" s="1199" t="s">
         <v>600</v>
       </c>
-      <c r="D33" s="1292"/>
-      <c r="E33" s="1293"/>
+      <c r="D33" s="1317"/>
+      <c r="E33" s="1318"/>
       <c r="F33" s="1200"/>
       <c r="G33" s="1201"/>
       <c r="H33" s="1201"/>
@@ -18005,19 +18002,19 @@
         <v>611</v>
       </c>
       <c r="B35" s="1217"/>
-      <c r="C35" s="1283"/>
-      <c r="D35" s="1284"/>
+      <c r="C35" s="1319"/>
+      <c r="D35" s="1320"/>
       <c r="E35" s="1218"/>
-      <c r="F35" s="1281" t="s">
+      <c r="F35" s="1323" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="1281" t="s">
+      <c r="G35" s="1323" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="1281" t="s">
+      <c r="H35" s="1323" t="s">
         <v>612</v>
       </c>
-      <c r="I35" s="1281" t="s">
+      <c r="I35" s="1323" t="s">
         <v>231</v>
       </c>
     </row>
@@ -18026,21 +18023,21 @@
         <v>613</v>
       </c>
       <c r="B36" s="1220"/>
-      <c r="C36" s="1283"/>
-      <c r="D36" s="1284"/>
+      <c r="C36" s="1319"/>
+      <c r="D36" s="1320"/>
       <c r="E36" s="1218"/>
-      <c r="F36" s="1282"/>
-      <c r="G36" s="1282"/>
-      <c r="H36" s="1282"/>
-      <c r="I36" s="1282"/>
+      <c r="F36" s="1324"/>
+      <c r="G36" s="1324"/>
+      <c r="H36" s="1324"/>
+      <c r="I36" s="1324"/>
     </row>
     <row r="37" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1219" t="s">
         <v>614</v>
       </c>
       <c r="B37" s="1220"/>
-      <c r="C37" s="1285"/>
-      <c r="D37" s="1284"/>
+      <c r="C37" s="1325"/>
+      <c r="D37" s="1320"/>
       <c r="E37" s="1221"/>
       <c r="F37" s="1222" t="s">
         <v>615</v>
@@ -18054,8 +18051,8 @@
         <v>616</v>
       </c>
       <c r="B38" s="1227"/>
-      <c r="C38" s="1283"/>
-      <c r="D38" s="1284"/>
+      <c r="C38" s="1319"/>
+      <c r="D38" s="1320"/>
       <c r="E38" s="1218"/>
       <c r="F38" s="1222" t="s">
         <v>617</v>
@@ -18069,8 +18066,8 @@
         <v>618</v>
       </c>
       <c r="B39" s="1220"/>
-      <c r="C39" s="1283"/>
-      <c r="D39" s="1284"/>
+      <c r="C39" s="1319"/>
+      <c r="D39" s="1320"/>
       <c r="E39" s="1218"/>
       <c r="F39" s="1222" t="s">
         <v>110</v>
@@ -18099,8 +18096,8 @@
         <v>619</v>
       </c>
       <c r="B41" s="1230"/>
-      <c r="C41" s="1277"/>
-      <c r="D41" s="1277"/>
+      <c r="C41" s="1326"/>
+      <c r="D41" s="1326"/>
       <c r="E41" s="1228"/>
       <c r="F41" s="1222" t="s">
         <v>620</v>
@@ -18114,8 +18111,8 @@
         <v>621</v>
       </c>
       <c r="B42" s="1232"/>
-      <c r="C42" s="1277"/>
-      <c r="D42" s="1277"/>
+      <c r="C42" s="1326"/>
+      <c r="D42" s="1326"/>
       <c r="E42" s="1233"/>
       <c r="J42" s="1234"/>
     </row>
@@ -18124,17 +18121,17 @@
         <v>622</v>
       </c>
       <c r="B43" s="1236"/>
-      <c r="C43" s="1277"/>
-      <c r="D43" s="1277"/>
+      <c r="C43" s="1326"/>
+      <c r="D43" s="1326"/>
       <c r="E43" s="1233"/>
-      <c r="F43" s="1286" t="s">
+      <c r="F43" s="1327" t="s">
         <v>623</v>
       </c>
-      <c r="G43" s="1287"/>
-      <c r="H43" s="1275" t="s">
+      <c r="G43" s="1328"/>
+      <c r="H43" s="1321" t="s">
         <v>624</v>
       </c>
-      <c r="I43" s="1276"/>
+      <c r="I43" s="1322"/>
       <c r="J43" s="1234"/>
     </row>
     <row r="44" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18142,31 +18139,31 @@
         <v>625</v>
       </c>
       <c r="B44" s="1232"/>
-      <c r="C44" s="1277"/>
-      <c r="D44" s="1277"/>
+      <c r="C44" s="1326"/>
+      <c r="D44" s="1326"/>
       <c r="E44" s="1233"/>
       <c r="F44" s="1237" t="s">
         <v>626</v>
       </c>
       <c r="G44" s="1238"/>
-      <c r="H44" s="1275"/>
-      <c r="I44" s="1276"/>
+      <c r="H44" s="1321"/>
+      <c r="I44" s="1322"/>
       <c r="J44" s="1234"/>
     </row>
     <row r="45" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1279" t="s">
+      <c r="A45" s="1330" t="s">
         <v>627</v>
       </c>
-      <c r="B45" s="1280"/>
-      <c r="C45" s="1277"/>
-      <c r="D45" s="1277"/>
+      <c r="B45" s="1331"/>
+      <c r="C45" s="1326"/>
+      <c r="D45" s="1326"/>
       <c r="E45" s="1233"/>
       <c r="F45" s="1237" t="s">
         <v>628</v>
       </c>
       <c r="G45" s="1238"/>
-      <c r="H45" s="1275"/>
-      <c r="I45" s="1276"/>
+      <c r="H45" s="1321"/>
+      <c r="I45" s="1322"/>
       <c r="J45" s="1234"/>
     </row>
     <row r="46" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18180,8 +18177,8 @@
         <v>629</v>
       </c>
       <c r="G46" s="1238"/>
-      <c r="H46" s="1275"/>
-      <c r="I46" s="1276"/>
+      <c r="H46" s="1321"/>
+      <c r="I46" s="1322"/>
     </row>
     <row r="47" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1242"/>
@@ -18192,8 +18189,8 @@
         <v>630</v>
       </c>
       <c r="G47" s="1238"/>
-      <c r="H47" s="1275"/>
-      <c r="I47" s="1276"/>
+      <c r="H47" s="1321"/>
+      <c r="I47" s="1322"/>
     </row>
     <row r="48" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1242"/>
@@ -18204,8 +18201,8 @@
         <v>582</v>
       </c>
       <c r="G48" s="1245"/>
-      <c r="H48" s="1275"/>
-      <c r="I48" s="1276"/>
+      <c r="H48" s="1321"/>
+      <c r="I48" s="1322"/>
     </row>
     <row r="49" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1246"/>
@@ -18216,8 +18213,8 @@
         <v>631</v>
       </c>
       <c r="G49" s="1238"/>
-      <c r="H49" s="1277"/>
-      <c r="I49" s="1277"/>
+      <c r="H49" s="1326"/>
+      <c r="I49" s="1326"/>
     </row>
     <row r="50" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E50" s="352"/>
@@ -18258,17 +18255,17 @@
     </row>
     <row r="55" spans="1:9" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1278" t="s">
+      <c r="A56" s="1329" t="s">
         <v>634</v>
       </c>
-      <c r="B56" s="1278"/>
-      <c r="C56" s="1278"/>
-      <c r="D56" s="1278"/>
-      <c r="E56" s="1278"/>
-      <c r="F56" s="1278"/>
-      <c r="G56" s="1278"/>
-      <c r="H56" s="1278"/>
-      <c r="I56" s="1278"/>
+      <c r="B56" s="1329"/>
+      <c r="C56" s="1329"/>
+      <c r="D56" s="1329"/>
+      <c r="E56" s="1329"/>
+      <c r="F56" s="1329"/>
+      <c r="G56" s="1329"/>
+      <c r="H56" s="1329"/>
+      <c r="I56" s="1329"/>
     </row>
     <row r="57" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -18278,54 +18275,16 @@
     <protectedRange sqref="B9:C10" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="71">
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="H35:H36"/>
@@ -18339,16 +18298,54 @@
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -18454,33 +18451,33 @@
       <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1522" t="s">
+      <c r="A8" s="1505" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1522"/>
-      <c r="C8" s="1522"/>
-      <c r="D8" s="1522"/>
-      <c r="E8" s="1522"/>
-      <c r="F8" s="1522"/>
-      <c r="G8" s="1522"/>
-      <c r="H8" s="1522"/>
-      <c r="I8" s="1522"/>
-      <c r="J8" s="1522"/>
+      <c r="B8" s="1505"/>
+      <c r="C8" s="1505"/>
+      <c r="D8" s="1505"/>
+      <c r="E8" s="1505"/>
+      <c r="F8" s="1505"/>
+      <c r="G8" s="1505"/>
+      <c r="H8" s="1505"/>
+      <c r="I8" s="1505"/>
+      <c r="J8" s="1505"/>
     </row>
     <row r="9" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1525">
+      <c r="A9" s="1530">
         <f>J13</f>
         <v>1</v>
       </c>
-      <c r="B9" s="1525"/>
-      <c r="C9" s="1525"/>
-      <c r="D9" s="1525"/>
-      <c r="E9" s="1525"/>
-      <c r="F9" s="1525"/>
-      <c r="G9" s="1525"/>
-      <c r="H9" s="1525"/>
-      <c r="I9" s="1525"/>
-      <c r="J9" s="1525"/>
+      <c r="B9" s="1530"/>
+      <c r="C9" s="1530"/>
+      <c r="D9" s="1530"/>
+      <c r="E9" s="1530"/>
+      <c r="F9" s="1530"/>
+      <c r="G9" s="1530"/>
+      <c r="H9" s="1530"/>
+      <c r="I9" s="1530"/>
+      <c r="J9" s="1530"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -18502,13 +18499,13 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1524" t="s">
+      <c r="C11" s="1507" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="1524"/>
-      <c r="E11" s="1524"/>
-      <c r="F11" s="1524"/>
-      <c r="G11" s="1524"/>
+      <c r="D11" s="1507"/>
+      <c r="E11" s="1507"/>
+      <c r="F11" s="1507"/>
+      <c r="G11" s="1507"/>
       <c r="H11" s="121" t="s">
         <v>3</v>
       </c>
@@ -18530,13 +18527,13 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1524" t="s">
+      <c r="C12" s="1507" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="1524"/>
-      <c r="E12" s="1524"/>
-      <c r="F12" s="1524"/>
-      <c r="G12" s="1524"/>
+      <c r="D12" s="1507"/>
+      <c r="E12" s="1507"/>
+      <c r="F12" s="1507"/>
+      <c r="G12" s="1507"/>
       <c r="H12" s="26" t="s">
         <v>6</v>
       </c>
@@ -18560,13 +18557,13 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1524" t="s">
+      <c r="C13" s="1507" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="1524"/>
-      <c r="E13" s="1524"/>
-      <c r="F13" s="1524"/>
-      <c r="G13" s="1524"/>
+      <c r="D13" s="1507"/>
+      <c r="E13" s="1507"/>
+      <c r="F13" s="1507"/>
+      <c r="G13" s="1507"/>
       <c r="H13" s="26" t="s">
         <v>288</v>
       </c>
@@ -18579,8 +18576,8 @@
       <c r="K13" s="124"/>
       <c r="L13" s="124"/>
       <c r="M13" s="124"/>
-      <c r="P13" s="1521"/>
-      <c r="Q13" s="1521"/>
+      <c r="P13" s="1504"/>
+      <c r="Q13" s="1504"/>
     </row>
     <row r="14" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -18600,34 +18597,34 @@
       <c r="Q14" s="737"/>
     </row>
     <row r="15" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1510" t="s">
+      <c r="A15" s="1508" t="s">
         <v>367</v>
       </c>
-      <c r="B15" s="1511"/>
-      <c r="C15" s="1511"/>
-      <c r="D15" s="1511"/>
-      <c r="E15" s="1511"/>
-      <c r="F15" s="1511"/>
-      <c r="G15" s="1511"/>
-      <c r="H15" s="1511"/>
-      <c r="I15" s="1511"/>
-      <c r="J15" s="1512"/>
+      <c r="B15" s="1509"/>
+      <c r="C15" s="1509"/>
+      <c r="D15" s="1509"/>
+      <c r="E15" s="1509"/>
+      <c r="F15" s="1509"/>
+      <c r="G15" s="1509"/>
+      <c r="H15" s="1509"/>
+      <c r="I15" s="1509"/>
+      <c r="J15" s="1510"/>
       <c r="K15" s="124"/>
       <c r="L15" s="124"/>
     </row>
     <row r="16" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1513" t="s">
+      <c r="A16" s="1511" t="s">
         <v>368</v>
       </c>
-      <c r="B16" s="1514"/>
-      <c r="C16" s="1514"/>
-      <c r="D16" s="1514"/>
-      <c r="E16" s="1514"/>
-      <c r="F16" s="1514"/>
-      <c r="G16" s="1514"/>
-      <c r="H16" s="1514"/>
-      <c r="I16" s="1514"/>
-      <c r="J16" s="1515"/>
+      <c r="B16" s="1512"/>
+      <c r="C16" s="1512"/>
+      <c r="D16" s="1512"/>
+      <c r="E16" s="1512"/>
+      <c r="F16" s="1512"/>
+      <c r="G16" s="1512"/>
+      <c r="H16" s="1512"/>
+      <c r="I16" s="1512"/>
+      <c r="J16" s="1513"/>
       <c r="K16" s="124"/>
       <c r="L16" s="124"/>
     </row>
@@ -18646,18 +18643,18 @@
       <c r="L17" s="124"/>
     </row>
     <row r="18" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1485" t="s">
+      <c r="A18" s="1478" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1486"/>
-      <c r="C18" s="1486"/>
-      <c r="D18" s="1486"/>
-      <c r="E18" s="1486"/>
-      <c r="F18" s="1486"/>
-      <c r="G18" s="1486"/>
-      <c r="H18" s="1486"/>
-      <c r="I18" s="1486"/>
-      <c r="J18" s="1487"/>
+      <c r="B18" s="1479"/>
+      <c r="C18" s="1479"/>
+      <c r="D18" s="1479"/>
+      <c r="E18" s="1479"/>
+      <c r="F18" s="1479"/>
+      <c r="G18" s="1479"/>
+      <c r="H18" s="1479"/>
+      <c r="I18" s="1479"/>
+      <c r="J18" s="1480"/>
       <c r="L18" s="124"/>
     </row>
     <row r="19" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -19355,18 +19352,18 @@
     </row>
     <row r="53" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1463" t="s">
+      <c r="A54" s="1486" t="s">
         <v>345</v>
       </c>
-      <c r="B54" s="1463"/>
-      <c r="C54" s="1463"/>
-      <c r="D54" s="1463"/>
-      <c r="E54" s="1463"/>
-      <c r="F54" s="1463"/>
-      <c r="G54" s="1463"/>
-      <c r="H54" s="1463"/>
-      <c r="I54" s="1463"/>
-      <c r="J54" s="1463"/>
+      <c r="B54" s="1486"/>
+      <c r="C54" s="1486"/>
+      <c r="D54" s="1486"/>
+      <c r="E54" s="1486"/>
+      <c r="F54" s="1486"/>
+      <c r="G54" s="1486"/>
+      <c r="H54" s="1486"/>
+      <c r="I54" s="1486"/>
+      <c r="J54" s="1486"/>
     </row>
     <row r="55" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19376,6 +19373,12 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="13">
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A16:J16"/>
@@ -19383,12 +19386,6 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -19420,15 +19417,15 @@
       <c r="A1" s="82" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="1547" t="s">
+      <c r="B1" s="1531" t="s">
         <v>390</v>
       </c>
-      <c r="C1" s="1547"/>
-      <c r="D1" s="1547"/>
-      <c r="E1" s="1547"/>
-      <c r="F1" s="1547"/>
-      <c r="G1" s="1547"/>
-      <c r="H1" s="1547"/>
+      <c r="C1" s="1531"/>
+      <c r="D1" s="1531"/>
+      <c r="E1" s="1531"/>
+      <c r="F1" s="1531"/>
+      <c r="G1" s="1531"/>
+      <c r="H1" s="1531"/>
       <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -19566,29 +19563,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="82"/>
-      <c r="B8" s="1548" t="s">
+      <c r="B8" s="1532" t="s">
         <v>402</v>
       </c>
-      <c r="C8" s="1548"/>
-      <c r="D8" s="1548"/>
+      <c r="C8" s="1532"/>
+      <c r="D8" s="1532"/>
       <c r="E8" s="830" t="s">
         <v>403</v>
       </c>
       <c r="F8" s="831" t="s">
         <v>404</v>
       </c>
-      <c r="G8" s="1549" t="s">
+      <c r="G8" s="1533" t="s">
         <v>405</v>
       </c>
-      <c r="H8" s="1549"/>
+      <c r="H8" s="1533"/>
       <c r="I8" s="82"/>
       <c r="L8" s="90" t="s">
         <v>406</v>
       </c>
-      <c r="M8" s="1550" t="s">
+      <c r="M8" s="1534" t="s">
         <v>407</v>
       </c>
-      <c r="N8" s="1550"/>
+      <c r="N8" s="1534"/>
       <c r="O8" s="91" t="s">
         <v>408</v>
       </c>
@@ -19601,13 +19598,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82"/>
-      <c r="B9" s="1551" t="s">
+      <c r="B9" s="1535" t="s">
         <v>411</v>
       </c>
-      <c r="C9" s="1553" t="s">
+      <c r="C9" s="1537" t="s">
         <v>412</v>
       </c>
-      <c r="D9" s="1555" t="s">
+      <c r="D9" s="1539" t="s">
         <v>413</v>
       </c>
       <c r="E9" s="832" t="s">
@@ -19616,10 +19613,10 @@
       <c r="F9" s="833" t="s">
         <v>415</v>
       </c>
-      <c r="G9" s="1556" t="s">
+      <c r="G9" s="1540" t="s">
         <v>416</v>
       </c>
-      <c r="H9" s="1557"/>
+      <c r="H9" s="1541"/>
       <c r="I9" s="82"/>
       <c r="L9" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -19648,19 +19645,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="82"/>
-      <c r="B10" s="1551"/>
-      <c r="C10" s="1553"/>
-      <c r="D10" s="1555"/>
+      <c r="B10" s="1535"/>
+      <c r="C10" s="1537"/>
+      <c r="D10" s="1539"/>
       <c r="E10" s="834" t="s">
         <v>417</v>
       </c>
       <c r="F10" s="835" t="s">
         <v>418</v>
       </c>
-      <c r="G10" s="1558" t="s">
+      <c r="G10" s="1542" t="s">
         <v>419</v>
       </c>
-      <c r="H10" s="1559"/>
+      <c r="H10" s="1543"/>
       <c r="I10" s="82"/>
       <c r="L10" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -19685,9 +19682,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="82"/>
-      <c r="B11" s="1551"/>
-      <c r="C11" s="1553"/>
-      <c r="D11" s="1555" t="s">
+      <c r="B11" s="1535"/>
+      <c r="C11" s="1537"/>
+      <c r="D11" s="1539" t="s">
         <v>420</v>
       </c>
       <c r="E11" s="834" t="s">
@@ -19699,7 +19696,7 @@
       <c r="G11" s="837" t="s">
         <v>423</v>
       </c>
-      <c r="H11" s="1560" t="s">
+      <c r="H11" s="1544" t="s">
         <v>424</v>
       </c>
       <c r="I11" s="82"/>
@@ -19718,9 +19715,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="82"/>
-      <c r="B12" s="1551"/>
-      <c r="C12" s="1554"/>
-      <c r="D12" s="1555"/>
+      <c r="B12" s="1535"/>
+      <c r="C12" s="1538"/>
+      <c r="D12" s="1539"/>
       <c r="E12" s="93" t="s">
         <v>425</v>
       </c>
@@ -19730,7 +19727,7 @@
       <c r="G12" s="837" t="s">
         <v>427</v>
       </c>
-      <c r="H12" s="1561"/>
+      <c r="H12" s="1545"/>
       <c r="I12" s="82"/>
       <c r="L12" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -19743,11 +19740,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="82"/>
-      <c r="B13" s="1551"/>
-      <c r="C13" s="1553" t="s">
+      <c r="B13" s="1535"/>
+      <c r="C13" s="1537" t="s">
         <v>428</v>
       </c>
-      <c r="D13" s="1555" t="s">
+      <c r="D13" s="1539" t="s">
         <v>429</v>
       </c>
       <c r="E13" s="838" t="s">
@@ -19756,10 +19753,10 @@
       <c r="F13" s="839" t="s">
         <v>431</v>
       </c>
-      <c r="G13" s="1562" t="s">
+      <c r="G13" s="1546" t="s">
         <v>432</v>
       </c>
-      <c r="H13" s="1563"/>
+      <c r="H13" s="1547"/>
       <c r="I13" s="82"/>
       <c r="L13" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -19784,19 +19781,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="82"/>
-      <c r="B14" s="1551"/>
-      <c r="C14" s="1553"/>
-      <c r="D14" s="1555"/>
+      <c r="B14" s="1535"/>
+      <c r="C14" s="1537"/>
+      <c r="D14" s="1539"/>
       <c r="E14" s="838" t="s">
         <v>433</v>
       </c>
       <c r="F14" s="839" t="s">
         <v>434</v>
       </c>
-      <c r="G14" s="1562" t="s">
+      <c r="G14" s="1546" t="s">
         <v>435</v>
       </c>
-      <c r="H14" s="1563"/>
+      <c r="H14" s="1547"/>
       <c r="I14" s="82"/>
       <c r="L14" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -19821,9 +19818,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="82"/>
-      <c r="B15" s="1551"/>
-      <c r="C15" s="1553"/>
-      <c r="D15" s="1555" t="s">
+      <c r="B15" s="1535"/>
+      <c r="C15" s="1537"/>
+      <c r="D15" s="1539" t="s">
         <v>436</v>
       </c>
       <c r="E15" s="838" t="s">
@@ -19835,7 +19832,7 @@
       <c r="G15" s="841" t="s">
         <v>439</v>
       </c>
-      <c r="H15" s="1530" t="s">
+      <c r="H15" s="1548" t="s">
         <v>440</v>
       </c>
       <c r="I15" s="82"/>
@@ -19854,9 +19851,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="82"/>
-      <c r="B16" s="1552"/>
-      <c r="C16" s="1553"/>
-      <c r="D16" s="1555"/>
+      <c r="B16" s="1536"/>
+      <c r="C16" s="1537"/>
+      <c r="D16" s="1539"/>
       <c r="E16" s="94" t="s">
         <v>441</v>
       </c>
@@ -19866,7 +19863,7 @@
       <c r="G16" s="839" t="s">
         <v>443</v>
       </c>
-      <c r="H16" s="1531"/>
+      <c r="H16" s="1549"/>
       <c r="I16" s="82"/>
       <c r="L16" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -19879,23 +19876,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="82"/>
-      <c r="B17" s="1532" t="s">
+      <c r="B17" s="1550" t="s">
         <v>444</v>
       </c>
-      <c r="C17" s="1535" t="s">
+      <c r="C17" s="1553" t="s">
         <v>445</v>
       </c>
-      <c r="D17" s="1536"/>
+      <c r="D17" s="1554"/>
       <c r="E17" s="842" t="s">
         <v>446</v>
       </c>
       <c r="F17" s="843" t="s">
         <v>447</v>
       </c>
-      <c r="G17" s="1541" t="s">
+      <c r="G17" s="1559" t="s">
         <v>448</v>
       </c>
-      <c r="H17" s="1542"/>
+      <c r="H17" s="1560"/>
       <c r="I17" s="82"/>
       <c r="L17" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -19908,17 +19905,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="82"/>
-      <c r="B18" s="1533"/>
-      <c r="C18" s="1537"/>
-      <c r="D18" s="1538"/>
+      <c r="B18" s="1551"/>
+      <c r="C18" s="1555"/>
+      <c r="D18" s="1556"/>
       <c r="E18" s="842" t="s">
         <v>449</v>
       </c>
       <c r="F18" s="843" t="s">
         <v>450</v>
       </c>
-      <c r="G18" s="1543"/>
-      <c r="H18" s="1544"/>
+      <c r="G18" s="1561"/>
+      <c r="H18" s="1562"/>
       <c r="I18" s="82"/>
       <c r="L18" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -19931,9 +19928,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="82"/>
-      <c r="B19" s="1533"/>
-      <c r="C19" s="1539"/>
-      <c r="D19" s="1540"/>
+      <c r="B19" s="1551"/>
+      <c r="C19" s="1557"/>
+      <c r="D19" s="1558"/>
       <c r="E19" s="842" t="s">
         <v>451</v>
       </c>
@@ -19954,11 +19951,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="82"/>
-      <c r="B20" s="1533"/>
-      <c r="C20" s="1537" t="s">
+      <c r="B20" s="1551"/>
+      <c r="C20" s="1555" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="1545"/>
+      <c r="D20" s="1563"/>
       <c r="E20" s="844" t="s">
         <v>454</v>
       </c>
@@ -19979,9 +19976,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="82"/>
-      <c r="B21" s="1533"/>
-      <c r="C21" s="1537"/>
-      <c r="D21" s="1545"/>
+      <c r="B21" s="1551"/>
+      <c r="C21" s="1555"/>
+      <c r="D21" s="1563"/>
       <c r="E21" s="844" t="s">
         <v>141</v>
       </c>
@@ -20002,9 +19999,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="82"/>
-      <c r="B22" s="1533"/>
-      <c r="C22" s="1539"/>
-      <c r="D22" s="1546"/>
+      <c r="B22" s="1551"/>
+      <c r="C22" s="1557"/>
+      <c r="D22" s="1564"/>
       <c r="E22" s="98" t="s">
         <v>457</v>
       </c>
@@ -20025,11 +20022,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="82"/>
-      <c r="B23" s="1533"/>
-      <c r="C23" s="1535" t="s">
+      <c r="B23" s="1551"/>
+      <c r="C23" s="1553" t="s">
         <v>459</v>
       </c>
-      <c r="D23" s="1536"/>
+      <c r="D23" s="1554"/>
       <c r="E23" s="845" t="s">
         <v>460</v>
       </c>
@@ -20050,7 +20047,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="82"/>
-      <c r="B24" s="1534"/>
+      <c r="B24" s="1552"/>
       <c r="C24" s="847"/>
       <c r="D24" s="848"/>
       <c r="E24" s="849"/>
@@ -20157,6 +20154,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -20173,12 +20176,6 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20254,71 +20251,71 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="1570" t="s">
+      <c r="B4" s="1571" t="s">
         <v>462</v>
       </c>
-      <c r="C4" s="1571"/>
-      <c r="D4" s="1572" t="s">
+      <c r="C4" s="1572"/>
+      <c r="D4" s="1573" t="s">
         <v>463</v>
       </c>
-      <c r="E4" s="1572"/>
-      <c r="F4" s="1572"/>
-      <c r="G4" s="1572"/>
-      <c r="H4" s="1572"/>
-      <c r="I4" s="1572"/>
-      <c r="J4" s="1572"/>
-      <c r="K4" s="1573" t="s">
+      <c r="E4" s="1573"/>
+      <c r="F4" s="1573"/>
+      <c r="G4" s="1573"/>
+      <c r="H4" s="1573"/>
+      <c r="I4" s="1573"/>
+      <c r="J4" s="1573"/>
+      <c r="K4" s="1574" t="s">
         <v>464</v>
       </c>
-      <c r="L4" s="1574"/>
-      <c r="M4" s="1574"/>
-      <c r="N4" s="1574"/>
-      <c r="O4" s="1575"/>
+      <c r="L4" s="1575"/>
+      <c r="M4" s="1575"/>
+      <c r="N4" s="1575"/>
+      <c r="O4" s="1576"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="53"/>
-      <c r="B5" s="1576" t="s">
+      <c r="B5" s="1577" t="s">
         <v>465</v>
       </c>
-      <c r="C5" s="1577"/>
-      <c r="D5" s="1580" t="s">
+      <c r="C5" s="1578"/>
+      <c r="D5" s="1581" t="s">
         <v>466</v>
       </c>
-      <c r="E5" s="1581"/>
-      <c r="F5" s="1582" t="s">
+      <c r="E5" s="1582"/>
+      <c r="F5" s="1583" t="s">
         <v>467</v>
       </c>
-      <c r="G5" s="1580" t="s">
+      <c r="G5" s="1581" t="s">
         <v>468</v>
       </c>
-      <c r="H5" s="1584"/>
-      <c r="I5" s="1584"/>
-      <c r="J5" s="1581"/>
-      <c r="K5" s="1585" t="s">
+      <c r="H5" s="1585"/>
+      <c r="I5" s="1585"/>
+      <c r="J5" s="1582"/>
+      <c r="K5" s="1586" t="s">
         <v>469</v>
       </c>
-      <c r="L5" s="1587" t="s">
+      <c r="L5" s="1588" t="s">
         <v>470</v>
       </c>
-      <c r="M5" s="1589" t="s">
+      <c r="M5" s="1590" t="s">
         <v>471</v>
       </c>
-      <c r="N5" s="1591" t="s">
+      <c r="N5" s="1592" t="s">
         <v>472</v>
       </c>
-      <c r="O5" s="1592"/>
+      <c r="O5" s="1593"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="53"/>
-      <c r="B6" s="1578"/>
-      <c r="C6" s="1579"/>
+      <c r="B6" s="1579"/>
+      <c r="C6" s="1580"/>
       <c r="D6" s="851" t="s">
         <v>473</v>
       </c>
       <c r="E6" s="852" t="s">
         <v>474</v>
       </c>
-      <c r="F6" s="1583"/>
+      <c r="F6" s="1584"/>
       <c r="G6" s="851" t="s">
         <v>475</v>
       </c>
@@ -20331,9 +20328,9 @@
       <c r="J6" s="852" t="s">
         <v>478</v>
       </c>
-      <c r="K6" s="1586"/>
-      <c r="L6" s="1588"/>
-      <c r="M6" s="1590"/>
+      <c r="K6" s="1587"/>
+      <c r="L6" s="1589"/>
+      <c r="M6" s="1591"/>
       <c r="N6" s="855" t="s">
         <v>479</v>
       </c>
@@ -20733,21 +20730,21 @@
         <f>+D38</f>
         <v>0</v>
       </c>
-      <c r="D23" s="1564">
+      <c r="D23" s="1565">
         <v>0</v>
       </c>
-      <c r="E23" s="1565"/>
+      <c r="E23" s="1566"/>
       <c r="F23" s="889">
         <v>0</v>
       </c>
-      <c r="G23" s="1564">
+      <c r="G23" s="1565">
         <v>0</v>
       </c>
-      <c r="H23" s="1566"/>
-      <c r="I23" s="1567" t="s">
+      <c r="H23" s="1567"/>
+      <c r="I23" s="1568" t="s">
         <v>506</v>
       </c>
-      <c r="J23" s="1565"/>
+      <c r="J23" s="1566"/>
       <c r="K23" s="890" t="s">
         <v>507</v>
       </c>
@@ -20810,11 +20807,11 @@
       <c r="G26" s="76"/>
       <c r="H26" s="55"/>
       <c r="I26" s="55"/>
-      <c r="J26" s="1568" t="str">
+      <c r="J26" s="1569" t="str">
         <f>+D31&amp;" "&amp;F38</f>
         <v>A-1-a (0)</v>
       </c>
-      <c r="K26" s="1569"/>
+      <c r="K26" s="1570"/>
       <c r="L26" s="53"/>
       <c r="M26" s="53"/>
       <c r="N26" s="53"/>
@@ -21074,10 +21071,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1593" t="s">
+      <c r="A2" s="1594" t="s">
         <v>512</v>
       </c>
-      <c r="B2" s="1593"/>
+      <c r="B2" s="1594"/>
       <c r="C2" s="894" t="s">
         <v>513</v>
       </c>
@@ -22185,10 +22182,10 @@
       <c r="J26" s="330"/>
       <c r="K26" s="478"/>
       <c r="L26" s="972"/>
-      <c r="N26" s="1332" t="s">
+      <c r="N26" s="1369" t="s">
         <v>49</v>
       </c>
-      <c r="O26" s="1333"/>
+      <c r="O26" s="1370"/>
       <c r="Y26" s="1103"/>
       <c r="Z26" s="475"/>
       <c r="AA26" s="1103"/>
@@ -22453,11 +22450,11 @@
       <c r="D32" s="1125"/>
       <c r="E32" s="1125"/>
       <c r="F32" s="1126"/>
-      <c r="G32" s="1354">
+      <c r="G32" s="1388">
         <f>DATOS!F41</f>
         <v>0</v>
       </c>
-      <c r="H32" s="1354"/>
+      <c r="H32" s="1388"/>
       <c r="I32" s="991"/>
       <c r="J32" s="330"/>
       <c r="K32" s="478"/>
@@ -22549,13 +22546,13 @@
       <c r="AN34" s="722"/>
     </row>
     <row r="35" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1350" t="s">
+      <c r="A35" s="1342" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="1350"/>
-      <c r="C35" s="1350"/>
-      <c r="D35" s="1350"/>
-      <c r="E35" s="1350"/>
+      <c r="B35" s="1342"/>
+      <c r="C35" s="1342"/>
+      <c r="D35" s="1342"/>
+      <c r="E35" s="1342"/>
       <c r="F35" s="1082">
         <v>1</v>
       </c>
@@ -22591,13 +22588,13 @@
       <c r="AN35" s="722"/>
     </row>
     <row r="36" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1350" t="s">
+      <c r="A36" s="1342" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="1350"/>
-      <c r="C36" s="1350"/>
-      <c r="D36" s="1350"/>
-      <c r="E36" s="1350"/>
+      <c r="B36" s="1342"/>
+      <c r="C36" s="1342"/>
+      <c r="D36" s="1342"/>
+      <c r="E36" s="1342"/>
       <c r="F36" s="1083">
         <f>+DATOS!F15</f>
         <v>5</v>
@@ -22637,13 +22634,13 @@
       <c r="AN36" s="722"/>
     </row>
     <row r="37" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1350" t="s">
+      <c r="A37" s="1342" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="1350"/>
-      <c r="C37" s="1350"/>
-      <c r="D37" s="1350"/>
-      <c r="E37" s="1350"/>
+      <c r="B37" s="1342"/>
+      <c r="C37" s="1342"/>
+      <c r="D37" s="1342"/>
+      <c r="E37" s="1342"/>
       <c r="F37" s="1083">
         <f>+DATOS!F16</f>
         <v>0</v>
@@ -22683,13 +22680,13 @@
       <c r="AN37" s="722"/>
     </row>
     <row r="38" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1350" t="s">
+      <c r="A38" s="1342" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="1350"/>
-      <c r="C38" s="1350"/>
-      <c r="D38" s="1350"/>
-      <c r="E38" s="1350"/>
+      <c r="B38" s="1342"/>
+      <c r="C38" s="1342"/>
+      <c r="D38" s="1342"/>
+      <c r="E38" s="1342"/>
       <c r="F38" s="1085" t="e">
         <f>+DATOS!F21</f>
         <v>#DIV/0!</v>
@@ -22768,13 +22765,13 @@
       <c r="AN39" s="722"/>
     </row>
     <row r="40" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1350" t="s">
+      <c r="A40" s="1342" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="1350"/>
-      <c r="C40" s="1350"/>
-      <c r="D40" s="1350"/>
-      <c r="E40" s="1350"/>
+      <c r="B40" s="1342"/>
+      <c r="C40" s="1342"/>
+      <c r="D40" s="1342"/>
+      <c r="E40" s="1342"/>
       <c r="F40" s="1088" t="e">
         <f>+DATOS!F31</f>
         <v>#DIV/0!</v>
@@ -22791,9 +22788,9 @@
         <f>+DATOS!L31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="1351"/>
-      <c r="K40" s="1352"/>
-      <c r="L40" s="1353"/>
+      <c r="J40" s="1385"/>
+      <c r="K40" s="1386"/>
+      <c r="L40" s="1387"/>
       <c r="M40" s="1107"/>
       <c r="N40" s="1101"/>
       <c r="Q40" s="1108"/>
@@ -22818,13 +22815,13 @@
       <c r="AN40" s="722"/>
     </row>
     <row r="41" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1350" t="s">
+      <c r="A41" s="1342" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="1350"/>
-      <c r="C41" s="1350"/>
-      <c r="D41" s="1350"/>
-      <c r="E41" s="1350"/>
+      <c r="B41" s="1342"/>
+      <c r="C41" s="1342"/>
+      <c r="D41" s="1342"/>
+      <c r="E41" s="1342"/>
       <c r="F41" s="1085" t="e">
         <f>+DATOS!F32</f>
         <v>#DIV/0!</v>
@@ -22841,9 +22838,9 @@
         <f>+DATOS!L32</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="1351"/>
-      <c r="K41" s="1352"/>
-      <c r="L41" s="1353"/>
+      <c r="J41" s="1385"/>
+      <c r="K41" s="1386"/>
+      <c r="L41" s="1387"/>
       <c r="M41" s="1109"/>
       <c r="N41" s="1101"/>
       <c r="V41" s="718"/>
@@ -22890,9 +22887,9 @@
         <f>+DATOS!L33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J42" s="1351"/>
-      <c r="K42" s="1352"/>
-      <c r="L42" s="1353"/>
+      <c r="J42" s="1385"/>
+      <c r="K42" s="1386"/>
+      <c r="L42" s="1387"/>
       <c r="M42" s="1109"/>
       <c r="N42" s="1101"/>
       <c r="V42" s="718"/>
@@ -22960,16 +22957,16 @@
       <c r="G44" s="480"/>
       <c r="H44" s="407"/>
       <c r="I44" s="997"/>
-      <c r="J44" s="1368" t="s">
+      <c r="J44" s="1343" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="1369"/>
-      <c r="L44" s="1370"/>
+      <c r="K44" s="1344"/>
+      <c r="L44" s="1345"/>
       <c r="M44" s="1101"/>
-      <c r="N44" s="1334" t="s">
+      <c r="N44" s="1371" t="s">
         <v>38</v>
       </c>
-      <c r="O44" s="1334"/>
+      <c r="O44" s="1371"/>
       <c r="V44" s="718"/>
       <c r="W44" s="475"/>
       <c r="X44" s="475"/>
@@ -23000,12 +22997,12 @@
       <c r="G45" s="480"/>
       <c r="H45" s="407"/>
       <c r="I45" s="997"/>
-      <c r="J45" s="1371" t="e">
+      <c r="J45" s="1346" t="e">
         <f>+DATOS!C50</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K45" s="1372"/>
-      <c r="L45" s="1373"/>
+      <c r="K45" s="1347"/>
+      <c r="L45" s="1348"/>
       <c r="M45" s="1101"/>
       <c r="N45" s="680">
         <v>0</v>
@@ -23044,11 +23041,11 @@
       <c r="G46" s="480"/>
       <c r="H46" s="407"/>
       <c r="I46" s="997"/>
-      <c r="J46" s="1335" t="s">
+      <c r="J46" s="1372" t="s">
         <v>36</v>
       </c>
-      <c r="K46" s="1336"/>
-      <c r="L46" s="1337"/>
+      <c r="K46" s="1373"/>
+      <c r="L46" s="1374"/>
       <c r="M46" s="1101"/>
       <c r="N46" s="680" t="e">
         <f>+DATOS!J75</f>
@@ -23088,12 +23085,12 @@
       <c r="G47" s="480"/>
       <c r="H47" s="480"/>
       <c r="I47" s="997"/>
-      <c r="J47" s="1338" t="e">
+      <c r="J47" s="1375" t="e">
         <f>MROUND(N52,0.02)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K47" s="1339"/>
-      <c r="L47" s="1340"/>
+      <c r="K47" s="1376"/>
+      <c r="L47" s="1377"/>
       <c r="M47" s="1101" t="s">
         <v>569</v>
       </c>
@@ -23134,11 +23131,11 @@
       <c r="G48" s="480"/>
       <c r="H48" s="480"/>
       <c r="I48" s="997"/>
-      <c r="J48" s="1374" t="s">
+      <c r="J48" s="1349" t="s">
         <v>37</v>
       </c>
-      <c r="K48" s="1375"/>
-      <c r="L48" s="1376"/>
+      <c r="K48" s="1350"/>
+      <c r="L48" s="1351"/>
       <c r="M48" s="1101"/>
       <c r="N48" s="728"/>
       <c r="O48" s="728"/>
@@ -23173,14 +23170,14 @@
       <c r="G49" s="480"/>
       <c r="H49" s="480"/>
       <c r="I49" s="997"/>
-      <c r="J49" s="1377"/>
-      <c r="K49" s="1378"/>
-      <c r="L49" s="1379"/>
+      <c r="J49" s="1352"/>
+      <c r="K49" s="1353"/>
+      <c r="L49" s="1354"/>
       <c r="M49" s="1101"/>
-      <c r="N49" s="1334" t="s">
+      <c r="N49" s="1371" t="s">
         <v>566</v>
       </c>
-      <c r="O49" s="1334"/>
+      <c r="O49" s="1371"/>
       <c r="S49" s="348"/>
       <c r="V49" s="718"/>
       <c r="W49" s="475"/>
@@ -23212,12 +23209,12 @@
       <c r="G50" s="480"/>
       <c r="H50" s="480"/>
       <c r="I50" s="997"/>
-      <c r="J50" s="1342" t="e">
+      <c r="J50" s="1378" t="e">
         <f>+DATOS!J74</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K50" s="1343"/>
-      <c r="L50" s="1344"/>
+      <c r="K50" s="1379"/>
+      <c r="L50" s="1380"/>
       <c r="M50" s="1107"/>
       <c r="N50" s="987">
         <v>0</v>
@@ -23256,9 +23253,9 @@
       <c r="G51" s="480"/>
       <c r="H51" s="480"/>
       <c r="I51" s="997"/>
-      <c r="J51" s="1345"/>
-      <c r="K51" s="1346"/>
-      <c r="L51" s="1347"/>
+      <c r="J51" s="1381"/>
+      <c r="K51" s="1382"/>
+      <c r="L51" s="1383"/>
       <c r="M51" s="1101"/>
       <c r="N51" s="680" t="e">
         <f>+N46*9.8066</f>
@@ -23555,9 +23552,9 @@
       <c r="G60" s="480"/>
       <c r="H60" s="480"/>
       <c r="I60" s="997"/>
-      <c r="J60" s="1341"/>
-      <c r="K60" s="1341"/>
-      <c r="L60" s="1341"/>
+      <c r="J60" s="1335"/>
+      <c r="K60" s="1335"/>
+      <c r="L60" s="1335"/>
       <c r="M60" s="1101"/>
       <c r="Q60" s="1000"/>
       <c r="R60" s="1000"/>
@@ -23593,9 +23590,9 @@
       <c r="G61" s="480"/>
       <c r="H61" s="480"/>
       <c r="I61" s="997"/>
-      <c r="J61" s="1381"/>
-      <c r="K61" s="1381"/>
-      <c r="L61" s="1381"/>
+      <c r="J61" s="1334"/>
+      <c r="K61" s="1334"/>
+      <c r="L61" s="1334"/>
       <c r="M61" s="1101"/>
       <c r="Q61" s="1001"/>
       <c r="R61" s="1001"/>
@@ -23621,7 +23618,7 @@
     </row>
     <row r="62" spans="1:40" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="316" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B62" s="1112"/>
       <c r="C62" s="1112"/>
@@ -23631,9 +23628,9 @@
       <c r="G62" s="480"/>
       <c r="H62" s="480"/>
       <c r="I62" s="997"/>
-      <c r="J62" s="1341"/>
-      <c r="K62" s="1341"/>
-      <c r="L62" s="1341"/>
+      <c r="J62" s="1335"/>
+      <c r="K62" s="1335"/>
+      <c r="L62" s="1335"/>
       <c r="M62" s="1101"/>
       <c r="P62" s="1000"/>
       <c r="Q62" s="1000"/>
@@ -23660,7 +23657,7 @@
     </row>
     <row r="63" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="316"/>
-      <c r="C63" s="1594"/>
+      <c r="C63" s="1275"/>
       <c r="D63" s="997"/>
       <c r="E63" s="997"/>
       <c r="F63" s="997"/>
@@ -23775,11 +23772,11 @@
       <c r="C66" s="1114"/>
       <c r="D66" s="478"/>
       <c r="E66" s="478"/>
-      <c r="F66" s="1382">
+      <c r="F66" s="1336">
         <f>+formato!C36</f>
         <v>0</v>
       </c>
-      <c r="G66" s="1382"/>
+      <c r="G66" s="1336"/>
       <c r="H66" s="478"/>
       <c r="I66" s="378"/>
       <c r="J66" s="478"/>
@@ -23813,11 +23810,11 @@
       <c r="C67" s="1114"/>
       <c r="D67" s="478"/>
       <c r="E67" s="478"/>
-      <c r="F67" s="1383">
+      <c r="F67" s="1337">
         <f>+formato!C37</f>
         <v>0</v>
       </c>
-      <c r="G67" s="1383"/>
+      <c r="G67" s="1337"/>
       <c r="H67" s="478"/>
       <c r="I67" s="378"/>
       <c r="J67" s="1115"/>
@@ -23851,11 +23848,11 @@
       <c r="C68" s="1114"/>
       <c r="D68" s="478"/>
       <c r="E68" s="478"/>
-      <c r="F68" s="1382">
+      <c r="F68" s="1336">
         <f>+formato!C38</f>
         <v>0</v>
       </c>
-      <c r="G68" s="1382"/>
+      <c r="G68" s="1336"/>
       <c r="H68" s="478"/>
       <c r="I68" s="1116"/>
       <c r="J68" s="1115"/>
@@ -24072,11 +24069,11 @@
       <c r="G74" s="1014" t="s">
         <v>67</v>
       </c>
-      <c r="H74" s="1384">
+      <c r="H74" s="1338">
         <f>DATOS!F37</f>
         <v>0</v>
       </c>
-      <c r="I74" s="1385"/>
+      <c r="I74" s="1339"/>
       <c r="J74" s="1115"/>
       <c r="K74" s="478"/>
       <c r="L74" s="478"/>
@@ -24117,11 +24114,11 @@
       <c r="G75" s="1014" t="s">
         <v>67</v>
       </c>
-      <c r="H75" s="1386">
+      <c r="H75" s="1340">
         <f>DATOS!F38</f>
         <v>0</v>
       </c>
-      <c r="I75" s="1387"/>
+      <c r="I75" s="1341"/>
       <c r="J75" s="1115"/>
       <c r="K75" s="478"/>
       <c r="L75" s="478"/>
@@ -24186,18 +24183,18 @@
       <c r="AN76" s="722"/>
     </row>
     <row r="77" spans="1:40" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1349"/>
-      <c r="B77" s="1349"/>
-      <c r="C77" s="1349"/>
-      <c r="D77" s="1349"/>
-      <c r="E77" s="1349"/>
-      <c r="F77" s="1349"/>
-      <c r="G77" s="1349"/>
-      <c r="H77" s="1349"/>
-      <c r="I77" s="1349"/>
-      <c r="J77" s="1349"/>
-      <c r="K77" s="1349"/>
-      <c r="L77" s="1349"/>
+      <c r="A77" s="1333"/>
+      <c r="B77" s="1333"/>
+      <c r="C77" s="1333"/>
+      <c r="D77" s="1333"/>
+      <c r="E77" s="1333"/>
+      <c r="F77" s="1333"/>
+      <c r="G77" s="1333"/>
+      <c r="H77" s="1333"/>
+      <c r="I77" s="1333"/>
+      <c r="J77" s="1333"/>
+      <c r="K77" s="1333"/>
+      <c r="L77" s="1333"/>
       <c r="V77" s="718"/>
       <c r="W77" s="475"/>
       <c r="X77" s="475"/>
@@ -24256,20 +24253,20 @@
       <c r="AN78" s="722"/>
     </row>
     <row r="79" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1380" t="s">
+      <c r="A79" s="1332" t="s">
         <v>662</v>
       </c>
-      <c r="B79" s="1380"/>
-      <c r="C79" s="1380"/>
-      <c r="D79" s="1380"/>
-      <c r="E79" s="1380"/>
-      <c r="F79" s="1380"/>
-      <c r="G79" s="1380"/>
-      <c r="H79" s="1380"/>
-      <c r="I79" s="1380"/>
-      <c r="J79" s="1380"/>
-      <c r="K79" s="1380"/>
-      <c r="L79" s="1380"/>
+      <c r="B79" s="1332"/>
+      <c r="C79" s="1332"/>
+      <c r="D79" s="1332"/>
+      <c r="E79" s="1332"/>
+      <c r="F79" s="1332"/>
+      <c r="G79" s="1332"/>
+      <c r="H79" s="1332"/>
+      <c r="I79" s="1332"/>
+      <c r="J79" s="1332"/>
+      <c r="K79" s="1332"/>
+      <c r="L79" s="1332"/>
       <c r="M79" s="1016"/>
       <c r="N79" s="1016"/>
       <c r="V79" s="718"/>
@@ -24293,20 +24290,20 @@
       <c r="AN79" s="722"/>
     </row>
     <row r="80" spans="1:40" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1349" t="s">
+      <c r="A80" s="1333" t="s">
         <v>663</v>
       </c>
-      <c r="B80" s="1349"/>
-      <c r="C80" s="1349"/>
-      <c r="D80" s="1349"/>
-      <c r="E80" s="1349"/>
-      <c r="F80" s="1349"/>
-      <c r="G80" s="1349"/>
-      <c r="H80" s="1349"/>
-      <c r="I80" s="1349"/>
-      <c r="J80" s="1349"/>
-      <c r="K80" s="1349"/>
-      <c r="L80" s="1349"/>
+      <c r="B80" s="1333"/>
+      <c r="C80" s="1333"/>
+      <c r="D80" s="1333"/>
+      <c r="E80" s="1333"/>
+      <c r="F80" s="1333"/>
+      <c r="G80" s="1333"/>
+      <c r="H80" s="1333"/>
+      <c r="I80" s="1333"/>
+      <c r="J80" s="1333"/>
+      <c r="K80" s="1333"/>
+      <c r="L80" s="1333"/>
       <c r="M80" s="1119"/>
       <c r="N80" s="1119"/>
       <c r="V80" s="718"/>
@@ -24330,20 +24327,20 @@
       <c r="AN80" s="722"/>
     </row>
     <row r="81" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1349" t="s">
+      <c r="A81" s="1333" t="s">
         <v>664</v>
       </c>
-      <c r="B81" s="1349"/>
-      <c r="C81" s="1349"/>
-      <c r="D81" s="1349"/>
-      <c r="E81" s="1349"/>
-      <c r="F81" s="1349"/>
-      <c r="G81" s="1349"/>
-      <c r="H81" s="1349"/>
-      <c r="I81" s="1349"/>
-      <c r="J81" s="1349"/>
-      <c r="K81" s="1349"/>
-      <c r="L81" s="1349"/>
+      <c r="B81" s="1333"/>
+      <c r="C81" s="1333"/>
+      <c r="D81" s="1333"/>
+      <c r="E81" s="1333"/>
+      <c r="F81" s="1333"/>
+      <c r="G81" s="1333"/>
+      <c r="H81" s="1333"/>
+      <c r="I81" s="1333"/>
+      <c r="J81" s="1333"/>
+      <c r="K81" s="1333"/>
+      <c r="L81" s="1333"/>
       <c r="M81" s="1017"/>
       <c r="N81" s="1017"/>
       <c r="V81" s="718"/>
@@ -24367,20 +24364,20 @@
       <c r="AN81" s="722"/>
     </row>
     <row r="82" spans="1:40" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1349" t="s">
+      <c r="A82" s="1333" t="s">
         <v>665</v>
       </c>
-      <c r="B82" s="1349"/>
-      <c r="C82" s="1349"/>
-      <c r="D82" s="1349"/>
-      <c r="E82" s="1349"/>
-      <c r="F82" s="1349"/>
-      <c r="G82" s="1349"/>
-      <c r="H82" s="1349"/>
-      <c r="I82" s="1349"/>
-      <c r="J82" s="1349"/>
-      <c r="K82" s="1349"/>
-      <c r="L82" s="1349"/>
+      <c r="B82" s="1333"/>
+      <c r="C82" s="1333"/>
+      <c r="D82" s="1333"/>
+      <c r="E82" s="1333"/>
+      <c r="F82" s="1333"/>
+      <c r="G82" s="1333"/>
+      <c r="H82" s="1333"/>
+      <c r="I82" s="1333"/>
+      <c r="J82" s="1333"/>
+      <c r="K82" s="1333"/>
+      <c r="L82" s="1333"/>
       <c r="M82" s="1119"/>
       <c r="N82" s="1119"/>
       <c r="V82" s="718"/>
@@ -24404,20 +24401,20 @@
       <c r="AN82" s="722"/>
     </row>
     <row r="83" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1348" t="s">
+      <c r="A83" s="1384" t="s">
         <v>666</v>
       </c>
-      <c r="B83" s="1348"/>
-      <c r="C83" s="1348"/>
-      <c r="D83" s="1348"/>
-      <c r="E83" s="1348"/>
-      <c r="F83" s="1348"/>
-      <c r="G83" s="1348"/>
-      <c r="H83" s="1348"/>
-      <c r="I83" s="1348"/>
-      <c r="J83" s="1348"/>
-      <c r="K83" s="1348"/>
-      <c r="L83" s="1348"/>
+      <c r="B83" s="1384"/>
+      <c r="C83" s="1384"/>
+      <c r="D83" s="1384"/>
+      <c r="E83" s="1384"/>
+      <c r="F83" s="1384"/>
+      <c r="G83" s="1384"/>
+      <c r="H83" s="1384"/>
+      <c r="I83" s="1384"/>
+      <c r="J83" s="1384"/>
+      <c r="K83" s="1384"/>
+      <c r="L83" s="1384"/>
       <c r="M83" s="1119"/>
       <c r="N83" s="1119"/>
       <c r="V83" s="718"/>
@@ -24513,18 +24510,18 @@
       <c r="AN85" s="722"/>
     </row>
     <row r="86" spans="1:40" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1331"/>
-      <c r="B86" s="1331"/>
-      <c r="C86" s="1331"/>
-      <c r="D86" s="1331"/>
-      <c r="E86" s="1331"/>
-      <c r="F86" s="1331"/>
-      <c r="G86" s="1331"/>
-      <c r="H86" s="1331"/>
-      <c r="I86" s="1331"/>
-      <c r="J86" s="1331"/>
-      <c r="K86" s="1331"/>
-      <c r="L86" s="1331"/>
+      <c r="A86" s="1368"/>
+      <c r="B86" s="1368"/>
+      <c r="C86" s="1368"/>
+      <c r="D86" s="1368"/>
+      <c r="E86" s="1368"/>
+      <c r="F86" s="1368"/>
+      <c r="G86" s="1368"/>
+      <c r="H86" s="1368"/>
+      <c r="I86" s="1368"/>
+      <c r="J86" s="1368"/>
+      <c r="K86" s="1368"/>
+      <c r="L86" s="1368"/>
       <c r="M86" s="1119"/>
       <c r="N86" s="1119"/>
       <c r="V86" s="718"/>
@@ -25818,37 +25815,6 @@
     <protectedRange sqref="E9:E10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="47">
-    <mergeCell ref="A79:L79"/>
-    <mergeCell ref="A80:L80"/>
-    <mergeCell ref="A82:L82"/>
-    <mergeCell ref="A81:L81"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J48:L49"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
     <mergeCell ref="A86:L86"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="N44:O44"/>
@@ -25865,6 +25831,37 @@
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="J40:L40"/>
     <mergeCell ref="J38:L38"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J48:L49"/>
+    <mergeCell ref="A79:L79"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A82:L82"/>
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.70866141732283472" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -25907,40 +25904,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1406" t="s">
+      <c r="B2" s="1395" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1407"/>
-      <c r="D2" s="1407"/>
-      <c r="E2" s="1407"/>
-      <c r="F2" s="1407"/>
-      <c r="G2" s="1407"/>
-      <c r="H2" s="1407"/>
-      <c r="I2" s="1407"/>
-      <c r="J2" s="1407"/>
-      <c r="K2" s="1407"/>
-      <c r="L2" s="1407"/>
-      <c r="M2" s="1407"/>
-      <c r="N2" s="1407"/>
-      <c r="O2" s="1408"/>
+      <c r="C2" s="1396"/>
+      <c r="D2" s="1396"/>
+      <c r="E2" s="1396"/>
+      <c r="F2" s="1396"/>
+      <c r="G2" s="1396"/>
+      <c r="H2" s="1396"/>
+      <c r="I2" s="1396"/>
+      <c r="J2" s="1396"/>
+      <c r="K2" s="1396"/>
+      <c r="L2" s="1396"/>
+      <c r="M2" s="1396"/>
+      <c r="N2" s="1396"/>
+      <c r="O2" s="1397"/>
     </row>
     <row r="3" spans="2:19" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1409" t="s">
+      <c r="B3" s="1398" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1410"/>
-      <c r="D3" s="1410"/>
-      <c r="E3" s="1410"/>
-      <c r="F3" s="1410"/>
-      <c r="G3" s="1410"/>
-      <c r="H3" s="1410"/>
-      <c r="I3" s="1410"/>
-      <c r="J3" s="1410"/>
-      <c r="K3" s="1410"/>
-      <c r="L3" s="1410"/>
-      <c r="M3" s="1410"/>
-      <c r="N3" s="1410"/>
-      <c r="O3" s="1411"/>
+      <c r="C3" s="1399"/>
+      <c r="D3" s="1399"/>
+      <c r="E3" s="1399"/>
+      <c r="F3" s="1399"/>
+      <c r="G3" s="1399"/>
+      <c r="H3" s="1399"/>
+      <c r="I3" s="1399"/>
+      <c r="J3" s="1399"/>
+      <c r="K3" s="1399"/>
+      <c r="L3" s="1399"/>
+      <c r="M3" s="1399"/>
+      <c r="N3" s="1399"/>
+      <c r="O3" s="1400"/>
     </row>
     <row r="5" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="682" t="s">
@@ -26130,31 +26127,31 @@
       <c r="N11" s="494"/>
     </row>
     <row r="12" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1402" t="s">
+      <c r="B12" s="1389" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="1402"/>
-      <c r="D12" s="1402"/>
-      <c r="E12" s="1402">
+      <c r="C12" s="1389"/>
+      <c r="D12" s="1389"/>
+      <c r="E12" s="1389">
         <v>1</v>
       </c>
-      <c r="F12" s="1402"/>
-      <c r="G12" s="1402">
+      <c r="F12" s="1389"/>
+      <c r="G12" s="1389">
         <v>2</v>
       </c>
-      <c r="H12" s="1402"/>
-      <c r="I12" s="1402">
+      <c r="H12" s="1389"/>
+      <c r="I12" s="1389">
         <v>3</v>
       </c>
-      <c r="J12" s="1402"/>
-      <c r="K12" s="1402">
+      <c r="J12" s="1389"/>
+      <c r="K12" s="1389">
         <v>4</v>
       </c>
-      <c r="L12" s="1402"/>
-      <c r="M12" s="1402">
+      <c r="L12" s="1389"/>
+      <c r="M12" s="1389">
         <v>5</v>
       </c>
-      <c r="N12" s="1402"/>
+      <c r="N12" s="1389"/>
       <c r="Q12" s="1138" t="s">
         <v>579</v>
       </c>
@@ -26166,9 +26163,9 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1402"/>
-      <c r="C13" s="1402"/>
-      <c r="D13" s="1402"/>
+      <c r="B13" s="1389"/>
+      <c r="C13" s="1389"/>
+      <c r="D13" s="1389"/>
       <c r="E13" s="730" t="s">
         <v>84</v>
       </c>
@@ -26210,11 +26207,11 @@
       </c>
     </row>
     <row r="14" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1396" t="s">
+      <c r="B14" s="1401" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1396"/>
-      <c r="D14" s="1397"/>
+      <c r="C14" s="1401"/>
+      <c r="D14" s="1402"/>
       <c r="E14" s="1255">
         <v>1</v>
       </c>
@@ -26240,11 +26237,11 @@
       </c>
     </row>
     <row r="15" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1391" t="s">
+      <c r="B15" s="1390" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="1391"/>
-      <c r="D15" s="1392"/>
+      <c r="C15" s="1390"/>
+      <c r="D15" s="1391"/>
       <c r="E15" s="1139">
         <v>5</v>
       </c>
@@ -26289,11 +26286,11 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1391" t="s">
+      <c r="B16" s="1390" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="1391"/>
-      <c r="D16" s="1392"/>
+      <c r="C16" s="1390"/>
+      <c r="D16" s="1391"/>
       <c r="E16" s="1139">
         <f>+formato!D17</f>
         <v>0</v>
@@ -26339,11 +26336,11 @@
       </c>
     </row>
     <row r="17" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="1391" t="s">
+      <c r="B17" s="1390" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="1391"/>
-      <c r="D17" s="1392"/>
+      <c r="C17" s="1390"/>
+      <c r="D17" s="1391"/>
       <c r="E17" s="1139">
         <f>+formato!D18</f>
         <v>0</v>
@@ -26389,11 +26386,11 @@
       </c>
     </row>
     <row r="18" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1391" t="s">
+      <c r="B18" s="1390" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="1391"/>
-      <c r="D18" s="1392"/>
+      <c r="C18" s="1390"/>
+      <c r="D18" s="1391"/>
       <c r="E18" s="1139">
         <f>+formato!D19</f>
         <v>0</v>
@@ -26430,11 +26427,11 @@
       <c r="N18" s="1145"/>
     </row>
     <row r="19" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="1392" t="s">
+      <c r="B19" s="1391" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1393"/>
-      <c r="D19" s="1393"/>
+      <c r="C19" s="1412"/>
+      <c r="D19" s="1412"/>
       <c r="E19" s="1142">
         <f t="shared" ref="E19:K19" si="0">+E17-E18</f>
         <v>0</v>
@@ -26471,11 +26468,11 @@
       <c r="N19" s="1145"/>
     </row>
     <row r="20" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="1391" t="s">
+      <c r="B20" s="1390" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="1391"/>
-      <c r="D20" s="1392"/>
+      <c r="C20" s="1390"/>
+      <c r="D20" s="1391"/>
       <c r="E20" s="1139">
         <f>+formato!D21</f>
         <v>0</v>
@@ -26525,11 +26522,11 @@
       <c r="U20" s="948"/>
     </row>
     <row r="21" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="1394" t="s">
+      <c r="B21" s="1413" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="1394"/>
-      <c r="D21" s="1395"/>
+      <c r="C21" s="1413"/>
+      <c r="D21" s="1414"/>
       <c r="E21" s="1142" t="e">
         <f t="shared" ref="E21:K21" si="1">+E19/E20</f>
         <v>#DIV/0!</v>
@@ -26610,11 +26607,11 @@
       <c r="U22" s="950"/>
     </row>
     <row r="23" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="1396" t="s">
+      <c r="B23" s="1401" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="1396"/>
-      <c r="D23" s="1397"/>
+      <c r="C23" s="1401"/>
+      <c r="D23" s="1402"/>
       <c r="E23" s="1139">
         <f>+formato!D24</f>
         <v>0</v>
@@ -26653,11 +26650,11 @@
       <c r="U23" s="953"/>
     </row>
     <row r="24" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="1391" t="s">
+      <c r="B24" s="1390" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="1391"/>
-      <c r="D24" s="1392"/>
+      <c r="C24" s="1390"/>
+      <c r="D24" s="1391"/>
       <c r="E24" s="1139">
         <f>+formato!D25</f>
         <v>0</v>
@@ -26713,11 +26710,11 @@
       </c>
     </row>
     <row r="25" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="1391" t="s">
+      <c r="B25" s="1390" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="1391"/>
-      <c r="D25" s="1392"/>
+      <c r="C25" s="1390"/>
+      <c r="D25" s="1391"/>
       <c r="E25" s="1139">
         <f>+formato!D26</f>
         <v>0</v>
@@ -26769,11 +26766,11 @@
       </c>
     </row>
     <row r="26" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="1391" t="s">
+      <c r="B26" s="1390" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="1391"/>
-      <c r="D26" s="1392"/>
+      <c r="C26" s="1390"/>
+      <c r="D26" s="1391"/>
       <c r="E26" s="1139">
         <f>+formato!D27</f>
         <v>0</v>
@@ -26829,11 +26826,11 @@
       </c>
     </row>
     <row r="27" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="1391" t="s">
+      <c r="B27" s="1390" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="1391"/>
-      <c r="D27" s="1392"/>
+      <c r="C27" s="1390"/>
+      <c r="D27" s="1391"/>
       <c r="E27" s="1139">
         <f>+formato!D28</f>
         <v>0</v>
@@ -26877,11 +26874,11 @@
       </c>
     </row>
     <row r="28" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="1391" t="s">
+      <c r="B28" s="1390" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="1391"/>
-      <c r="D28" s="1392"/>
+      <c r="C28" s="1390"/>
+      <c r="D28" s="1391"/>
       <c r="E28" s="1155">
         <f t="shared" ref="E28:L28" si="6">+E24-E27</f>
         <v>0</v>
@@ -26918,11 +26915,11 @@
       <c r="N28" s="1145"/>
     </row>
     <row r="29" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="1391" t="s">
+      <c r="B29" s="1390" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="1391"/>
-      <c r="D29" s="1392"/>
+      <c r="C29" s="1390"/>
+      <c r="D29" s="1391"/>
       <c r="E29" s="1139">
         <f>+formato!D30</f>
         <v>0</v>
@@ -26959,11 +26956,11 @@
       <c r="N29" s="1145"/>
     </row>
     <row r="30" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="1392" t="s">
+      <c r="B30" s="1391" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="1393"/>
-      <c r="D30" s="1393"/>
+      <c r="C30" s="1412"/>
+      <c r="D30" s="1412"/>
       <c r="E30" s="1142"/>
       <c r="F30" s="1142" t="e">
         <f t="shared" ref="F30:L30" si="7">+F27-F29</f>
@@ -26988,11 +26985,11 @@
       <c r="N30" s="1145"/>
     </row>
     <row r="31" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="1392" t="s">
+      <c r="B31" s="1391" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="1393"/>
-      <c r="D31" s="1393"/>
+      <c r="C31" s="1412"/>
+      <c r="D31" s="1412"/>
       <c r="E31" s="1142"/>
       <c r="F31" s="1142" t="e">
         <f t="shared" ref="F31:L31" si="8">+F28/F30*100</f>
@@ -27020,11 +27017,11 @@
       </c>
     </row>
     <row r="32" spans="2:21" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="1395" t="s">
+      <c r="B32" s="1414" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="1398"/>
-      <c r="D32" s="1398"/>
+      <c r="C32" s="1415"/>
+      <c r="D32" s="1415"/>
       <c r="E32" s="1142"/>
       <c r="F32" s="1142" t="e">
         <f t="shared" ref="F32:L32" si="9">+F21/(1+F31/100)</f>
@@ -27150,11 +27147,11 @@
       </c>
       <c r="D37" s="706"/>
       <c r="E37" s="707"/>
-      <c r="F37" s="1399">
+      <c r="F37" s="1406">
         <v>0</v>
       </c>
-      <c r="G37" s="1399"/>
-      <c r="H37" s="1399"/>
+      <c r="G37" s="1406"/>
+      <c r="H37" s="1406"/>
     </row>
     <row r="38" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="678" t="s">
@@ -27162,11 +27159,11 @@
       </c>
       <c r="D38" s="706"/>
       <c r="E38" s="707"/>
-      <c r="F38" s="1400">
+      <c r="F38" s="1407">
         <v>0</v>
       </c>
-      <c r="G38" s="1400"/>
-      <c r="H38" s="1400"/>
+      <c r="G38" s="1407"/>
+      <c r="H38" s="1407"/>
     </row>
     <row r="39" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27191,17 +27188,17 @@
       </c>
       <c r="D41" s="1029"/>
       <c r="E41" s="1030"/>
-      <c r="F41" s="1401">
+      <c r="F41" s="1408">
         <v>0</v>
       </c>
-      <c r="G41" s="1401"/>
-      <c r="H41" s="1401"/>
-      <c r="K41" s="1414" t="s">
+      <c r="G41" s="1408"/>
+      <c r="H41" s="1408"/>
+      <c r="K41" s="1405" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="1414"/>
+      <c r="L41" s="1405"/>
       <c r="M41" s="478"/>
-      <c r="N41" s="1412" t="s">
+      <c r="N41" s="1403" t="s">
         <v>102</v>
       </c>
     </row>
@@ -27214,7 +27211,7 @@
         <v>52</v>
       </c>
       <c r="M42" s="478"/>
-      <c r="N42" s="1413"/>
+      <c r="N42" s="1404"/>
     </row>
     <row r="43" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1027"/>
@@ -27387,21 +27384,21 @@
     </row>
     <row r="49" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="711"/>
-      <c r="C49" s="1403" t="s">
+      <c r="C49" s="1392" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="1404"/>
-      <c r="E49" s="1405"/>
+      <c r="D49" s="1393"/>
+      <c r="E49" s="1394"/>
       <c r="N49" s="712"/>
     </row>
     <row r="50" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="711"/>
-      <c r="C50" s="1388" t="e">
+      <c r="C50" s="1409" t="e">
         <f>IF(G54="","",IF(AND(G54&lt;=25),"A",IF(AND(G54&gt;25,G53&lt;=25),"B",IF(AND(G53&gt;25,G52&lt;30),"C"))))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D50" s="1389"/>
-      <c r="E50" s="1390"/>
+      <c r="D50" s="1410"/>
+      <c r="E50" s="1411"/>
       <c r="F50" s="475"/>
       <c r="N50" s="712"/>
       <c r="O50" s="713"/>
@@ -29066,6 +29063,23 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="e49E/OysaywdZI0JcuM+C0cQuCvqe9PMqZ/ilP9GIY/P45QRK0Ai6JyKU7eB4WtZltnkC9BaQI8vpXNlfCIiIw==" saltValue="LOl5Rt57JcvlkUy4kBpOXg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="33">
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="I12:J12"/>
@@ -29082,23 +29096,6 @@
     <mergeCell ref="N41:N42"/>
     <mergeCell ref="K41:L41"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
   </mergeCells>
   <conditionalFormatting sqref="F34:F35">
     <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="No Cumple">
@@ -29241,17 +29238,17 @@
       <c r="A6" s="744" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="1434" t="s">
+      <c r="B6" s="1419" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="1435"/>
-      <c r="D6" s="1435"/>
-      <c r="E6" s="1435"/>
-      <c r="F6" s="1435"/>
-      <c r="G6" s="1435"/>
-      <c r="H6" s="1435"/>
-      <c r="I6" s="1435"/>
-      <c r="J6" s="1436"/>
+      <c r="C6" s="1420"/>
+      <c r="D6" s="1420"/>
+      <c r="E6" s="1420"/>
+      <c r="F6" s="1420"/>
+      <c r="G6" s="1420"/>
+      <c r="H6" s="1420"/>
+      <c r="I6" s="1420"/>
+      <c r="J6" s="1421"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="744" t="s">
@@ -29527,8 +29524,8 @@
       <c r="G30" s="471"/>
       <c r="H30" s="470"/>
       <c r="L30" s="1425"/>
-      <c r="R30" s="1437"/>
-      <c r="S30" s="1437"/>
+      <c r="R30" s="1422"/>
+      <c r="S30" s="1422"/>
       <c r="T30" s="674"/>
       <c r="U30" s="675"/>
     </row>
@@ -29542,8 +29539,8 @@
       <c r="G31" s="471"/>
       <c r="H31" s="471"/>
       <c r="L31" s="1425"/>
-      <c r="R31" s="1437"/>
-      <c r="S31" s="1437"/>
+      <c r="R31" s="1422"/>
+      <c r="S31" s="1422"/>
       <c r="T31" s="674"/>
       <c r="U31" s="675"/>
     </row>
@@ -29557,8 +29554,8 @@
       <c r="G32" s="471"/>
       <c r="H32" s="471"/>
       <c r="L32" s="1425"/>
-      <c r="R32" s="1437"/>
-      <c r="S32" s="1437"/>
+      <c r="R32" s="1422"/>
+      <c r="S32" s="1422"/>
       <c r="T32" s="674"/>
       <c r="U32" s="675"/>
     </row>
@@ -29573,8 +29570,8 @@
       <c r="H33" s="471"/>
       <c r="L33" s="1425"/>
       <c r="O33" s="673"/>
-      <c r="R33" s="1437"/>
-      <c r="S33" s="1437"/>
+      <c r="R33" s="1422"/>
+      <c r="S33" s="1422"/>
       <c r="T33" s="488"/>
       <c r="U33" s="675"/>
     </row>
@@ -32142,12 +32139,12 @@
       <c r="M74" s="471"/>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A75" s="1433" t="s">
+      <c r="A75" s="1418" t="s">
         <v>188</v>
       </c>
-      <c r="B75" s="1433"/>
-      <c r="C75" s="1433"/>
-      <c r="D75" s="1433"/>
+      <c r="B75" s="1418"/>
+      <c r="C75" s="1418"/>
+      <c r="D75" s="1418"/>
       <c r="E75" s="467"/>
       <c r="F75" s="467"/>
       <c r="G75" s="467"/>
@@ -32157,10 +32154,10 @@
       <c r="M75" s="471"/>
     </row>
     <row r="76" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1432" t="s">
+      <c r="A76" s="1417" t="s">
         <v>189</v>
       </c>
-      <c r="B76" s="1432"/>
+      <c r="B76" s="1417"/>
       <c r="C76" s="641" t="s">
         <v>190</v>
       </c>
@@ -32347,16 +32344,16 @@
       <c r="R87" s="486" t="s">
         <v>198</v>
       </c>
-      <c r="T87" s="1431" t="s">
+      <c r="T87" s="1416" t="s">
         <v>527</v>
       </c>
-      <c r="U87" s="1431"/>
-      <c r="V87" s="1431"/>
-      <c r="W87" s="1431" t="s">
+      <c r="U87" s="1416"/>
+      <c r="V87" s="1416"/>
+      <c r="W87" s="1416" t="s">
         <v>528</v>
       </c>
-      <c r="X87" s="1431"/>
-      <c r="Y87" s="1431"/>
+      <c r="X87" s="1416"/>
+      <c r="Y87" s="1416"/>
     </row>
     <row r="88" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="596" t="s">
@@ -32880,19 +32877,19 @@
       <c r="A100" s="1262" t="s">
         <v>648</v>
       </c>
-      <c r="B100" s="1415" t="s">
+      <c r="B100" s="1431" t="s">
         <v>649</v>
       </c>
-      <c r="C100" s="1416"/>
+      <c r="C100" s="1432"/>
       <c r="D100" s="1263"/>
-      <c r="E100" s="1417" t="s">
+      <c r="E100" s="1433" t="s">
         <v>650</v>
       </c>
-      <c r="F100" s="1417"/>
-      <c r="G100" s="1418" t="s">
+      <c r="F100" s="1433"/>
+      <c r="G100" s="1434" t="s">
         <v>651</v>
       </c>
-      <c r="H100" s="1419"/>
+      <c r="H100" s="1435"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="940"/>
@@ -32908,19 +32905,19 @@
       <c r="A102" s="1264" t="s">
         <v>652</v>
       </c>
-      <c r="B102" s="1420">
+      <c r="B102" s="1436">
         <v>44944</v>
       </c>
-      <c r="C102" s="1421"/>
+      <c r="C102" s="1437"/>
       <c r="D102" s="940"/>
-      <c r="E102" s="1422" t="s">
+      <c r="E102" s="1438" t="s">
         <v>653</v>
       </c>
-      <c r="F102" s="1422"/>
-      <c r="G102" s="1420">
+      <c r="F102" s="1438"/>
+      <c r="G102" s="1436">
         <v>44944</v>
       </c>
-      <c r="H102" s="1421"/>
+      <c r="H102" s="1437"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="940"/>
@@ -32935,12 +32932,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wd0Sk3J/OeT0TxJIAnp4S2dGatByENh6gH5lE7pLCIYYn5xv110dK84OeIJzfd1un3raa/Q0kk7gUzEP+5w5+g==" saltValue="Nxfv9eN1cqS8LPjiSFaCXw==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="T87:V87"/>
-    <mergeCell ref="W87:Y87"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="R30:S33"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G102:H102"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:H4"/>
     <mergeCell ref="L30:L33"/>
@@ -32949,12 +32946,12 @@
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="S35:S36"/>
     <mergeCell ref="T35:U36"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="T87:V87"/>
+    <mergeCell ref="W87:Y87"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="R30:S33"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -33008,22 +33005,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B2" s="1438" t="s">
+      <c r="B2" s="1439" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="1438"/>
-      <c r="D2" s="1438"/>
-      <c r="E2" s="1438"/>
-      <c r="F2" s="1438"/>
-      <c r="G2" s="1438"/>
-      <c r="L2" s="1438" t="s">
+      <c r="C2" s="1439"/>
+      <c r="D2" s="1439"/>
+      <c r="E2" s="1439"/>
+      <c r="F2" s="1439"/>
+      <c r="G2" s="1439"/>
+      <c r="L2" s="1439" t="s">
         <v>206</v>
       </c>
-      <c r="M2" s="1438"/>
-      <c r="N2" s="1438"/>
-      <c r="O2" s="1438"/>
-      <c r="P2" s="1438"/>
-      <c r="Q2" s="1438"/>
+      <c r="M2" s="1439"/>
+      <c r="N2" s="1439"/>
+      <c r="O2" s="1439"/>
+      <c r="P2" s="1439"/>
+      <c r="Q2" s="1439"/>
       <c r="T2" s="471"/>
       <c r="U2" s="471"/>
       <c r="V2" s="1050" t="s">
@@ -33066,10 +33063,10 @@
       <c r="AA5" s="471"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="I6" s="1439" t="s">
+      <c r="I6" s="1440" t="s">
         <v>207</v>
       </c>
-      <c r="J6" s="1440"/>
+      <c r="J6" s="1441"/>
       <c r="T6" s="471"/>
       <c r="U6" s="471"/>
       <c r="V6" s="471"/>
@@ -34452,39 +34449,39 @@
       <c r="A7" s="1135" t="s">
         <v>574</v>
       </c>
-      <c r="B7" s="1441">
+      <c r="B7" s="1442">
         <v>2.0947951371589977E-2</v>
       </c>
-      <c r="C7" s="1441"/>
-      <c r="D7" s="1441"/>
+      <c r="C7" s="1442"/>
+      <c r="D7" s="1442"/>
       <c r="E7" s="482"/>
       <c r="G7" s="1135" t="s">
         <v>574</v>
       </c>
-      <c r="H7" s="1441">
+      <c r="H7" s="1442">
         <v>0.11030261405182915</v>
       </c>
-      <c r="I7" s="1441"/>
-      <c r="J7" s="1441"/>
+      <c r="I7" s="1442"/>
+      <c r="J7" s="1442"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1135" t="s">
         <v>575</v>
       </c>
-      <c r="B8" s="1441">
+      <c r="B8" s="1442">
         <v>2.1813476975842898E-2</v>
       </c>
-      <c r="C8" s="1441"/>
-      <c r="D8" s="1441"/>
+      <c r="C8" s="1442"/>
+      <c r="D8" s="1442"/>
       <c r="E8" s="482"/>
       <c r="G8" s="1135" t="s">
         <v>575</v>
       </c>
-      <c r="H8" s="1441">
+      <c r="H8" s="1442">
         <v>0.11377365443927613</v>
       </c>
-      <c r="I8" s="1441"/>
-      <c r="J8" s="1441"/>
+      <c r="I8" s="1442"/>
+      <c r="J8" s="1442"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="FYJq3GhyQBF7Pmjc4398tmgpF0gfeMaFowah8hdIzkRnEppsVQu7MC046WcPkrhdaONzABmyez2teHVIMA3rRQ==" saltValue="QmbXxEwr+jVZyr/mMxd6pw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -34607,18 +34604,18 @@
       <c r="V7" s="365"/>
     </row>
     <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1445">
+      <c r="A8" s="1450">
         <v>1</v>
       </c>
-      <c r="B8" s="1445"/>
-      <c r="C8" s="1445"/>
-      <c r="D8" s="1445"/>
-      <c r="E8" s="1445"/>
-      <c r="F8" s="1445"/>
-      <c r="G8" s="1445"/>
-      <c r="H8" s="1445"/>
-      <c r="I8" s="1445"/>
-      <c r="J8" s="1445"/>
+      <c r="B8" s="1450"/>
+      <c r="C8" s="1450"/>
+      <c r="D8" s="1450"/>
+      <c r="E8" s="1450"/>
+      <c r="F8" s="1450"/>
+      <c r="G8" s="1450"/>
+      <c r="H8" s="1450"/>
+      <c r="I8" s="1450"/>
+      <c r="J8" s="1450"/>
       <c r="L8" s="334"/>
       <c r="M8" s="366"/>
       <c r="N8" s="367"/>
@@ -34897,18 +34894,18 @@
       <c r="AL14" s="315"/>
     </row>
     <row r="15" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1446" t="s">
+      <c r="A15" s="1451" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="1447"/>
-      <c r="C15" s="1447"/>
-      <c r="D15" s="1447"/>
-      <c r="E15" s="1447"/>
-      <c r="F15" s="1447"/>
-      <c r="G15" s="1447"/>
-      <c r="H15" s="1447"/>
-      <c r="I15" s="1447"/>
-      <c r="J15" s="1448"/>
+      <c r="B15" s="1452"/>
+      <c r="C15" s="1452"/>
+      <c r="D15" s="1452"/>
+      <c r="E15" s="1452"/>
+      <c r="F15" s="1452"/>
+      <c r="G15" s="1452"/>
+      <c r="H15" s="1452"/>
+      <c r="I15" s="1452"/>
+      <c r="J15" s="1453"/>
       <c r="K15" s="341"/>
       <c r="M15" s="365"/>
       <c r="N15" s="365"/>
@@ -34937,18 +34934,18 @@
       <c r="AL15" s="315"/>
     </row>
     <row r="16" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1449" t="s">
+      <c r="A16" s="1454" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="1450"/>
-      <c r="C16" s="1450"/>
-      <c r="D16" s="1450"/>
-      <c r="E16" s="1450"/>
-      <c r="F16" s="1450"/>
-      <c r="G16" s="1450"/>
-      <c r="H16" s="1450"/>
-      <c r="I16" s="1450"/>
-      <c r="J16" s="1451"/>
+      <c r="B16" s="1455"/>
+      <c r="C16" s="1455"/>
+      <c r="D16" s="1455"/>
+      <c r="E16" s="1455"/>
+      <c r="F16" s="1455"/>
+      <c r="G16" s="1455"/>
+      <c r="H16" s="1455"/>
+      <c r="I16" s="1455"/>
+      <c r="J16" s="1456"/>
       <c r="K16" s="341"/>
       <c r="L16" s="341"/>
       <c r="M16" s="365"/>
@@ -35074,10 +35071,10 @@
       </c>
       <c r="L19" s="341"/>
       <c r="M19" s="361"/>
-      <c r="N19" s="1443" t="s">
+      <c r="N19" s="1448" t="s">
         <v>230</v>
       </c>
-      <c r="O19" s="1443" t="s">
+      <c r="O19" s="1448" t="s">
         <v>231</v>
       </c>
       <c r="P19" s="361"/>
@@ -35129,8 +35126,8 @@
       </c>
       <c r="L20" s="341"/>
       <c r="M20" s="361"/>
-      <c r="N20" s="1444"/>
-      <c r="O20" s="1444"/>
+      <c r="N20" s="1449"/>
+      <c r="O20" s="1449"/>
       <c r="P20" s="371"/>
       <c r="Q20" s="372"/>
       <c r="R20" s="361"/>
@@ -35259,18 +35256,18 @@
       <c r="AL22" s="315"/>
     </row>
     <row r="23" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1452" t="s">
+      <c r="A23" s="1457" t="s">
         <v>235</v>
       </c>
-      <c r="B23" s="1452"/>
-      <c r="C23" s="1452"/>
-      <c r="D23" s="1452"/>
-      <c r="E23" s="1452"/>
-      <c r="F23" s="1452"/>
-      <c r="G23" s="1452"/>
-      <c r="H23" s="1452"/>
-      <c r="I23" s="1452"/>
-      <c r="J23" s="1452"/>
+      <c r="B23" s="1457"/>
+      <c r="C23" s="1457"/>
+      <c r="D23" s="1457"/>
+      <c r="E23" s="1457"/>
+      <c r="F23" s="1457"/>
+      <c r="G23" s="1457"/>
+      <c r="H23" s="1457"/>
+      <c r="I23" s="1457"/>
+      <c r="J23" s="1457"/>
       <c r="K23" s="341"/>
       <c r="L23" s="344"/>
       <c r="M23" s="361"/>
@@ -35713,18 +35710,18 @@
       <c r="AL32" s="315"/>
     </row>
     <row r="33" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1452" t="s">
+      <c r="A33" s="1457" t="s">
         <v>253</v>
       </c>
-      <c r="B33" s="1452"/>
-      <c r="C33" s="1452"/>
-      <c r="D33" s="1452"/>
-      <c r="E33" s="1452"/>
-      <c r="F33" s="1452"/>
-      <c r="G33" s="1452"/>
-      <c r="H33" s="1452"/>
-      <c r="I33" s="1452"/>
-      <c r="J33" s="1452"/>
+      <c r="B33" s="1457"/>
+      <c r="C33" s="1457"/>
+      <c r="D33" s="1457"/>
+      <c r="E33" s="1457"/>
+      <c r="F33" s="1457"/>
+      <c r="G33" s="1457"/>
+      <c r="H33" s="1457"/>
+      <c r="I33" s="1457"/>
+      <c r="J33" s="1457"/>
       <c r="K33" s="437"/>
       <c r="L33" s="437"/>
       <c r="T33" s="314"/>
@@ -35749,15 +35746,15 @@
     </row>
     <row r="34" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="749"/>
-      <c r="B34" s="1442" t="s">
+      <c r="B34" s="1447" t="s">
         <v>254</v>
       </c>
-      <c r="C34" s="1442"/>
-      <c r="D34" s="1442"/>
-      <c r="E34" s="1442"/>
-      <c r="F34" s="1442"/>
-      <c r="G34" s="1442"/>
-      <c r="H34" s="1442"/>
+      <c r="C34" s="1447"/>
+      <c r="D34" s="1447"/>
+      <c r="E34" s="1447"/>
+      <c r="F34" s="1447"/>
+      <c r="G34" s="1447"/>
+      <c r="H34" s="1447"/>
       <c r="I34" s="757"/>
       <c r="J34" s="758"/>
       <c r="K34" s="341"/>
@@ -35827,18 +35824,18 @@
       <c r="AL35" s="315"/>
     </row>
     <row r="36" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1452" t="s">
+      <c r="A36" s="1457" t="s">
         <v>257</v>
       </c>
-      <c r="B36" s="1452"/>
-      <c r="C36" s="1452"/>
-      <c r="D36" s="1452"/>
-      <c r="E36" s="1452"/>
-      <c r="F36" s="1452"/>
-      <c r="G36" s="1452"/>
-      <c r="H36" s="1452"/>
-      <c r="I36" s="1452"/>
-      <c r="J36" s="1452"/>
+      <c r="B36" s="1457"/>
+      <c r="C36" s="1457"/>
+      <c r="D36" s="1457"/>
+      <c r="E36" s="1457"/>
+      <c r="F36" s="1457"/>
+      <c r="G36" s="1457"/>
+      <c r="H36" s="1457"/>
+      <c r="I36" s="1457"/>
+      <c r="J36" s="1457"/>
       <c r="K36" s="341"/>
       <c r="L36" s="341"/>
       <c r="T36" s="314"/>
@@ -35863,15 +35860,15 @@
     </row>
     <row r="37" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="749"/>
-      <c r="B37" s="1442" t="s">
+      <c r="B37" s="1447" t="s">
         <v>258</v>
       </c>
-      <c r="C37" s="1442"/>
-      <c r="D37" s="1442"/>
-      <c r="E37" s="1442"/>
-      <c r="F37" s="1442"/>
-      <c r="G37" s="1442"/>
-      <c r="H37" s="1442"/>
+      <c r="C37" s="1447"/>
+      <c r="D37" s="1447"/>
+      <c r="E37" s="1447"/>
+      <c r="F37" s="1447"/>
+      <c r="G37" s="1447"/>
+      <c r="H37" s="1447"/>
       <c r="I37" s="757"/>
       <c r="J37" s="758"/>
       <c r="K37" s="341"/>
@@ -35974,18 +35971,18 @@
       <c r="AL39" s="315"/>
     </row>
     <row r="40" spans="1:38" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1456" t="s">
+      <c r="A40" s="1443" t="s">
         <v>261</v>
       </c>
-      <c r="B40" s="1456"/>
-      <c r="C40" s="1456"/>
-      <c r="D40" s="1456"/>
-      <c r="E40" s="1456"/>
-      <c r="F40" s="1456"/>
-      <c r="G40" s="1456"/>
-      <c r="H40" s="1456"/>
-      <c r="I40" s="1456"/>
-      <c r="J40" s="1456"/>
+      <c r="B40" s="1443"/>
+      <c r="C40" s="1443"/>
+      <c r="D40" s="1443"/>
+      <c r="E40" s="1443"/>
+      <c r="F40" s="1443"/>
+      <c r="G40" s="1443"/>
+      <c r="H40" s="1443"/>
+      <c r="I40" s="1443"/>
+      <c r="J40" s="1443"/>
       <c r="K40" s="341"/>
       <c r="L40" s="341"/>
       <c r="T40" s="314"/>
@@ -36009,16 +36006,16 @@
       <c r="AL40" s="315"/>
     </row>
     <row r="41" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1456"/>
-      <c r="B41" s="1456"/>
-      <c r="C41" s="1456"/>
-      <c r="D41" s="1456"/>
-      <c r="E41" s="1456"/>
-      <c r="F41" s="1456"/>
-      <c r="G41" s="1456"/>
-      <c r="H41" s="1456"/>
-      <c r="I41" s="1456"/>
-      <c r="J41" s="1456"/>
+      <c r="A41" s="1443"/>
+      <c r="B41" s="1443"/>
+      <c r="C41" s="1443"/>
+      <c r="D41" s="1443"/>
+      <c r="E41" s="1443"/>
+      <c r="F41" s="1443"/>
+      <c r="G41" s="1443"/>
+      <c r="H41" s="1443"/>
+      <c r="I41" s="1443"/>
+      <c r="J41" s="1443"/>
       <c r="K41" s="341"/>
       <c r="L41" s="341"/>
       <c r="T41" s="314"/>
@@ -36042,16 +36039,16 @@
       <c r="AL41" s="315"/>
     </row>
     <row r="42" spans="1:38" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1456"/>
-      <c r="B42" s="1456"/>
-      <c r="C42" s="1456"/>
-      <c r="D42" s="1456"/>
-      <c r="E42" s="1456"/>
-      <c r="F42" s="1456"/>
-      <c r="G42" s="1456"/>
-      <c r="H42" s="1456"/>
-      <c r="I42" s="1456"/>
-      <c r="J42" s="1456"/>
+      <c r="A42" s="1443"/>
+      <c r="B42" s="1443"/>
+      <c r="C42" s="1443"/>
+      <c r="D42" s="1443"/>
+      <c r="E42" s="1443"/>
+      <c r="F42" s="1443"/>
+      <c r="G42" s="1443"/>
+      <c r="H42" s="1443"/>
+      <c r="I42" s="1443"/>
+      <c r="J42" s="1443"/>
       <c r="K42" s="418"/>
       <c r="L42" s="381"/>
       <c r="N42" s="378"/>
@@ -36131,9 +36128,9 @@
       <c r="K44" s="341"/>
       <c r="L44" s="383"/>
       <c r="M44" s="383"/>
-      <c r="N44" s="1341"/>
-      <c r="O44" s="1341"/>
-      <c r="P44" s="1341"/>
+      <c r="N44" s="1335"/>
+      <c r="O44" s="1335"/>
+      <c r="P44" s="1335"/>
       <c r="T44" s="314"/>
       <c r="U44" s="325"/>
       <c r="V44" s="325"/>
@@ -36162,15 +36159,15 @@
       <c r="E45" s="197"/>
       <c r="F45" s="197"/>
       <c r="G45" s="200"/>
-      <c r="H45" s="1381"/>
-      <c r="I45" s="1381"/>
-      <c r="J45" s="1381"/>
+      <c r="H45" s="1334"/>
+      <c r="I45" s="1334"/>
+      <c r="J45" s="1334"/>
       <c r="K45" s="341"/>
       <c r="L45" s="384"/>
       <c r="M45" s="385"/>
-      <c r="N45" s="1453"/>
-      <c r="O45" s="1453"/>
-      <c r="P45" s="1453"/>
+      <c r="N45" s="1445"/>
+      <c r="O45" s="1445"/>
+      <c r="P45" s="1445"/>
       <c r="T45" s="314"/>
       <c r="U45" s="325"/>
       <c r="V45" s="325"/>
@@ -36199,15 +36196,15 @@
       <c r="E46" s="197"/>
       <c r="F46" s="197"/>
       <c r="G46" s="200"/>
-      <c r="H46" s="1341"/>
-      <c r="I46" s="1341"/>
-      <c r="J46" s="1341"/>
+      <c r="H46" s="1335"/>
+      <c r="I46" s="1335"/>
+      <c r="J46" s="1335"/>
       <c r="K46" s="341"/>
       <c r="L46" s="386"/>
       <c r="M46" s="387"/>
-      <c r="N46" s="1341"/>
-      <c r="O46" s="1341"/>
-      <c r="P46" s="1341"/>
+      <c r="N46" s="1335"/>
+      <c r="O46" s="1335"/>
+      <c r="P46" s="1335"/>
       <c r="T46" s="314"/>
       <c r="U46" s="325"/>
       <c r="V46" s="325"/>
@@ -36236,15 +36233,15 @@
       <c r="E47" s="197"/>
       <c r="F47" s="197"/>
       <c r="G47" s="200"/>
-      <c r="H47" s="1453"/>
-      <c r="I47" s="1453"/>
-      <c r="J47" s="1453"/>
+      <c r="H47" s="1445"/>
+      <c r="I47" s="1445"/>
+      <c r="J47" s="1445"/>
       <c r="K47" s="341"/>
       <c r="L47" s="386"/>
       <c r="M47" s="387"/>
-      <c r="N47" s="1381"/>
-      <c r="O47" s="1381"/>
-      <c r="P47" s="1381"/>
+      <c r="N47" s="1334"/>
+      <c r="O47" s="1334"/>
+      <c r="P47" s="1334"/>
       <c r="T47" s="314"/>
       <c r="U47" s="325"/>
       <c r="V47" s="325"/>
@@ -36273,15 +36270,15 @@
       <c r="E48" s="197"/>
       <c r="F48" s="197"/>
       <c r="G48" s="200"/>
-      <c r="H48" s="1341"/>
-      <c r="I48" s="1341"/>
-      <c r="J48" s="1341"/>
+      <c r="H48" s="1335"/>
+      <c r="I48" s="1335"/>
+      <c r="J48" s="1335"/>
       <c r="K48" s="341"/>
       <c r="L48" s="386"/>
       <c r="M48" s="387"/>
-      <c r="N48" s="1455"/>
-      <c r="O48" s="1455"/>
-      <c r="P48" s="1455"/>
+      <c r="N48" s="1446"/>
+      <c r="O48" s="1446"/>
+      <c r="P48" s="1446"/>
       <c r="T48" s="314"/>
       <c r="U48" s="325"/>
       <c r="V48" s="325"/>
@@ -36310,15 +36307,15 @@
       <c r="E49" s="200"/>
       <c r="F49" s="200"/>
       <c r="G49" s="200"/>
-      <c r="H49" s="1381"/>
-      <c r="I49" s="1381"/>
-      <c r="J49" s="1381"/>
+      <c r="H49" s="1334"/>
+      <c r="I49" s="1334"/>
+      <c r="J49" s="1334"/>
       <c r="K49" s="341"/>
       <c r="L49" s="386"/>
       <c r="M49" s="387"/>
-      <c r="N49" s="1453"/>
-      <c r="O49" s="1453"/>
-      <c r="P49" s="1453"/>
+      <c r="N49" s="1445"/>
+      <c r="O49" s="1445"/>
+      <c r="P49" s="1445"/>
       <c r="T49" s="314"/>
       <c r="U49" s="325"/>
       <c r="V49" s="325"/>
@@ -37088,16 +37085,16 @@
       <c r="AL74" s="315"/>
     </row>
     <row r="75" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1456"/>
-      <c r="B75" s="1456"/>
-      <c r="C75" s="1456"/>
-      <c r="D75" s="1456"/>
-      <c r="E75" s="1456"/>
-      <c r="F75" s="1456"/>
-      <c r="G75" s="1456"/>
-      <c r="H75" s="1456"/>
-      <c r="I75" s="1456"/>
-      <c r="J75" s="1456"/>
+      <c r="A75" s="1443"/>
+      <c r="B75" s="1443"/>
+      <c r="C75" s="1443"/>
+      <c r="D75" s="1443"/>
+      <c r="E75" s="1443"/>
+      <c r="F75" s="1443"/>
+      <c r="G75" s="1443"/>
+      <c r="H75" s="1443"/>
+      <c r="I75" s="1443"/>
+      <c r="J75" s="1443"/>
       <c r="T75" s="314"/>
       <c r="U75" s="325"/>
       <c r="V75" s="325"/>
@@ -37119,16 +37116,16 @@
       <c r="AL75" s="315"/>
     </row>
     <row r="76" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1456"/>
-      <c r="B76" s="1456"/>
-      <c r="C76" s="1456"/>
-      <c r="D76" s="1456"/>
-      <c r="E76" s="1456"/>
-      <c r="F76" s="1456"/>
-      <c r="G76" s="1456"/>
-      <c r="H76" s="1456"/>
-      <c r="I76" s="1456"/>
-      <c r="J76" s="1456"/>
+      <c r="A76" s="1443"/>
+      <c r="B76" s="1443"/>
+      <c r="C76" s="1443"/>
+      <c r="D76" s="1443"/>
+      <c r="E76" s="1443"/>
+      <c r="F76" s="1443"/>
+      <c r="G76" s="1443"/>
+      <c r="H76" s="1443"/>
+      <c r="I76" s="1443"/>
+      <c r="J76" s="1443"/>
       <c r="T76" s="314"/>
       <c r="U76" s="325"/>
       <c r="V76" s="325"/>
@@ -37150,16 +37147,16 @@
       <c r="AL76" s="315"/>
     </row>
     <row r="77" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1456"/>
-      <c r="B77" s="1456"/>
-      <c r="C77" s="1456"/>
-      <c r="D77" s="1456"/>
-      <c r="E77" s="1456"/>
-      <c r="F77" s="1456"/>
-      <c r="G77" s="1456"/>
-      <c r="H77" s="1456"/>
-      <c r="I77" s="1456"/>
-      <c r="J77" s="1456"/>
+      <c r="A77" s="1443"/>
+      <c r="B77" s="1443"/>
+      <c r="C77" s="1443"/>
+      <c r="D77" s="1443"/>
+      <c r="E77" s="1443"/>
+      <c r="F77" s="1443"/>
+      <c r="G77" s="1443"/>
+      <c r="H77" s="1443"/>
+      <c r="I77" s="1443"/>
+      <c r="J77" s="1443"/>
       <c r="T77" s="314"/>
       <c r="U77" s="325"/>
       <c r="V77" s="325"/>
@@ -37274,10 +37271,10 @@
       <c r="AL80" s="315"/>
     </row>
     <row r="81" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G81" s="1454"/>
-      <c r="H81" s="1454"/>
-      <c r="I81" s="1454"/>
-      <c r="J81" s="1454"/>
+      <c r="G81" s="1444"/>
+      <c r="H81" s="1444"/>
+      <c r="I81" s="1444"/>
+      <c r="J81" s="1444"/>
       <c r="T81" s="314"/>
       <c r="U81" s="325"/>
       <c r="V81" s="325"/>
@@ -37322,10 +37319,10 @@
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" s="313"/>
-      <c r="G83" s="1454"/>
-      <c r="H83" s="1454"/>
-      <c r="I83" s="1454"/>
-      <c r="J83" s="1454"/>
+      <c r="G83" s="1444"/>
+      <c r="H83" s="1444"/>
+      <c r="I83" s="1444"/>
+      <c r="J83" s="1444"/>
       <c r="T83" s="314"/>
       <c r="U83" s="325"/>
       <c r="V83" s="325"/>
@@ -39807,23 +39804,6 @@
     <protectedRange sqref="C10:C13" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="29">
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J42"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A76:J77"/>
-    <mergeCell ref="G81:J81"/>
-    <mergeCell ref="H47:J47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="G83:J83"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="N46:P46"/>
     <mergeCell ref="B37:H37"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
@@ -39836,6 +39816,23 @@
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="B34:H34"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A41:J42"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A76:J77"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="H47:J47"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.78740157480314965" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -40048,19 +40045,19 @@
       <c r="Z6" s="37"/>
     </row>
     <row r="7" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1464" t="s">
+      <c r="A7" s="1487" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1464"/>
-      <c r="C7" s="1464"/>
-      <c r="D7" s="1464"/>
-      <c r="E7" s="1464"/>
-      <c r="F7" s="1464"/>
-      <c r="G7" s="1464"/>
-      <c r="H7" s="1464"/>
-      <c r="I7" s="1464"/>
-      <c r="J7" s="1464"/>
-      <c r="K7" s="1464"/>
+      <c r="B7" s="1487"/>
+      <c r="C7" s="1487"/>
+      <c r="D7" s="1487"/>
+      <c r="E7" s="1487"/>
+      <c r="F7" s="1487"/>
+      <c r="G7" s="1487"/>
+      <c r="H7" s="1487"/>
+      <c r="I7" s="1487"/>
+      <c r="J7" s="1487"/>
+      <c r="K7" s="1487"/>
       <c r="N7" s="309" t="s">
         <v>272</v>
       </c>
@@ -40085,20 +40082,20 @@
       <c r="Z7" s="37"/>
     </row>
     <row r="8" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1465">
+      <c r="A8" s="1488">
         <f>+K12</f>
         <v>1</v>
       </c>
-      <c r="B8" s="1465"/>
-      <c r="C8" s="1465"/>
-      <c r="D8" s="1465"/>
-      <c r="E8" s="1465"/>
-      <c r="F8" s="1465"/>
-      <c r="G8" s="1465"/>
-      <c r="H8" s="1465"/>
-      <c r="I8" s="1465"/>
-      <c r="J8" s="1465"/>
-      <c r="K8" s="1465"/>
+      <c r="B8" s="1488"/>
+      <c r="C8" s="1488"/>
+      <c r="D8" s="1488"/>
+      <c r="E8" s="1488"/>
+      <c r="F8" s="1488"/>
+      <c r="G8" s="1488"/>
+      <c r="H8" s="1488"/>
+      <c r="I8" s="1488"/>
+      <c r="J8" s="1488"/>
+      <c r="K8" s="1488"/>
       <c r="N8" s="769" t="s">
         <v>274</v>
       </c>
@@ -40153,14 +40150,14 @@
       <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1488" t="s">
+      <c r="C10" s="1481" t="s">
         <v>277</v>
       </c>
-      <c r="D10" s="1488"/>
-      <c r="E10" s="1488"/>
-      <c r="F10" s="1488"/>
-      <c r="G10" s="1488"/>
-      <c r="H10" s="1488"/>
+      <c r="D10" s="1481"/>
+      <c r="E10" s="1481"/>
+      <c r="F10" s="1481"/>
+      <c r="G10" s="1481"/>
+      <c r="H10" s="1481"/>
       <c r="I10" s="23" t="s">
         <v>3</v>
       </c>
@@ -40203,14 +40200,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1488" t="s">
+      <c r="C11" s="1481" t="s">
         <v>282</v>
       </c>
-      <c r="D11" s="1488"/>
-      <c r="E11" s="1488"/>
-      <c r="F11" s="1488"/>
-      <c r="G11" s="1488"/>
-      <c r="H11" s="1488"/>
+      <c r="D11" s="1481"/>
+      <c r="E11" s="1481"/>
+      <c r="F11" s="1481"/>
+      <c r="G11" s="1481"/>
+      <c r="H11" s="1481"/>
       <c r="I11" s="26" t="s">
         <v>6</v>
       </c>
@@ -40252,14 +40249,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1488" t="s">
+      <c r="C12" s="1481" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="1488"/>
-      <c r="E12" s="1488"/>
-      <c r="F12" s="1488"/>
-      <c r="G12" s="1488"/>
-      <c r="H12" s="1488"/>
+      <c r="D12" s="1481"/>
+      <c r="E12" s="1481"/>
+      <c r="F12" s="1481"/>
+      <c r="G12" s="1481"/>
+      <c r="H12" s="1481"/>
       <c r="I12" s="26" t="s">
         <v>288</v>
       </c>
@@ -40339,19 +40336,19 @@
       <c r="Z13" s="37"/>
     </row>
     <row r="14" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1446" t="s">
+      <c r="A14" s="1451" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="1447"/>
-      <c r="C14" s="1447"/>
-      <c r="D14" s="1447"/>
-      <c r="E14" s="1447"/>
-      <c r="F14" s="1447"/>
-      <c r="G14" s="1447"/>
-      <c r="H14" s="1447"/>
-      <c r="I14" s="1447"/>
-      <c r="J14" s="1447"/>
-      <c r="K14" s="1448"/>
+      <c r="B14" s="1452"/>
+      <c r="C14" s="1452"/>
+      <c r="D14" s="1452"/>
+      <c r="E14" s="1452"/>
+      <c r="F14" s="1452"/>
+      <c r="G14" s="1452"/>
+      <c r="H14" s="1452"/>
+      <c r="I14" s="1452"/>
+      <c r="J14" s="1452"/>
+      <c r="K14" s="1453"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="769" t="s">
@@ -40374,19 +40371,19 @@
       <c r="Z14" s="37"/>
     </row>
     <row r="15" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1449" t="s">
+      <c r="A15" s="1454" t="s">
         <v>295</v>
       </c>
-      <c r="B15" s="1450"/>
-      <c r="C15" s="1450"/>
-      <c r="D15" s="1450"/>
-      <c r="E15" s="1450"/>
-      <c r="F15" s="1450"/>
-      <c r="G15" s="1450"/>
-      <c r="H15" s="1450"/>
-      <c r="I15" s="1450"/>
-      <c r="J15" s="1450"/>
-      <c r="K15" s="1451"/>
+      <c r="B15" s="1455"/>
+      <c r="C15" s="1455"/>
+      <c r="D15" s="1455"/>
+      <c r="E15" s="1455"/>
+      <c r="F15" s="1455"/>
+      <c r="G15" s="1455"/>
+      <c r="H15" s="1455"/>
+      <c r="I15" s="1455"/>
+      <c r="J15" s="1455"/>
+      <c r="K15" s="1456"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="25"/>
@@ -40433,30 +40430,30 @@
       <c r="S16" s="232" t="s">
         <v>299</v>
       </c>
-      <c r="T16" s="1492" t="s">
+      <c r="T16" s="1461" t="s">
         <v>300</v>
       </c>
-      <c r="U16" s="1493"/>
-      <c r="V16" s="1494"/>
+      <c r="U16" s="1462"/>
+      <c r="V16" s="1463"/>
       <c r="W16" s="37"/>
       <c r="X16" s="37"/>
       <c r="Y16" s="37"/>
       <c r="Z16" s="37"/>
     </row>
     <row r="17" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1485" t="s">
+      <c r="A17" s="1478" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1486"/>
-      <c r="C17" s="1486"/>
-      <c r="D17" s="1486"/>
-      <c r="E17" s="1486"/>
-      <c r="F17" s="1486"/>
-      <c r="G17" s="1486"/>
-      <c r="H17" s="1486"/>
-      <c r="I17" s="1486"/>
-      <c r="J17" s="1486"/>
-      <c r="K17" s="1487"/>
+      <c r="B17" s="1479"/>
+      <c r="C17" s="1479"/>
+      <c r="D17" s="1479"/>
+      <c r="E17" s="1479"/>
+      <c r="F17" s="1479"/>
+      <c r="G17" s="1479"/>
+      <c r="H17" s="1479"/>
+      <c r="I17" s="1479"/>
+      <c r="J17" s="1479"/>
+      <c r="K17" s="1480"/>
       <c r="M17" s="3"/>
       <c r="N17" s="775" t="s">
         <v>230</v>
@@ -40476,11 +40473,11 @@
       <c r="S17" s="776" t="s">
         <v>305</v>
       </c>
-      <c r="T17" s="1489" t="s">
+      <c r="T17" s="1458" t="s">
         <v>306</v>
       </c>
-      <c r="U17" s="1490"/>
-      <c r="V17" s="1491"/>
+      <c r="U17" s="1459"/>
+      <c r="V17" s="1460"/>
       <c r="W17" s="37"/>
       <c r="X17" s="37"/>
       <c r="Y17" s="37"/>
@@ -40740,21 +40737,21 @@
       <c r="Z22" s="37"/>
     </row>
     <row r="23" spans="1:26" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1468" t="s">
+      <c r="A23" s="1491" t="s">
         <v>230</v>
       </c>
-      <c r="B23" s="1469"/>
-      <c r="C23" s="1470"/>
-      <c r="D23" s="1496" t="s">
+      <c r="B23" s="1492"/>
+      <c r="C23" s="1493"/>
+      <c r="D23" s="1466" t="s">
         <v>320</v>
       </c>
       <c r="E23" s="197"/>
-      <c r="F23" s="1472" t="s">
+      <c r="F23" s="1494" t="s">
         <v>321</v>
       </c>
-      <c r="G23" s="1473"/>
-      <c r="H23" s="1474"/>
-      <c r="I23" s="1478" t="s">
+      <c r="G23" s="1495"/>
+      <c r="H23" s="1496"/>
+      <c r="I23" s="1471" t="s">
         <v>317</v>
       </c>
       <c r="J23" s="191"/>
@@ -40798,16 +40795,16 @@
       <c r="A24" s="785" t="s">
         <v>323</v>
       </c>
-      <c r="B24" s="1467" t="s">
+      <c r="B24" s="1490" t="s">
         <v>301</v>
       </c>
-      <c r="C24" s="1467"/>
-      <c r="D24" s="1497"/>
+      <c r="C24" s="1490"/>
+      <c r="D24" s="1467"/>
       <c r="E24" s="197"/>
-      <c r="F24" s="1475"/>
-      <c r="G24" s="1476"/>
-      <c r="H24" s="1477"/>
-      <c r="I24" s="1479"/>
+      <c r="F24" s="1497"/>
+      <c r="G24" s="1498"/>
+      <c r="H24" s="1499"/>
+      <c r="I24" s="1500"/>
       <c r="J24" s="191"/>
       <c r="K24" s="192"/>
       <c r="L24" s="3"/>
@@ -40845,10 +40842,10 @@
       <c r="A25" s="786" t="s">
         <v>310</v>
       </c>
-      <c r="B25" s="1466">
+      <c r="B25" s="1489">
         <v>76.2</v>
       </c>
-      <c r="C25" s="1466"/>
+      <c r="C25" s="1489"/>
       <c r="D25" s="787">
         <f>+S18</f>
         <v>100</v>
@@ -40899,21 +40896,21 @@
       <c r="A26" s="198" t="s">
         <v>317</v>
       </c>
-      <c r="B26" s="1471">
+      <c r="B26" s="1465">
         <v>50.6</v>
       </c>
-      <c r="C26" s="1471"/>
+      <c r="C26" s="1465"/>
       <c r="D26" s="199">
         <f>+S20</f>
         <v>96.737365729020368</v>
       </c>
       <c r="E26" s="197"/>
-      <c r="F26" s="1468" t="s">
+      <c r="F26" s="1491" t="s">
         <v>326</v>
       </c>
-      <c r="G26" s="1469"/>
-      <c r="H26" s="1469"/>
-      <c r="I26" s="1470"/>
+      <c r="G26" s="1492"/>
+      <c r="H26" s="1492"/>
+      <c r="I26" s="1493"/>
       <c r="J26" s="200"/>
       <c r="K26" s="201"/>
       <c r="L26" s="3"/>
@@ -40951,19 +40948,19 @@
       <c r="A27" s="202" t="s">
         <v>318</v>
       </c>
-      <c r="B27" s="1471">
+      <c r="B27" s="1465">
         <v>38.1</v>
       </c>
-      <c r="C27" s="1471"/>
+      <c r="C27" s="1465"/>
       <c r="D27" s="199">
         <f>+S21</f>
         <v>90.324022891039832</v>
       </c>
       <c r="E27" s="197"/>
-      <c r="F27" s="1480"/>
-      <c r="G27" s="1481"/>
-      <c r="H27" s="1481"/>
-      <c r="I27" s="1482"/>
+      <c r="F27" s="1501"/>
+      <c r="G27" s="1502"/>
+      <c r="H27" s="1502"/>
+      <c r="I27" s="1503"/>
       <c r="J27" s="200"/>
       <c r="K27" s="201"/>
       <c r="L27" s="3"/>
@@ -41005,19 +41002,19 @@
       <c r="A28" s="198" t="s">
         <v>319</v>
       </c>
-      <c r="B28" s="1471">
+      <c r="B28" s="1465">
         <v>25.4</v>
       </c>
-      <c r="C28" s="1471"/>
+      <c r="C28" s="1465"/>
       <c r="D28" s="199">
         <f>+S22</f>
         <v>84.873241107276272</v>
       </c>
       <c r="E28" s="197"/>
-      <c r="F28" s="1483" t="s">
+      <c r="F28" s="1474" t="s">
         <v>329</v>
       </c>
-      <c r="G28" s="1484">
+      <c r="G28" s="1476">
         <f>R27</f>
         <v>45.788805497693524</v>
       </c>
@@ -41065,17 +41062,17 @@
       <c r="A29" s="198" t="s">
         <v>322</v>
       </c>
-      <c r="B29" s="1471">
+      <c r="B29" s="1465">
         <v>19.05</v>
       </c>
-      <c r="C29" s="1471"/>
+      <c r="C29" s="1465"/>
       <c r="D29" s="199">
         <f>+S23</f>
         <v>73.456819301447041</v>
       </c>
       <c r="E29" s="197"/>
-      <c r="F29" s="1459"/>
-      <c r="G29" s="1462"/>
+      <c r="F29" s="1475"/>
+      <c r="G29" s="1477"/>
       <c r="H29" s="203" t="s">
         <v>331</v>
       </c>
@@ -41124,19 +41121,19 @@
       <c r="A30" s="198" t="s">
         <v>325</v>
       </c>
-      <c r="B30" s="1471">
+      <c r="B30" s="1465">
         <v>9.5250000000000004</v>
       </c>
-      <c r="C30" s="1471"/>
+      <c r="C30" s="1465"/>
       <c r="D30" s="199">
         <f>+S25</f>
         <v>62.661585152699679</v>
       </c>
       <c r="E30" s="197"/>
-      <c r="F30" s="1457" t="s">
+      <c r="F30" s="1482" t="s">
         <v>332</v>
       </c>
-      <c r="G30" s="1460">
+      <c r="G30" s="1484">
         <f>100-(G28+G33)</f>
         <v>40.754382185876274</v>
       </c>
@@ -41184,17 +41181,17 @@
       <c r="A31" s="198" t="s">
         <v>328</v>
       </c>
-      <c r="B31" s="1471">
+      <c r="B31" s="1465">
         <v>4.76</v>
       </c>
-      <c r="C31" s="1471"/>
+      <c r="C31" s="1465"/>
       <c r="D31" s="199">
         <f>+S27</f>
         <v>54.211194502306476</v>
       </c>
       <c r="E31" s="197"/>
-      <c r="F31" s="1458"/>
-      <c r="G31" s="1461"/>
+      <c r="F31" s="1483"/>
+      <c r="G31" s="1485"/>
       <c r="H31" s="203" t="s">
         <v>333</v>
       </c>
@@ -41242,17 +41239,17 @@
       <c r="A32" s="198">
         <v>8</v>
       </c>
-      <c r="B32" s="1471">
+      <c r="B32" s="1465">
         <v>2.36</v>
       </c>
-      <c r="C32" s="1471"/>
+      <c r="C32" s="1465"/>
       <c r="D32" s="199">
         <f>+S28</f>
         <v>49.032616067382399</v>
       </c>
       <c r="E32" s="197"/>
-      <c r="F32" s="1459"/>
-      <c r="G32" s="1462"/>
+      <c r="F32" s="1475"/>
+      <c r="G32" s="1477"/>
       <c r="H32" s="203" t="s">
         <v>331</v>
       </c>
@@ -41304,10 +41301,10 @@
       <c r="A33" s="198">
         <v>16</v>
       </c>
-      <c r="B33" s="1471">
+      <c r="B33" s="1465">
         <v>1.19</v>
       </c>
-      <c r="C33" s="1471"/>
+      <c r="C33" s="1465"/>
       <c r="D33" s="199">
         <f t="shared" ref="D33:D38" si="4">+S30</f>
         <v>40.351707913359583</v>
@@ -41362,10 +41359,10 @@
       <c r="A34" s="198">
         <v>30</v>
       </c>
-      <c r="B34" s="1471">
+      <c r="B34" s="1465">
         <v>0.6</v>
       </c>
-      <c r="C34" s="1471"/>
+      <c r="C34" s="1465"/>
       <c r="D34" s="199">
         <f t="shared" si="4"/>
         <v>31.408593256302638</v>
@@ -41412,25 +41409,25 @@
       <c r="A35" s="198">
         <v>40</v>
       </c>
-      <c r="B35" s="1471">
+      <c r="B35" s="1465">
         <v>0.42</v>
       </c>
-      <c r="C35" s="1471"/>
+      <c r="C35" s="1465"/>
       <c r="D35" s="199">
         <f t="shared" si="4"/>
         <v>27.175831135894526</v>
       </c>
       <c r="E35" s="197"/>
-      <c r="F35" s="1498" t="str">
+      <c r="F35" s="1468" t="str">
         <f>IF(O3="No","","Clasificacion SUCS")</f>
         <v/>
       </c>
-      <c r="G35" s="1498"/>
-      <c r="H35" s="1478" t="str">
+      <c r="G35" s="1468"/>
+      <c r="H35" s="1471" t="str">
         <f>IF(O3="No","",'Sucs '!G4)</f>
         <v/>
       </c>
-      <c r="I35" s="1478"/>
+      <c r="I35" s="1471"/>
       <c r="J35" s="200"/>
       <c r="K35" s="201"/>
       <c r="L35" s="3"/>
@@ -41472,19 +41469,19 @@
       <c r="A36" s="198">
         <v>50</v>
       </c>
-      <c r="B36" s="1471">
+      <c r="B36" s="1465">
         <v>0.3</v>
       </c>
-      <c r="C36" s="1471"/>
+      <c r="C36" s="1465"/>
       <c r="D36" s="199">
         <f t="shared" si="4"/>
         <v>23.785875632381845</v>
       </c>
       <c r="E36" s="197"/>
-      <c r="F36" s="1499"/>
-      <c r="G36" s="1499"/>
-      <c r="H36" s="1501"/>
-      <c r="I36" s="1501"/>
+      <c r="F36" s="1469"/>
+      <c r="G36" s="1469"/>
+      <c r="H36" s="1472"/>
+      <c r="I36" s="1472"/>
       <c r="J36" s="200"/>
       <c r="K36" s="201"/>
       <c r="L36" s="3"/>
@@ -41523,25 +41520,25 @@
       <c r="A37" s="198">
         <v>100</v>
       </c>
-      <c r="B37" s="1471">
+      <c r="B37" s="1465">
         <v>0.14899999999999999</v>
       </c>
-      <c r="C37" s="1471"/>
+      <c r="C37" s="1465"/>
       <c r="D37" s="199">
         <f t="shared" si="4"/>
         <v>17.820677688355374</v>
       </c>
       <c r="E37" s="197"/>
-      <c r="F37" s="1499" t="str">
+      <c r="F37" s="1469" t="str">
         <f>IF(O3="No","","Clasificacion AASHTO")</f>
         <v/>
       </c>
-      <c r="G37" s="1499"/>
-      <c r="H37" s="1501" t="str">
+      <c r="G37" s="1469"/>
+      <c r="H37" s="1472" t="str">
         <f>IF(O3="No","",Aashto!J26)</f>
         <v/>
       </c>
-      <c r="I37" s="1501"/>
+      <c r="I37" s="1472"/>
       <c r="J37" s="200"/>
       <c r="K37" s="201"/>
       <c r="L37" s="3"/>
@@ -41567,19 +41564,19 @@
       <c r="A38" s="208">
         <v>200</v>
       </c>
-      <c r="B38" s="1495">
+      <c r="B38" s="1464">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="C38" s="1495"/>
+      <c r="C38" s="1464"/>
       <c r="D38" s="209">
         <f t="shared" si="4"/>
         <v>13.456812316430202</v>
       </c>
       <c r="E38" s="197"/>
-      <c r="F38" s="1500"/>
-      <c r="G38" s="1500"/>
-      <c r="H38" s="1502"/>
-      <c r="I38" s="1502"/>
+      <c r="F38" s="1470"/>
+      <c r="G38" s="1470"/>
+      <c r="H38" s="1473"/>
+      <c r="I38" s="1473"/>
       <c r="J38" s="200"/>
       <c r="K38" s="201"/>
       <c r="L38" s="3"/>
@@ -42471,19 +42468,19 @@
       <c r="Z63" s="37"/>
     </row>
     <row r="64" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1463" t="s">
+      <c r="A64" s="1486" t="s">
         <v>345</v>
       </c>
-      <c r="B64" s="1463"/>
-      <c r="C64" s="1463"/>
-      <c r="D64" s="1463"/>
-      <c r="E64" s="1463"/>
-      <c r="F64" s="1463"/>
-      <c r="G64" s="1463"/>
-      <c r="H64" s="1463"/>
-      <c r="I64" s="1463"/>
-      <c r="J64" s="1463"/>
-      <c r="K64" s="1463"/>
+      <c r="B64" s="1486"/>
+      <c r="C64" s="1486"/>
+      <c r="D64" s="1486"/>
+      <c r="E64" s="1486"/>
+      <c r="F64" s="1486"/>
+      <c r="G64" s="1486"/>
+      <c r="H64" s="1486"/>
+      <c r="I64" s="1486"/>
+      <c r="J64" s="1486"/>
+      <c r="K64" s="1486"/>
       <c r="W64" s="37"/>
       <c r="X64" s="37"/>
       <c r="Y64" s="37"/>
@@ -42519,6 +42516,29 @@
     <protectedRange sqref="C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="F26:I27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="T17:V17"/>
     <mergeCell ref="T16:V16"/>
     <mergeCell ref="B38:C38"/>
@@ -42535,29 +42555,6 @@
     <mergeCell ref="F37:G38"/>
     <mergeCell ref="H35:I36"/>
     <mergeCell ref="H37:I38"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="A64:K64"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -42685,35 +42682,35 @@
       <c r="K7" s="118"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1522" t="s">
+      <c r="A8" s="1505" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1522"/>
-      <c r="C8" s="1522"/>
-      <c r="D8" s="1522"/>
-      <c r="E8" s="1522"/>
-      <c r="F8" s="1522"/>
-      <c r="G8" s="1522"/>
-      <c r="H8" s="1522"/>
-      <c r="I8" s="1522"/>
-      <c r="J8" s="1522"/>
-      <c r="K8" s="1522"/>
+      <c r="B8" s="1505"/>
+      <c r="C8" s="1505"/>
+      <c r="D8" s="1505"/>
+      <c r="E8" s="1505"/>
+      <c r="F8" s="1505"/>
+      <c r="G8" s="1505"/>
+      <c r="H8" s="1505"/>
+      <c r="I8" s="1505"/>
+      <c r="J8" s="1505"/>
+      <c r="K8" s="1505"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1523">
+      <c r="A9" s="1506">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="1523"/>
-      <c r="C9" s="1523"/>
-      <c r="D9" s="1523"/>
-      <c r="E9" s="1523"/>
-      <c r="F9" s="1523"/>
-      <c r="G9" s="1523"/>
-      <c r="H9" s="1523"/>
-      <c r="I9" s="1523"/>
-      <c r="J9" s="1523"/>
-      <c r="K9" s="1523"/>
+      <c r="B9" s="1506"/>
+      <c r="C9" s="1506"/>
+      <c r="D9" s="1506"/>
+      <c r="E9" s="1506"/>
+      <c r="F9" s="1506"/>
+      <c r="G9" s="1506"/>
+      <c r="H9" s="1506"/>
+      <c r="I9" s="1506"/>
+      <c r="J9" s="1506"/>
+      <c r="K9" s="1506"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -42736,14 +42733,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1524" t="s">
+      <c r="C11" s="1507" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="1524"/>
-      <c r="E11" s="1524"/>
-      <c r="F11" s="1524"/>
-      <c r="G11" s="1524"/>
-      <c r="H11" s="1524"/>
+      <c r="D11" s="1507"/>
+      <c r="E11" s="1507"/>
+      <c r="F11" s="1507"/>
+      <c r="G11" s="1507"/>
+      <c r="H11" s="1507"/>
       <c r="I11" s="121" t="s">
         <v>3</v>
       </c>
@@ -42764,14 +42761,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1524" t="s">
+      <c r="C12" s="1507" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="1524"/>
-      <c r="E12" s="1524"/>
-      <c r="F12" s="1524"/>
-      <c r="G12" s="1524"/>
-      <c r="H12" s="1524"/>
+      <c r="D12" s="1507"/>
+      <c r="E12" s="1507"/>
+      <c r="F12" s="1507"/>
+      <c r="G12" s="1507"/>
+      <c r="H12" s="1507"/>
       <c r="I12" s="26" t="s">
         <v>6</v>
       </c>
@@ -42795,14 +42792,14 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1524" t="s">
+      <c r="C13" s="1507" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="1524"/>
-      <c r="E13" s="1524"/>
-      <c r="F13" s="1524"/>
-      <c r="G13" s="1524"/>
-      <c r="H13" s="1524"/>
+      <c r="D13" s="1507"/>
+      <c r="E13" s="1507"/>
+      <c r="F13" s="1507"/>
+      <c r="G13" s="1507"/>
+      <c r="H13" s="1507"/>
       <c r="I13" s="26" t="s">
         <v>288</v>
       </c>
@@ -42816,8 +42813,8 @@
       <c r="M13" s="124"/>
       <c r="P13" s="127"/>
       <c r="Q13" s="127"/>
-      <c r="R13" s="1521"/>
-      <c r="S13" s="1521"/>
+      <c r="R13" s="1504"/>
+      <c r="S13" s="1504"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -42839,19 +42836,19 @@
       <c r="S14" s="737"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1510" t="s">
+      <c r="A15" s="1508" t="s">
         <v>347</v>
       </c>
-      <c r="B15" s="1511"/>
-      <c r="C15" s="1511"/>
-      <c r="D15" s="1511"/>
-      <c r="E15" s="1511"/>
-      <c r="F15" s="1511"/>
-      <c r="G15" s="1511"/>
-      <c r="H15" s="1511"/>
-      <c r="I15" s="1511"/>
-      <c r="J15" s="1511"/>
-      <c r="K15" s="1512"/>
+      <c r="B15" s="1509"/>
+      <c r="C15" s="1509"/>
+      <c r="D15" s="1509"/>
+      <c r="E15" s="1509"/>
+      <c r="F15" s="1509"/>
+      <c r="G15" s="1509"/>
+      <c r="H15" s="1509"/>
+      <c r="I15" s="1509"/>
+      <c r="J15" s="1509"/>
+      <c r="K15" s="1510"/>
       <c r="L15" s="124"/>
       <c r="M15" s="124"/>
       <c r="P15" s="127"/>
@@ -42860,19 +42857,19 @@
       <c r="S15" s="737"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1513" t="s">
+      <c r="A16" s="1511" t="s">
         <v>348</v>
       </c>
-      <c r="B16" s="1514"/>
-      <c r="C16" s="1514"/>
-      <c r="D16" s="1514"/>
-      <c r="E16" s="1514"/>
-      <c r="F16" s="1514"/>
-      <c r="G16" s="1514"/>
-      <c r="H16" s="1514"/>
-      <c r="I16" s="1514"/>
-      <c r="J16" s="1514"/>
-      <c r="K16" s="1515"/>
+      <c r="B16" s="1512"/>
+      <c r="C16" s="1512"/>
+      <c r="D16" s="1512"/>
+      <c r="E16" s="1512"/>
+      <c r="F16" s="1512"/>
+      <c r="G16" s="1512"/>
+      <c r="H16" s="1512"/>
+      <c r="I16" s="1512"/>
+      <c r="J16" s="1512"/>
+      <c r="K16" s="1513"/>
       <c r="L16" s="124"/>
       <c r="M16" s="124"/>
       <c r="P16" s="127"/>
@@ -42900,19 +42897,19 @@
       <c r="S17" s="737"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1485" t="s">
+      <c r="A18" s="1478" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1486"/>
-      <c r="C18" s="1486"/>
-      <c r="D18" s="1486"/>
-      <c r="E18" s="1486"/>
-      <c r="F18" s="1486"/>
-      <c r="G18" s="1486"/>
-      <c r="H18" s="1486"/>
-      <c r="I18" s="1486"/>
-      <c r="J18" s="1486"/>
-      <c r="K18" s="1487"/>
+      <c r="B18" s="1479"/>
+      <c r="C18" s="1479"/>
+      <c r="D18" s="1479"/>
+      <c r="E18" s="1479"/>
+      <c r="F18" s="1479"/>
+      <c r="G18" s="1479"/>
+      <c r="H18" s="1479"/>
+      <c r="I18" s="1479"/>
+      <c r="J18" s="1479"/>
+      <c r="K18" s="1480"/>
       <c r="M18" s="124"/>
       <c r="P18" s="127"/>
       <c r="Q18" s="127"/>
@@ -43029,8 +43026,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="805"/>
-      <c r="I23" s="1516"/>
-      <c r="J23" s="1516"/>
+      <c r="I23" s="1514"/>
+      <c r="J23" s="1514"/>
       <c r="K23" s="806"/>
       <c r="L23" s="124"/>
       <c r="M23" s="139"/>
@@ -43038,41 +43035,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="141"/>
-      <c r="D24" s="1517" t="s">
+      <c r="D24" s="1515" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="1518"/>
-      <c r="F24" s="1518"/>
-      <c r="G24" s="1519" t="s">
+      <c r="E24" s="1516"/>
+      <c r="F24" s="1516"/>
+      <c r="G24" s="1517" t="s">
         <v>352</v>
       </c>
-      <c r="H24" s="1520"/>
-      <c r="I24" s="1508"/>
-      <c r="J24" s="1508"/>
+      <c r="H24" s="1518"/>
+      <c r="I24" s="1519"/>
+      <c r="J24" s="1519"/>
       <c r="K24" s="142"/>
       <c r="L24" s="124"/>
       <c r="M24" s="143"/>
-      <c r="O24" s="1503" t="s">
+      <c r="O24" s="1520" t="s">
         <v>351</v>
       </c>
-      <c r="P24" s="1504"/>
+      <c r="P24" s="1521"/>
       <c r="Q24" s="807" t="s">
         <v>350</v>
       </c>
-      <c r="R24" s="1503" t="s">
+      <c r="R24" s="1520" t="s">
         <v>352</v>
       </c>
-      <c r="S24" s="1505"/>
+      <c r="S24" s="1522"/>
       <c r="T24" s="807" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="141"/>
-      <c r="B25" s="1506" t="s">
+      <c r="B25" s="1523" t="s">
         <v>353</v>
       </c>
-      <c r="C25" s="1507"/>
+      <c r="C25" s="1524"/>
       <c r="D25" s="808" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -43093,8 +43090,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="1508"/>
-      <c r="J25" s="1508"/>
+      <c r="I25" s="1519"/>
+      <c r="J25" s="1519"/>
       <c r="K25" s="142"/>
       <c r="L25" s="124"/>
       <c r="M25" s="143"/>
@@ -43143,8 +43140,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="1509"/>
-      <c r="J26" s="1509"/>
+      <c r="I26" s="1525"/>
+      <c r="J26" s="1525"/>
       <c r="K26" s="151"/>
       <c r="L26" s="152"/>
       <c r="M26" s="143"/>
@@ -43859,19 +43856,19 @@
     </row>
     <row r="49" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1463" t="s">
+      <c r="A50" s="1486" t="s">
         <v>345</v>
       </c>
-      <c r="B50" s="1463"/>
-      <c r="C50" s="1463"/>
-      <c r="D50" s="1463"/>
-      <c r="E50" s="1463"/>
-      <c r="F50" s="1463"/>
-      <c r="G50" s="1463"/>
-      <c r="H50" s="1463"/>
-      <c r="I50" s="1463"/>
-      <c r="J50" s="1463"/>
-      <c r="K50" s="1463"/>
+      <c r="B50" s="1486"/>
+      <c r="C50" s="1486"/>
+      <c r="D50" s="1486"/>
+      <c r="E50" s="1486"/>
+      <c r="F50" s="1486"/>
+      <c r="G50" s="1486"/>
+      <c r="H50" s="1486"/>
+      <c r="I50" s="1486"/>
+      <c r="J50" s="1486"/>
+      <c r="K50" s="1486"/>
     </row>
     <row r="51" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -43881,12 +43878,11 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -43895,11 +43891,12 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0700-000000000000}">

--- a/app/templates/informes/Proctor/Template_Proctor.xlsx
+++ b/app/templates/informes/Proctor/Template_Proctor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Proctor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32786F6F-23D0-48A5-A7B1-610B1D93056E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B9F1C5-446E-4175-B179-EEFC5781977D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="613" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2613,7 +2613,7 @@
     <numFmt numFmtId="209" formatCode="&quot;CERTIFICADO N°&quot;000&quot;-20 SU08&quot;"/>
     <numFmt numFmtId="210" formatCode="000&quot;-20 SU08&quot;"/>
   </numFmts>
-  <fonts count="125" x14ac:knownFonts="1">
+  <fonts count="124" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3393,12 +3393,6 @@
       <u/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -5676,7 +5670,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1595">
+  <cellXfs count="1594">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
@@ -9658,8 +9652,140 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9713,211 +9839,80 @@
     <xf numFmtId="0" fontId="122" fillId="3" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9961,73 +9956,75 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10036,32 +10033,14 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -10069,48 +10048,108 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10132,54 +10171,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="18" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="104" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10190,146 +10181,78 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="193" fontId="81" fillId="0" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="189" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="189" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10358,6 +10281,10 @@
     <xf numFmtId="0" fontId="58" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -10376,6 +10303,9 @@
     <xf numFmtId="164" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10387,6 +10317,127 @@
     </xf>
     <xf numFmtId="0" fontId="58" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="51" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="58" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -10402,65 +10453,9 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="51" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="58" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10478,9 +10473,56 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="122" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="131" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="124" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="128" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="125" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="126" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="127" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10532,57 +10574,6 @@
     </xf>
     <xf numFmtId="0" fontId="49" fillId="11" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="122" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="131" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="124" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="128" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="125" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="126" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="127" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="9" borderId="149" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11219,7 +11210,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="141997568"/>
@@ -11348,7 +11339,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="141818880"/>
@@ -11395,7 +11386,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11548,7 +11539,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="145561856"/>
@@ -11584,7 +11575,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="145560320"/>
@@ -11622,7 +11613,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12160,7 +12151,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="182790784"/>
@@ -12260,7 +12251,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="182788096"/>
@@ -12303,7 +12294,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12635,7 +12626,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="239970560"/>
@@ -12738,7 +12729,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="239913984"/>
@@ -12787,7 +12778,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -16378,7 +16369,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16437,7 +16428,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -16556,7 +16547,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16607,7 +16598,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16659,7 +16650,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -16691,7 +16682,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16733,7 +16724,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -17451,90 +17442,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1279"/>
-      <c r="B1" s="1280"/>
-      <c r="C1" s="1280"/>
-      <c r="D1" s="1280"/>
-      <c r="E1" s="1280"/>
-      <c r="F1" s="1280"/>
-      <c r="G1" s="1280"/>
-      <c r="H1" s="1280"/>
-      <c r="I1" s="1281"/>
+      <c r="A1" s="1317"/>
+      <c r="B1" s="1318"/>
+      <c r="C1" s="1318"/>
+      <c r="D1" s="1318"/>
+      <c r="E1" s="1318"/>
+      <c r="F1" s="1318"/>
+      <c r="G1" s="1318"/>
+      <c r="H1" s="1318"/>
+      <c r="I1" s="1319"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1282"/>
-      <c r="B2" s="1283"/>
-      <c r="C2" s="1283"/>
-      <c r="D2" s="1283"/>
-      <c r="E2" s="1283"/>
-      <c r="F2" s="1283"/>
-      <c r="G2" s="1283"/>
-      <c r="H2" s="1283"/>
-      <c r="I2" s="1284"/>
+      <c r="A2" s="1320"/>
+      <c r="B2" s="1321"/>
+      <c r="C2" s="1321"/>
+      <c r="D2" s="1321"/>
+      <c r="E2" s="1321"/>
+      <c r="F2" s="1321"/>
+      <c r="G2" s="1321"/>
+      <c r="H2" s="1321"/>
+      <c r="I2" s="1322"/>
       <c r="K2" s="1266" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="1267"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1282"/>
-      <c r="B3" s="1283"/>
-      <c r="C3" s="1283"/>
-      <c r="D3" s="1283"/>
-      <c r="E3" s="1283"/>
-      <c r="F3" s="1283"/>
-      <c r="G3" s="1283"/>
-      <c r="H3" s="1283"/>
-      <c r="I3" s="1284"/>
+      <c r="A3" s="1320"/>
+      <c r="B3" s="1321"/>
+      <c r="C3" s="1321"/>
+      <c r="D3" s="1321"/>
+      <c r="E3" s="1321"/>
+      <c r="F3" s="1321"/>
+      <c r="G3" s="1321"/>
+      <c r="H3" s="1321"/>
+      <c r="I3" s="1322"/>
       <c r="K3" s="1266" t="s">
         <v>5</v>
       </c>
       <c r="L3" s="1268"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1285"/>
-      <c r="B4" s="1286"/>
-      <c r="C4" s="1286"/>
-      <c r="D4" s="1286"/>
-      <c r="E4" s="1286"/>
-      <c r="F4" s="1286"/>
-      <c r="G4" s="1286"/>
-      <c r="H4" s="1286"/>
-      <c r="I4" s="1287"/>
+      <c r="A4" s="1323"/>
+      <c r="B4" s="1324"/>
+      <c r="C4" s="1324"/>
+      <c r="D4" s="1324"/>
+      <c r="E4" s="1324"/>
+      <c r="F4" s="1324"/>
+      <c r="G4" s="1324"/>
+      <c r="H4" s="1324"/>
+      <c r="I4" s="1325"/>
       <c r="K4" s="1266" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="1268"/>
     </row>
     <row r="5" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1288" t="s">
+      <c r="A5" s="1326" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1288"/>
-      <c r="C5" s="1288"/>
-      <c r="D5" s="1288"/>
-      <c r="E5" s="1288"/>
-      <c r="F5" s="1288"/>
-      <c r="G5" s="1288"/>
-      <c r="H5" s="1288"/>
-      <c r="I5" s="1288"/>
+      <c r="B5" s="1326"/>
+      <c r="C5" s="1326"/>
+      <c r="D5" s="1326"/>
+      <c r="E5" s="1326"/>
+      <c r="F5" s="1326"/>
+      <c r="G5" s="1326"/>
+      <c r="H5" s="1326"/>
+      <c r="I5" s="1326"/>
       <c r="K5" s="1266" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="1268"/>
     </row>
     <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1289" t="s">
+      <c r="A6" s="1327" t="s">
         <v>587</v>
       </c>
-      <c r="B6" s="1289"/>
-      <c r="C6" s="1289"/>
-      <c r="D6" s="1289"/>
-      <c r="E6" s="1289"/>
-      <c r="F6" s="1289"/>
-      <c r="G6" s="1289"/>
-      <c r="H6" s="1289"/>
-      <c r="I6" s="1289"/>
+      <c r="B6" s="1327"/>
+      <c r="C6" s="1327"/>
+      <c r="D6" s="1327"/>
+      <c r="E6" s="1327"/>
+      <c r="F6" s="1327"/>
+      <c r="G6" s="1327"/>
+      <c r="H6" s="1327"/>
+      <c r="I6" s="1327"/>
       <c r="K6" s="1269"/>
       <c r="L6" s="1270"/>
     </row>
@@ -17558,15 +17549,15 @@
       <c r="B8" s="1170" t="s">
         <v>588</v>
       </c>
-      <c r="C8" s="1290" t="s">
+      <c r="C8" s="1328" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1291"/>
+      <c r="D8" s="1329"/>
       <c r="E8" s="1172"/>
-      <c r="F8" s="1292" t="s">
+      <c r="F8" s="1330" t="s">
         <v>589</v>
       </c>
-      <c r="G8" s="1291"/>
+      <c r="G8" s="1329"/>
       <c r="H8" s="1171" t="s">
         <v>590</v>
       </c>
@@ -17578,11 +17569,11 @@
     </row>
     <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1173"/>
-      <c r="C9" s="1276"/>
-      <c r="D9" s="1277"/>
+      <c r="C9" s="1314"/>
+      <c r="D9" s="1315"/>
       <c r="E9" s="1174"/>
-      <c r="F9" s="1278"/>
-      <c r="G9" s="1277"/>
+      <c r="F9" s="1316"/>
+      <c r="G9" s="1315"/>
       <c r="H9" s="1175"/>
       <c r="I9" s="243"/>
       <c r="K9" s="1266" t="s">
@@ -17592,46 +17583,46 @@
     </row>
     <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1176"/>
-      <c r="B10" s="1293"/>
-      <c r="C10" s="1293"/>
-      <c r="D10" s="1293"/>
+      <c r="B10" s="1305"/>
+      <c r="C10" s="1305"/>
+      <c r="D10" s="1305"/>
       <c r="E10" s="1177"/>
-      <c r="F10" s="1293"/>
-      <c r="G10" s="1293"/>
+      <c r="F10" s="1305"/>
+      <c r="G10" s="1305"/>
       <c r="H10" s="1177"/>
       <c r="I10" s="1178"/>
       <c r="K10" s="1269"/>
       <c r="L10" s="1270"/>
     </row>
     <row r="11" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1294" t="s">
+      <c r="A11" s="1306" t="s">
         <v>591</v>
       </c>
-      <c r="B11" s="1295"/>
-      <c r="C11" s="1295"/>
-      <c r="D11" s="1295"/>
-      <c r="E11" s="1295"/>
-      <c r="F11" s="1295"/>
-      <c r="G11" s="1295"/>
-      <c r="H11" s="1295"/>
-      <c r="I11" s="1296"/>
+      <c r="B11" s="1307"/>
+      <c r="C11" s="1307"/>
+      <c r="D11" s="1307"/>
+      <c r="E11" s="1307"/>
+      <c r="F11" s="1307"/>
+      <c r="G11" s="1307"/>
+      <c r="H11" s="1307"/>
+      <c r="I11" s="1308"/>
       <c r="K11" s="1266" t="s">
         <v>15</v>
       </c>
       <c r="L11" s="1270"/>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1297" t="s">
+      <c r="A12" s="1309" t="s">
         <v>531</v>
       </c>
-      <c r="B12" s="1298"/>
-      <c r="C12" s="1298"/>
-      <c r="D12" s="1298"/>
-      <c r="E12" s="1298"/>
-      <c r="F12" s="1298"/>
-      <c r="G12" s="1298"/>
-      <c r="H12" s="1298"/>
-      <c r="I12" s="1299"/>
+      <c r="B12" s="1310"/>
+      <c r="C12" s="1310"/>
+      <c r="D12" s="1310"/>
+      <c r="E12" s="1310"/>
+      <c r="F12" s="1310"/>
+      <c r="G12" s="1310"/>
+      <c r="H12" s="1310"/>
+      <c r="I12" s="1311"/>
       <c r="K12" s="1266" t="s">
         <v>18</v>
       </c>
@@ -17670,17 +17661,17 @@
       <c r="L14" s="1270"/>
     </row>
     <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1300" t="s">
+      <c r="A15" s="1296" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1300"/>
+      <c r="B15" s="1296"/>
       <c r="C15" s="1188" t="s">
         <v>593</v>
       </c>
-      <c r="D15" s="1301">
+      <c r="D15" s="1312">
         <v>1</v>
       </c>
-      <c r="E15" s="1302"/>
+      <c r="E15" s="1313"/>
       <c r="F15" s="1190">
         <v>2</v>
       </c>
@@ -17699,17 +17690,17 @@
       <c r="L15" s="1272"/>
     </row>
     <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1303" t="s">
+      <c r="A16" s="1288" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1303"/>
+      <c r="B16" s="1288"/>
       <c r="C16" s="1191" t="s">
         <v>593</v>
       </c>
-      <c r="D16" s="1304">
+      <c r="D16" s="1299">
         <v>5</v>
       </c>
-      <c r="E16" s="1305"/>
+      <c r="E16" s="1300"/>
       <c r="F16" s="1193">
         <v>5</v>
       </c>
@@ -17728,15 +17719,15 @@
       <c r="L16" s="1272"/>
     </row>
     <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1303" t="s">
+      <c r="A17" s="1288" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1303"/>
+      <c r="B17" s="1288"/>
       <c r="C17" s="1191" t="s">
         <v>593</v>
       </c>
-      <c r="D17" s="1304"/>
-      <c r="E17" s="1305"/>
+      <c r="D17" s="1299"/>
+      <c r="E17" s="1300"/>
       <c r="F17" s="1193"/>
       <c r="G17" s="1192"/>
       <c r="H17" s="1192"/>
@@ -17747,75 +17738,75 @@
       <c r="L17" s="1273"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1303" t="s">
+      <c r="A18" s="1288" t="s">
         <v>594</v>
       </c>
-      <c r="B18" s="1303"/>
+      <c r="B18" s="1288"/>
       <c r="C18" s="1192" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="1304"/>
-      <c r="E18" s="1305"/>
+      <c r="D18" s="1299"/>
+      <c r="E18" s="1300"/>
       <c r="F18" s="1194"/>
       <c r="G18" s="1195"/>
       <c r="H18" s="1195"/>
       <c r="I18" s="1194"/>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1303" t="s">
+      <c r="A19" s="1288" t="s">
         <v>595</v>
       </c>
-      <c r="B19" s="1303"/>
+      <c r="B19" s="1288"/>
       <c r="C19" s="1192" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="1304"/>
-      <c r="E19" s="1305"/>
+      <c r="D19" s="1299"/>
+      <c r="E19" s="1300"/>
       <c r="F19" s="1193"/>
       <c r="G19" s="1192"/>
       <c r="H19" s="1196"/>
       <c r="I19" s="1197"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1306" t="s">
+      <c r="A20" s="1301" t="s">
         <v>596</v>
       </c>
-      <c r="B20" s="1307"/>
+      <c r="B20" s="1302"/>
       <c r="C20" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D20" s="1304"/>
-      <c r="E20" s="1305"/>
+      <c r="D20" s="1299"/>
+      <c r="E20" s="1300"/>
       <c r="F20" s="1193"/>
       <c r="G20" s="1192"/>
       <c r="H20" s="1196"/>
       <c r="I20" s="1197"/>
     </row>
     <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1303" t="s">
+      <c r="A21" s="1288" t="s">
         <v>597</v>
       </c>
-      <c r="B21" s="1303"/>
+      <c r="B21" s="1288"/>
       <c r="C21" s="1192" t="s">
         <v>598</v>
       </c>
-      <c r="D21" s="1308"/>
-      <c r="E21" s="1309"/>
+      <c r="D21" s="1303"/>
+      <c r="E21" s="1304"/>
       <c r="F21" s="1193"/>
       <c r="G21" s="1192"/>
       <c r="H21" s="1192"/>
       <c r="I21" s="1193"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1310" t="s">
+      <c r="A22" s="1291" t="s">
         <v>599</v>
       </c>
-      <c r="B22" s="1310"/>
+      <c r="B22" s="1291"/>
       <c r="C22" s="1199" t="s">
         <v>600</v>
       </c>
-      <c r="D22" s="1311"/>
-      <c r="E22" s="1312"/>
+      <c r="D22" s="1294"/>
+      <c r="E22" s="1295"/>
       <c r="F22" s="1200"/>
       <c r="G22" s="1201"/>
       <c r="H22" s="1201"/>
@@ -17835,148 +17826,148 @@
       <c r="I23" s="1202"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1300" t="s">
+      <c r="A24" s="1296" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="1300"/>
+      <c r="B24" s="1296"/>
       <c r="C24" s="1203"/>
-      <c r="D24" s="1313"/>
-      <c r="E24" s="1314"/>
+      <c r="D24" s="1297"/>
+      <c r="E24" s="1298"/>
       <c r="F24" s="1205"/>
       <c r="G24" s="1204"/>
       <c r="H24" s="1204"/>
       <c r="I24" s="1205"/>
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1303" t="s">
+      <c r="A25" s="1288" t="s">
         <v>601</v>
       </c>
-      <c r="B25" s="1303"/>
+      <c r="B25" s="1288"/>
       <c r="C25" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D25" s="1315"/>
-      <c r="E25" s="1316"/>
+      <c r="D25" s="1289"/>
+      <c r="E25" s="1290"/>
       <c r="F25" s="1207"/>
       <c r="G25" s="1206"/>
       <c r="H25" s="1206"/>
       <c r="I25" s="1207"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1303" t="s">
+      <c r="A26" s="1288" t="s">
         <v>602</v>
       </c>
-      <c r="B26" s="1303"/>
+      <c r="B26" s="1288"/>
       <c r="C26" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="1315"/>
-      <c r="E26" s="1316"/>
+      <c r="D26" s="1289"/>
+      <c r="E26" s="1290"/>
       <c r="F26" s="1207"/>
       <c r="G26" s="1206"/>
       <c r="H26" s="1206"/>
       <c r="I26" s="1207"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1303" t="s">
+      <c r="A27" s="1288" t="s">
         <v>603</v>
       </c>
-      <c r="B27" s="1303"/>
+      <c r="B27" s="1288"/>
       <c r="C27" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="1315"/>
-      <c r="E27" s="1316"/>
+      <c r="D27" s="1289"/>
+      <c r="E27" s="1290"/>
       <c r="F27" s="1207"/>
       <c r="G27" s="1206"/>
       <c r="H27" s="1206"/>
       <c r="I27" s="1207"/>
     </row>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1303" t="s">
+      <c r="A28" s="1288" t="s">
         <v>604</v>
       </c>
-      <c r="B28" s="1303"/>
+      <c r="B28" s="1288"/>
       <c r="C28" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D28" s="1315"/>
-      <c r="E28" s="1316"/>
+      <c r="D28" s="1289"/>
+      <c r="E28" s="1290"/>
       <c r="F28" s="1207"/>
       <c r="G28" s="1206"/>
       <c r="H28" s="1206"/>
       <c r="I28" s="1207"/>
     </row>
     <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1303" t="s">
+      <c r="A29" s="1288" t="s">
         <v>605</v>
       </c>
-      <c r="B29" s="1303"/>
+      <c r="B29" s="1288"/>
       <c r="C29" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="1315"/>
-      <c r="E29" s="1316"/>
+      <c r="D29" s="1289"/>
+      <c r="E29" s="1290"/>
       <c r="F29" s="1208"/>
       <c r="G29" s="1209"/>
       <c r="H29" s="1209"/>
       <c r="I29" s="1208"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1303" t="s">
+      <c r="A30" s="1288" t="s">
         <v>606</v>
       </c>
-      <c r="B30" s="1303"/>
+      <c r="B30" s="1288"/>
       <c r="C30" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D30" s="1315"/>
-      <c r="E30" s="1316"/>
+      <c r="D30" s="1289"/>
+      <c r="E30" s="1290"/>
       <c r="F30" s="1208"/>
       <c r="G30" s="1209"/>
       <c r="H30" s="1209"/>
       <c r="I30" s="1208"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1303" t="s">
+      <c r="A31" s="1288" t="s">
         <v>607</v>
       </c>
-      <c r="B31" s="1303"/>
+      <c r="B31" s="1288"/>
       <c r="C31" s="1198" t="s">
         <v>182</v>
       </c>
-      <c r="D31" s="1315"/>
-      <c r="E31" s="1316"/>
+      <c r="D31" s="1289"/>
+      <c r="E31" s="1290"/>
       <c r="F31" s="1208"/>
       <c r="G31" s="1209"/>
       <c r="H31" s="1209"/>
       <c r="I31" s="1208"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1303" t="s">
+      <c r="A32" s="1288" t="s">
         <v>608</v>
       </c>
-      <c r="B32" s="1303"/>
+      <c r="B32" s="1288"/>
       <c r="C32" s="1192" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="1315"/>
-      <c r="E32" s="1316"/>
+      <c r="D32" s="1289"/>
+      <c r="E32" s="1290"/>
       <c r="F32" s="1210"/>
       <c r="G32" s="1211"/>
       <c r="H32" s="1211"/>
       <c r="I32" s="1210"/>
     </row>
     <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1310" t="s">
+      <c r="A33" s="1291" t="s">
         <v>609</v>
       </c>
-      <c r="B33" s="1310"/>
+      <c r="B33" s="1291"/>
       <c r="C33" s="1199" t="s">
         <v>600</v>
       </c>
-      <c r="D33" s="1317"/>
-      <c r="E33" s="1318"/>
+      <c r="D33" s="1292"/>
+      <c r="E33" s="1293"/>
       <c r="F33" s="1200"/>
       <c r="G33" s="1201"/>
       <c r="H33" s="1201"/>
@@ -18002,19 +17993,19 @@
         <v>611</v>
       </c>
       <c r="B35" s="1217"/>
-      <c r="C35" s="1319"/>
-      <c r="D35" s="1320"/>
+      <c r="C35" s="1283"/>
+      <c r="D35" s="1284"/>
       <c r="E35" s="1218"/>
-      <c r="F35" s="1323" t="s">
+      <c r="F35" s="1281" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="1323" t="s">
+      <c r="G35" s="1281" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="1323" t="s">
+      <c r="H35" s="1281" t="s">
         <v>612</v>
       </c>
-      <c r="I35" s="1323" t="s">
+      <c r="I35" s="1281" t="s">
         <v>231</v>
       </c>
     </row>
@@ -18023,21 +18014,21 @@
         <v>613</v>
       </c>
       <c r="B36" s="1220"/>
-      <c r="C36" s="1319"/>
-      <c r="D36" s="1320"/>
+      <c r="C36" s="1283"/>
+      <c r="D36" s="1284"/>
       <c r="E36" s="1218"/>
-      <c r="F36" s="1324"/>
-      <c r="G36" s="1324"/>
-      <c r="H36" s="1324"/>
-      <c r="I36" s="1324"/>
+      <c r="F36" s="1282"/>
+      <c r="G36" s="1282"/>
+      <c r="H36" s="1282"/>
+      <c r="I36" s="1282"/>
     </row>
     <row r="37" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1219" t="s">
         <v>614</v>
       </c>
       <c r="B37" s="1220"/>
-      <c r="C37" s="1325"/>
-      <c r="D37" s="1320"/>
+      <c r="C37" s="1285"/>
+      <c r="D37" s="1284"/>
       <c r="E37" s="1221"/>
       <c r="F37" s="1222" t="s">
         <v>615</v>
@@ -18051,8 +18042,8 @@
         <v>616</v>
       </c>
       <c r="B38" s="1227"/>
-      <c r="C38" s="1319"/>
-      <c r="D38" s="1320"/>
+      <c r="C38" s="1283"/>
+      <c r="D38" s="1284"/>
       <c r="E38" s="1218"/>
       <c r="F38" s="1222" t="s">
         <v>617</v>
@@ -18066,8 +18057,8 @@
         <v>618</v>
       </c>
       <c r="B39" s="1220"/>
-      <c r="C39" s="1319"/>
-      <c r="D39" s="1320"/>
+      <c r="C39" s="1283"/>
+      <c r="D39" s="1284"/>
       <c r="E39" s="1218"/>
       <c r="F39" s="1222" t="s">
         <v>110</v>
@@ -18096,8 +18087,8 @@
         <v>619</v>
       </c>
       <c r="B41" s="1230"/>
-      <c r="C41" s="1326"/>
-      <c r="D41" s="1326"/>
+      <c r="C41" s="1277"/>
+      <c r="D41" s="1277"/>
       <c r="E41" s="1228"/>
       <c r="F41" s="1222" t="s">
         <v>620</v>
@@ -18111,8 +18102,8 @@
         <v>621</v>
       </c>
       <c r="B42" s="1232"/>
-      <c r="C42" s="1326"/>
-      <c r="D42" s="1326"/>
+      <c r="C42" s="1277"/>
+      <c r="D42" s="1277"/>
       <c r="E42" s="1233"/>
       <c r="J42" s="1234"/>
     </row>
@@ -18121,17 +18112,17 @@
         <v>622</v>
       </c>
       <c r="B43" s="1236"/>
-      <c r="C43" s="1326"/>
-      <c r="D43" s="1326"/>
+      <c r="C43" s="1277"/>
+      <c r="D43" s="1277"/>
       <c r="E43" s="1233"/>
-      <c r="F43" s="1327" t="s">
+      <c r="F43" s="1286" t="s">
         <v>623</v>
       </c>
-      <c r="G43" s="1328"/>
-      <c r="H43" s="1321" t="s">
+      <c r="G43" s="1287"/>
+      <c r="H43" s="1275" t="s">
         <v>624</v>
       </c>
-      <c r="I43" s="1322"/>
+      <c r="I43" s="1276"/>
       <c r="J43" s="1234"/>
     </row>
     <row r="44" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18139,31 +18130,31 @@
         <v>625</v>
       </c>
       <c r="B44" s="1232"/>
-      <c r="C44" s="1326"/>
-      <c r="D44" s="1326"/>
+      <c r="C44" s="1277"/>
+      <c r="D44" s="1277"/>
       <c r="E44" s="1233"/>
       <c r="F44" s="1237" t="s">
         <v>626</v>
       </c>
       <c r="G44" s="1238"/>
-      <c r="H44" s="1321"/>
-      <c r="I44" s="1322"/>
+      <c r="H44" s="1275"/>
+      <c r="I44" s="1276"/>
       <c r="J44" s="1234"/>
     </row>
     <row r="45" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1330" t="s">
+      <c r="A45" s="1279" t="s">
         <v>627</v>
       </c>
-      <c r="B45" s="1331"/>
-      <c r="C45" s="1326"/>
-      <c r="D45" s="1326"/>
+      <c r="B45" s="1280"/>
+      <c r="C45" s="1277"/>
+      <c r="D45" s="1277"/>
       <c r="E45" s="1233"/>
       <c r="F45" s="1237" t="s">
         <v>628</v>
       </c>
       <c r="G45" s="1238"/>
-      <c r="H45" s="1321"/>
-      <c r="I45" s="1322"/>
+      <c r="H45" s="1275"/>
+      <c r="I45" s="1276"/>
       <c r="J45" s="1234"/>
     </row>
     <row r="46" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18177,8 +18168,8 @@
         <v>629</v>
       </c>
       <c r="G46" s="1238"/>
-      <c r="H46" s="1321"/>
-      <c r="I46" s="1322"/>
+      <c r="H46" s="1275"/>
+      <c r="I46" s="1276"/>
     </row>
     <row r="47" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1242"/>
@@ -18189,8 +18180,8 @@
         <v>630</v>
       </c>
       <c r="G47" s="1238"/>
-      <c r="H47" s="1321"/>
-      <c r="I47" s="1322"/>
+      <c r="H47" s="1275"/>
+      <c r="I47" s="1276"/>
     </row>
     <row r="48" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1242"/>
@@ -18201,8 +18192,8 @@
         <v>582</v>
       </c>
       <c r="G48" s="1245"/>
-      <c r="H48" s="1321"/>
-      <c r="I48" s="1322"/>
+      <c r="H48" s="1275"/>
+      <c r="I48" s="1276"/>
     </row>
     <row r="49" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1246"/>
@@ -18213,8 +18204,8 @@
         <v>631</v>
       </c>
       <c r="G49" s="1238"/>
-      <c r="H49" s="1326"/>
-      <c r="I49" s="1326"/>
+      <c r="H49" s="1277"/>
+      <c r="I49" s="1277"/>
     </row>
     <row r="50" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E50" s="352"/>
@@ -18255,17 +18246,17 @@
     </row>
     <row r="55" spans="1:9" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1329" t="s">
+      <c r="A56" s="1278" t="s">
         <v>634</v>
       </c>
-      <c r="B56" s="1329"/>
-      <c r="C56" s="1329"/>
-      <c r="D56" s="1329"/>
-      <c r="E56" s="1329"/>
-      <c r="F56" s="1329"/>
-      <c r="G56" s="1329"/>
-      <c r="H56" s="1329"/>
-      <c r="I56" s="1329"/>
+      <c r="B56" s="1278"/>
+      <c r="C56" s="1278"/>
+      <c r="D56" s="1278"/>
+      <c r="E56" s="1278"/>
+      <c r="F56" s="1278"/>
+      <c r="G56" s="1278"/>
+      <c r="H56" s="1278"/>
+      <c r="I56" s="1278"/>
     </row>
     <row r="57" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -18275,16 +18266,54 @@
     <protectedRange sqref="B9:C10" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="71">
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="H35:H36"/>
@@ -18298,54 +18327,16 @@
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -18451,33 +18442,33 @@
       <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1505" t="s">
+      <c r="A8" s="1522" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1505"/>
-      <c r="C8" s="1505"/>
-      <c r="D8" s="1505"/>
-      <c r="E8" s="1505"/>
-      <c r="F8" s="1505"/>
-      <c r="G8" s="1505"/>
-      <c r="H8" s="1505"/>
-      <c r="I8" s="1505"/>
-      <c r="J8" s="1505"/>
+      <c r="B8" s="1522"/>
+      <c r="C8" s="1522"/>
+      <c r="D8" s="1522"/>
+      <c r="E8" s="1522"/>
+      <c r="F8" s="1522"/>
+      <c r="G8" s="1522"/>
+      <c r="H8" s="1522"/>
+      <c r="I8" s="1522"/>
+      <c r="J8" s="1522"/>
     </row>
     <row r="9" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1530">
+      <c r="A9" s="1525">
         <f>J13</f>
         <v>1</v>
       </c>
-      <c r="B9" s="1530"/>
-      <c r="C9" s="1530"/>
-      <c r="D9" s="1530"/>
-      <c r="E9" s="1530"/>
-      <c r="F9" s="1530"/>
-      <c r="G9" s="1530"/>
-      <c r="H9" s="1530"/>
-      <c r="I9" s="1530"/>
-      <c r="J9" s="1530"/>
+      <c r="B9" s="1525"/>
+      <c r="C9" s="1525"/>
+      <c r="D9" s="1525"/>
+      <c r="E9" s="1525"/>
+      <c r="F9" s="1525"/>
+      <c r="G9" s="1525"/>
+      <c r="H9" s="1525"/>
+      <c r="I9" s="1525"/>
+      <c r="J9" s="1525"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -18499,13 +18490,13 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1507" t="s">
+      <c r="C11" s="1524" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="1507"/>
-      <c r="E11" s="1507"/>
-      <c r="F11" s="1507"/>
-      <c r="G11" s="1507"/>
+      <c r="D11" s="1524"/>
+      <c r="E11" s="1524"/>
+      <c r="F11" s="1524"/>
+      <c r="G11" s="1524"/>
       <c r="H11" s="121" t="s">
         <v>3</v>
       </c>
@@ -18527,13 +18518,13 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1507" t="s">
+      <c r="C12" s="1524" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="1507"/>
-      <c r="E12" s="1507"/>
-      <c r="F12" s="1507"/>
-      <c r="G12" s="1507"/>
+      <c r="D12" s="1524"/>
+      <c r="E12" s="1524"/>
+      <c r="F12" s="1524"/>
+      <c r="G12" s="1524"/>
       <c r="H12" s="26" t="s">
         <v>6</v>
       </c>
@@ -18557,13 +18548,13 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1507" t="s">
+      <c r="C13" s="1524" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="1507"/>
-      <c r="E13" s="1507"/>
-      <c r="F13" s="1507"/>
-      <c r="G13" s="1507"/>
+      <c r="D13" s="1524"/>
+      <c r="E13" s="1524"/>
+      <c r="F13" s="1524"/>
+      <c r="G13" s="1524"/>
       <c r="H13" s="26" t="s">
         <v>288</v>
       </c>
@@ -18576,8 +18567,8 @@
       <c r="K13" s="124"/>
       <c r="L13" s="124"/>
       <c r="M13" s="124"/>
-      <c r="P13" s="1504"/>
-      <c r="Q13" s="1504"/>
+      <c r="P13" s="1521"/>
+      <c r="Q13" s="1521"/>
     </row>
     <row r="14" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -18597,34 +18588,34 @@
       <c r="Q14" s="737"/>
     </row>
     <row r="15" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1508" t="s">
+      <c r="A15" s="1510" t="s">
         <v>367</v>
       </c>
-      <c r="B15" s="1509"/>
-      <c r="C15" s="1509"/>
-      <c r="D15" s="1509"/>
-      <c r="E15" s="1509"/>
-      <c r="F15" s="1509"/>
-      <c r="G15" s="1509"/>
-      <c r="H15" s="1509"/>
-      <c r="I15" s="1509"/>
-      <c r="J15" s="1510"/>
+      <c r="B15" s="1511"/>
+      <c r="C15" s="1511"/>
+      <c r="D15" s="1511"/>
+      <c r="E15" s="1511"/>
+      <c r="F15" s="1511"/>
+      <c r="G15" s="1511"/>
+      <c r="H15" s="1511"/>
+      <c r="I15" s="1511"/>
+      <c r="J15" s="1512"/>
       <c r="K15" s="124"/>
       <c r="L15" s="124"/>
     </row>
     <row r="16" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1511" t="s">
+      <c r="A16" s="1513" t="s">
         <v>368</v>
       </c>
-      <c r="B16" s="1512"/>
-      <c r="C16" s="1512"/>
-      <c r="D16" s="1512"/>
-      <c r="E16" s="1512"/>
-      <c r="F16" s="1512"/>
-      <c r="G16" s="1512"/>
-      <c r="H16" s="1512"/>
-      <c r="I16" s="1512"/>
-      <c r="J16" s="1513"/>
+      <c r="B16" s="1514"/>
+      <c r="C16" s="1514"/>
+      <c r="D16" s="1514"/>
+      <c r="E16" s="1514"/>
+      <c r="F16" s="1514"/>
+      <c r="G16" s="1514"/>
+      <c r="H16" s="1514"/>
+      <c r="I16" s="1514"/>
+      <c r="J16" s="1515"/>
       <c r="K16" s="124"/>
       <c r="L16" s="124"/>
     </row>
@@ -18643,18 +18634,18 @@
       <c r="L17" s="124"/>
     </row>
     <row r="18" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1478" t="s">
+      <c r="A18" s="1485" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1479"/>
-      <c r="C18" s="1479"/>
-      <c r="D18" s="1479"/>
-      <c r="E18" s="1479"/>
-      <c r="F18" s="1479"/>
-      <c r="G18" s="1479"/>
-      <c r="H18" s="1479"/>
-      <c r="I18" s="1479"/>
-      <c r="J18" s="1480"/>
+      <c r="B18" s="1486"/>
+      <c r="C18" s="1486"/>
+      <c r="D18" s="1486"/>
+      <c r="E18" s="1486"/>
+      <c r="F18" s="1486"/>
+      <c r="G18" s="1486"/>
+      <c r="H18" s="1486"/>
+      <c r="I18" s="1486"/>
+      <c r="J18" s="1487"/>
       <c r="L18" s="124"/>
     </row>
     <row r="19" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -19352,18 +19343,18 @@
     </row>
     <row r="53" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1486" t="s">
+      <c r="A54" s="1463" t="s">
         <v>345</v>
       </c>
-      <c r="B54" s="1486"/>
-      <c r="C54" s="1486"/>
-      <c r="D54" s="1486"/>
-      <c r="E54" s="1486"/>
-      <c r="F54" s="1486"/>
-      <c r="G54" s="1486"/>
-      <c r="H54" s="1486"/>
-      <c r="I54" s="1486"/>
-      <c r="J54" s="1486"/>
+      <c r="B54" s="1463"/>
+      <c r="C54" s="1463"/>
+      <c r="D54" s="1463"/>
+      <c r="E54" s="1463"/>
+      <c r="F54" s="1463"/>
+      <c r="G54" s="1463"/>
+      <c r="H54" s="1463"/>
+      <c r="I54" s="1463"/>
+      <c r="J54" s="1463"/>
     </row>
     <row r="55" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19373,12 +19364,6 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="13">
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A16:J16"/>
@@ -19386,6 +19371,12 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -19417,15 +19408,15 @@
       <c r="A1" s="82" t="s">
         <v>389</v>
       </c>
-      <c r="B1" s="1531" t="s">
+      <c r="B1" s="1547" t="s">
         <v>390</v>
       </c>
-      <c r="C1" s="1531"/>
-      <c r="D1" s="1531"/>
-      <c r="E1" s="1531"/>
-      <c r="F1" s="1531"/>
-      <c r="G1" s="1531"/>
-      <c r="H1" s="1531"/>
+      <c r="C1" s="1547"/>
+      <c r="D1" s="1547"/>
+      <c r="E1" s="1547"/>
+      <c r="F1" s="1547"/>
+      <c r="G1" s="1547"/>
+      <c r="H1" s="1547"/>
       <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -19563,29 +19554,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="82"/>
-      <c r="B8" s="1532" t="s">
+      <c r="B8" s="1548" t="s">
         <v>402</v>
       </c>
-      <c r="C8" s="1532"/>
-      <c r="D8" s="1532"/>
+      <c r="C8" s="1548"/>
+      <c r="D8" s="1548"/>
       <c r="E8" s="830" t="s">
         <v>403</v>
       </c>
       <c r="F8" s="831" t="s">
         <v>404</v>
       </c>
-      <c r="G8" s="1533" t="s">
+      <c r="G8" s="1549" t="s">
         <v>405</v>
       </c>
-      <c r="H8" s="1533"/>
+      <c r="H8" s="1549"/>
       <c r="I8" s="82"/>
       <c r="L8" s="90" t="s">
         <v>406</v>
       </c>
-      <c r="M8" s="1534" t="s">
+      <c r="M8" s="1550" t="s">
         <v>407</v>
       </c>
-      <c r="N8" s="1534"/>
+      <c r="N8" s="1550"/>
       <c r="O8" s="91" t="s">
         <v>408</v>
       </c>
@@ -19598,13 +19589,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82"/>
-      <c r="B9" s="1535" t="s">
+      <c r="B9" s="1551" t="s">
         <v>411</v>
       </c>
-      <c r="C9" s="1537" t="s">
+      <c r="C9" s="1553" t="s">
         <v>412</v>
       </c>
-      <c r="D9" s="1539" t="s">
+      <c r="D9" s="1555" t="s">
         <v>413</v>
       </c>
       <c r="E9" s="832" t="s">
@@ -19613,10 +19604,10 @@
       <c r="F9" s="833" t="s">
         <v>415</v>
       </c>
-      <c r="G9" s="1540" t="s">
+      <c r="G9" s="1556" t="s">
         <v>416</v>
       </c>
-      <c r="H9" s="1541"/>
+      <c r="H9" s="1557"/>
       <c r="I9" s="82"/>
       <c r="L9" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -19645,19 +19636,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="82"/>
-      <c r="B10" s="1535"/>
-      <c r="C10" s="1537"/>
-      <c r="D10" s="1539"/>
+      <c r="B10" s="1551"/>
+      <c r="C10" s="1553"/>
+      <c r="D10" s="1555"/>
       <c r="E10" s="834" t="s">
         <v>417</v>
       </c>
       <c r="F10" s="835" t="s">
         <v>418</v>
       </c>
-      <c r="G10" s="1542" t="s">
+      <c r="G10" s="1558" t="s">
         <v>419</v>
       </c>
-      <c r="H10" s="1543"/>
+      <c r="H10" s="1559"/>
       <c r="I10" s="82"/>
       <c r="L10" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -19682,9 +19673,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="82"/>
-      <c r="B11" s="1535"/>
-      <c r="C11" s="1537"/>
-      <c r="D11" s="1539" t="s">
+      <c r="B11" s="1551"/>
+      <c r="C11" s="1553"/>
+      <c r="D11" s="1555" t="s">
         <v>420</v>
       </c>
       <c r="E11" s="834" t="s">
@@ -19696,7 +19687,7 @@
       <c r="G11" s="837" t="s">
         <v>423</v>
       </c>
-      <c r="H11" s="1544" t="s">
+      <c r="H11" s="1560" t="s">
         <v>424</v>
       </c>
       <c r="I11" s="82"/>
@@ -19715,9 +19706,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="82"/>
-      <c r="B12" s="1535"/>
-      <c r="C12" s="1538"/>
-      <c r="D12" s="1539"/>
+      <c r="B12" s="1551"/>
+      <c r="C12" s="1554"/>
+      <c r="D12" s="1555"/>
       <c r="E12" s="93" t="s">
         <v>425</v>
       </c>
@@ -19727,7 +19718,7 @@
       <c r="G12" s="837" t="s">
         <v>427</v>
       </c>
-      <c r="H12" s="1545"/>
+      <c r="H12" s="1561"/>
       <c r="I12" s="82"/>
       <c r="L12" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -19740,11 +19731,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="82"/>
-      <c r="B13" s="1535"/>
-      <c r="C13" s="1537" t="s">
+      <c r="B13" s="1551"/>
+      <c r="C13" s="1553" t="s">
         <v>428</v>
       </c>
-      <c r="D13" s="1539" t="s">
+      <c r="D13" s="1555" t="s">
         <v>429</v>
       </c>
       <c r="E13" s="838" t="s">
@@ -19753,10 +19744,10 @@
       <c r="F13" s="839" t="s">
         <v>431</v>
       </c>
-      <c r="G13" s="1546" t="s">
+      <c r="G13" s="1562" t="s">
         <v>432</v>
       </c>
-      <c r="H13" s="1547"/>
+      <c r="H13" s="1563"/>
       <c r="I13" s="82"/>
       <c r="L13" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -19781,19 +19772,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="82"/>
-      <c r="B14" s="1535"/>
-      <c r="C14" s="1537"/>
-      <c r="D14" s="1539"/>
+      <c r="B14" s="1551"/>
+      <c r="C14" s="1553"/>
+      <c r="D14" s="1555"/>
       <c r="E14" s="838" t="s">
         <v>433</v>
       </c>
       <c r="F14" s="839" t="s">
         <v>434</v>
       </c>
-      <c r="G14" s="1546" t="s">
+      <c r="G14" s="1562" t="s">
         <v>435</v>
       </c>
-      <c r="H14" s="1547"/>
+      <c r="H14" s="1563"/>
       <c r="I14" s="82"/>
       <c r="L14" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -19818,9 +19809,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="82"/>
-      <c r="B15" s="1535"/>
-      <c r="C15" s="1537"/>
-      <c r="D15" s="1539" t="s">
+      <c r="B15" s="1551"/>
+      <c r="C15" s="1553"/>
+      <c r="D15" s="1555" t="s">
         <v>436</v>
       </c>
       <c r="E15" s="838" t="s">
@@ -19832,7 +19823,7 @@
       <c r="G15" s="841" t="s">
         <v>439</v>
       </c>
-      <c r="H15" s="1548" t="s">
+      <c r="H15" s="1530" t="s">
         <v>440</v>
       </c>
       <c r="I15" s="82"/>
@@ -19851,9 +19842,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="82"/>
-      <c r="B16" s="1536"/>
-      <c r="C16" s="1537"/>
-      <c r="D16" s="1539"/>
+      <c r="B16" s="1552"/>
+      <c r="C16" s="1553"/>
+      <c r="D16" s="1555"/>
       <c r="E16" s="94" t="s">
         <v>441</v>
       </c>
@@ -19863,7 +19854,7 @@
       <c r="G16" s="839" t="s">
         <v>443</v>
       </c>
-      <c r="H16" s="1549"/>
+      <c r="H16" s="1531"/>
       <c r="I16" s="82"/>
       <c r="L16" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -19876,23 +19867,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="82"/>
-      <c r="B17" s="1550" t="s">
+      <c r="B17" s="1532" t="s">
         <v>444</v>
       </c>
-      <c r="C17" s="1553" t="s">
+      <c r="C17" s="1535" t="s">
         <v>445</v>
       </c>
-      <c r="D17" s="1554"/>
+      <c r="D17" s="1536"/>
       <c r="E17" s="842" t="s">
         <v>446</v>
       </c>
       <c r="F17" s="843" t="s">
         <v>447</v>
       </c>
-      <c r="G17" s="1559" t="s">
+      <c r="G17" s="1541" t="s">
         <v>448</v>
       </c>
-      <c r="H17" s="1560"/>
+      <c r="H17" s="1542"/>
       <c r="I17" s="82"/>
       <c r="L17" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -19905,17 +19896,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="82"/>
-      <c r="B18" s="1551"/>
-      <c r="C18" s="1555"/>
-      <c r="D18" s="1556"/>
+      <c r="B18" s="1533"/>
+      <c r="C18" s="1537"/>
+      <c r="D18" s="1538"/>
       <c r="E18" s="842" t="s">
         <v>449</v>
       </c>
       <c r="F18" s="843" t="s">
         <v>450</v>
       </c>
-      <c r="G18" s="1561"/>
-      <c r="H18" s="1562"/>
+      <c r="G18" s="1543"/>
+      <c r="H18" s="1544"/>
       <c r="I18" s="82"/>
       <c r="L18" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -19928,9 +19919,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="82"/>
-      <c r="B19" s="1551"/>
-      <c r="C19" s="1557"/>
-      <c r="D19" s="1558"/>
+      <c r="B19" s="1533"/>
+      <c r="C19" s="1539"/>
+      <c r="D19" s="1540"/>
       <c r="E19" s="842" t="s">
         <v>451</v>
       </c>
@@ -19951,11 +19942,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="82"/>
-      <c r="B20" s="1551"/>
-      <c r="C20" s="1555" t="s">
+      <c r="B20" s="1533"/>
+      <c r="C20" s="1537" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="1563"/>
+      <c r="D20" s="1545"/>
       <c r="E20" s="844" t="s">
         <v>454</v>
       </c>
@@ -19976,9 +19967,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="82"/>
-      <c r="B21" s="1551"/>
-      <c r="C21" s="1555"/>
-      <c r="D21" s="1563"/>
+      <c r="B21" s="1533"/>
+      <c r="C21" s="1537"/>
+      <c r="D21" s="1545"/>
       <c r="E21" s="844" t="s">
         <v>141</v>
       </c>
@@ -19999,9 +19990,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="82"/>
-      <c r="B22" s="1551"/>
-      <c r="C22" s="1557"/>
-      <c r="D22" s="1564"/>
+      <c r="B22" s="1533"/>
+      <c r="C22" s="1539"/>
+      <c r="D22" s="1546"/>
       <c r="E22" s="98" t="s">
         <v>457</v>
       </c>
@@ -20022,11 +20013,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="82"/>
-      <c r="B23" s="1551"/>
-      <c r="C23" s="1553" t="s">
+      <c r="B23" s="1533"/>
+      <c r="C23" s="1535" t="s">
         <v>459</v>
       </c>
-      <c r="D23" s="1554"/>
+      <c r="D23" s="1536"/>
       <c r="E23" s="845" t="s">
         <v>460</v>
       </c>
@@ -20047,7 +20038,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="82"/>
-      <c r="B24" s="1552"/>
+      <c r="B24" s="1534"/>
       <c r="C24" s="847"/>
       <c r="D24" s="848"/>
       <c r="E24" s="849"/>
@@ -20154,12 +20145,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -20176,6 +20161,12 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20251,71 +20242,71 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="1571" t="s">
+      <c r="B4" s="1570" t="s">
         <v>462</v>
       </c>
-      <c r="C4" s="1572"/>
-      <c r="D4" s="1573" t="s">
+      <c r="C4" s="1571"/>
+      <c r="D4" s="1572" t="s">
         <v>463</v>
       </c>
-      <c r="E4" s="1573"/>
-      <c r="F4" s="1573"/>
-      <c r="G4" s="1573"/>
-      <c r="H4" s="1573"/>
-      <c r="I4" s="1573"/>
-      <c r="J4" s="1573"/>
-      <c r="K4" s="1574" t="s">
+      <c r="E4" s="1572"/>
+      <c r="F4" s="1572"/>
+      <c r="G4" s="1572"/>
+      <c r="H4" s="1572"/>
+      <c r="I4" s="1572"/>
+      <c r="J4" s="1572"/>
+      <c r="K4" s="1573" t="s">
         <v>464</v>
       </c>
-      <c r="L4" s="1575"/>
-      <c r="M4" s="1575"/>
-      <c r="N4" s="1575"/>
-      <c r="O4" s="1576"/>
+      <c r="L4" s="1574"/>
+      <c r="M4" s="1574"/>
+      <c r="N4" s="1574"/>
+      <c r="O4" s="1575"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="53"/>
-      <c r="B5" s="1577" t="s">
+      <c r="B5" s="1576" t="s">
         <v>465</v>
       </c>
-      <c r="C5" s="1578"/>
-      <c r="D5" s="1581" t="s">
+      <c r="C5" s="1577"/>
+      <c r="D5" s="1580" t="s">
         <v>466</v>
       </c>
-      <c r="E5" s="1582"/>
-      <c r="F5" s="1583" t="s">
+      <c r="E5" s="1581"/>
+      <c r="F5" s="1582" t="s">
         <v>467</v>
       </c>
-      <c r="G5" s="1581" t="s">
+      <c r="G5" s="1580" t="s">
         <v>468</v>
       </c>
-      <c r="H5" s="1585"/>
-      <c r="I5" s="1585"/>
-      <c r="J5" s="1582"/>
-      <c r="K5" s="1586" t="s">
+      <c r="H5" s="1584"/>
+      <c r="I5" s="1584"/>
+      <c r="J5" s="1581"/>
+      <c r="K5" s="1585" t="s">
         <v>469</v>
       </c>
-      <c r="L5" s="1588" t="s">
+      <c r="L5" s="1587" t="s">
         <v>470</v>
       </c>
-      <c r="M5" s="1590" t="s">
+      <c r="M5" s="1589" t="s">
         <v>471</v>
       </c>
-      <c r="N5" s="1592" t="s">
+      <c r="N5" s="1591" t="s">
         <v>472</v>
       </c>
-      <c r="O5" s="1593"/>
+      <c r="O5" s="1592"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="53"/>
-      <c r="B6" s="1579"/>
-      <c r="C6" s="1580"/>
+      <c r="B6" s="1578"/>
+      <c r="C6" s="1579"/>
       <c r="D6" s="851" t="s">
         <v>473</v>
       </c>
       <c r="E6" s="852" t="s">
         <v>474</v>
       </c>
-      <c r="F6" s="1584"/>
+      <c r="F6" s="1583"/>
       <c r="G6" s="851" t="s">
         <v>475</v>
       </c>
@@ -20328,9 +20319,9 @@
       <c r="J6" s="852" t="s">
         <v>478</v>
       </c>
-      <c r="K6" s="1587"/>
-      <c r="L6" s="1589"/>
-      <c r="M6" s="1591"/>
+      <c r="K6" s="1586"/>
+      <c r="L6" s="1588"/>
+      <c r="M6" s="1590"/>
       <c r="N6" s="855" t="s">
         <v>479</v>
       </c>
@@ -20730,21 +20721,21 @@
         <f>+D38</f>
         <v>0</v>
       </c>
-      <c r="D23" s="1565">
+      <c r="D23" s="1564">
         <v>0</v>
       </c>
-      <c r="E23" s="1566"/>
+      <c r="E23" s="1565"/>
       <c r="F23" s="889">
         <v>0</v>
       </c>
-      <c r="G23" s="1565">
+      <c r="G23" s="1564">
         <v>0</v>
       </c>
-      <c r="H23" s="1567"/>
-      <c r="I23" s="1568" t="s">
+      <c r="H23" s="1566"/>
+      <c r="I23" s="1567" t="s">
         <v>506</v>
       </c>
-      <c r="J23" s="1566"/>
+      <c r="J23" s="1565"/>
       <c r="K23" s="890" t="s">
         <v>507</v>
       </c>
@@ -20807,11 +20798,11 @@
       <c r="G26" s="76"/>
       <c r="H26" s="55"/>
       <c r="I26" s="55"/>
-      <c r="J26" s="1569" t="str">
+      <c r="J26" s="1568" t="str">
         <f>+D31&amp;" "&amp;F38</f>
         <v>A-1-a (0)</v>
       </c>
-      <c r="K26" s="1570"/>
+      <c r="K26" s="1569"/>
       <c r="L26" s="53"/>
       <c r="M26" s="53"/>
       <c r="N26" s="53"/>
@@ -21071,10 +21062,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1594" t="s">
+      <c r="A2" s="1593" t="s">
         <v>512</v>
       </c>
-      <c r="B2" s="1594"/>
+      <c r="B2" s="1593"/>
       <c r="C2" s="894" t="s">
         <v>513</v>
       </c>
@@ -22182,10 +22173,10 @@
       <c r="J26" s="330"/>
       <c r="K26" s="478"/>
       <c r="L26" s="972"/>
-      <c r="N26" s="1369" t="s">
+      <c r="N26" s="1332" t="s">
         <v>49</v>
       </c>
-      <c r="O26" s="1370"/>
+      <c r="O26" s="1333"/>
       <c r="Y26" s="1103"/>
       <c r="Z26" s="475"/>
       <c r="AA26" s="1103"/>
@@ -22450,11 +22441,11 @@
       <c r="D32" s="1125"/>
       <c r="E32" s="1125"/>
       <c r="F32" s="1126"/>
-      <c r="G32" s="1388">
+      <c r="G32" s="1354">
         <f>DATOS!F41</f>
         <v>0</v>
       </c>
-      <c r="H32" s="1388"/>
+      <c r="H32" s="1354"/>
       <c r="I32" s="991"/>
       <c r="J32" s="330"/>
       <c r="K32" s="478"/>
@@ -22546,13 +22537,13 @@
       <c r="AN34" s="722"/>
     </row>
     <row r="35" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1342" t="s">
+      <c r="A35" s="1350" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="1342"/>
-      <c r="C35" s="1342"/>
-      <c r="D35" s="1342"/>
-      <c r="E35" s="1342"/>
+      <c r="B35" s="1350"/>
+      <c r="C35" s="1350"/>
+      <c r="D35" s="1350"/>
+      <c r="E35" s="1350"/>
       <c r="F35" s="1082">
         <v>1</v>
       </c>
@@ -22588,13 +22579,13 @@
       <c r="AN35" s="722"/>
     </row>
     <row r="36" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1342" t="s">
+      <c r="A36" s="1350" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="1342"/>
-      <c r="C36" s="1342"/>
-      <c r="D36" s="1342"/>
-      <c r="E36" s="1342"/>
+      <c r="B36" s="1350"/>
+      <c r="C36" s="1350"/>
+      <c r="D36" s="1350"/>
+      <c r="E36" s="1350"/>
       <c r="F36" s="1083">
         <f>+DATOS!F15</f>
         <v>5</v>
@@ -22634,13 +22625,13 @@
       <c r="AN36" s="722"/>
     </row>
     <row r="37" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1342" t="s">
+      <c r="A37" s="1350" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="1342"/>
-      <c r="C37" s="1342"/>
-      <c r="D37" s="1342"/>
-      <c r="E37" s="1342"/>
+      <c r="B37" s="1350"/>
+      <c r="C37" s="1350"/>
+      <c r="D37" s="1350"/>
+      <c r="E37" s="1350"/>
       <c r="F37" s="1083">
         <f>+DATOS!F16</f>
         <v>0</v>
@@ -22680,13 +22671,13 @@
       <c r="AN37" s="722"/>
     </row>
     <row r="38" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1342" t="s">
+      <c r="A38" s="1350" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="1342"/>
-      <c r="C38" s="1342"/>
-      <c r="D38" s="1342"/>
-      <c r="E38" s="1342"/>
+      <c r="B38" s="1350"/>
+      <c r="C38" s="1350"/>
+      <c r="D38" s="1350"/>
+      <c r="E38" s="1350"/>
       <c r="F38" s="1085" t="e">
         <f>+DATOS!F21</f>
         <v>#DIV/0!</v>
@@ -22765,13 +22756,13 @@
       <c r="AN39" s="722"/>
     </row>
     <row r="40" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1342" t="s">
+      <c r="A40" s="1350" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="1342"/>
-      <c r="C40" s="1342"/>
-      <c r="D40" s="1342"/>
-      <c r="E40" s="1342"/>
+      <c r="B40" s="1350"/>
+      <c r="C40" s="1350"/>
+      <c r="D40" s="1350"/>
+      <c r="E40" s="1350"/>
       <c r="F40" s="1088" t="e">
         <f>+DATOS!F31</f>
         <v>#DIV/0!</v>
@@ -22788,9 +22779,9 @@
         <f>+DATOS!L31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="1385"/>
-      <c r="K40" s="1386"/>
-      <c r="L40" s="1387"/>
+      <c r="J40" s="1351"/>
+      <c r="K40" s="1352"/>
+      <c r="L40" s="1353"/>
       <c r="M40" s="1107"/>
       <c r="N40" s="1101"/>
       <c r="Q40" s="1108"/>
@@ -22815,13 +22806,13 @@
       <c r="AN40" s="722"/>
     </row>
     <row r="41" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1342" t="s">
+      <c r="A41" s="1350" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="1342"/>
-      <c r="C41" s="1342"/>
-      <c r="D41" s="1342"/>
-      <c r="E41" s="1342"/>
+      <c r="B41" s="1350"/>
+      <c r="C41" s="1350"/>
+      <c r="D41" s="1350"/>
+      <c r="E41" s="1350"/>
       <c r="F41" s="1085" t="e">
         <f>+DATOS!F32</f>
         <v>#DIV/0!</v>
@@ -22838,9 +22829,9 @@
         <f>+DATOS!L32</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="1385"/>
-      <c r="K41" s="1386"/>
-      <c r="L41" s="1387"/>
+      <c r="J41" s="1351"/>
+      <c r="K41" s="1352"/>
+      <c r="L41" s="1353"/>
       <c r="M41" s="1109"/>
       <c r="N41" s="1101"/>
       <c r="V41" s="718"/>
@@ -22887,9 +22878,9 @@
         <f>+DATOS!L33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J42" s="1385"/>
-      <c r="K42" s="1386"/>
-      <c r="L42" s="1387"/>
+      <c r="J42" s="1351"/>
+      <c r="K42" s="1352"/>
+      <c r="L42" s="1353"/>
       <c r="M42" s="1109"/>
       <c r="N42" s="1101"/>
       <c r="V42" s="718"/>
@@ -22957,16 +22948,16 @@
       <c r="G44" s="480"/>
       <c r="H44" s="407"/>
       <c r="I44" s="997"/>
-      <c r="J44" s="1343" t="s">
+      <c r="J44" s="1368" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="1344"/>
-      <c r="L44" s="1345"/>
+      <c r="K44" s="1369"/>
+      <c r="L44" s="1370"/>
       <c r="M44" s="1101"/>
-      <c r="N44" s="1371" t="s">
+      <c r="N44" s="1334" t="s">
         <v>38</v>
       </c>
-      <c r="O44" s="1371"/>
+      <c r="O44" s="1334"/>
       <c r="V44" s="718"/>
       <c r="W44" s="475"/>
       <c r="X44" s="475"/>
@@ -22997,12 +22988,12 @@
       <c r="G45" s="480"/>
       <c r="H45" s="407"/>
       <c r="I45" s="997"/>
-      <c r="J45" s="1346" t="e">
+      <c r="J45" s="1371" t="e">
         <f>+DATOS!C50</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K45" s="1347"/>
-      <c r="L45" s="1348"/>
+      <c r="K45" s="1372"/>
+      <c r="L45" s="1373"/>
       <c r="M45" s="1101"/>
       <c r="N45" s="680">
         <v>0</v>
@@ -23041,11 +23032,11 @@
       <c r="G46" s="480"/>
       <c r="H46" s="407"/>
       <c r="I46" s="997"/>
-      <c r="J46" s="1372" t="s">
+      <c r="J46" s="1335" t="s">
         <v>36</v>
       </c>
-      <c r="K46" s="1373"/>
-      <c r="L46" s="1374"/>
+      <c r="K46" s="1336"/>
+      <c r="L46" s="1337"/>
       <c r="M46" s="1101"/>
       <c r="N46" s="680" t="e">
         <f>+DATOS!J75</f>
@@ -23085,12 +23076,12 @@
       <c r="G47" s="480"/>
       <c r="H47" s="480"/>
       <c r="I47" s="997"/>
-      <c r="J47" s="1375" t="e">
+      <c r="J47" s="1338" t="e">
         <f>MROUND(N52,0.02)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K47" s="1376"/>
-      <c r="L47" s="1377"/>
+      <c r="K47" s="1339"/>
+      <c r="L47" s="1340"/>
       <c r="M47" s="1101" t="s">
         <v>569</v>
       </c>
@@ -23131,11 +23122,11 @@
       <c r="G48" s="480"/>
       <c r="H48" s="480"/>
       <c r="I48" s="997"/>
-      <c r="J48" s="1349" t="s">
+      <c r="J48" s="1374" t="s">
         <v>37</v>
       </c>
-      <c r="K48" s="1350"/>
-      <c r="L48" s="1351"/>
+      <c r="K48" s="1375"/>
+      <c r="L48" s="1376"/>
       <c r="M48" s="1101"/>
       <c r="N48" s="728"/>
       <c r="O48" s="728"/>
@@ -23170,14 +23161,14 @@
       <c r="G49" s="480"/>
       <c r="H49" s="480"/>
       <c r="I49" s="997"/>
-      <c r="J49" s="1352"/>
-      <c r="K49" s="1353"/>
-      <c r="L49" s="1354"/>
+      <c r="J49" s="1377"/>
+      <c r="K49" s="1378"/>
+      <c r="L49" s="1379"/>
       <c r="M49" s="1101"/>
-      <c r="N49" s="1371" t="s">
+      <c r="N49" s="1334" t="s">
         <v>566</v>
       </c>
-      <c r="O49" s="1371"/>
+      <c r="O49" s="1334"/>
       <c r="S49" s="348"/>
       <c r="V49" s="718"/>
       <c r="W49" s="475"/>
@@ -23209,12 +23200,12 @@
       <c r="G50" s="480"/>
       <c r="H50" s="480"/>
       <c r="I50" s="997"/>
-      <c r="J50" s="1378" t="e">
+      <c r="J50" s="1342" t="e">
         <f>+DATOS!J74</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K50" s="1379"/>
-      <c r="L50" s="1380"/>
+      <c r="K50" s="1343"/>
+      <c r="L50" s="1344"/>
       <c r="M50" s="1107"/>
       <c r="N50" s="987">
         <v>0</v>
@@ -23253,9 +23244,9 @@
       <c r="G51" s="480"/>
       <c r="H51" s="480"/>
       <c r="I51" s="997"/>
-      <c r="J51" s="1381"/>
-      <c r="K51" s="1382"/>
-      <c r="L51" s="1383"/>
+      <c r="J51" s="1345"/>
+      <c r="K51" s="1346"/>
+      <c r="L51" s="1347"/>
       <c r="M51" s="1101"/>
       <c r="N51" s="680" t="e">
         <f>+N46*9.8066</f>
@@ -23552,9 +23543,9 @@
       <c r="G60" s="480"/>
       <c r="H60" s="480"/>
       <c r="I60" s="997"/>
-      <c r="J60" s="1335"/>
-      <c r="K60" s="1335"/>
-      <c r="L60" s="1335"/>
+      <c r="J60" s="1341"/>
+      <c r="K60" s="1341"/>
+      <c r="L60" s="1341"/>
       <c r="M60" s="1101"/>
       <c r="Q60" s="1000"/>
       <c r="R60" s="1000"/>
@@ -23590,9 +23581,9 @@
       <c r="G61" s="480"/>
       <c r="H61" s="480"/>
       <c r="I61" s="997"/>
-      <c r="J61" s="1334"/>
-      <c r="K61" s="1334"/>
-      <c r="L61" s="1334"/>
+      <c r="J61" s="1381"/>
+      <c r="K61" s="1381"/>
+      <c r="L61" s="1381"/>
       <c r="M61" s="1101"/>
       <c r="Q61" s="1001"/>
       <c r="R61" s="1001"/>
@@ -23628,9 +23619,9 @@
       <c r="G62" s="480"/>
       <c r="H62" s="480"/>
       <c r="I62" s="997"/>
-      <c r="J62" s="1335"/>
-      <c r="K62" s="1335"/>
-      <c r="L62" s="1335"/>
+      <c r="J62" s="1341"/>
+      <c r="K62" s="1341"/>
+      <c r="L62" s="1341"/>
       <c r="M62" s="1101"/>
       <c r="P62" s="1000"/>
       <c r="Q62" s="1000"/>
@@ -23657,7 +23648,7 @@
     </row>
     <row r="63" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="316"/>
-      <c r="C63" s="1275"/>
+      <c r="C63" s="316"/>
       <c r="D63" s="997"/>
       <c r="E63" s="997"/>
       <c r="F63" s="997"/>
@@ -23772,11 +23763,11 @@
       <c r="C66" s="1114"/>
       <c r="D66" s="478"/>
       <c r="E66" s="478"/>
-      <c r="F66" s="1336">
+      <c r="F66" s="1382">
         <f>+formato!C36</f>
         <v>0</v>
       </c>
-      <c r="G66" s="1336"/>
+      <c r="G66" s="1382"/>
       <c r="H66" s="478"/>
       <c r="I66" s="378"/>
       <c r="J66" s="478"/>
@@ -23810,11 +23801,11 @@
       <c r="C67" s="1114"/>
       <c r="D67" s="478"/>
       <c r="E67" s="478"/>
-      <c r="F67" s="1337">
+      <c r="F67" s="1383">
         <f>+formato!C37</f>
         <v>0</v>
       </c>
-      <c r="G67" s="1337"/>
+      <c r="G67" s="1383"/>
       <c r="H67" s="478"/>
       <c r="I67" s="378"/>
       <c r="J67" s="1115"/>
@@ -23848,11 +23839,11 @@
       <c r="C68" s="1114"/>
       <c r="D68" s="478"/>
       <c r="E68" s="478"/>
-      <c r="F68" s="1336">
+      <c r="F68" s="1382">
         <f>+formato!C38</f>
         <v>0</v>
       </c>
-      <c r="G68" s="1336"/>
+      <c r="G68" s="1382"/>
       <c r="H68" s="478"/>
       <c r="I68" s="1116"/>
       <c r="J68" s="1115"/>
@@ -24069,11 +24060,11 @@
       <c r="G74" s="1014" t="s">
         <v>67</v>
       </c>
-      <c r="H74" s="1338">
+      <c r="H74" s="1384">
         <f>DATOS!F37</f>
         <v>0</v>
       </c>
-      <c r="I74" s="1339"/>
+      <c r="I74" s="1385"/>
       <c r="J74" s="1115"/>
       <c r="K74" s="478"/>
       <c r="L74" s="478"/>
@@ -24114,11 +24105,11 @@
       <c r="G75" s="1014" t="s">
         <v>67</v>
       </c>
-      <c r="H75" s="1340">
+      <c r="H75" s="1386">
         <f>DATOS!F38</f>
         <v>0</v>
       </c>
-      <c r="I75" s="1341"/>
+      <c r="I75" s="1387"/>
       <c r="J75" s="1115"/>
       <c r="K75" s="478"/>
       <c r="L75" s="478"/>
@@ -24183,18 +24174,18 @@
       <c r="AN76" s="722"/>
     </row>
     <row r="77" spans="1:40" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1333"/>
-      <c r="B77" s="1333"/>
-      <c r="C77" s="1333"/>
-      <c r="D77" s="1333"/>
-      <c r="E77" s="1333"/>
-      <c r="F77" s="1333"/>
-      <c r="G77" s="1333"/>
-      <c r="H77" s="1333"/>
-      <c r="I77" s="1333"/>
-      <c r="J77" s="1333"/>
-      <c r="K77" s="1333"/>
-      <c r="L77" s="1333"/>
+      <c r="A77" s="1349"/>
+      <c r="B77" s="1349"/>
+      <c r="C77" s="1349"/>
+      <c r="D77" s="1349"/>
+      <c r="E77" s="1349"/>
+      <c r="F77" s="1349"/>
+      <c r="G77" s="1349"/>
+      <c r="H77" s="1349"/>
+      <c r="I77" s="1349"/>
+      <c r="J77" s="1349"/>
+      <c r="K77" s="1349"/>
+      <c r="L77" s="1349"/>
       <c r="V77" s="718"/>
       <c r="W77" s="475"/>
       <c r="X77" s="475"/>
@@ -24253,20 +24244,20 @@
       <c r="AN78" s="722"/>
     </row>
     <row r="79" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1332" t="s">
+      <c r="A79" s="1380" t="s">
         <v>662</v>
       </c>
-      <c r="B79" s="1332"/>
-      <c r="C79" s="1332"/>
-      <c r="D79" s="1332"/>
-      <c r="E79" s="1332"/>
-      <c r="F79" s="1332"/>
-      <c r="G79" s="1332"/>
-      <c r="H79" s="1332"/>
-      <c r="I79" s="1332"/>
-      <c r="J79" s="1332"/>
-      <c r="K79" s="1332"/>
-      <c r="L79" s="1332"/>
+      <c r="B79" s="1380"/>
+      <c r="C79" s="1380"/>
+      <c r="D79" s="1380"/>
+      <c r="E79" s="1380"/>
+      <c r="F79" s="1380"/>
+      <c r="G79" s="1380"/>
+      <c r="H79" s="1380"/>
+      <c r="I79" s="1380"/>
+      <c r="J79" s="1380"/>
+      <c r="K79" s="1380"/>
+      <c r="L79" s="1380"/>
       <c r="M79" s="1016"/>
       <c r="N79" s="1016"/>
       <c r="V79" s="718"/>
@@ -24290,20 +24281,20 @@
       <c r="AN79" s="722"/>
     </row>
     <row r="80" spans="1:40" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1333" t="s">
+      <c r="A80" s="1349" t="s">
         <v>663</v>
       </c>
-      <c r="B80" s="1333"/>
-      <c r="C80" s="1333"/>
-      <c r="D80" s="1333"/>
-      <c r="E80" s="1333"/>
-      <c r="F80" s="1333"/>
-      <c r="G80" s="1333"/>
-      <c r="H80" s="1333"/>
-      <c r="I80" s="1333"/>
-      <c r="J80" s="1333"/>
-      <c r="K80" s="1333"/>
-      <c r="L80" s="1333"/>
+      <c r="B80" s="1349"/>
+      <c r="C80" s="1349"/>
+      <c r="D80" s="1349"/>
+      <c r="E80" s="1349"/>
+      <c r="F80" s="1349"/>
+      <c r="G80" s="1349"/>
+      <c r="H80" s="1349"/>
+      <c r="I80" s="1349"/>
+      <c r="J80" s="1349"/>
+      <c r="K80" s="1349"/>
+      <c r="L80" s="1349"/>
       <c r="M80" s="1119"/>
       <c r="N80" s="1119"/>
       <c r="V80" s="718"/>
@@ -24327,20 +24318,20 @@
       <c r="AN80" s="722"/>
     </row>
     <row r="81" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1333" t="s">
+      <c r="A81" s="1349" t="s">
         <v>664</v>
       </c>
-      <c r="B81" s="1333"/>
-      <c r="C81" s="1333"/>
-      <c r="D81" s="1333"/>
-      <c r="E81" s="1333"/>
-      <c r="F81" s="1333"/>
-      <c r="G81" s="1333"/>
-      <c r="H81" s="1333"/>
-      <c r="I81" s="1333"/>
-      <c r="J81" s="1333"/>
-      <c r="K81" s="1333"/>
-      <c r="L81" s="1333"/>
+      <c r="B81" s="1349"/>
+      <c r="C81" s="1349"/>
+      <c r="D81" s="1349"/>
+      <c r="E81" s="1349"/>
+      <c r="F81" s="1349"/>
+      <c r="G81" s="1349"/>
+      <c r="H81" s="1349"/>
+      <c r="I81" s="1349"/>
+      <c r="J81" s="1349"/>
+      <c r="K81" s="1349"/>
+      <c r="L81" s="1349"/>
       <c r="M81" s="1017"/>
       <c r="N81" s="1017"/>
       <c r="V81" s="718"/>
@@ -24364,20 +24355,20 @@
       <c r="AN81" s="722"/>
     </row>
     <row r="82" spans="1:40" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1333" t="s">
+      <c r="A82" s="1349" t="s">
         <v>665</v>
       </c>
-      <c r="B82" s="1333"/>
-      <c r="C82" s="1333"/>
-      <c r="D82" s="1333"/>
-      <c r="E82" s="1333"/>
-      <c r="F82" s="1333"/>
-      <c r="G82" s="1333"/>
-      <c r="H82" s="1333"/>
-      <c r="I82" s="1333"/>
-      <c r="J82" s="1333"/>
-      <c r="K82" s="1333"/>
-      <c r="L82" s="1333"/>
+      <c r="B82" s="1349"/>
+      <c r="C82" s="1349"/>
+      <c r="D82" s="1349"/>
+      <c r="E82" s="1349"/>
+      <c r="F82" s="1349"/>
+      <c r="G82" s="1349"/>
+      <c r="H82" s="1349"/>
+      <c r="I82" s="1349"/>
+      <c r="J82" s="1349"/>
+      <c r="K82" s="1349"/>
+      <c r="L82" s="1349"/>
       <c r="M82" s="1119"/>
       <c r="N82" s="1119"/>
       <c r="V82" s="718"/>
@@ -24401,20 +24392,20 @@
       <c r="AN82" s="722"/>
     </row>
     <row r="83" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1384" t="s">
+      <c r="A83" s="1348" t="s">
         <v>666</v>
       </c>
-      <c r="B83" s="1384"/>
-      <c r="C83" s="1384"/>
-      <c r="D83" s="1384"/>
-      <c r="E83" s="1384"/>
-      <c r="F83" s="1384"/>
-      <c r="G83" s="1384"/>
-      <c r="H83" s="1384"/>
-      <c r="I83" s="1384"/>
-      <c r="J83" s="1384"/>
-      <c r="K83" s="1384"/>
-      <c r="L83" s="1384"/>
+      <c r="B83" s="1348"/>
+      <c r="C83" s="1348"/>
+      <c r="D83" s="1348"/>
+      <c r="E83" s="1348"/>
+      <c r="F83" s="1348"/>
+      <c r="G83" s="1348"/>
+      <c r="H83" s="1348"/>
+      <c r="I83" s="1348"/>
+      <c r="J83" s="1348"/>
+      <c r="K83" s="1348"/>
+      <c r="L83" s="1348"/>
       <c r="M83" s="1119"/>
       <c r="N83" s="1119"/>
       <c r="V83" s="718"/>
@@ -24510,18 +24501,18 @@
       <c r="AN85" s="722"/>
     </row>
     <row r="86" spans="1:40" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1368"/>
-      <c r="B86" s="1368"/>
-      <c r="C86" s="1368"/>
-      <c r="D86" s="1368"/>
-      <c r="E86" s="1368"/>
-      <c r="F86" s="1368"/>
-      <c r="G86" s="1368"/>
-      <c r="H86" s="1368"/>
-      <c r="I86" s="1368"/>
-      <c r="J86" s="1368"/>
-      <c r="K86" s="1368"/>
-      <c r="L86" s="1368"/>
+      <c r="A86" s="1331"/>
+      <c r="B86" s="1331"/>
+      <c r="C86" s="1331"/>
+      <c r="D86" s="1331"/>
+      <c r="E86" s="1331"/>
+      <c r="F86" s="1331"/>
+      <c r="G86" s="1331"/>
+      <c r="H86" s="1331"/>
+      <c r="I86" s="1331"/>
+      <c r="J86" s="1331"/>
+      <c r="K86" s="1331"/>
+      <c r="L86" s="1331"/>
       <c r="M86" s="1119"/>
       <c r="N86" s="1119"/>
       <c r="V86" s="718"/>
@@ -25808,13 +25799,44 @@
       <c r="AN136" s="722"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="b5xBW32WPInh12yRiHEb2pKiSOFVvrkzOic/isP6yN7qCoEEowW/7cImBYCxbXiw/5A2wDw4Ui9ZmyW11lP1QA==" saltValue="lWFMcnZxpiNum4Xe5dfNoA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="E16" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E11:E13" name="Rango3_3_1_1_1_1_1_1_1_1_2"/>
     <protectedRange sqref="E9:E10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="47">
+    <mergeCell ref="A79:L79"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A82:L82"/>
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J48:L49"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="A86:L86"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="N44:O44"/>
@@ -25831,37 +25853,6 @@
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="J40:L40"/>
     <mergeCell ref="J38:L38"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J48:L49"/>
-    <mergeCell ref="A79:L79"/>
-    <mergeCell ref="A80:L80"/>
-    <mergeCell ref="A82:L82"/>
-    <mergeCell ref="A81:L81"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.70866141732283472" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -25872,6 +25863,9 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="63" max="11" man="1"/>
   </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="12" max="1048575" man="1"/>
+  </colBreaks>
   <drawing r:id="rId2"/>
   <legacyDrawingHF r:id="rId3"/>
 </worksheet>
@@ -25904,40 +25898,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1395" t="s">
+      <c r="B2" s="1406" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1396"/>
-      <c r="D2" s="1396"/>
-      <c r="E2" s="1396"/>
-      <c r="F2" s="1396"/>
-      <c r="G2" s="1396"/>
-      <c r="H2" s="1396"/>
-      <c r="I2" s="1396"/>
-      <c r="J2" s="1396"/>
-      <c r="K2" s="1396"/>
-      <c r="L2" s="1396"/>
-      <c r="M2" s="1396"/>
-      <c r="N2" s="1396"/>
-      <c r="O2" s="1397"/>
+      <c r="C2" s="1407"/>
+      <c r="D2" s="1407"/>
+      <c r="E2" s="1407"/>
+      <c r="F2" s="1407"/>
+      <c r="G2" s="1407"/>
+      <c r="H2" s="1407"/>
+      <c r="I2" s="1407"/>
+      <c r="J2" s="1407"/>
+      <c r="K2" s="1407"/>
+      <c r="L2" s="1407"/>
+      <c r="M2" s="1407"/>
+      <c r="N2" s="1407"/>
+      <c r="O2" s="1408"/>
     </row>
     <row r="3" spans="2:19" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1398" t="s">
+      <c r="B3" s="1409" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1399"/>
-      <c r="D3" s="1399"/>
-      <c r="E3" s="1399"/>
-      <c r="F3" s="1399"/>
-      <c r="G3" s="1399"/>
-      <c r="H3" s="1399"/>
-      <c r="I3" s="1399"/>
-      <c r="J3" s="1399"/>
-      <c r="K3" s="1399"/>
-      <c r="L3" s="1399"/>
-      <c r="M3" s="1399"/>
-      <c r="N3" s="1399"/>
-      <c r="O3" s="1400"/>
+      <c r="C3" s="1410"/>
+      <c r="D3" s="1410"/>
+      <c r="E3" s="1410"/>
+      <c r="F3" s="1410"/>
+      <c r="G3" s="1410"/>
+      <c r="H3" s="1410"/>
+      <c r="I3" s="1410"/>
+      <c r="J3" s="1410"/>
+      <c r="K3" s="1410"/>
+      <c r="L3" s="1410"/>
+      <c r="M3" s="1410"/>
+      <c r="N3" s="1410"/>
+      <c r="O3" s="1411"/>
     </row>
     <row r="5" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="682" t="s">
@@ -26127,31 +26121,31 @@
       <c r="N11" s="494"/>
     </row>
     <row r="12" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1389" t="s">
+      <c r="B12" s="1402" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="1389"/>
-      <c r="D12" s="1389"/>
-      <c r="E12" s="1389">
+      <c r="C12" s="1402"/>
+      <c r="D12" s="1402"/>
+      <c r="E12" s="1402">
         <v>1</v>
       </c>
-      <c r="F12" s="1389"/>
-      <c r="G12" s="1389">
+      <c r="F12" s="1402"/>
+      <c r="G12" s="1402">
         <v>2</v>
       </c>
-      <c r="H12" s="1389"/>
-      <c r="I12" s="1389">
+      <c r="H12" s="1402"/>
+      <c r="I12" s="1402">
         <v>3</v>
       </c>
-      <c r="J12" s="1389"/>
-      <c r="K12" s="1389">
+      <c r="J12" s="1402"/>
+      <c r="K12" s="1402">
         <v>4</v>
       </c>
-      <c r="L12" s="1389"/>
-      <c r="M12" s="1389">
+      <c r="L12" s="1402"/>
+      <c r="M12" s="1402">
         <v>5</v>
       </c>
-      <c r="N12" s="1389"/>
+      <c r="N12" s="1402"/>
       <c r="Q12" s="1138" t="s">
         <v>579</v>
       </c>
@@ -26163,9 +26157,9 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1389"/>
-      <c r="C13" s="1389"/>
-      <c r="D13" s="1389"/>
+      <c r="B13" s="1402"/>
+      <c r="C13" s="1402"/>
+      <c r="D13" s="1402"/>
       <c r="E13" s="730" t="s">
         <v>84</v>
       </c>
@@ -26207,11 +26201,11 @@
       </c>
     </row>
     <row r="14" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1401" t="s">
+      <c r="B14" s="1396" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1401"/>
-      <c r="D14" s="1402"/>
+      <c r="C14" s="1396"/>
+      <c r="D14" s="1397"/>
       <c r="E14" s="1255">
         <v>1</v>
       </c>
@@ -26237,11 +26231,11 @@
       </c>
     </row>
     <row r="15" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1390" t="s">
+      <c r="B15" s="1391" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="1390"/>
-      <c r="D15" s="1391"/>
+      <c r="C15" s="1391"/>
+      <c r="D15" s="1392"/>
       <c r="E15" s="1139">
         <v>5</v>
       </c>
@@ -26286,11 +26280,11 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1390" t="s">
+      <c r="B16" s="1391" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="1390"/>
-      <c r="D16" s="1391"/>
+      <c r="C16" s="1391"/>
+      <c r="D16" s="1392"/>
       <c r="E16" s="1139">
         <f>+formato!D17</f>
         <v>0</v>
@@ -26336,11 +26330,11 @@
       </c>
     </row>
     <row r="17" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="1390" t="s">
+      <c r="B17" s="1391" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="1390"/>
-      <c r="D17" s="1391"/>
+      <c r="C17" s="1391"/>
+      <c r="D17" s="1392"/>
       <c r="E17" s="1139">
         <f>+formato!D18</f>
         <v>0</v>
@@ -26386,11 +26380,11 @@
       </c>
     </row>
     <row r="18" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1390" t="s">
+      <c r="B18" s="1391" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="1390"/>
-      <c r="D18" s="1391"/>
+      <c r="C18" s="1391"/>
+      <c r="D18" s="1392"/>
       <c r="E18" s="1139">
         <f>+formato!D19</f>
         <v>0</v>
@@ -26427,11 +26421,11 @@
       <c r="N18" s="1145"/>
     </row>
     <row r="19" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="1391" t="s">
+      <c r="B19" s="1392" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1412"/>
-      <c r="D19" s="1412"/>
+      <c r="C19" s="1393"/>
+      <c r="D19" s="1393"/>
       <c r="E19" s="1142">
         <f t="shared" ref="E19:K19" si="0">+E17-E18</f>
         <v>0</v>
@@ -26468,11 +26462,11 @@
       <c r="N19" s="1145"/>
     </row>
     <row r="20" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="1390" t="s">
+      <c r="B20" s="1391" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="1390"/>
-      <c r="D20" s="1391"/>
+      <c r="C20" s="1391"/>
+      <c r="D20" s="1392"/>
       <c r="E20" s="1139">
         <f>+formato!D21</f>
         <v>0</v>
@@ -26522,11 +26516,11 @@
       <c r="U20" s="948"/>
     </row>
     <row r="21" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="1413" t="s">
+      <c r="B21" s="1394" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="1413"/>
-      <c r="D21" s="1414"/>
+      <c r="C21" s="1394"/>
+      <c r="D21" s="1395"/>
       <c r="E21" s="1142" t="e">
         <f t="shared" ref="E21:K21" si="1">+E19/E20</f>
         <v>#DIV/0!</v>
@@ -26607,11 +26601,11 @@
       <c r="U22" s="950"/>
     </row>
     <row r="23" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="1401" t="s">
+      <c r="B23" s="1396" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="1401"/>
-      <c r="D23" s="1402"/>
+      <c r="C23" s="1396"/>
+      <c r="D23" s="1397"/>
       <c r="E23" s="1139">
         <f>+formato!D24</f>
         <v>0</v>
@@ -26650,11 +26644,11 @@
       <c r="U23" s="953"/>
     </row>
     <row r="24" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="1390" t="s">
+      <c r="B24" s="1391" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="1390"/>
-      <c r="D24" s="1391"/>
+      <c r="C24" s="1391"/>
+      <c r="D24" s="1392"/>
       <c r="E24" s="1139">
         <f>+formato!D25</f>
         <v>0</v>
@@ -26710,11 +26704,11 @@
       </c>
     </row>
     <row r="25" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="1390" t="s">
+      <c r="B25" s="1391" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="1390"/>
-      <c r="D25" s="1391"/>
+      <c r="C25" s="1391"/>
+      <c r="D25" s="1392"/>
       <c r="E25" s="1139">
         <f>+formato!D26</f>
         <v>0</v>
@@ -26766,11 +26760,11 @@
       </c>
     </row>
     <row r="26" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="1390" t="s">
+      <c r="B26" s="1391" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="1390"/>
-      <c r="D26" s="1391"/>
+      <c r="C26" s="1391"/>
+      <c r="D26" s="1392"/>
       <c r="E26" s="1139">
         <f>+formato!D27</f>
         <v>0</v>
@@ -26826,11 +26820,11 @@
       </c>
     </row>
     <row r="27" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="1390" t="s">
+      <c r="B27" s="1391" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="1390"/>
-      <c r="D27" s="1391"/>
+      <c r="C27" s="1391"/>
+      <c r="D27" s="1392"/>
       <c r="E27" s="1139">
         <f>+formato!D28</f>
         <v>0</v>
@@ -26874,11 +26868,11 @@
       </c>
     </row>
     <row r="28" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="1390" t="s">
+      <c r="B28" s="1391" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="1390"/>
-      <c r="D28" s="1391"/>
+      <c r="C28" s="1391"/>
+      <c r="D28" s="1392"/>
       <c r="E28" s="1155">
         <f t="shared" ref="E28:L28" si="6">+E24-E27</f>
         <v>0</v>
@@ -26915,11 +26909,11 @@
       <c r="N28" s="1145"/>
     </row>
     <row r="29" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="1390" t="s">
+      <c r="B29" s="1391" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="1390"/>
-      <c r="D29" s="1391"/>
+      <c r="C29" s="1391"/>
+      <c r="D29" s="1392"/>
       <c r="E29" s="1139">
         <f>+formato!D30</f>
         <v>0</v>
@@ -26956,11 +26950,11 @@
       <c r="N29" s="1145"/>
     </row>
     <row r="30" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="1391" t="s">
+      <c r="B30" s="1392" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="1412"/>
-      <c r="D30" s="1412"/>
+      <c r="C30" s="1393"/>
+      <c r="D30" s="1393"/>
       <c r="E30" s="1142"/>
       <c r="F30" s="1142" t="e">
         <f t="shared" ref="F30:L30" si="7">+F27-F29</f>
@@ -26985,11 +26979,11 @@
       <c r="N30" s="1145"/>
     </row>
     <row r="31" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="1391" t="s">
+      <c r="B31" s="1392" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="1412"/>
-      <c r="D31" s="1412"/>
+      <c r="C31" s="1393"/>
+      <c r="D31" s="1393"/>
       <c r="E31" s="1142"/>
       <c r="F31" s="1142" t="e">
         <f t="shared" ref="F31:L31" si="8">+F28/F30*100</f>
@@ -27017,11 +27011,11 @@
       </c>
     </row>
     <row r="32" spans="2:21" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="1414" t="s">
+      <c r="B32" s="1395" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="1415"/>
-      <c r="D32" s="1415"/>
+      <c r="C32" s="1398"/>
+      <c r="D32" s="1398"/>
       <c r="E32" s="1142"/>
       <c r="F32" s="1142" t="e">
         <f t="shared" ref="F32:L32" si="9">+F21/(1+F31/100)</f>
@@ -27147,11 +27141,11 @@
       </c>
       <c r="D37" s="706"/>
       <c r="E37" s="707"/>
-      <c r="F37" s="1406">
+      <c r="F37" s="1399">
         <v>0</v>
       </c>
-      <c r="G37" s="1406"/>
-      <c r="H37" s="1406"/>
+      <c r="G37" s="1399"/>
+      <c r="H37" s="1399"/>
     </row>
     <row r="38" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="678" t="s">
@@ -27159,11 +27153,11 @@
       </c>
       <c r="D38" s="706"/>
       <c r="E38" s="707"/>
-      <c r="F38" s="1407">
+      <c r="F38" s="1400">
         <v>0</v>
       </c>
-      <c r="G38" s="1407"/>
-      <c r="H38" s="1407"/>
+      <c r="G38" s="1400"/>
+      <c r="H38" s="1400"/>
     </row>
     <row r="39" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27188,17 +27182,17 @@
       </c>
       <c r="D41" s="1029"/>
       <c r="E41" s="1030"/>
-      <c r="F41" s="1408">
+      <c r="F41" s="1401">
         <v>0</v>
       </c>
-      <c r="G41" s="1408"/>
-      <c r="H41" s="1408"/>
-      <c r="K41" s="1405" t="s">
+      <c r="G41" s="1401"/>
+      <c r="H41" s="1401"/>
+      <c r="K41" s="1414" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="1405"/>
+      <c r="L41" s="1414"/>
       <c r="M41" s="478"/>
-      <c r="N41" s="1403" t="s">
+      <c r="N41" s="1412" t="s">
         <v>102</v>
       </c>
     </row>
@@ -27211,7 +27205,7 @@
         <v>52</v>
       </c>
       <c r="M42" s="478"/>
-      <c r="N42" s="1404"/>
+      <c r="N42" s="1413"/>
     </row>
     <row r="43" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1027"/>
@@ -27384,21 +27378,21 @@
     </row>
     <row r="49" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="711"/>
-      <c r="C49" s="1392" t="s">
+      <c r="C49" s="1403" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="1393"/>
-      <c r="E49" s="1394"/>
+      <c r="D49" s="1404"/>
+      <c r="E49" s="1405"/>
       <c r="N49" s="712"/>
     </row>
     <row r="50" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="711"/>
-      <c r="C50" s="1409" t="e">
+      <c r="C50" s="1388" t="e">
         <f>IF(G54="","",IF(AND(G54&lt;=25),"A",IF(AND(G54&gt;25,G53&lt;=25),"B",IF(AND(G53&gt;25,G52&lt;30),"C"))))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D50" s="1410"/>
-      <c r="E50" s="1411"/>
+      <c r="D50" s="1389"/>
+      <c r="E50" s="1390"/>
       <c r="F50" s="475"/>
       <c r="N50" s="712"/>
       <c r="O50" s="713"/>
@@ -29063,23 +29057,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="e49E/OysaywdZI0JcuM+C0cQuCvqe9PMqZ/ilP9GIY/P45QRK0Ai6JyKU7eB4WtZltnkC9BaQI8vpXNlfCIiIw==" saltValue="LOl5Rt57JcvlkUy4kBpOXg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="33">
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B29:D29"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="I12:J12"/>
@@ -29096,6 +29073,23 @@
     <mergeCell ref="N41:N42"/>
     <mergeCell ref="K41:L41"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
   </mergeCells>
   <conditionalFormatting sqref="F34:F35">
     <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="No Cumple">
@@ -29238,17 +29232,17 @@
       <c r="A6" s="744" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="1419" t="s">
+      <c r="B6" s="1434" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="1420"/>
-      <c r="D6" s="1420"/>
-      <c r="E6" s="1420"/>
-      <c r="F6" s="1420"/>
-      <c r="G6" s="1420"/>
-      <c r="H6" s="1420"/>
-      <c r="I6" s="1420"/>
-      <c r="J6" s="1421"/>
+      <c r="C6" s="1435"/>
+      <c r="D6" s="1435"/>
+      <c r="E6" s="1435"/>
+      <c r="F6" s="1435"/>
+      <c r="G6" s="1435"/>
+      <c r="H6" s="1435"/>
+      <c r="I6" s="1435"/>
+      <c r="J6" s="1436"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="744" t="s">
@@ -29524,8 +29518,8 @@
       <c r="G30" s="471"/>
       <c r="H30" s="470"/>
       <c r="L30" s="1425"/>
-      <c r="R30" s="1422"/>
-      <c r="S30" s="1422"/>
+      <c r="R30" s="1437"/>
+      <c r="S30" s="1437"/>
       <c r="T30" s="674"/>
       <c r="U30" s="675"/>
     </row>
@@ -29539,8 +29533,8 @@
       <c r="G31" s="471"/>
       <c r="H31" s="471"/>
       <c r="L31" s="1425"/>
-      <c r="R31" s="1422"/>
-      <c r="S31" s="1422"/>
+      <c r="R31" s="1437"/>
+      <c r="S31" s="1437"/>
       <c r="T31" s="674"/>
       <c r="U31" s="675"/>
     </row>
@@ -29554,8 +29548,8 @@
       <c r="G32" s="471"/>
       <c r="H32" s="471"/>
       <c r="L32" s="1425"/>
-      <c r="R32" s="1422"/>
-      <c r="S32" s="1422"/>
+      <c r="R32" s="1437"/>
+      <c r="S32" s="1437"/>
       <c r="T32" s="674"/>
       <c r="U32" s="675"/>
     </row>
@@ -29570,8 +29564,8 @@
       <c r="H33" s="471"/>
       <c r="L33" s="1425"/>
       <c r="O33" s="673"/>
-      <c r="R33" s="1422"/>
-      <c r="S33" s="1422"/>
+      <c r="R33" s="1437"/>
+      <c r="S33" s="1437"/>
       <c r="T33" s="488"/>
       <c r="U33" s="675"/>
     </row>
@@ -32139,12 +32133,12 @@
       <c r="M74" s="471"/>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A75" s="1418" t="s">
+      <c r="A75" s="1433" t="s">
         <v>188</v>
       </c>
-      <c r="B75" s="1418"/>
-      <c r="C75" s="1418"/>
-      <c r="D75" s="1418"/>
+      <c r="B75" s="1433"/>
+      <c r="C75" s="1433"/>
+      <c r="D75" s="1433"/>
       <c r="E75" s="467"/>
       <c r="F75" s="467"/>
       <c r="G75" s="467"/>
@@ -32154,10 +32148,10 @@
       <c r="M75" s="471"/>
     </row>
     <row r="76" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1417" t="s">
+      <c r="A76" s="1432" t="s">
         <v>189</v>
       </c>
-      <c r="B76" s="1417"/>
+      <c r="B76" s="1432"/>
       <c r="C76" s="641" t="s">
         <v>190</v>
       </c>
@@ -32344,16 +32338,16 @@
       <c r="R87" s="486" t="s">
         <v>198</v>
       </c>
-      <c r="T87" s="1416" t="s">
+      <c r="T87" s="1431" t="s">
         <v>527</v>
       </c>
-      <c r="U87" s="1416"/>
-      <c r="V87" s="1416"/>
-      <c r="W87" s="1416" t="s">
+      <c r="U87" s="1431"/>
+      <c r="V87" s="1431"/>
+      <c r="W87" s="1431" t="s">
         <v>528</v>
       </c>
-      <c r="X87" s="1416"/>
-      <c r="Y87" s="1416"/>
+      <c r="X87" s="1431"/>
+      <c r="Y87" s="1431"/>
     </row>
     <row r="88" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="596" t="s">
@@ -32877,19 +32871,19 @@
       <c r="A100" s="1262" t="s">
         <v>648</v>
       </c>
-      <c r="B100" s="1431" t="s">
+      <c r="B100" s="1415" t="s">
         <v>649</v>
       </c>
-      <c r="C100" s="1432"/>
+      <c r="C100" s="1416"/>
       <c r="D100" s="1263"/>
-      <c r="E100" s="1433" t="s">
+      <c r="E100" s="1417" t="s">
         <v>650</v>
       </c>
-      <c r="F100" s="1433"/>
-      <c r="G100" s="1434" t="s">
+      <c r="F100" s="1417"/>
+      <c r="G100" s="1418" t="s">
         <v>651</v>
       </c>
-      <c r="H100" s="1435"/>
+      <c r="H100" s="1419"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="940"/>
@@ -32905,19 +32899,19 @@
       <c r="A102" s="1264" t="s">
         <v>652</v>
       </c>
-      <c r="B102" s="1436">
+      <c r="B102" s="1420">
         <v>44944</v>
       </c>
-      <c r="C102" s="1437"/>
+      <c r="C102" s="1421"/>
       <c r="D102" s="940"/>
-      <c r="E102" s="1438" t="s">
+      <c r="E102" s="1422" t="s">
         <v>653</v>
       </c>
-      <c r="F102" s="1438"/>
-      <c r="G102" s="1436">
+      <c r="F102" s="1422"/>
+      <c r="G102" s="1420">
         <v>44944</v>
       </c>
-      <c r="H102" s="1437"/>
+      <c r="H102" s="1421"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="940"/>
@@ -32932,12 +32926,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wd0Sk3J/OeT0TxJIAnp4S2dGatByENh6gH5lE7pLCIYYn5xv110dK84OeIJzfd1un3raa/Q0kk7gUzEP+5w5+g==" saltValue="Nxfv9eN1cqS8LPjiSFaCXw==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="T87:V87"/>
+    <mergeCell ref="W87:Y87"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="R30:S33"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:H4"/>
     <mergeCell ref="L30:L33"/>
@@ -32946,12 +32940,12 @@
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="S35:S36"/>
     <mergeCell ref="T35:U36"/>
-    <mergeCell ref="T87:V87"/>
-    <mergeCell ref="W87:Y87"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="R30:S33"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G102:H102"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -33005,22 +32999,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B2" s="1439" t="s">
+      <c r="B2" s="1438" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="1439"/>
-      <c r="D2" s="1439"/>
-      <c r="E2" s="1439"/>
-      <c r="F2" s="1439"/>
-      <c r="G2" s="1439"/>
-      <c r="L2" s="1439" t="s">
+      <c r="C2" s="1438"/>
+      <c r="D2" s="1438"/>
+      <c r="E2" s="1438"/>
+      <c r="F2" s="1438"/>
+      <c r="G2" s="1438"/>
+      <c r="L2" s="1438" t="s">
         <v>206</v>
       </c>
-      <c r="M2" s="1439"/>
-      <c r="N2" s="1439"/>
-      <c r="O2" s="1439"/>
-      <c r="P2" s="1439"/>
-      <c r="Q2" s="1439"/>
+      <c r="M2" s="1438"/>
+      <c r="N2" s="1438"/>
+      <c r="O2" s="1438"/>
+      <c r="P2" s="1438"/>
+      <c r="Q2" s="1438"/>
       <c r="T2" s="471"/>
       <c r="U2" s="471"/>
       <c r="V2" s="1050" t="s">
@@ -33063,10 +33057,10 @@
       <c r="AA5" s="471"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="I6" s="1440" t="s">
+      <c r="I6" s="1439" t="s">
         <v>207</v>
       </c>
-      <c r="J6" s="1441"/>
+      <c r="J6" s="1440"/>
       <c r="T6" s="471"/>
       <c r="U6" s="471"/>
       <c r="V6" s="471"/>
@@ -34449,39 +34443,39 @@
       <c r="A7" s="1135" t="s">
         <v>574</v>
       </c>
-      <c r="B7" s="1442">
+      <c r="B7" s="1441">
         <v>2.0947951371589977E-2</v>
       </c>
-      <c r="C7" s="1442"/>
-      <c r="D7" s="1442"/>
+      <c r="C7" s="1441"/>
+      <c r="D7" s="1441"/>
       <c r="E7" s="482"/>
       <c r="G7" s="1135" t="s">
         <v>574</v>
       </c>
-      <c r="H7" s="1442">
+      <c r="H7" s="1441">
         <v>0.11030261405182915</v>
       </c>
-      <c r="I7" s="1442"/>
-      <c r="J7" s="1442"/>
+      <c r="I7" s="1441"/>
+      <c r="J7" s="1441"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1135" t="s">
         <v>575</v>
       </c>
-      <c r="B8" s="1442">
+      <c r="B8" s="1441">
         <v>2.1813476975842898E-2</v>
       </c>
-      <c r="C8" s="1442"/>
-      <c r="D8" s="1442"/>
+      <c r="C8" s="1441"/>
+      <c r="D8" s="1441"/>
       <c r="E8" s="482"/>
       <c r="G8" s="1135" t="s">
         <v>575</v>
       </c>
-      <c r="H8" s="1442">
+      <c r="H8" s="1441">
         <v>0.11377365443927613</v>
       </c>
-      <c r="I8" s="1442"/>
-      <c r="J8" s="1442"/>
+      <c r="I8" s="1441"/>
+      <c r="J8" s="1441"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="FYJq3GhyQBF7Pmjc4398tmgpF0gfeMaFowah8hdIzkRnEppsVQu7MC046WcPkrhdaONzABmyez2teHVIMA3rRQ==" saltValue="QmbXxEwr+jVZyr/mMxd6pw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -34604,18 +34598,18 @@
       <c r="V7" s="365"/>
     </row>
     <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1450">
+      <c r="A8" s="1445">
         <v>1</v>
       </c>
-      <c r="B8" s="1450"/>
-      <c r="C8" s="1450"/>
-      <c r="D8" s="1450"/>
-      <c r="E8" s="1450"/>
-      <c r="F8" s="1450"/>
-      <c r="G8" s="1450"/>
-      <c r="H8" s="1450"/>
-      <c r="I8" s="1450"/>
-      <c r="J8" s="1450"/>
+      <c r="B8" s="1445"/>
+      <c r="C8" s="1445"/>
+      <c r="D8" s="1445"/>
+      <c r="E8" s="1445"/>
+      <c r="F8" s="1445"/>
+      <c r="G8" s="1445"/>
+      <c r="H8" s="1445"/>
+      <c r="I8" s="1445"/>
+      <c r="J8" s="1445"/>
       <c r="L8" s="334"/>
       <c r="M8" s="366"/>
       <c r="N8" s="367"/>
@@ -34894,18 +34888,18 @@
       <c r="AL14" s="315"/>
     </row>
     <row r="15" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1451" t="s">
+      <c r="A15" s="1446" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="1452"/>
-      <c r="C15" s="1452"/>
-      <c r="D15" s="1452"/>
-      <c r="E15" s="1452"/>
-      <c r="F15" s="1452"/>
-      <c r="G15" s="1452"/>
-      <c r="H15" s="1452"/>
-      <c r="I15" s="1452"/>
-      <c r="J15" s="1453"/>
+      <c r="B15" s="1447"/>
+      <c r="C15" s="1447"/>
+      <c r="D15" s="1447"/>
+      <c r="E15" s="1447"/>
+      <c r="F15" s="1447"/>
+      <c r="G15" s="1447"/>
+      <c r="H15" s="1447"/>
+      <c r="I15" s="1447"/>
+      <c r="J15" s="1448"/>
       <c r="K15" s="341"/>
       <c r="M15" s="365"/>
       <c r="N15" s="365"/>
@@ -34934,18 +34928,18 @@
       <c r="AL15" s="315"/>
     </row>
     <row r="16" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1454" t="s">
+      <c r="A16" s="1449" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="1455"/>
-      <c r="C16" s="1455"/>
-      <c r="D16" s="1455"/>
-      <c r="E16" s="1455"/>
-      <c r="F16" s="1455"/>
-      <c r="G16" s="1455"/>
-      <c r="H16" s="1455"/>
-      <c r="I16" s="1455"/>
-      <c r="J16" s="1456"/>
+      <c r="B16" s="1450"/>
+      <c r="C16" s="1450"/>
+      <c r="D16" s="1450"/>
+      <c r="E16" s="1450"/>
+      <c r="F16" s="1450"/>
+      <c r="G16" s="1450"/>
+      <c r="H16" s="1450"/>
+      <c r="I16" s="1450"/>
+      <c r="J16" s="1451"/>
       <c r="K16" s="341"/>
       <c r="L16" s="341"/>
       <c r="M16" s="365"/>
@@ -35071,10 +35065,10 @@
       </c>
       <c r="L19" s="341"/>
       <c r="M19" s="361"/>
-      <c r="N19" s="1448" t="s">
+      <c r="N19" s="1443" t="s">
         <v>230</v>
       </c>
-      <c r="O19" s="1448" t="s">
+      <c r="O19" s="1443" t="s">
         <v>231</v>
       </c>
       <c r="P19" s="361"/>
@@ -35126,8 +35120,8 @@
       </c>
       <c r="L20" s="341"/>
       <c r="M20" s="361"/>
-      <c r="N20" s="1449"/>
-      <c r="O20" s="1449"/>
+      <c r="N20" s="1444"/>
+      <c r="O20" s="1444"/>
       <c r="P20" s="371"/>
       <c r="Q20" s="372"/>
       <c r="R20" s="361"/>
@@ -35256,18 +35250,18 @@
       <c r="AL22" s="315"/>
     </row>
     <row r="23" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1457" t="s">
+      <c r="A23" s="1452" t="s">
         <v>235</v>
       </c>
-      <c r="B23" s="1457"/>
-      <c r="C23" s="1457"/>
-      <c r="D23" s="1457"/>
-      <c r="E23" s="1457"/>
-      <c r="F23" s="1457"/>
-      <c r="G23" s="1457"/>
-      <c r="H23" s="1457"/>
-      <c r="I23" s="1457"/>
-      <c r="J23" s="1457"/>
+      <c r="B23" s="1452"/>
+      <c r="C23" s="1452"/>
+      <c r="D23" s="1452"/>
+      <c r="E23" s="1452"/>
+      <c r="F23" s="1452"/>
+      <c r="G23" s="1452"/>
+      <c r="H23" s="1452"/>
+      <c r="I23" s="1452"/>
+      <c r="J23" s="1452"/>
       <c r="K23" s="341"/>
       <c r="L23" s="344"/>
       <c r="M23" s="361"/>
@@ -35710,18 +35704,18 @@
       <c r="AL32" s="315"/>
     </row>
     <row r="33" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1457" t="s">
+      <c r="A33" s="1452" t="s">
         <v>253</v>
       </c>
-      <c r="B33" s="1457"/>
-      <c r="C33" s="1457"/>
-      <c r="D33" s="1457"/>
-      <c r="E33" s="1457"/>
-      <c r="F33" s="1457"/>
-      <c r="G33" s="1457"/>
-      <c r="H33" s="1457"/>
-      <c r="I33" s="1457"/>
-      <c r="J33" s="1457"/>
+      <c r="B33" s="1452"/>
+      <c r="C33" s="1452"/>
+      <c r="D33" s="1452"/>
+      <c r="E33" s="1452"/>
+      <c r="F33" s="1452"/>
+      <c r="G33" s="1452"/>
+      <c r="H33" s="1452"/>
+      <c r="I33" s="1452"/>
+      <c r="J33" s="1452"/>
       <c r="K33" s="437"/>
       <c r="L33" s="437"/>
       <c r="T33" s="314"/>
@@ -35746,15 +35740,15 @@
     </row>
     <row r="34" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="749"/>
-      <c r="B34" s="1447" t="s">
+      <c r="B34" s="1442" t="s">
         <v>254</v>
       </c>
-      <c r="C34" s="1447"/>
-      <c r="D34" s="1447"/>
-      <c r="E34" s="1447"/>
-      <c r="F34" s="1447"/>
-      <c r="G34" s="1447"/>
-      <c r="H34" s="1447"/>
+      <c r="C34" s="1442"/>
+      <c r="D34" s="1442"/>
+      <c r="E34" s="1442"/>
+      <c r="F34" s="1442"/>
+      <c r="G34" s="1442"/>
+      <c r="H34" s="1442"/>
       <c r="I34" s="757"/>
       <c r="J34" s="758"/>
       <c r="K34" s="341"/>
@@ -35824,18 +35818,18 @@
       <c r="AL35" s="315"/>
     </row>
     <row r="36" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1457" t="s">
+      <c r="A36" s="1452" t="s">
         <v>257</v>
       </c>
-      <c r="B36" s="1457"/>
-      <c r="C36" s="1457"/>
-      <c r="D36" s="1457"/>
-      <c r="E36" s="1457"/>
-      <c r="F36" s="1457"/>
-      <c r="G36" s="1457"/>
-      <c r="H36" s="1457"/>
-      <c r="I36" s="1457"/>
-      <c r="J36" s="1457"/>
+      <c r="B36" s="1452"/>
+      <c r="C36" s="1452"/>
+      <c r="D36" s="1452"/>
+      <c r="E36" s="1452"/>
+      <c r="F36" s="1452"/>
+      <c r="G36" s="1452"/>
+      <c r="H36" s="1452"/>
+      <c r="I36" s="1452"/>
+      <c r="J36" s="1452"/>
       <c r="K36" s="341"/>
       <c r="L36" s="341"/>
       <c r="T36" s="314"/>
@@ -35860,15 +35854,15 @@
     </row>
     <row r="37" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="749"/>
-      <c r="B37" s="1447" t="s">
+      <c r="B37" s="1442" t="s">
         <v>258</v>
       </c>
-      <c r="C37" s="1447"/>
-      <c r="D37" s="1447"/>
-      <c r="E37" s="1447"/>
-      <c r="F37" s="1447"/>
-      <c r="G37" s="1447"/>
-      <c r="H37" s="1447"/>
+      <c r="C37" s="1442"/>
+      <c r="D37" s="1442"/>
+      <c r="E37" s="1442"/>
+      <c r="F37" s="1442"/>
+      <c r="G37" s="1442"/>
+      <c r="H37" s="1442"/>
       <c r="I37" s="757"/>
       <c r="J37" s="758"/>
       <c r="K37" s="341"/>
@@ -35971,18 +35965,18 @@
       <c r="AL39" s="315"/>
     </row>
     <row r="40" spans="1:38" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1443" t="s">
+      <c r="A40" s="1456" t="s">
         <v>261</v>
       </c>
-      <c r="B40" s="1443"/>
-      <c r="C40" s="1443"/>
-      <c r="D40" s="1443"/>
-      <c r="E40" s="1443"/>
-      <c r="F40" s="1443"/>
-      <c r="G40" s="1443"/>
-      <c r="H40" s="1443"/>
-      <c r="I40" s="1443"/>
-      <c r="J40" s="1443"/>
+      <c r="B40" s="1456"/>
+      <c r="C40" s="1456"/>
+      <c r="D40" s="1456"/>
+      <c r="E40" s="1456"/>
+      <c r="F40" s="1456"/>
+      <c r="G40" s="1456"/>
+      <c r="H40" s="1456"/>
+      <c r="I40" s="1456"/>
+      <c r="J40" s="1456"/>
       <c r="K40" s="341"/>
       <c r="L40" s="341"/>
       <c r="T40" s="314"/>
@@ -36006,16 +36000,16 @@
       <c r="AL40" s="315"/>
     </row>
     <row r="41" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1443"/>
-      <c r="B41" s="1443"/>
-      <c r="C41" s="1443"/>
-      <c r="D41" s="1443"/>
-      <c r="E41" s="1443"/>
-      <c r="F41" s="1443"/>
-      <c r="G41" s="1443"/>
-      <c r="H41" s="1443"/>
-      <c r="I41" s="1443"/>
-      <c r="J41" s="1443"/>
+      <c r="A41" s="1456"/>
+      <c r="B41" s="1456"/>
+      <c r="C41" s="1456"/>
+      <c r="D41" s="1456"/>
+      <c r="E41" s="1456"/>
+      <c r="F41" s="1456"/>
+      <c r="G41" s="1456"/>
+      <c r="H41" s="1456"/>
+      <c r="I41" s="1456"/>
+      <c r="J41" s="1456"/>
       <c r="K41" s="341"/>
       <c r="L41" s="341"/>
       <c r="T41" s="314"/>
@@ -36039,16 +36033,16 @@
       <c r="AL41" s="315"/>
     </row>
     <row r="42" spans="1:38" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1443"/>
-      <c r="B42" s="1443"/>
-      <c r="C42" s="1443"/>
-      <c r="D42" s="1443"/>
-      <c r="E42" s="1443"/>
-      <c r="F42" s="1443"/>
-      <c r="G42" s="1443"/>
-      <c r="H42" s="1443"/>
-      <c r="I42" s="1443"/>
-      <c r="J42" s="1443"/>
+      <c r="A42" s="1456"/>
+      <c r="B42" s="1456"/>
+      <c r="C42" s="1456"/>
+      <c r="D42" s="1456"/>
+      <c r="E42" s="1456"/>
+      <c r="F42" s="1456"/>
+      <c r="G42" s="1456"/>
+      <c r="H42" s="1456"/>
+      <c r="I42" s="1456"/>
+      <c r="J42" s="1456"/>
       <c r="K42" s="418"/>
       <c r="L42" s="381"/>
       <c r="N42" s="378"/>
@@ -36128,9 +36122,9 @@
       <c r="K44" s="341"/>
       <c r="L44" s="383"/>
       <c r="M44" s="383"/>
-      <c r="N44" s="1335"/>
-      <c r="O44" s="1335"/>
-      <c r="P44" s="1335"/>
+      <c r="N44" s="1341"/>
+      <c r="O44" s="1341"/>
+      <c r="P44" s="1341"/>
       <c r="T44" s="314"/>
       <c r="U44" s="325"/>
       <c r="V44" s="325"/>
@@ -36159,15 +36153,15 @@
       <c r="E45" s="197"/>
       <c r="F45" s="197"/>
       <c r="G45" s="200"/>
-      <c r="H45" s="1334"/>
-      <c r="I45" s="1334"/>
-      <c r="J45" s="1334"/>
+      <c r="H45" s="1381"/>
+      <c r="I45" s="1381"/>
+      <c r="J45" s="1381"/>
       <c r="K45" s="341"/>
       <c r="L45" s="384"/>
       <c r="M45" s="385"/>
-      <c r="N45" s="1445"/>
-      <c r="O45" s="1445"/>
-      <c r="P45" s="1445"/>
+      <c r="N45" s="1453"/>
+      <c r="O45" s="1453"/>
+      <c r="P45" s="1453"/>
       <c r="T45" s="314"/>
       <c r="U45" s="325"/>
       <c r="V45" s="325"/>
@@ -36196,15 +36190,15 @@
       <c r="E46" s="197"/>
       <c r="F46" s="197"/>
       <c r="G46" s="200"/>
-      <c r="H46" s="1335"/>
-      <c r="I46" s="1335"/>
-      <c r="J46" s="1335"/>
+      <c r="H46" s="1341"/>
+      <c r="I46" s="1341"/>
+      <c r="J46" s="1341"/>
       <c r="K46" s="341"/>
       <c r="L46" s="386"/>
       <c r="M46" s="387"/>
-      <c r="N46" s="1335"/>
-      <c r="O46" s="1335"/>
-      <c r="P46" s="1335"/>
+      <c r="N46" s="1341"/>
+      <c r="O46" s="1341"/>
+      <c r="P46" s="1341"/>
       <c r="T46" s="314"/>
       <c r="U46" s="325"/>
       <c r="V46" s="325"/>
@@ -36233,15 +36227,15 @@
       <c r="E47" s="197"/>
       <c r="F47" s="197"/>
       <c r="G47" s="200"/>
-      <c r="H47" s="1445"/>
-      <c r="I47" s="1445"/>
-      <c r="J47" s="1445"/>
+      <c r="H47" s="1453"/>
+      <c r="I47" s="1453"/>
+      <c r="J47" s="1453"/>
       <c r="K47" s="341"/>
       <c r="L47" s="386"/>
       <c r="M47" s="387"/>
-      <c r="N47" s="1334"/>
-      <c r="O47" s="1334"/>
-      <c r="P47" s="1334"/>
+      <c r="N47" s="1381"/>
+      <c r="O47" s="1381"/>
+      <c r="P47" s="1381"/>
       <c r="T47" s="314"/>
       <c r="U47" s="325"/>
       <c r="V47" s="325"/>
@@ -36270,15 +36264,15 @@
       <c r="E48" s="197"/>
       <c r="F48" s="197"/>
       <c r="G48" s="200"/>
-      <c r="H48" s="1335"/>
-      <c r="I48" s="1335"/>
-      <c r="J48" s="1335"/>
+      <c r="H48" s="1341"/>
+      <c r="I48" s="1341"/>
+      <c r="J48" s="1341"/>
       <c r="K48" s="341"/>
       <c r="L48" s="386"/>
       <c r="M48" s="387"/>
-      <c r="N48" s="1446"/>
-      <c r="O48" s="1446"/>
-      <c r="P48" s="1446"/>
+      <c r="N48" s="1455"/>
+      <c r="O48" s="1455"/>
+      <c r="P48" s="1455"/>
       <c r="T48" s="314"/>
       <c r="U48" s="325"/>
       <c r="V48" s="325"/>
@@ -36307,15 +36301,15 @@
       <c r="E49" s="200"/>
       <c r="F49" s="200"/>
       <c r="G49" s="200"/>
-      <c r="H49" s="1334"/>
-      <c r="I49" s="1334"/>
-      <c r="J49" s="1334"/>
+      <c r="H49" s="1381"/>
+      <c r="I49" s="1381"/>
+      <c r="J49" s="1381"/>
       <c r="K49" s="341"/>
       <c r="L49" s="386"/>
       <c r="M49" s="387"/>
-      <c r="N49" s="1445"/>
-      <c r="O49" s="1445"/>
-      <c r="P49" s="1445"/>
+      <c r="N49" s="1453"/>
+      <c r="O49" s="1453"/>
+      <c r="P49" s="1453"/>
       <c r="T49" s="314"/>
       <c r="U49" s="325"/>
       <c r="V49" s="325"/>
@@ -37085,16 +37079,16 @@
       <c r="AL74" s="315"/>
     </row>
     <row r="75" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1443"/>
-      <c r="B75" s="1443"/>
-      <c r="C75" s="1443"/>
-      <c r="D75" s="1443"/>
-      <c r="E75" s="1443"/>
-      <c r="F75" s="1443"/>
-      <c r="G75" s="1443"/>
-      <c r="H75" s="1443"/>
-      <c r="I75" s="1443"/>
-      <c r="J75" s="1443"/>
+      <c r="A75" s="1456"/>
+      <c r="B75" s="1456"/>
+      <c r="C75" s="1456"/>
+      <c r="D75" s="1456"/>
+      <c r="E75" s="1456"/>
+      <c r="F75" s="1456"/>
+      <c r="G75" s="1456"/>
+      <c r="H75" s="1456"/>
+      <c r="I75" s="1456"/>
+      <c r="J75" s="1456"/>
       <c r="T75" s="314"/>
       <c r="U75" s="325"/>
       <c r="V75" s="325"/>
@@ -37116,16 +37110,16 @@
       <c r="AL75" s="315"/>
     </row>
     <row r="76" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1443"/>
-      <c r="B76" s="1443"/>
-      <c r="C76" s="1443"/>
-      <c r="D76" s="1443"/>
-      <c r="E76" s="1443"/>
-      <c r="F76" s="1443"/>
-      <c r="G76" s="1443"/>
-      <c r="H76" s="1443"/>
-      <c r="I76" s="1443"/>
-      <c r="J76" s="1443"/>
+      <c r="A76" s="1456"/>
+      <c r="B76" s="1456"/>
+      <c r="C76" s="1456"/>
+      <c r="D76" s="1456"/>
+      <c r="E76" s="1456"/>
+      <c r="F76" s="1456"/>
+      <c r="G76" s="1456"/>
+      <c r="H76" s="1456"/>
+      <c r="I76" s="1456"/>
+      <c r="J76" s="1456"/>
       <c r="T76" s="314"/>
       <c r="U76" s="325"/>
       <c r="V76" s="325"/>
@@ -37147,16 +37141,16 @@
       <c r="AL76" s="315"/>
     </row>
     <row r="77" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1443"/>
-      <c r="B77" s="1443"/>
-      <c r="C77" s="1443"/>
-      <c r="D77" s="1443"/>
-      <c r="E77" s="1443"/>
-      <c r="F77" s="1443"/>
-      <c r="G77" s="1443"/>
-      <c r="H77" s="1443"/>
-      <c r="I77" s="1443"/>
-      <c r="J77" s="1443"/>
+      <c r="A77" s="1456"/>
+      <c r="B77" s="1456"/>
+      <c r="C77" s="1456"/>
+      <c r="D77" s="1456"/>
+      <c r="E77" s="1456"/>
+      <c r="F77" s="1456"/>
+      <c r="G77" s="1456"/>
+      <c r="H77" s="1456"/>
+      <c r="I77" s="1456"/>
+      <c r="J77" s="1456"/>
       <c r="T77" s="314"/>
       <c r="U77" s="325"/>
       <c r="V77" s="325"/>
@@ -37271,10 +37265,10 @@
       <c r="AL80" s="315"/>
     </row>
     <row r="81" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G81" s="1444"/>
-      <c r="H81" s="1444"/>
-      <c r="I81" s="1444"/>
-      <c r="J81" s="1444"/>
+      <c r="G81" s="1454"/>
+      <c r="H81" s="1454"/>
+      <c r="I81" s="1454"/>
+      <c r="J81" s="1454"/>
       <c r="T81" s="314"/>
       <c r="U81" s="325"/>
       <c r="V81" s="325"/>
@@ -37319,10 +37313,10 @@
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" s="313"/>
-      <c r="G83" s="1444"/>
-      <c r="H83" s="1444"/>
-      <c r="I83" s="1444"/>
-      <c r="J83" s="1444"/>
+      <c r="G83" s="1454"/>
+      <c r="H83" s="1454"/>
+      <c r="I83" s="1454"/>
+      <c r="J83" s="1454"/>
       <c r="T83" s="314"/>
       <c r="U83" s="325"/>
       <c r="V83" s="325"/>
@@ -39804,6 +39798,23 @@
     <protectedRange sqref="C10:C13" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="29">
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A41:J42"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A76:J77"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="N46:P46"/>
     <mergeCell ref="B37:H37"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
@@ -39816,23 +39827,6 @@
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="B34:H34"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="G83:J83"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J42"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A76:J77"/>
-    <mergeCell ref="G81:J81"/>
-    <mergeCell ref="H47:J47"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.78740157480314965" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -40045,19 +40039,19 @@
       <c r="Z6" s="37"/>
     </row>
     <row r="7" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1487" t="s">
+      <c r="A7" s="1464" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1487"/>
-      <c r="C7" s="1487"/>
-      <c r="D7" s="1487"/>
-      <c r="E7" s="1487"/>
-      <c r="F7" s="1487"/>
-      <c r="G7" s="1487"/>
-      <c r="H7" s="1487"/>
-      <c r="I7" s="1487"/>
-      <c r="J7" s="1487"/>
-      <c r="K7" s="1487"/>
+      <c r="B7" s="1464"/>
+      <c r="C7" s="1464"/>
+      <c r="D7" s="1464"/>
+      <c r="E7" s="1464"/>
+      <c r="F7" s="1464"/>
+      <c r="G7" s="1464"/>
+      <c r="H7" s="1464"/>
+      <c r="I7" s="1464"/>
+      <c r="J7" s="1464"/>
+      <c r="K7" s="1464"/>
       <c r="N7" s="309" t="s">
         <v>272</v>
       </c>
@@ -40082,20 +40076,20 @@
       <c r="Z7" s="37"/>
     </row>
     <row r="8" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1488">
+      <c r="A8" s="1465">
         <f>+K12</f>
         <v>1</v>
       </c>
-      <c r="B8" s="1488"/>
-      <c r="C8" s="1488"/>
-      <c r="D8" s="1488"/>
-      <c r="E8" s="1488"/>
-      <c r="F8" s="1488"/>
-      <c r="G8" s="1488"/>
-      <c r="H8" s="1488"/>
-      <c r="I8" s="1488"/>
-      <c r="J8" s="1488"/>
-      <c r="K8" s="1488"/>
+      <c r="B8" s="1465"/>
+      <c r="C8" s="1465"/>
+      <c r="D8" s="1465"/>
+      <c r="E8" s="1465"/>
+      <c r="F8" s="1465"/>
+      <c r="G8" s="1465"/>
+      <c r="H8" s="1465"/>
+      <c r="I8" s="1465"/>
+      <c r="J8" s="1465"/>
+      <c r="K8" s="1465"/>
       <c r="N8" s="769" t="s">
         <v>274</v>
       </c>
@@ -40150,14 +40144,14 @@
       <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1481" t="s">
+      <c r="C10" s="1488" t="s">
         <v>277</v>
       </c>
-      <c r="D10" s="1481"/>
-      <c r="E10" s="1481"/>
-      <c r="F10" s="1481"/>
-      <c r="G10" s="1481"/>
-      <c r="H10" s="1481"/>
+      <c r="D10" s="1488"/>
+      <c r="E10" s="1488"/>
+      <c r="F10" s="1488"/>
+      <c r="G10" s="1488"/>
+      <c r="H10" s="1488"/>
       <c r="I10" s="23" t="s">
         <v>3</v>
       </c>
@@ -40200,14 +40194,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1481" t="s">
+      <c r="C11" s="1488" t="s">
         <v>282</v>
       </c>
-      <c r="D11" s="1481"/>
-      <c r="E11" s="1481"/>
-      <c r="F11" s="1481"/>
-      <c r="G11" s="1481"/>
-      <c r="H11" s="1481"/>
+      <c r="D11" s="1488"/>
+      <c r="E11" s="1488"/>
+      <c r="F11" s="1488"/>
+      <c r="G11" s="1488"/>
+      <c r="H11" s="1488"/>
       <c r="I11" s="26" t="s">
         <v>6</v>
       </c>
@@ -40249,14 +40243,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1481" t="s">
+      <c r="C12" s="1488" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="1481"/>
-      <c r="E12" s="1481"/>
-      <c r="F12" s="1481"/>
-      <c r="G12" s="1481"/>
-      <c r="H12" s="1481"/>
+      <c r="D12" s="1488"/>
+      <c r="E12" s="1488"/>
+      <c r="F12" s="1488"/>
+      <c r="G12" s="1488"/>
+      <c r="H12" s="1488"/>
       <c r="I12" s="26" t="s">
         <v>288</v>
       </c>
@@ -40336,19 +40330,19 @@
       <c r="Z13" s="37"/>
     </row>
     <row r="14" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1451" t="s">
+      <c r="A14" s="1446" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="1452"/>
-      <c r="C14" s="1452"/>
-      <c r="D14" s="1452"/>
-      <c r="E14" s="1452"/>
-      <c r="F14" s="1452"/>
-      <c r="G14" s="1452"/>
-      <c r="H14" s="1452"/>
-      <c r="I14" s="1452"/>
-      <c r="J14" s="1452"/>
-      <c r="K14" s="1453"/>
+      <c r="B14" s="1447"/>
+      <c r="C14" s="1447"/>
+      <c r="D14" s="1447"/>
+      <c r="E14" s="1447"/>
+      <c r="F14" s="1447"/>
+      <c r="G14" s="1447"/>
+      <c r="H14" s="1447"/>
+      <c r="I14" s="1447"/>
+      <c r="J14" s="1447"/>
+      <c r="K14" s="1448"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="769" t="s">
@@ -40371,19 +40365,19 @@
       <c r="Z14" s="37"/>
     </row>
     <row r="15" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1454" t="s">
+      <c r="A15" s="1449" t="s">
         <v>295</v>
       </c>
-      <c r="B15" s="1455"/>
-      <c r="C15" s="1455"/>
-      <c r="D15" s="1455"/>
-      <c r="E15" s="1455"/>
-      <c r="F15" s="1455"/>
-      <c r="G15" s="1455"/>
-      <c r="H15" s="1455"/>
-      <c r="I15" s="1455"/>
-      <c r="J15" s="1455"/>
-      <c r="K15" s="1456"/>
+      <c r="B15" s="1450"/>
+      <c r="C15" s="1450"/>
+      <c r="D15" s="1450"/>
+      <c r="E15" s="1450"/>
+      <c r="F15" s="1450"/>
+      <c r="G15" s="1450"/>
+      <c r="H15" s="1450"/>
+      <c r="I15" s="1450"/>
+      <c r="J15" s="1450"/>
+      <c r="K15" s="1451"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="25"/>
@@ -40430,30 +40424,30 @@
       <c r="S16" s="232" t="s">
         <v>299</v>
       </c>
-      <c r="T16" s="1461" t="s">
+      <c r="T16" s="1492" t="s">
         <v>300</v>
       </c>
-      <c r="U16" s="1462"/>
-      <c r="V16" s="1463"/>
+      <c r="U16" s="1493"/>
+      <c r="V16" s="1494"/>
       <c r="W16" s="37"/>
       <c r="X16" s="37"/>
       <c r="Y16" s="37"/>
       <c r="Z16" s="37"/>
     </row>
     <row r="17" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1478" t="s">
+      <c r="A17" s="1485" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1479"/>
-      <c r="C17" s="1479"/>
-      <c r="D17" s="1479"/>
-      <c r="E17" s="1479"/>
-      <c r="F17" s="1479"/>
-      <c r="G17" s="1479"/>
-      <c r="H17" s="1479"/>
-      <c r="I17" s="1479"/>
-      <c r="J17" s="1479"/>
-      <c r="K17" s="1480"/>
+      <c r="B17" s="1486"/>
+      <c r="C17" s="1486"/>
+      <c r="D17" s="1486"/>
+      <c r="E17" s="1486"/>
+      <c r="F17" s="1486"/>
+      <c r="G17" s="1486"/>
+      <c r="H17" s="1486"/>
+      <c r="I17" s="1486"/>
+      <c r="J17" s="1486"/>
+      <c r="K17" s="1487"/>
       <c r="M17" s="3"/>
       <c r="N17" s="775" t="s">
         <v>230</v>
@@ -40473,11 +40467,11 @@
       <c r="S17" s="776" t="s">
         <v>305</v>
       </c>
-      <c r="T17" s="1458" t="s">
+      <c r="T17" s="1489" t="s">
         <v>306</v>
       </c>
-      <c r="U17" s="1459"/>
-      <c r="V17" s="1460"/>
+      <c r="U17" s="1490"/>
+      <c r="V17" s="1491"/>
       <c r="W17" s="37"/>
       <c r="X17" s="37"/>
       <c r="Y17" s="37"/>
@@ -40737,21 +40731,21 @@
       <c r="Z22" s="37"/>
     </row>
     <row r="23" spans="1:26" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1491" t="s">
+      <c r="A23" s="1468" t="s">
         <v>230</v>
       </c>
-      <c r="B23" s="1492"/>
-      <c r="C23" s="1493"/>
-      <c r="D23" s="1466" t="s">
+      <c r="B23" s="1469"/>
+      <c r="C23" s="1470"/>
+      <c r="D23" s="1496" t="s">
         <v>320</v>
       </c>
       <c r="E23" s="197"/>
-      <c r="F23" s="1494" t="s">
+      <c r="F23" s="1472" t="s">
         <v>321</v>
       </c>
-      <c r="G23" s="1495"/>
-      <c r="H23" s="1496"/>
-      <c r="I23" s="1471" t="s">
+      <c r="G23" s="1473"/>
+      <c r="H23" s="1474"/>
+      <c r="I23" s="1478" t="s">
         <v>317</v>
       </c>
       <c r="J23" s="191"/>
@@ -40795,16 +40789,16 @@
       <c r="A24" s="785" t="s">
         <v>323</v>
       </c>
-      <c r="B24" s="1490" t="s">
+      <c r="B24" s="1467" t="s">
         <v>301</v>
       </c>
-      <c r="C24" s="1490"/>
-      <c r="D24" s="1467"/>
+      <c r="C24" s="1467"/>
+      <c r="D24" s="1497"/>
       <c r="E24" s="197"/>
-      <c r="F24" s="1497"/>
-      <c r="G24" s="1498"/>
-      <c r="H24" s="1499"/>
-      <c r="I24" s="1500"/>
+      <c r="F24" s="1475"/>
+      <c r="G24" s="1476"/>
+      <c r="H24" s="1477"/>
+      <c r="I24" s="1479"/>
       <c r="J24" s="191"/>
       <c r="K24" s="192"/>
       <c r="L24" s="3"/>
@@ -40842,10 +40836,10 @@
       <c r="A25" s="786" t="s">
         <v>310</v>
       </c>
-      <c r="B25" s="1489">
+      <c r="B25" s="1466">
         <v>76.2</v>
       </c>
-      <c r="C25" s="1489"/>
+      <c r="C25" s="1466"/>
       <c r="D25" s="787">
         <f>+S18</f>
         <v>100</v>
@@ -40896,21 +40890,21 @@
       <c r="A26" s="198" t="s">
         <v>317</v>
       </c>
-      <c r="B26" s="1465">
+      <c r="B26" s="1471">
         <v>50.6</v>
       </c>
-      <c r="C26" s="1465"/>
+      <c r="C26" s="1471"/>
       <c r="D26" s="199">
         <f>+S20</f>
         <v>96.737365729020368</v>
       </c>
       <c r="E26" s="197"/>
-      <c r="F26" s="1491" t="s">
+      <c r="F26" s="1468" t="s">
         <v>326</v>
       </c>
-      <c r="G26" s="1492"/>
-      <c r="H26" s="1492"/>
-      <c r="I26" s="1493"/>
+      <c r="G26" s="1469"/>
+      <c r="H26" s="1469"/>
+      <c r="I26" s="1470"/>
       <c r="J26" s="200"/>
       <c r="K26" s="201"/>
       <c r="L26" s="3"/>
@@ -40948,19 +40942,19 @@
       <c r="A27" s="202" t="s">
         <v>318</v>
       </c>
-      <c r="B27" s="1465">
+      <c r="B27" s="1471">
         <v>38.1</v>
       </c>
-      <c r="C27" s="1465"/>
+      <c r="C27" s="1471"/>
       <c r="D27" s="199">
         <f>+S21</f>
         <v>90.324022891039832</v>
       </c>
       <c r="E27" s="197"/>
-      <c r="F27" s="1501"/>
-      <c r="G27" s="1502"/>
-      <c r="H27" s="1502"/>
-      <c r="I27" s="1503"/>
+      <c r="F27" s="1480"/>
+      <c r="G27" s="1481"/>
+      <c r="H27" s="1481"/>
+      <c r="I27" s="1482"/>
       <c r="J27" s="200"/>
       <c r="K27" s="201"/>
       <c r="L27" s="3"/>
@@ -41002,19 +40996,19 @@
       <c r="A28" s="198" t="s">
         <v>319</v>
       </c>
-      <c r="B28" s="1465">
+      <c r="B28" s="1471">
         <v>25.4</v>
       </c>
-      <c r="C28" s="1465"/>
+      <c r="C28" s="1471"/>
       <c r="D28" s="199">
         <f>+S22</f>
         <v>84.873241107276272</v>
       </c>
       <c r="E28" s="197"/>
-      <c r="F28" s="1474" t="s">
+      <c r="F28" s="1483" t="s">
         <v>329</v>
       </c>
-      <c r="G28" s="1476">
+      <c r="G28" s="1484">
         <f>R27</f>
         <v>45.788805497693524</v>
       </c>
@@ -41062,17 +41056,17 @@
       <c r="A29" s="198" t="s">
         <v>322</v>
       </c>
-      <c r="B29" s="1465">
+      <c r="B29" s="1471">
         <v>19.05</v>
       </c>
-      <c r="C29" s="1465"/>
+      <c r="C29" s="1471"/>
       <c r="D29" s="199">
         <f>+S23</f>
         <v>73.456819301447041</v>
       </c>
       <c r="E29" s="197"/>
-      <c r="F29" s="1475"/>
-      <c r="G29" s="1477"/>
+      <c r="F29" s="1459"/>
+      <c r="G29" s="1462"/>
       <c r="H29" s="203" t="s">
         <v>331</v>
       </c>
@@ -41121,19 +41115,19 @@
       <c r="A30" s="198" t="s">
         <v>325</v>
       </c>
-      <c r="B30" s="1465">
+      <c r="B30" s="1471">
         <v>9.5250000000000004</v>
       </c>
-      <c r="C30" s="1465"/>
+      <c r="C30" s="1471"/>
       <c r="D30" s="199">
         <f>+S25</f>
         <v>62.661585152699679</v>
       </c>
       <c r="E30" s="197"/>
-      <c r="F30" s="1482" t="s">
+      <c r="F30" s="1457" t="s">
         <v>332</v>
       </c>
-      <c r="G30" s="1484">
+      <c r="G30" s="1460">
         <f>100-(G28+G33)</f>
         <v>40.754382185876274</v>
       </c>
@@ -41181,17 +41175,17 @@
       <c r="A31" s="198" t="s">
         <v>328</v>
       </c>
-      <c r="B31" s="1465">
+      <c r="B31" s="1471">
         <v>4.76</v>
       </c>
-      <c r="C31" s="1465"/>
+      <c r="C31" s="1471"/>
       <c r="D31" s="199">
         <f>+S27</f>
         <v>54.211194502306476</v>
       </c>
       <c r="E31" s="197"/>
-      <c r="F31" s="1483"/>
-      <c r="G31" s="1485"/>
+      <c r="F31" s="1458"/>
+      <c r="G31" s="1461"/>
       <c r="H31" s="203" t="s">
         <v>333</v>
       </c>
@@ -41239,17 +41233,17 @@
       <c r="A32" s="198">
         <v>8</v>
       </c>
-      <c r="B32" s="1465">
+      <c r="B32" s="1471">
         <v>2.36</v>
       </c>
-      <c r="C32" s="1465"/>
+      <c r="C32" s="1471"/>
       <c r="D32" s="199">
         <f>+S28</f>
         <v>49.032616067382399</v>
       </c>
       <c r="E32" s="197"/>
-      <c r="F32" s="1475"/>
-      <c r="G32" s="1477"/>
+      <c r="F32" s="1459"/>
+      <c r="G32" s="1462"/>
       <c r="H32" s="203" t="s">
         <v>331</v>
       </c>
@@ -41301,10 +41295,10 @@
       <c r="A33" s="198">
         <v>16</v>
       </c>
-      <c r="B33" s="1465">
+      <c r="B33" s="1471">
         <v>1.19</v>
       </c>
-      <c r="C33" s="1465"/>
+      <c r="C33" s="1471"/>
       <c r="D33" s="199">
         <f t="shared" ref="D33:D38" si="4">+S30</f>
         <v>40.351707913359583</v>
@@ -41359,10 +41353,10 @@
       <c r="A34" s="198">
         <v>30</v>
       </c>
-      <c r="B34" s="1465">
+      <c r="B34" s="1471">
         <v>0.6</v>
       </c>
-      <c r="C34" s="1465"/>
+      <c r="C34" s="1471"/>
       <c r="D34" s="199">
         <f t="shared" si="4"/>
         <v>31.408593256302638</v>
@@ -41409,25 +41403,25 @@
       <c r="A35" s="198">
         <v>40</v>
       </c>
-      <c r="B35" s="1465">
+      <c r="B35" s="1471">
         <v>0.42</v>
       </c>
-      <c r="C35" s="1465"/>
+      <c r="C35" s="1471"/>
       <c r="D35" s="199">
         <f t="shared" si="4"/>
         <v>27.175831135894526</v>
       </c>
       <c r="E35" s="197"/>
-      <c r="F35" s="1468" t="str">
+      <c r="F35" s="1498" t="str">
         <f>IF(O3="No","","Clasificacion SUCS")</f>
         <v/>
       </c>
-      <c r="G35" s="1468"/>
-      <c r="H35" s="1471" t="str">
+      <c r="G35" s="1498"/>
+      <c r="H35" s="1478" t="str">
         <f>IF(O3="No","",'Sucs '!G4)</f>
         <v/>
       </c>
-      <c r="I35" s="1471"/>
+      <c r="I35" s="1478"/>
       <c r="J35" s="200"/>
       <c r="K35" s="201"/>
       <c r="L35" s="3"/>
@@ -41469,19 +41463,19 @@
       <c r="A36" s="198">
         <v>50</v>
       </c>
-      <c r="B36" s="1465">
+      <c r="B36" s="1471">
         <v>0.3</v>
       </c>
-      <c r="C36" s="1465"/>
+      <c r="C36" s="1471"/>
       <c r="D36" s="199">
         <f t="shared" si="4"/>
         <v>23.785875632381845</v>
       </c>
       <c r="E36" s="197"/>
-      <c r="F36" s="1469"/>
-      <c r="G36" s="1469"/>
-      <c r="H36" s="1472"/>
-      <c r="I36" s="1472"/>
+      <c r="F36" s="1499"/>
+      <c r="G36" s="1499"/>
+      <c r="H36" s="1501"/>
+      <c r="I36" s="1501"/>
       <c r="J36" s="200"/>
       <c r="K36" s="201"/>
       <c r="L36" s="3"/>
@@ -41520,25 +41514,25 @@
       <c r="A37" s="198">
         <v>100</v>
       </c>
-      <c r="B37" s="1465">
+      <c r="B37" s="1471">
         <v>0.14899999999999999</v>
       </c>
-      <c r="C37" s="1465"/>
+      <c r="C37" s="1471"/>
       <c r="D37" s="199">
         <f t="shared" si="4"/>
         <v>17.820677688355374</v>
       </c>
       <c r="E37" s="197"/>
-      <c r="F37" s="1469" t="str">
+      <c r="F37" s="1499" t="str">
         <f>IF(O3="No","","Clasificacion AASHTO")</f>
         <v/>
       </c>
-      <c r="G37" s="1469"/>
-      <c r="H37" s="1472" t="str">
+      <c r="G37" s="1499"/>
+      <c r="H37" s="1501" t="str">
         <f>IF(O3="No","",Aashto!J26)</f>
         <v/>
       </c>
-      <c r="I37" s="1472"/>
+      <c r="I37" s="1501"/>
       <c r="J37" s="200"/>
       <c r="K37" s="201"/>
       <c r="L37" s="3"/>
@@ -41564,19 +41558,19 @@
       <c r="A38" s="208">
         <v>200</v>
       </c>
-      <c r="B38" s="1464">
+      <c r="B38" s="1495">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="C38" s="1464"/>
+      <c r="C38" s="1495"/>
       <c r="D38" s="209">
         <f t="shared" si="4"/>
         <v>13.456812316430202</v>
       </c>
       <c r="E38" s="197"/>
-      <c r="F38" s="1470"/>
-      <c r="G38" s="1470"/>
-      <c r="H38" s="1473"/>
-      <c r="I38" s="1473"/>
+      <c r="F38" s="1500"/>
+      <c r="G38" s="1500"/>
+      <c r="H38" s="1502"/>
+      <c r="I38" s="1502"/>
       <c r="J38" s="200"/>
       <c r="K38" s="201"/>
       <c r="L38" s="3"/>
@@ -42468,19 +42462,19 @@
       <c r="Z63" s="37"/>
     </row>
     <row r="64" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1486" t="s">
+      <c r="A64" s="1463" t="s">
         <v>345</v>
       </c>
-      <c r="B64" s="1486"/>
-      <c r="C64" s="1486"/>
-      <c r="D64" s="1486"/>
-      <c r="E64" s="1486"/>
-      <c r="F64" s="1486"/>
-      <c r="G64" s="1486"/>
-      <c r="H64" s="1486"/>
-      <c r="I64" s="1486"/>
-      <c r="J64" s="1486"/>
-      <c r="K64" s="1486"/>
+      <c r="B64" s="1463"/>
+      <c r="C64" s="1463"/>
+      <c r="D64" s="1463"/>
+      <c r="E64" s="1463"/>
+      <c r="F64" s="1463"/>
+      <c r="G64" s="1463"/>
+      <c r="H64" s="1463"/>
+      <c r="I64" s="1463"/>
+      <c r="J64" s="1463"/>
+      <c r="K64" s="1463"/>
       <c r="W64" s="37"/>
       <c r="X64" s="37"/>
       <c r="Y64" s="37"/>
@@ -42516,6 +42510,29 @@
     <protectedRange sqref="C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="F35:G36"/>
+    <mergeCell ref="F37:G38"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="F30:F32"/>
     <mergeCell ref="G30:G32"/>
     <mergeCell ref="A64:K64"/>
@@ -42532,29 +42549,6 @@
     <mergeCell ref="F23:H24"/>
     <mergeCell ref="I23:I24"/>
     <mergeCell ref="F26:I27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="F35:G36"/>
-    <mergeCell ref="F37:G38"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="H37:I38"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -42682,35 +42676,35 @@
       <c r="K7" s="118"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1505" t="s">
+      <c r="A8" s="1522" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1505"/>
-      <c r="C8" s="1505"/>
-      <c r="D8" s="1505"/>
-      <c r="E8" s="1505"/>
-      <c r="F8" s="1505"/>
-      <c r="G8" s="1505"/>
-      <c r="H8" s="1505"/>
-      <c r="I8" s="1505"/>
-      <c r="J8" s="1505"/>
-      <c r="K8" s="1505"/>
+      <c r="B8" s="1522"/>
+      <c r="C8" s="1522"/>
+      <c r="D8" s="1522"/>
+      <c r="E8" s="1522"/>
+      <c r="F8" s="1522"/>
+      <c r="G8" s="1522"/>
+      <c r="H8" s="1522"/>
+      <c r="I8" s="1522"/>
+      <c r="J8" s="1522"/>
+      <c r="K8" s="1522"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1506">
+      <c r="A9" s="1523">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="1506"/>
-      <c r="C9" s="1506"/>
-      <c r="D9" s="1506"/>
-      <c r="E9" s="1506"/>
-      <c r="F9" s="1506"/>
-      <c r="G9" s="1506"/>
-      <c r="H9" s="1506"/>
-      <c r="I9" s="1506"/>
-      <c r="J9" s="1506"/>
-      <c r="K9" s="1506"/>
+      <c r="B9" s="1523"/>
+      <c r="C9" s="1523"/>
+      <c r="D9" s="1523"/>
+      <c r="E9" s="1523"/>
+      <c r="F9" s="1523"/>
+      <c r="G9" s="1523"/>
+      <c r="H9" s="1523"/>
+      <c r="I9" s="1523"/>
+      <c r="J9" s="1523"/>
+      <c r="K9" s="1523"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -42733,14 +42727,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1507" t="s">
+      <c r="C11" s="1524" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="1507"/>
-      <c r="E11" s="1507"/>
-      <c r="F11" s="1507"/>
-      <c r="G11" s="1507"/>
-      <c r="H11" s="1507"/>
+      <c r="D11" s="1524"/>
+      <c r="E11" s="1524"/>
+      <c r="F11" s="1524"/>
+      <c r="G11" s="1524"/>
+      <c r="H11" s="1524"/>
       <c r="I11" s="121" t="s">
         <v>3</v>
       </c>
@@ -42761,14 +42755,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1507" t="s">
+      <c r="C12" s="1524" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="1507"/>
-      <c r="E12" s="1507"/>
-      <c r="F12" s="1507"/>
-      <c r="G12" s="1507"/>
-      <c r="H12" s="1507"/>
+      <c r="D12" s="1524"/>
+      <c r="E12" s="1524"/>
+      <c r="F12" s="1524"/>
+      <c r="G12" s="1524"/>
+      <c r="H12" s="1524"/>
       <c r="I12" s="26" t="s">
         <v>6</v>
       </c>
@@ -42792,14 +42786,14 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1507" t="s">
+      <c r="C13" s="1524" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="1507"/>
-      <c r="E13" s="1507"/>
-      <c r="F13" s="1507"/>
-      <c r="G13" s="1507"/>
-      <c r="H13" s="1507"/>
+      <c r="D13" s="1524"/>
+      <c r="E13" s="1524"/>
+      <c r="F13" s="1524"/>
+      <c r="G13" s="1524"/>
+      <c r="H13" s="1524"/>
       <c r="I13" s="26" t="s">
         <v>288</v>
       </c>
@@ -42813,8 +42807,8 @@
       <c r="M13" s="124"/>
       <c r="P13" s="127"/>
       <c r="Q13" s="127"/>
-      <c r="R13" s="1504"/>
-      <c r="S13" s="1504"/>
+      <c r="R13" s="1521"/>
+      <c r="S13" s="1521"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -42836,19 +42830,19 @@
       <c r="S14" s="737"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1508" t="s">
+      <c r="A15" s="1510" t="s">
         <v>347</v>
       </c>
-      <c r="B15" s="1509"/>
-      <c r="C15" s="1509"/>
-      <c r="D15" s="1509"/>
-      <c r="E15" s="1509"/>
-      <c r="F15" s="1509"/>
-      <c r="G15" s="1509"/>
-      <c r="H15" s="1509"/>
-      <c r="I15" s="1509"/>
-      <c r="J15" s="1509"/>
-      <c r="K15" s="1510"/>
+      <c r="B15" s="1511"/>
+      <c r="C15" s="1511"/>
+      <c r="D15" s="1511"/>
+      <c r="E15" s="1511"/>
+      <c r="F15" s="1511"/>
+      <c r="G15" s="1511"/>
+      <c r="H15" s="1511"/>
+      <c r="I15" s="1511"/>
+      <c r="J15" s="1511"/>
+      <c r="K15" s="1512"/>
       <c r="L15" s="124"/>
       <c r="M15" s="124"/>
       <c r="P15" s="127"/>
@@ -42857,19 +42851,19 @@
       <c r="S15" s="737"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1511" t="s">
+      <c r="A16" s="1513" t="s">
         <v>348</v>
       </c>
-      <c r="B16" s="1512"/>
-      <c r="C16" s="1512"/>
-      <c r="D16" s="1512"/>
-      <c r="E16" s="1512"/>
-      <c r="F16" s="1512"/>
-      <c r="G16" s="1512"/>
-      <c r="H16" s="1512"/>
-      <c r="I16" s="1512"/>
-      <c r="J16" s="1512"/>
-      <c r="K16" s="1513"/>
+      <c r="B16" s="1514"/>
+      <c r="C16" s="1514"/>
+      <c r="D16" s="1514"/>
+      <c r="E16" s="1514"/>
+      <c r="F16" s="1514"/>
+      <c r="G16" s="1514"/>
+      <c r="H16" s="1514"/>
+      <c r="I16" s="1514"/>
+      <c r="J16" s="1514"/>
+      <c r="K16" s="1515"/>
       <c r="L16" s="124"/>
       <c r="M16" s="124"/>
       <c r="P16" s="127"/>
@@ -42897,19 +42891,19 @@
       <c r="S17" s="737"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1478" t="s">
+      <c r="A18" s="1485" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1479"/>
-      <c r="C18" s="1479"/>
-      <c r="D18" s="1479"/>
-      <c r="E18" s="1479"/>
-      <c r="F18" s="1479"/>
-      <c r="G18" s="1479"/>
-      <c r="H18" s="1479"/>
-      <c r="I18" s="1479"/>
-      <c r="J18" s="1479"/>
-      <c r="K18" s="1480"/>
+      <c r="B18" s="1486"/>
+      <c r="C18" s="1486"/>
+      <c r="D18" s="1486"/>
+      <c r="E18" s="1486"/>
+      <c r="F18" s="1486"/>
+      <c r="G18" s="1486"/>
+      <c r="H18" s="1486"/>
+      <c r="I18" s="1486"/>
+      <c r="J18" s="1486"/>
+      <c r="K18" s="1487"/>
       <c r="M18" s="124"/>
       <c r="P18" s="127"/>
       <c r="Q18" s="127"/>
@@ -43026,8 +43020,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="805"/>
-      <c r="I23" s="1514"/>
-      <c r="J23" s="1514"/>
+      <c r="I23" s="1516"/>
+      <c r="J23" s="1516"/>
       <c r="K23" s="806"/>
       <c r="L23" s="124"/>
       <c r="M23" s="139"/>
@@ -43035,41 +43029,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="141"/>
-      <c r="D24" s="1515" t="s">
+      <c r="D24" s="1517" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="1516"/>
-      <c r="F24" s="1516"/>
-      <c r="G24" s="1517" t="s">
+      <c r="E24" s="1518"/>
+      <c r="F24" s="1518"/>
+      <c r="G24" s="1519" t="s">
         <v>352</v>
       </c>
-      <c r="H24" s="1518"/>
-      <c r="I24" s="1519"/>
-      <c r="J24" s="1519"/>
+      <c r="H24" s="1520"/>
+      <c r="I24" s="1508"/>
+      <c r="J24" s="1508"/>
       <c r="K24" s="142"/>
       <c r="L24" s="124"/>
       <c r="M24" s="143"/>
-      <c r="O24" s="1520" t="s">
+      <c r="O24" s="1503" t="s">
         <v>351</v>
       </c>
-      <c r="P24" s="1521"/>
+      <c r="P24" s="1504"/>
       <c r="Q24" s="807" t="s">
         <v>350</v>
       </c>
-      <c r="R24" s="1520" t="s">
+      <c r="R24" s="1503" t="s">
         <v>352</v>
       </c>
-      <c r="S24" s="1522"/>
+      <c r="S24" s="1505"/>
       <c r="T24" s="807" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="141"/>
-      <c r="B25" s="1523" t="s">
+      <c r="B25" s="1506" t="s">
         <v>353</v>
       </c>
-      <c r="C25" s="1524"/>
+      <c r="C25" s="1507"/>
       <c r="D25" s="808" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -43090,8 +43084,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="1519"/>
-      <c r="J25" s="1519"/>
+      <c r="I25" s="1508"/>
+      <c r="J25" s="1508"/>
       <c r="K25" s="142"/>
       <c r="L25" s="124"/>
       <c r="M25" s="143"/>
@@ -43140,8 +43134,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="1525"/>
-      <c r="J26" s="1525"/>
+      <c r="I26" s="1509"/>
+      <c r="J26" s="1509"/>
       <c r="K26" s="151"/>
       <c r="L26" s="152"/>
       <c r="M26" s="143"/>
@@ -43856,19 +43850,19 @@
     </row>
     <row r="49" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1486" t="s">
+      <c r="A50" s="1463" t="s">
         <v>345</v>
       </c>
-      <c r="B50" s="1486"/>
-      <c r="C50" s="1486"/>
-      <c r="D50" s="1486"/>
-      <c r="E50" s="1486"/>
-      <c r="F50" s="1486"/>
-      <c r="G50" s="1486"/>
-      <c r="H50" s="1486"/>
-      <c r="I50" s="1486"/>
-      <c r="J50" s="1486"/>
-      <c r="K50" s="1486"/>
+      <c r="B50" s="1463"/>
+      <c r="C50" s="1463"/>
+      <c r="D50" s="1463"/>
+      <c r="E50" s="1463"/>
+      <c r="F50" s="1463"/>
+      <c r="G50" s="1463"/>
+      <c r="H50" s="1463"/>
+      <c r="I50" s="1463"/>
+      <c r="J50" s="1463"/>
+      <c r="K50" s="1463"/>
     </row>
     <row r="51" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -43878,11 +43872,12 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -43891,12 +43886,11 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0700-000000000000}">
